--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -487,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5341,31 +5344,111 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>63659.53</v>
+      </c>
+      <c r="C58" t="n">
+        <v>63691.53</v>
+      </c>
+      <c r="D58" t="n">
+        <v>62726.18</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>965.35</v>
+      </c>
+      <c r="I58" t="n">
+        <v>59625.41</v>
+      </c>
+      <c r="J58" t="n">
+        <v>59933.68</v>
+      </c>
+      <c r="K58" t="n">
+        <v>62219.73</v>
+      </c>
+      <c r="L58" t="n">
+        <v>64505.79</v>
+      </c>
+      <c r="M58" t="n">
+        <v>65802.95</v>
+      </c>
+      <c r="N58" t="n">
+        <v>67100.11</v>
+      </c>
+      <c r="O58" t="n">
+        <v>70375.06</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I58" s="13" t="n">
-        <v>59625.41</v>
-      </c>
-      <c r="J58" s="13" t="n">
-        <v>59933.68</v>
-      </c>
-      <c r="K58" s="13" t="n">
-        <v>62219.73</v>
-      </c>
-      <c r="L58" s="13" t="n">
-        <v>64505.79</v>
-      </c>
-      <c r="M58" s="13" t="n">
-        <v>65802.95</v>
-      </c>
-      <c r="N58" s="13" t="n">
-        <v>67100.11</v>
-      </c>
-      <c r="O58" s="13" t="n">
-        <v>70375.06</v>
+      <c r="I59" s="14" t="n">
+        <v>61760.83</v>
+      </c>
+      <c r="J59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O59" s="14" t="n">
+        <v>64656.88</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,9 +120,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -5359,13 +5356,13 @@
         <v>62726.18</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>63492.99</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>-518.35</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>-0.0081</v>
       </c>
       <c r="H58" t="n">
         <v>965.35</v>
@@ -5391,10 +5388,8 @@
       <c r="O58" t="n">
         <v>70375.06</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5402,9 +5397,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5424,30 +5419,30 @@
       <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I59" s="14" t="n">
+      <c r="I59" s="13" t="n">
         <v>61760.83</v>
       </c>
-      <c r="J59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O59" s="14" t="n">
+      <c r="J59" s="13" t="n">
+        <v>62669.7</v>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>63010.31</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>63350.92</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>63975.66</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>64600.41</v>
+      </c>
+      <c r="O59" s="13" t="n">
         <v>64656.88</v>
       </c>
     </row>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -5350,22 +5350,22 @@
         <v>63659.53</v>
       </c>
       <c r="C58" t="n">
-        <v>63691.53</v>
+        <v>64101</v>
       </c>
       <c r="D58" t="n">
         <v>62726.18</v>
       </c>
       <c r="E58" t="n">
-        <v>63492.99</v>
+        <v>63484.1</v>
       </c>
       <c r="F58" t="n">
-        <v>-518.35</v>
+        <v>-527.24</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0081</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>965.35</v>
+        <v>1374.82</v>
       </c>
       <c r="I58" t="n">
         <v>59625.41</v>
@@ -5425,25 +5425,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>61760.83</v>
+        <v>61351.36</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>62669.7</v>
+        <v>62144.54</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>63010.31</v>
+        <v>62796.69</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>63350.92</v>
+        <v>63448.85</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>63975.66</v>
+        <v>64171.51</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>64600.41</v>
+        <v>64894.18</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>64656.88</v>
+        <v>65475.82</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -115,11 +115,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -666,35 +666,37 @@
         <v>1545.03</v>
       </c>
       <c r="I2" t="n">
-        <v>40715.7</v>
+        <v>41762</v>
       </c>
       <c r="J2" t="n">
-        <v>42315.82</v>
+        <v>42708.18</v>
       </c>
       <c r="K2" t="n">
-        <v>42694.37</v>
+        <v>42955.94</v>
       </c>
       <c r="L2" t="n">
-        <v>43072.91</v>
+        <v>43203.7</v>
       </c>
       <c r="M2" t="n">
-        <v>44062.25</v>
+        <v>43800.67</v>
       </c>
       <c r="N2" t="n">
-        <v>45051.59</v>
+        <v>44397.65</v>
       </c>
       <c r="O2" t="n">
-        <v>44819.34</v>
+        <v>44296.19</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
@@ -702,8 +704,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -713,7 +717,7 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -795,12 +799,12 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -881,12 +885,12 @@
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -967,7 +971,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="W5" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1047,7 +1051,7 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1127,7 +1131,7 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1217,7 +1221,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1305,7 +1309,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1385,7 +1389,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1471,7 +1475,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1555,7 +1559,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1637,7 +1641,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1719,7 +1723,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1807,7 +1811,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1889,7 +1893,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1973,7 +1977,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2055,7 +2059,7 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2143,7 +2147,7 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2223,7 +2227,7 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2307,7 +2311,7 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2395,7 +2399,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2479,7 +2483,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2561,7 +2565,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2645,7 +2649,7 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2733,7 +2737,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2817,7 +2821,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2895,7 +2899,7 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2983,7 +2987,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3067,7 +3071,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3147,7 +3151,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3225,7 +3229,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3313,7 +3317,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3397,7 +3401,7 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3483,7 +3487,7 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3567,7 +3571,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3651,7 +3655,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3737,7 +3741,7 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3825,7 +3829,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3905,7 +3909,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3993,7 +3997,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4077,7 +4081,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4157,7 +4161,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4239,7 +4243,7 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4327,7 +4331,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4407,7 +4411,7 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4491,7 +4495,7 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4575,7 +4579,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4663,7 +4667,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4743,7 +4747,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4831,7 +4835,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4911,7 +4915,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4997,7 +5001,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5083,7 +5087,7 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5161,7 +5165,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5247,7 +5251,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5329,7 +5333,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5350,22 +5354,22 @@
         <v>63659.53</v>
       </c>
       <c r="C58" t="n">
-        <v>64101</v>
+        <v>63691.53</v>
       </c>
       <c r="D58" t="n">
         <v>62726.18</v>
       </c>
       <c r="E58" t="n">
-        <v>63484.1</v>
+        <v>63492.99</v>
       </c>
       <c r="F58" t="n">
-        <v>-527.24</v>
+        <v>-518.35</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.0081</v>
       </c>
       <c r="H58" t="n">
-        <v>1374.82</v>
+        <v>965.35</v>
       </c>
       <c r="I58" t="n">
         <v>59625.41</v>
@@ -5411,7 +5415,7 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5425,25 +5429,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>61351.36</v>
+        <v>61760.83</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>62144.54</v>
+        <v>62669.7</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>62796.69</v>
+        <v>63010.31</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>63448.85</v>
+        <v>63350.92</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>64171.51</v>
+        <v>63975.66</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>64894.18</v>
+        <v>64600.41</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>65475.82</v>
+        <v>64656.88</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -5354,22 +5354,22 @@
         <v>63659.53</v>
       </c>
       <c r="C58" t="n">
-        <v>63691.53</v>
+        <v>64101</v>
       </c>
       <c r="D58" t="n">
         <v>62726.18</v>
       </c>
       <c r="E58" t="n">
-        <v>63492.99</v>
+        <v>63484.1</v>
       </c>
       <c r="F58" t="n">
-        <v>-518.35</v>
+        <v>-527.24</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0081</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>965.35</v>
+        <v>1374.82</v>
       </c>
       <c r="I58" t="n">
         <v>59625.41</v>
@@ -5429,25 +5429,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>61760.83</v>
+        <v>61351.36</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>62669.7</v>
+        <v>62144.54</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>63010.31</v>
+        <v>62796.69</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>63350.92</v>
+        <v>63448.85</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>63975.66</v>
+        <v>64171.51</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>64600.41</v>
+        <v>64894.18</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>64656.88</v>
+        <v>65475.82</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -5360,13 +5360,13 @@
         <v>62726.18</v>
       </c>
       <c r="E58" t="n">
-        <v>63484.1</v>
+        <v>63923</v>
       </c>
       <c r="F58" t="n">
-        <v>-527.24</v>
+        <v>-88.34</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.0014</v>
       </c>
       <c r="H58" t="n">
         <v>1374.82</v>
@@ -5432,19 +5432,19 @@
         <v>61351.36</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>62144.54</v>
+        <v>62802.88</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>62796.69</v>
+        <v>63235.59</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>63448.85</v>
+        <v>63668.29</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>64171.51</v>
+        <v>64610.41</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>64894.18</v>
+        <v>65552.53</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>65475.82</v>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -666,25 +666,25 @@
         <v>1545.03</v>
       </c>
       <c r="I2" t="n">
-        <v>41762</v>
+        <v>41808.03</v>
       </c>
       <c r="J2" t="n">
-        <v>42708.18</v>
+        <v>42765.72</v>
       </c>
       <c r="K2" t="n">
-        <v>42955.94</v>
+        <v>42978.96</v>
       </c>
       <c r="L2" t="n">
-        <v>43203.7</v>
+        <v>43192.19</v>
       </c>
       <c r="M2" t="n">
-        <v>43800.67</v>
+        <v>43777.66</v>
       </c>
       <c r="N2" t="n">
-        <v>44397.65</v>
+        <v>44363.12</v>
       </c>
       <c r="O2" t="n">
-        <v>44296.19</v>
+        <v>44204.13</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5360,13 +5360,13 @@
         <v>62726.18</v>
       </c>
       <c r="E58" t="n">
-        <v>63923</v>
+        <v>63484.1</v>
       </c>
       <c r="F58" t="n">
-        <v>-88.34</v>
+        <v>-527.24</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H58" t="n">
         <v>1374.82</v>
@@ -5432,19 +5432,19 @@
         <v>61351.36</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>62802.88</v>
+        <v>62144.54</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>63235.59</v>
+        <v>62796.69</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>63668.29</v>
+        <v>63448.85</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>64610.41</v>
+        <v>64171.51</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>65552.53</v>
+        <v>64894.18</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>65475.82</v>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -5354,22 +5354,22 @@
         <v>63659.53</v>
       </c>
       <c r="C58" t="n">
-        <v>64101</v>
+        <v>64643.58</v>
       </c>
       <c r="D58" t="n">
         <v>62726.18</v>
       </c>
       <c r="E58" t="n">
-        <v>63484.1</v>
+        <v>64136.25</v>
       </c>
       <c r="F58" t="n">
-        <v>-527.24</v>
+        <v>124.91</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.002</v>
       </c>
       <c r="H58" t="n">
-        <v>1374.82</v>
+        <v>1917.4</v>
       </c>
       <c r="I58" t="n">
         <v>59625.41</v>
@@ -5420,7 +5420,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -5429,25 +5433,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>61351.36</v>
+        <v>60808.78</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>62144.54</v>
+        <v>62444.54</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>62796.69</v>
+        <v>63177.55</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>63448.85</v>
+        <v>63910.56</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>64171.51</v>
+        <v>65094.95</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>64894.18</v>
+        <v>66279.33</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>65475.82</v>
+        <v>66560.98</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,8 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X59"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -666,25 +659,25 @@
         <v>1545.03</v>
       </c>
       <c r="I2" t="n">
-        <v>41808.03</v>
+        <v>42068.29</v>
       </c>
       <c r="J2" t="n">
-        <v>42765.72</v>
+        <v>42863.32</v>
       </c>
       <c r="K2" t="n">
-        <v>42978.96</v>
+        <v>43044.02</v>
       </c>
       <c r="L2" t="n">
-        <v>43192.19</v>
+        <v>43224.73</v>
       </c>
       <c r="M2" t="n">
-        <v>43777.66</v>
+        <v>43712.59</v>
       </c>
       <c r="N2" t="n">
-        <v>44363.12</v>
+        <v>44200.46</v>
       </c>
       <c r="O2" t="n">
-        <v>44204.13</v>
+        <v>44074</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5354,22 +5347,22 @@
         <v>63659.53</v>
       </c>
       <c r="C58" t="n">
-        <v>64643.58</v>
+        <v>64101</v>
       </c>
       <c r="D58" t="n">
         <v>62726.18</v>
       </c>
       <c r="E58" t="n">
-        <v>64136.25</v>
+        <v>63923</v>
       </c>
       <c r="F58" t="n">
-        <v>124.91</v>
+        <v>-88.34</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0014</v>
       </c>
       <c r="H58" t="n">
-        <v>1917.4</v>
+        <v>1374.82</v>
       </c>
       <c r="I58" t="n">
         <v>59625.41</v>
@@ -5420,39 +5413,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>下週預測</t>
-        </is>
-      </c>
-      <c r="I59" s="13" t="n">
-        <v>60808.78</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>62444.54</v>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>63177.55</v>
-      </c>
-      <c r="L59" s="13" t="n">
-        <v>63910.56</v>
-      </c>
-      <c r="M59" s="13" t="n">
-        <v>65094.95</v>
-      </c>
-      <c r="N59" s="13" t="n">
-        <v>66279.33</v>
-      </c>
-      <c r="O59" s="13" t="n">
-        <v>66560.98</v>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,73 +634,67 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43452.9</v>
+        <v>42977.27</v>
       </c>
       <c r="C2" t="n">
-        <v>43876.42</v>
+        <v>43201.42</v>
       </c>
       <c r="D2" t="n">
-        <v>42331.39</v>
+        <v>42137.62</v>
       </c>
       <c r="E2" t="n">
-        <v>42633.29</v>
+        <v>42718.47</v>
       </c>
       <c r="F2" t="n">
-        <v>-745.02</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0172</v>
+        <v>0.002</v>
       </c>
       <c r="H2" t="n">
-        <v>1545.03</v>
+        <v>1063.8</v>
       </c>
       <c r="I2" t="n">
-        <v>42068.29</v>
+        <v>40786.36</v>
       </c>
       <c r="J2" t="n">
-        <v>42863.32</v>
+        <v>40852.95</v>
       </c>
       <c r="K2" t="n">
-        <v>43044.02</v>
+        <v>41860.77</v>
       </c>
       <c r="L2" t="n">
-        <v>43224.73</v>
+        <v>42868.6</v>
       </c>
       <c r="M2" t="n">
-        <v>43712.59</v>
+        <v>43405.8</v>
       </c>
       <c r="N2" t="n">
-        <v>44200.46</v>
+        <v>43943.01</v>
       </c>
       <c r="O2" t="n">
-        <v>44074</v>
+        <v>45421.45</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -710,62 +704,62 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42977.27</v>
+        <v>42362.71</v>
       </c>
       <c r="C3" t="n">
-        <v>43201.42</v>
+        <v>43220.94</v>
       </c>
       <c r="D3" t="n">
-        <v>42137.62</v>
+        <v>41835.17</v>
       </c>
       <c r="E3" t="n">
-        <v>42718.47</v>
+        <v>43018.75</v>
       </c>
       <c r="F3" t="n">
-        <v>85.18000000000001</v>
+        <v>300.28</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H3" t="n">
-        <v>1063.8</v>
+        <v>1385.77</v>
       </c>
       <c r="I3" t="n">
-        <v>40786.36</v>
+        <v>41073.82</v>
       </c>
       <c r="J3" t="n">
-        <v>40852.95</v>
+        <v>41679.14</v>
       </c>
       <c r="K3" t="n">
-        <v>41860.77</v>
+        <v>42186.57</v>
       </c>
       <c r="L3" t="n">
-        <v>42868.6</v>
+        <v>42694</v>
       </c>
       <c r="M3" t="n">
-        <v>43405.8</v>
+        <v>43250.37</v>
       </c>
       <c r="N3" t="n">
-        <v>43943.01</v>
+        <v>43806.74</v>
       </c>
       <c r="O3" t="n">
-        <v>45421.45</v>
+        <v>44265.22</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -773,16 +767,20 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -792,7 +790,7 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -804,50 +802,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42362.71</v>
+        <v>43451.07</v>
       </c>
       <c r="C4" t="n">
-        <v>43220.94</v>
+        <v>44888.02</v>
       </c>
       <c r="D4" t="n">
-        <v>41835.17</v>
+        <v>43343.58</v>
       </c>
       <c r="E4" t="n">
-        <v>43018.75</v>
+        <v>44768.12</v>
       </c>
       <c r="F4" t="n">
-        <v>300.28</v>
+        <v>1749.37</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.007</v>
+        <v>0.0407</v>
       </c>
       <c r="H4" t="n">
-        <v>1385.77</v>
+        <v>1544.44</v>
       </c>
       <c r="I4" t="n">
-        <v>41073.82</v>
+        <v>40449.4</v>
       </c>
       <c r="J4" t="n">
-        <v>41679.14</v>
+        <v>41878.33</v>
       </c>
       <c r="K4" t="n">
-        <v>42186.57</v>
+        <v>42325.87</v>
       </c>
       <c r="L4" t="n">
-        <v>42694</v>
+        <v>42773.4</v>
       </c>
       <c r="M4" t="n">
-        <v>43250.37</v>
+        <v>43711.63</v>
       </c>
       <c r="N4" t="n">
-        <v>43806.74</v>
+        <v>44649.87</v>
       </c>
       <c r="O4" t="n">
-        <v>44265.22</v>
+        <v>44606.71</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -855,10 +853,8 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R4" s="6" t="n">
+        <v/>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
@@ -867,73 +863,73 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>43451.07</v>
+        <v>44948.85</v>
       </c>
       <c r="C5" t="n">
-        <v>44888.02</v>
+        <v>45852.75</v>
       </c>
       <c r="D5" t="n">
-        <v>43343.58</v>
+        <v>44495.46</v>
       </c>
       <c r="E5" t="n">
-        <v>44768.12</v>
+        <v>45045.81</v>
       </c>
       <c r="F5" t="n">
-        <v>1749.37</v>
+        <v>277.69</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0407</v>
+        <v>0.0062</v>
       </c>
       <c r="H5" t="n">
-        <v>1544.44</v>
+        <v>1357.29</v>
       </c>
       <c r="I5" t="n">
-        <v>40449.4</v>
+        <v>41799.14</v>
       </c>
       <c r="J5" t="n">
-        <v>41878.33</v>
+        <v>43549.84</v>
       </c>
       <c r="K5" t="n">
-        <v>42325.87</v>
+        <v>43995.9</v>
       </c>
       <c r="L5" t="n">
-        <v>42773.4</v>
+        <v>44441.96</v>
       </c>
       <c r="M5" t="n">
-        <v>43711.63</v>
+        <v>45540.34</v>
       </c>
       <c r="N5" t="n">
-        <v>44649.87</v>
+        <v>46638.72</v>
       </c>
       <c r="O5" t="n">
-        <v>44606.71</v>
+        <v>46432.46</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -951,20 +947,16 @@
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -974,50 +966,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44948.85</v>
+        <v>45193.77</v>
       </c>
       <c r="C6" t="n">
-        <v>45852.75</v>
+        <v>45824.69</v>
       </c>
       <c r="D6" t="n">
-        <v>44495.46</v>
+        <v>45193.77</v>
       </c>
       <c r="E6" t="n">
-        <v>45045.81</v>
+        <v>45354.99</v>
       </c>
       <c r="F6" t="n">
-        <v>277.69</v>
+        <v>309.18</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0062</v>
+        <v>0.0069</v>
       </c>
       <c r="H6" t="n">
-        <v>1357.29</v>
+        <v>630.92</v>
       </c>
       <c r="I6" t="n">
-        <v>41799.14</v>
+        <v>43138.17</v>
       </c>
       <c r="J6" t="n">
-        <v>43549.84</v>
+        <v>43624.37</v>
       </c>
       <c r="K6" t="n">
-        <v>43995.9</v>
+        <v>44367.16</v>
       </c>
       <c r="L6" t="n">
-        <v>44441.96</v>
+        <v>45109.96</v>
       </c>
       <c r="M6" t="n">
-        <v>45540.34</v>
+        <v>45724.45</v>
       </c>
       <c r="N6" t="n">
-        <v>46638.72</v>
+        <v>46338.95</v>
       </c>
       <c r="O6" t="n">
-        <v>46432.46</v>
+        <v>47210.04</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1030,12 +1022,12 @@
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U6" s="8" t="n">
@@ -1044,78 +1036,88 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>45193.77</v>
+        <v>45113.29</v>
       </c>
       <c r="C7" t="n">
-        <v>45824.69</v>
+        <v>45778.66</v>
       </c>
       <c r="D7" t="n">
-        <v>45193.77</v>
+        <v>44357.65</v>
       </c>
       <c r="E7" t="n">
-        <v>45354.99</v>
+        <v>45769.5</v>
       </c>
       <c r="F7" t="n">
-        <v>309.18</v>
+        <v>414.51</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0091</v>
       </c>
       <c r="H7" t="n">
-        <v>630.92</v>
+        <v>1421.01</v>
       </c>
       <c r="I7" t="n">
-        <v>43138.17</v>
+        <v>44562.85</v>
       </c>
       <c r="J7" t="n">
-        <v>43624.37</v>
+        <v>44646.95</v>
       </c>
       <c r="K7" t="n">
-        <v>44367.16</v>
+        <v>45039.53</v>
       </c>
       <c r="L7" t="n">
-        <v>45109.96</v>
+        <v>45432.11</v>
       </c>
       <c r="M7" t="n">
-        <v>45724.45</v>
+        <v>45670.45</v>
       </c>
       <c r="N7" t="n">
-        <v>46338.95</v>
+        <v>45908.79</v>
       </c>
       <c r="O7" t="n">
-        <v>47210.04</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+        <v>46455.61</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U7" s="8" t="n">
@@ -1124,79 +1126,73 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>45113.29</v>
+        <v>46636.07</v>
       </c>
       <c r="C8" t="n">
-        <v>45778.66</v>
+        <v>48597.08</v>
       </c>
       <c r="D8" t="n">
-        <v>44357.65</v>
+        <v>46592.99</v>
       </c>
       <c r="E8" t="n">
-        <v>45769.5</v>
+        <v>48088.8</v>
       </c>
       <c r="F8" t="n">
-        <v>414.51</v>
+        <v>2319.3</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0507</v>
       </c>
       <c r="H8" t="n">
-        <v>1421.01</v>
+        <v>2004.09</v>
       </c>
       <c r="I8" t="n">
-        <v>44562.85</v>
+        <v>42936.64</v>
       </c>
       <c r="J8" t="n">
-        <v>44646.95</v>
+        <v>44699.16</v>
       </c>
       <c r="K8" t="n">
-        <v>45039.53</v>
+        <v>45058.99</v>
       </c>
       <c r="L8" t="n">
-        <v>45432.11</v>
+        <v>45418.83</v>
       </c>
       <c r="M8" t="n">
-        <v>45670.45</v>
+        <v>46480.01</v>
       </c>
       <c r="N8" t="n">
-        <v>45908.79</v>
+        <v>47541.18</v>
       </c>
       <c r="O8" t="n">
-        <v>46455.61</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>47199.67</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
@@ -1205,73 +1201,73 @@
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46636.07</v>
+        <v>47446.73</v>
       </c>
       <c r="C9" t="n">
-        <v>48597.08</v>
+        <v>48317.34</v>
       </c>
       <c r="D9" t="n">
-        <v>46592.99</v>
+        <v>46544.05</v>
       </c>
       <c r="E9" t="n">
-        <v>48088.8</v>
+        <v>47582.15</v>
       </c>
       <c r="F9" t="n">
-        <v>2319.3</v>
+        <v>-506.65</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0507</v>
+        <v>-0.0105</v>
       </c>
       <c r="H9" t="n">
-        <v>2004.09</v>
+        <v>1773.29</v>
       </c>
       <c r="I9" t="n">
-        <v>42936.64</v>
+        <v>44588.9</v>
       </c>
       <c r="J9" t="n">
-        <v>44699.16</v>
+        <v>46331.59</v>
       </c>
       <c r="K9" t="n">
-        <v>45058.99</v>
+        <v>47086.76</v>
       </c>
       <c r="L9" t="n">
-        <v>45418.83</v>
+        <v>47841.92</v>
       </c>
       <c r="M9" t="n">
-        <v>46480.01</v>
+        <v>49090.85</v>
       </c>
       <c r="N9" t="n">
-        <v>47541.18</v>
+        <v>50339.77</v>
       </c>
       <c r="O9" t="n">
-        <v>47199.67</v>
+        <v>50601.17</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1279,83 +1275,83 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47446.73</v>
+        <v>48332.71</v>
       </c>
       <c r="C10" t="n">
-        <v>48317.34</v>
+        <v>49945.95</v>
       </c>
       <c r="D10" t="n">
-        <v>46544.05</v>
+        <v>48254.83</v>
       </c>
       <c r="E10" t="n">
-        <v>47582.15</v>
+        <v>49299.65</v>
       </c>
       <c r="F10" t="n">
-        <v>-506.65</v>
+        <v>1717.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0105</v>
+        <v>0.0361</v>
       </c>
       <c r="H10" t="n">
-        <v>1773.29</v>
+        <v>1691.12</v>
       </c>
       <c r="I10" t="n">
-        <v>44588.9</v>
+        <v>44770.76</v>
       </c>
       <c r="J10" t="n">
-        <v>46331.59</v>
+        <v>45884.59</v>
       </c>
       <c r="K10" t="n">
-        <v>47086.76</v>
+        <v>46695.5</v>
       </c>
       <c r="L10" t="n">
-        <v>47841.92</v>
+        <v>47506.42</v>
       </c>
       <c r="M10" t="n">
-        <v>49090.85</v>
+        <v>48468.79</v>
       </c>
       <c r="N10" t="n">
-        <v>50339.77</v>
+        <v>49431.16</v>
       </c>
       <c r="O10" t="n">
-        <v>50601.17</v>
+        <v>50090.63</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1363,83 +1359,81 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>48332.71</v>
+        <v>49905.8</v>
       </c>
       <c r="C11" t="n">
-        <v>49945.95</v>
+        <v>52411.34</v>
       </c>
       <c r="D11" t="n">
-        <v>48254.83</v>
+        <v>49838.98</v>
       </c>
       <c r="E11" t="n">
-        <v>49299.65</v>
+        <v>52411.34</v>
       </c>
       <c r="F11" t="n">
-        <v>1717.5</v>
+        <v>3111.69</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0361</v>
+        <v>0.0631</v>
       </c>
       <c r="H11" t="n">
-        <v>1691.12</v>
+        <v>2572.36</v>
       </c>
       <c r="I11" t="n">
-        <v>44770.76</v>
+        <v>46563.71</v>
       </c>
       <c r="J11" t="n">
-        <v>45884.59</v>
+        <v>47708.16</v>
       </c>
       <c r="K11" t="n">
-        <v>46695.5</v>
+        <v>48454.09</v>
       </c>
       <c r="L11" t="n">
-        <v>47506.42</v>
+        <v>49200.02</v>
       </c>
       <c r="M11" t="n">
-        <v>48468.79</v>
+        <v>50145.21</v>
       </c>
       <c r="N11" t="n">
-        <v>49431.16</v>
+        <v>51090.4</v>
       </c>
       <c r="O11" t="n">
-        <v>50090.63</v>
+        <v>51637.07</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1462,13 +1456,15 @@
       </c>
       <c r="U11" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1478,151 +1474,149 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49905.8</v>
+        <v>52294.31</v>
       </c>
       <c r="C12" t="n">
-        <v>52411.34</v>
+        <v>52636.87</v>
       </c>
       <c r="D12" t="n">
-        <v>49838.98</v>
+        <v>49073.58</v>
       </c>
       <c r="E12" t="n">
-        <v>52411.34</v>
+        <v>50276.37</v>
       </c>
       <c r="F12" t="n">
-        <v>3111.69</v>
+        <v>-2134.97</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0631</v>
+        <v>-0.0407</v>
       </c>
       <c r="H12" t="n">
-        <v>2572.36</v>
+        <v>3563.29</v>
       </c>
       <c r="I12" t="n">
-        <v>46563.71</v>
+        <v>47266.62</v>
       </c>
       <c r="J12" t="n">
-        <v>47708.16</v>
+        <v>50482.07</v>
       </c>
       <c r="K12" t="n">
-        <v>48454.09</v>
+        <v>51125.16</v>
       </c>
       <c r="L12" t="n">
-        <v>49200.02</v>
+        <v>51768.25</v>
       </c>
       <c r="M12" t="n">
-        <v>50145.21</v>
+        <v>53697.52</v>
       </c>
       <c r="N12" t="n">
-        <v>51090.4</v>
+        <v>55626.79</v>
       </c>
       <c r="O12" t="n">
-        <v>51637.07</v>
+        <v>54983.7</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="inlineStr">
+      <c r="Q12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v/>
+      </c>
       <c r="W12" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52294.31</v>
+        <v>50645.27</v>
       </c>
       <c r="C13" t="n">
-        <v>52636.87</v>
+        <v>51513.16</v>
       </c>
       <c r="D13" t="n">
-        <v>49073.58</v>
+        <v>50246.6</v>
       </c>
       <c r="E13" t="n">
-        <v>50276.37</v>
+        <v>50376.53</v>
       </c>
       <c r="F13" t="n">
-        <v>-2134.97</v>
+        <v>100.16</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0407</v>
+        <v>0.002</v>
       </c>
       <c r="H13" t="n">
-        <v>3563.29</v>
+        <v>1266.56</v>
       </c>
       <c r="I13" t="n">
-        <v>47266.62</v>
+        <v>45510.29</v>
       </c>
       <c r="J13" t="n">
-        <v>50482.07</v>
+        <v>46423.65</v>
       </c>
       <c r="K13" t="n">
-        <v>51125.16</v>
+        <v>48494.72</v>
       </c>
       <c r="L13" t="n">
-        <v>51768.25</v>
+        <v>50565.8</v>
       </c>
       <c r="M13" t="n">
-        <v>53697.52</v>
+        <v>52058.02</v>
       </c>
       <c r="N13" t="n">
-        <v>55626.79</v>
+        <v>53550.24</v>
       </c>
       <c r="O13" t="n">
-        <v>54983.7</v>
+        <v>56200.16</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1634,77 +1628,83 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>50645.27</v>
+        <v>50282.39</v>
       </c>
       <c r="C14" t="n">
-        <v>51513.16</v>
+        <v>50574.82</v>
       </c>
       <c r="D14" t="n">
-        <v>50246.6</v>
+        <v>48235.3</v>
       </c>
       <c r="E14" t="n">
-        <v>50376.53</v>
+        <v>48625.88</v>
       </c>
       <c r="F14" t="n">
-        <v>100.16</v>
+        <v>-1750.65</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0348</v>
       </c>
       <c r="H14" t="n">
-        <v>1266.56</v>
+        <v>2339.52</v>
       </c>
       <c r="I14" t="n">
-        <v>45510.29</v>
+        <v>48980.04</v>
       </c>
       <c r="J14" t="n">
-        <v>46423.65</v>
+        <v>48858.3</v>
       </c>
       <c r="K14" t="n">
-        <v>48494.72</v>
+        <v>49743.25</v>
       </c>
       <c r="L14" t="n">
-        <v>50565.8</v>
+        <v>50628.21</v>
       </c>
       <c r="M14" t="n">
-        <v>52058.02</v>
+        <v>51009.81</v>
       </c>
       <c r="N14" t="n">
-        <v>53550.24</v>
+        <v>51391.42</v>
       </c>
       <c r="O14" t="n">
-        <v>56200.16</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+        <v>52779.72</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1716,148 +1716,146 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>50282.39</v>
+        <v>49113.82</v>
       </c>
       <c r="C15" t="n">
-        <v>50574.82</v>
+        <v>50322.14</v>
       </c>
       <c r="D15" t="n">
-        <v>48235.3</v>
+        <v>48511.95</v>
       </c>
       <c r="E15" t="n">
-        <v>48625.88</v>
+        <v>50253.91</v>
       </c>
       <c r="F15" t="n">
-        <v>-1750.65</v>
+        <v>1628.03</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0348</v>
+        <v>0.0335</v>
       </c>
       <c r="H15" t="n">
-        <v>2339.52</v>
+        <v>1810.19</v>
       </c>
       <c r="I15" t="n">
-        <v>48980.04</v>
+        <v>45895.78</v>
       </c>
       <c r="J15" t="n">
-        <v>48858.3</v>
+        <v>45896.77</v>
       </c>
       <c r="K15" t="n">
-        <v>49743.25</v>
+        <v>47456.12</v>
       </c>
       <c r="L15" t="n">
-        <v>50628.21</v>
+        <v>49015.47</v>
       </c>
       <c r="M15" t="n">
-        <v>51009.81</v>
+        <v>49795.64</v>
       </c>
       <c r="N15" t="n">
-        <v>51391.42</v>
+        <v>50575.81</v>
       </c>
       <c r="O15" t="n">
-        <v>52779.72</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
+        <v>52914.34</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>49113.82</v>
+        <v>50318.59</v>
       </c>
       <c r="C16" t="n">
-        <v>50322.14</v>
+        <v>51028.42</v>
       </c>
       <c r="D16" t="n">
-        <v>48511.95</v>
+        <v>49215.96</v>
       </c>
       <c r="E16" t="n">
-        <v>50253.91</v>
+        <v>50491.87</v>
       </c>
       <c r="F16" t="n">
-        <v>1628.03</v>
+        <v>237.96</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0335</v>
+        <v>0.0047</v>
       </c>
       <c r="H16" t="n">
-        <v>1810.19</v>
+        <v>1812.46</v>
       </c>
       <c r="I16" t="n">
-        <v>45895.78</v>
+        <v>46701.76</v>
       </c>
       <c r="J16" t="n">
-        <v>45896.77</v>
+        <v>48862.15</v>
       </c>
       <c r="K16" t="n">
-        <v>47456.12</v>
+        <v>49348.81</v>
       </c>
       <c r="L16" t="n">
-        <v>49015.47</v>
+        <v>49835.48</v>
       </c>
       <c r="M16" t="n">
-        <v>49795.64</v>
+        <v>51159.01</v>
       </c>
       <c r="N16" t="n">
-        <v>50575.81</v>
+        <v>52482.53</v>
       </c>
       <c r="O16" t="n">
-        <v>52914.34</v>
+        <v>52132.33</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1865,85 +1863,83 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>50318.59</v>
+        <v>50643.09</v>
       </c>
       <c r="C17" t="n">
-        <v>51028.42</v>
+        <v>51127.69</v>
       </c>
       <c r="D17" t="n">
-        <v>49215.96</v>
+        <v>49926.27</v>
       </c>
       <c r="E17" t="n">
-        <v>50491.87</v>
+        <v>50836.55</v>
       </c>
       <c r="F17" t="n">
-        <v>237.96</v>
+        <v>344.68</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0047</v>
+        <v>0.0068</v>
       </c>
       <c r="H17" t="n">
-        <v>1812.46</v>
+        <v>1201.42</v>
       </c>
       <c r="I17" t="n">
-        <v>46701.76</v>
+        <v>47403.5</v>
       </c>
       <c r="J17" t="n">
-        <v>48862.15</v>
+        <v>48864.25</v>
       </c>
       <c r="K17" t="n">
-        <v>49348.81</v>
+        <v>49585.64</v>
       </c>
       <c r="L17" t="n">
-        <v>49835.48</v>
+        <v>50307.03</v>
       </c>
       <c r="M17" t="n">
-        <v>51159.01</v>
+        <v>51398.1</v>
       </c>
       <c r="N17" t="n">
-        <v>52482.53</v>
+        <v>52489.17</v>
       </c>
       <c r="O17" t="n">
-        <v>52132.33</v>
+        <v>52840.88</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1951,10 +1947,8 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R17" s="6" t="n">
+        <v/>
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
@@ -1970,7 +1964,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1984,63 +1978,69 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50643.09</v>
+        <v>50352.09</v>
       </c>
       <c r="C18" t="n">
-        <v>51127.69</v>
+        <v>50432.1</v>
       </c>
       <c r="D18" t="n">
-        <v>49926.27</v>
+        <v>48643.78</v>
       </c>
       <c r="E18" t="n">
-        <v>50836.55</v>
+        <v>49507.21</v>
       </c>
       <c r="F18" t="n">
-        <v>344.68</v>
+        <v>-1329.34</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0261</v>
       </c>
       <c r="H18" t="n">
-        <v>1201.42</v>
+        <v>1788.32</v>
       </c>
       <c r="I18" t="n">
-        <v>47403.5</v>
+        <v>48724.85</v>
       </c>
       <c r="J18" t="n">
-        <v>48864.25</v>
+        <v>49789.91</v>
       </c>
       <c r="K18" t="n">
-        <v>49585.64</v>
+        <v>50235.84</v>
       </c>
       <c r="L18" t="n">
-        <v>50307.03</v>
+        <v>50681.77</v>
       </c>
       <c r="M18" t="n">
-        <v>51398.1</v>
+        <v>51437.26</v>
       </c>
       <c r="N18" t="n">
-        <v>52489.17</v>
+        <v>52192.76</v>
       </c>
       <c r="O18" t="n">
-        <v>52840.88</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>52329.11</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2052,148 +2052,144 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>50352.09</v>
+        <v>50084.55</v>
       </c>
       <c r="C19" t="n">
-        <v>50432.1</v>
+        <v>50941.89</v>
       </c>
       <c r="D19" t="n">
-        <v>48643.78</v>
+        <v>49982.2</v>
       </c>
       <c r="E19" t="n">
-        <v>49507.21</v>
+        <v>50750.39</v>
       </c>
       <c r="F19" t="n">
-        <v>-1329.34</v>
+        <v>1243.18</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0261</v>
+        <v>0.0251</v>
       </c>
       <c r="H19" t="n">
-        <v>1788.32</v>
+        <v>959.6900000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>48724.85</v>
+        <v>46855.46</v>
       </c>
       <c r="J19" t="n">
-        <v>49789.91</v>
+        <v>47703.53</v>
       </c>
       <c r="K19" t="n">
-        <v>50235.84</v>
+        <v>48613.05</v>
       </c>
       <c r="L19" t="n">
-        <v>50681.77</v>
+        <v>49522.58</v>
       </c>
       <c r="M19" t="n">
-        <v>51437.26</v>
+        <v>50401.37</v>
       </c>
       <c r="N19" t="n">
-        <v>52192.76</v>
+        <v>51280.17</v>
       </c>
       <c r="O19" t="n">
-        <v>52329.11</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q19" s="6" t="inlineStr">
+        <v>52220.42</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>50084.55</v>
+        <v>50691.22</v>
       </c>
       <c r="C20" t="n">
-        <v>50941.89</v>
+        <v>50707.23</v>
       </c>
       <c r="D20" t="n">
-        <v>49982.2</v>
+        <v>50198.97</v>
       </c>
       <c r="E20" t="n">
-        <v>50750.39</v>
+        <v>50339.48</v>
       </c>
       <c r="F20" t="n">
-        <v>1243.18</v>
+        <v>-410.91</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0251</v>
+        <v>-0.0081</v>
       </c>
       <c r="H20" t="n">
-        <v>959.6900000000001</v>
+        <v>508.26</v>
       </c>
       <c r="I20" t="n">
-        <v>46855.46</v>
+        <v>49022.51</v>
       </c>
       <c r="J20" t="n">
-        <v>47703.53</v>
+        <v>49934.87</v>
       </c>
       <c r="K20" t="n">
-        <v>48613.05</v>
+        <v>50270.54</v>
       </c>
       <c r="L20" t="n">
-        <v>49522.58</v>
+        <v>50606.22</v>
       </c>
       <c r="M20" t="n">
-        <v>50401.37</v>
+        <v>51230.24</v>
       </c>
       <c r="N20" t="n">
-        <v>51280.17</v>
+        <v>51854.25</v>
       </c>
       <c r="O20" t="n">
-        <v>52220.42</v>
+        <v>51901.58</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2201,83 +2197,83 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>50691.22</v>
+        <v>51010.28</v>
       </c>
       <c r="C21" t="n">
-        <v>50707.23</v>
+        <v>52523.77</v>
       </c>
       <c r="D21" t="n">
-        <v>50198.97</v>
+        <v>50995.67</v>
       </c>
       <c r="E21" t="n">
-        <v>50339.48</v>
+        <v>51939.89</v>
       </c>
       <c r="F21" t="n">
-        <v>-410.91</v>
+        <v>1600.41</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0081</v>
+        <v>0.0318</v>
       </c>
       <c r="H21" t="n">
-        <v>508.26</v>
+        <v>1528.1</v>
       </c>
       <c r="I21" t="n">
-        <v>49022.51</v>
+        <v>49690.71</v>
       </c>
       <c r="J21" t="n">
-        <v>49934.87</v>
+        <v>49774.41</v>
       </c>
       <c r="K21" t="n">
-        <v>50270.54</v>
+        <v>50085.35</v>
       </c>
       <c r="L21" t="n">
-        <v>50606.22</v>
+        <v>50396.29</v>
       </c>
       <c r="M21" t="n">
-        <v>51230.24</v>
+        <v>50593.61</v>
       </c>
       <c r="N21" t="n">
-        <v>51854.25</v>
+        <v>50790.93</v>
       </c>
       <c r="O21" t="n">
-        <v>51901.58</v>
+        <v>51215.49</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2285,83 +2281,83 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
-      </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>51010.28</v>
+        <v>52808.29</v>
       </c>
       <c r="C22" t="n">
-        <v>52523.77</v>
+        <v>54487.32</v>
       </c>
       <c r="D22" t="n">
-        <v>50995.67</v>
+        <v>52741.64</v>
       </c>
       <c r="E22" t="n">
-        <v>51939.89</v>
+        <v>53936.17</v>
       </c>
       <c r="F22" t="n">
-        <v>1600.41</v>
+        <v>1996.28</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0318</v>
+        <v>0.0384</v>
       </c>
       <c r="H22" t="n">
-        <v>1528.1</v>
+        <v>1745.68</v>
       </c>
       <c r="I22" t="n">
-        <v>49690.71</v>
+        <v>49467.57</v>
       </c>
       <c r="J22" t="n">
-        <v>49774.41</v>
+        <v>50501.88</v>
       </c>
       <c r="K22" t="n">
-        <v>50085.35</v>
+        <v>51175.84</v>
       </c>
       <c r="L22" t="n">
-        <v>50396.29</v>
+        <v>51849.81</v>
       </c>
       <c r="M22" t="n">
-        <v>50593.61</v>
+        <v>52703.94</v>
       </c>
       <c r="N22" t="n">
-        <v>50790.93</v>
+        <v>53558.07</v>
       </c>
       <c r="O22" t="n">
-        <v>51215.49</v>
+        <v>54051.87</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2392,7 +2388,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2402,151 +2398,151 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>52808.29</v>
+        <v>53390.05</v>
       </c>
       <c r="C23" t="n">
-        <v>54487.32</v>
+        <v>54050.84</v>
       </c>
       <c r="D23" t="n">
-        <v>52741.64</v>
+        <v>52194.81</v>
       </c>
       <c r="E23" t="n">
-        <v>53936.17</v>
+        <v>53846.87</v>
       </c>
       <c r="F23" t="n">
-        <v>1996.28</v>
+        <v>-89.3</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0384</v>
+        <v>-0.0017</v>
       </c>
       <c r="H23" t="n">
-        <v>1745.68</v>
+        <v>1856.03</v>
       </c>
       <c r="I23" t="n">
-        <v>49467.57</v>
+        <v>50995.96</v>
       </c>
       <c r="J23" t="n">
-        <v>50501.88</v>
+        <v>52351.34</v>
       </c>
       <c r="K23" t="n">
-        <v>51175.84</v>
+        <v>53063.33</v>
       </c>
       <c r="L23" t="n">
-        <v>51849.81</v>
+        <v>53775.33</v>
       </c>
       <c r="M23" t="n">
-        <v>52703.94</v>
+        <v>54809.01</v>
       </c>
       <c r="N23" t="n">
-        <v>53558.07</v>
+        <v>55842.7</v>
       </c>
       <c r="O23" t="n">
-        <v>54051.87</v>
+        <v>56233</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W23" s="11" t="inlineStr">
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>53390.05</v>
+        <v>53023.28</v>
       </c>
       <c r="C24" t="n">
-        <v>54050.84</v>
+        <v>53742.69</v>
       </c>
       <c r="D24" t="n">
-        <v>52194.81</v>
+        <v>52637.66</v>
       </c>
       <c r="E24" t="n">
-        <v>53846.87</v>
+        <v>53322.85</v>
       </c>
       <c r="F24" t="n">
-        <v>-89.3</v>
+        <v>-524.02</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0097</v>
       </c>
       <c r="H24" t="n">
-        <v>1856.03</v>
+        <v>1105.03</v>
       </c>
       <c r="I24" t="n">
-        <v>50995.96</v>
+        <v>50338.78</v>
       </c>
       <c r="J24" t="n">
-        <v>52351.34</v>
+        <v>52352.86</v>
       </c>
       <c r="K24" t="n">
-        <v>53063.33</v>
+        <v>52918.86</v>
       </c>
       <c r="L24" t="n">
-        <v>53775.33</v>
+        <v>53484.85</v>
       </c>
       <c r="M24" t="n">
-        <v>54809.01</v>
+        <v>54774.89</v>
       </c>
       <c r="N24" t="n">
-        <v>55842.7</v>
+        <v>56064.93</v>
       </c>
       <c r="O24" t="n">
-        <v>56233</v>
+        <v>55906.87</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q24" s="6" t="n">
+        <v/>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2558,64 +2554,64 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>53023.28</v>
+        <v>53575.37</v>
       </c>
       <c r="C25" t="n">
-        <v>53742.69</v>
+        <v>54782.83</v>
       </c>
       <c r="D25" t="n">
-        <v>52637.66</v>
+        <v>52655.18</v>
       </c>
       <c r="E25" t="n">
-        <v>53322.85</v>
+        <v>54253.68</v>
       </c>
       <c r="F25" t="n">
-        <v>-524.02</v>
+        <v>930.83</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0175</v>
       </c>
       <c r="H25" t="n">
-        <v>1105.03</v>
+        <v>2127.65</v>
       </c>
       <c r="I25" t="n">
-        <v>50338.78</v>
+        <v>51532.63</v>
       </c>
       <c r="J25" t="n">
-        <v>52352.86</v>
+        <v>52284.16</v>
       </c>
       <c r="K25" t="n">
-        <v>52918.86</v>
+        <v>52770.34</v>
       </c>
       <c r="L25" t="n">
-        <v>53484.85</v>
+        <v>53256.51</v>
       </c>
       <c r="M25" t="n">
-        <v>54774.89</v>
+        <v>53875.37</v>
       </c>
       <c r="N25" t="n">
-        <v>56064.93</v>
+        <v>54494.22</v>
       </c>
       <c r="O25" t="n">
-        <v>55906.87</v>
+        <v>54847.72</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2628,78 +2624,78 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>53575.37</v>
+        <v>55130.63</v>
       </c>
       <c r="C26" t="n">
-        <v>54782.83</v>
+        <v>58015.08</v>
       </c>
       <c r="D26" t="n">
-        <v>52655.18</v>
+        <v>55018.57</v>
       </c>
       <c r="E26" t="n">
-        <v>54253.68</v>
+        <v>56941.97</v>
       </c>
       <c r="F26" t="n">
-        <v>930.83</v>
+        <v>2688.29</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0496</v>
       </c>
       <c r="H26" t="n">
-        <v>2127.65</v>
+        <v>2996.51</v>
       </c>
       <c r="I26" t="n">
-        <v>51532.63</v>
+        <v>50527.53</v>
       </c>
       <c r="J26" t="n">
-        <v>52284.16</v>
+        <v>52393.37</v>
       </c>
       <c r="K26" t="n">
-        <v>52770.34</v>
+        <v>53189.86</v>
       </c>
       <c r="L26" t="n">
-        <v>53256.51</v>
+        <v>53986.34</v>
       </c>
       <c r="M26" t="n">
-        <v>53875.37</v>
+        <v>55317.5</v>
       </c>
       <c r="N26" t="n">
-        <v>54494.22</v>
+        <v>56648.67</v>
       </c>
       <c r="O26" t="n">
-        <v>54847.72</v>
+        <v>56910.48</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2707,10 +2703,8 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
@@ -2724,13 +2718,15 @@
       </c>
       <c r="U26" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2740,50 +2736,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>55130.63</v>
+        <v>57212.97</v>
       </c>
       <c r="C27" t="n">
-        <v>58015.08</v>
+        <v>57709.82</v>
       </c>
       <c r="D27" t="n">
-        <v>55018.57</v>
+        <v>56135.12</v>
       </c>
       <c r="E27" t="n">
-        <v>56941.97</v>
+        <v>56825.7</v>
       </c>
       <c r="F27" t="n">
-        <v>2688.29</v>
+        <v>-116.27</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0496</v>
+        <v>-0.002</v>
       </c>
       <c r="H27" t="n">
-        <v>2996.51</v>
+        <v>1574.7</v>
       </c>
       <c r="I27" t="n">
-        <v>50527.53</v>
+        <v>52022.06</v>
       </c>
       <c r="J27" t="n">
-        <v>52393.37</v>
+        <v>54158.03</v>
       </c>
       <c r="K27" t="n">
-        <v>53189.86</v>
+        <v>55443.71</v>
       </c>
       <c r="L27" t="n">
-        <v>53986.34</v>
+        <v>56729.4</v>
       </c>
       <c r="M27" t="n">
-        <v>55317.5</v>
+        <v>58440.22</v>
       </c>
       <c r="N27" t="n">
-        <v>56648.67</v>
+        <v>60151.05</v>
       </c>
       <c r="O27" t="n">
-        <v>56910.48</v>
+        <v>61011.59</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2796,78 +2792,76 @@
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W27" s="11" t="inlineStr">
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>57212.97</v>
+        <v>56764.14</v>
       </c>
       <c r="C28" t="n">
-        <v>57709.82</v>
+        <v>59332.43</v>
       </c>
       <c r="D28" t="n">
-        <v>56135.12</v>
+        <v>56732.93</v>
       </c>
       <c r="E28" t="n">
-        <v>56825.7</v>
+        <v>58850.27</v>
       </c>
       <c r="F28" t="n">
-        <v>-116.27</v>
+        <v>2024.57</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0356</v>
       </c>
       <c r="H28" t="n">
-        <v>1574.7</v>
+        <v>2599.5</v>
       </c>
       <c r="I28" t="n">
-        <v>52022.06</v>
+        <v>54560.42</v>
       </c>
       <c r="J28" t="n">
-        <v>54158.03</v>
+        <v>55202.61</v>
       </c>
       <c r="K28" t="n">
-        <v>55443.71</v>
+        <v>56038.35</v>
       </c>
       <c r="L28" t="n">
-        <v>56729.4</v>
+        <v>56874.08</v>
       </c>
       <c r="M28" t="n">
-        <v>58440.22</v>
+        <v>57613.05</v>
       </c>
       <c r="N28" t="n">
-        <v>60151.05</v>
+        <v>58352.01</v>
       </c>
       <c r="O28" t="n">
-        <v>61011.59</v>
+        <v>59284.52</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2880,109 +2874,111 @@
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W28" s="11" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>56764.14</v>
+        <v>57976.2</v>
       </c>
       <c r="C29" t="n">
-        <v>59332.43</v>
+        <v>58365.21</v>
       </c>
       <c r="D29" t="n">
-        <v>56732.93</v>
+        <v>53618.2</v>
       </c>
       <c r="E29" t="n">
-        <v>58850.27</v>
+        <v>55620.84</v>
       </c>
       <c r="F29" t="n">
-        <v>2024.57</v>
+        <v>-3229.43</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0356</v>
+        <v>-0.0549</v>
       </c>
       <c r="H29" t="n">
-        <v>2599.5</v>
+        <v>4747.01</v>
       </c>
       <c r="I29" t="n">
-        <v>54560.42</v>
+        <v>54133.43</v>
       </c>
       <c r="J29" t="n">
-        <v>55202.61</v>
+        <v>56659.56</v>
       </c>
       <c r="K29" t="n">
-        <v>56038.35</v>
+        <v>57550.52</v>
       </c>
       <c r="L29" t="n">
-        <v>56874.08</v>
+        <v>58441.47</v>
       </c>
       <c r="M29" t="n">
-        <v>57613.05</v>
+        <v>60150.02</v>
       </c>
       <c r="N29" t="n">
-        <v>58352.01</v>
+        <v>61858.56</v>
       </c>
       <c r="O29" t="n">
-        <v>59284.52</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
+        <v>61931.93</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
+      </c>
       <c r="W29" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
@@ -2990,66 +2986,62 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>57976.2</v>
+        <v>54608.63</v>
       </c>
       <c r="C30" t="n">
-        <v>58365.21</v>
+        <v>55745.38</v>
       </c>
       <c r="D30" t="n">
-        <v>53618.2</v>
+        <v>51407.66</v>
       </c>
       <c r="E30" t="n">
-        <v>55620.84</v>
+        <v>53819.61</v>
       </c>
       <c r="F30" t="n">
-        <v>-3229.43</v>
+        <v>-1801.23</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0549</v>
+        <v>-0.0324</v>
       </c>
       <c r="H30" t="n">
-        <v>4747.01</v>
+        <v>4337.72</v>
       </c>
       <c r="I30" t="n">
-        <v>54133.43</v>
+        <v>48871.19</v>
       </c>
       <c r="J30" t="n">
-        <v>56659.56</v>
+        <v>50688.4</v>
       </c>
       <c r="K30" t="n">
-        <v>57550.52</v>
+        <v>53247.33</v>
       </c>
       <c r="L30" t="n">
-        <v>58441.47</v>
+        <v>55806.27</v>
       </c>
       <c r="M30" t="n">
-        <v>60150.02</v>
+        <v>57994.35</v>
       </c>
       <c r="N30" t="n">
-        <v>61858.56</v>
+        <v>60182.42</v>
       </c>
       <c r="O30" t="n">
-        <v>61931.93</v>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q30" s="6" t="inlineStr">
+        <v>63112.22</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -3064,7 +3056,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3074,50 +3066,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>54608.63</v>
+        <v>53627.86</v>
       </c>
       <c r="C31" t="n">
-        <v>55745.38</v>
+        <v>55239.4</v>
       </c>
       <c r="D31" t="n">
-        <v>51407.66</v>
+        <v>53113.95</v>
       </c>
       <c r="E31" t="n">
-        <v>53819.61</v>
+        <v>53372.53</v>
       </c>
       <c r="F31" t="n">
-        <v>-1801.23</v>
+        <v>-447.08</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0324</v>
+        <v>-0.0083</v>
       </c>
       <c r="H31" t="n">
-        <v>4337.72</v>
+        <v>2125.45</v>
       </c>
       <c r="I31" t="n">
-        <v>48871.19</v>
+        <v>47069.94</v>
       </c>
       <c r="J31" t="n">
-        <v>50688.4</v>
+        <v>49603.44</v>
       </c>
       <c r="K31" t="n">
-        <v>53247.33</v>
+        <v>51650.75</v>
       </c>
       <c r="L31" t="n">
-        <v>55806.27</v>
+        <v>53698.06</v>
       </c>
       <c r="M31" t="n">
-        <v>57994.35</v>
+        <v>55988.47</v>
       </c>
       <c r="N31" t="n">
-        <v>60182.42</v>
+        <v>58278.87</v>
       </c>
       <c r="O31" t="n">
-        <v>63112.22</v>
+        <v>60083.1</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3125,14 +3117,12 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R31" s="6" t="n">
+        <v/>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3144,69 +3134,79 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>53627.86</v>
+        <v>52468.72</v>
       </c>
       <c r="C32" t="n">
-        <v>55239.4</v>
+        <v>54175.8</v>
       </c>
       <c r="D32" t="n">
-        <v>53113.95</v>
+        <v>50688.76</v>
       </c>
       <c r="E32" t="n">
-        <v>53372.53</v>
+        <v>53373.07</v>
       </c>
       <c r="F32" t="n">
-        <v>-447.08</v>
+        <v>0.54</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0083</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2125.45</v>
+        <v>3487.04</v>
       </c>
       <c r="I32" t="n">
-        <v>47069.94</v>
+        <v>50988.5</v>
       </c>
       <c r="J32" t="n">
-        <v>49603.44</v>
+        <v>50845.01</v>
       </c>
       <c r="K32" t="n">
-        <v>51650.75</v>
+        <v>52309.81</v>
       </c>
       <c r="L32" t="n">
-        <v>53698.06</v>
+        <v>53774.6</v>
       </c>
       <c r="M32" t="n">
-        <v>55988.47</v>
+        <v>54435.26</v>
       </c>
       <c r="N32" t="n">
-        <v>58278.87</v>
+        <v>55095.91</v>
       </c>
       <c r="O32" t="n">
-        <v>60083.1</v>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+        <v>57364.85</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3236,69 +3236,65 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>52468.72</v>
+        <v>52054.68</v>
       </c>
       <c r="C33" t="n">
-        <v>54175.8</v>
+        <v>54258.48</v>
       </c>
       <c r="D33" t="n">
-        <v>50688.76</v>
+        <v>50558.91</v>
       </c>
       <c r="E33" t="n">
-        <v>53373.07</v>
+        <v>53123.49</v>
       </c>
       <c r="F33" t="n">
-        <v>0.54</v>
+        <v>-249.58</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0</v>
+        <v>-0.0047</v>
       </c>
       <c r="H33" t="n">
-        <v>3487.04</v>
+        <v>3699.57</v>
       </c>
       <c r="I33" t="n">
-        <v>50988.5</v>
+        <v>47201.72</v>
       </c>
       <c r="J33" t="n">
-        <v>50845.01</v>
+        <v>50356.43</v>
       </c>
       <c r="K33" t="n">
-        <v>52309.81</v>
+        <v>51629.55</v>
       </c>
       <c r="L33" t="n">
-        <v>53774.6</v>
+        <v>52902.68</v>
       </c>
       <c r="M33" t="n">
-        <v>54435.26</v>
+        <v>55116.59</v>
       </c>
       <c r="N33" t="n">
-        <v>55095.91</v>
+        <v>57330.5</v>
       </c>
       <c r="O33" t="n">
-        <v>57364.85</v>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>57662.84</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <v/>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3310,7 +3306,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3324,50 +3320,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>52054.68</v>
+        <v>53205.93</v>
       </c>
       <c r="C34" t="n">
-        <v>54258.48</v>
+        <v>57012.77</v>
       </c>
       <c r="D34" t="n">
-        <v>50558.91</v>
+        <v>53156.94</v>
       </c>
       <c r="E34" t="n">
-        <v>53123.49</v>
+        <v>56924.11</v>
       </c>
       <c r="F34" t="n">
-        <v>-249.58</v>
+        <v>3800.62</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0047</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>3699.57</v>
+        <v>3855.83</v>
       </c>
       <c r="I34" t="n">
-        <v>47201.72</v>
+        <v>46859.34</v>
       </c>
       <c r="J34" t="n">
-        <v>50356.43</v>
+        <v>49781.31</v>
       </c>
       <c r="K34" t="n">
-        <v>51629.55</v>
+        <v>51273.7</v>
       </c>
       <c r="L34" t="n">
-        <v>52902.68</v>
+        <v>52766.09</v>
       </c>
       <c r="M34" t="n">
-        <v>55116.59</v>
+        <v>54973.27</v>
       </c>
       <c r="N34" t="n">
-        <v>57330.5</v>
+        <v>57180.46</v>
       </c>
       <c r="O34" t="n">
-        <v>57662.84</v>
+        <v>57958.05</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3375,83 +3371,85 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R34" s="6" t="n">
+        <v/>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>53205.93</v>
+        <v>56421.46</v>
       </c>
       <c r="C35" t="n">
-        <v>57012.77</v>
+        <v>59688.1</v>
       </c>
       <c r="D35" t="n">
-        <v>53156.94</v>
+        <v>56232.78</v>
       </c>
       <c r="E35" t="n">
-        <v>56924.11</v>
+        <v>58475.9</v>
       </c>
       <c r="F35" t="n">
-        <v>3800.62</v>
+        <v>1551.79</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0273</v>
       </c>
       <c r="H35" t="n">
-        <v>3855.83</v>
+        <v>3455.32</v>
       </c>
       <c r="I35" t="n">
-        <v>46859.34</v>
+        <v>49301.11</v>
       </c>
       <c r="J35" t="n">
-        <v>49781.31</v>
+        <v>53987.91</v>
       </c>
       <c r="K35" t="n">
-        <v>51273.7</v>
+        <v>54996.2</v>
       </c>
       <c r="L35" t="n">
-        <v>52766.09</v>
+        <v>56004.48</v>
       </c>
       <c r="M35" t="n">
-        <v>54973.27</v>
+        <v>58852.02</v>
       </c>
       <c r="N35" t="n">
-        <v>57180.46</v>
+        <v>61699.56</v>
       </c>
       <c r="O35" t="n">
-        <v>57958.05</v>
+        <v>60868.6</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3469,18 +3467,16 @@
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3494,50 +3490,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>56421.46</v>
+        <v>58821.16</v>
       </c>
       <c r="C36" t="n">
-        <v>59688.1</v>
+        <v>60013.98</v>
       </c>
       <c r="D36" t="n">
-        <v>56232.78</v>
+        <v>58621.48</v>
       </c>
       <c r="E36" t="n">
-        <v>58475.9</v>
+        <v>59716.18</v>
       </c>
       <c r="F36" t="n">
-        <v>1551.79</v>
+        <v>1240.28</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0273</v>
+        <v>0.0212</v>
       </c>
       <c r="H36" t="n">
-        <v>3455.32</v>
+        <v>1392.5</v>
       </c>
       <c r="I36" t="n">
-        <v>49301.11</v>
+        <v>52777.46</v>
       </c>
       <c r="J36" t="n">
-        <v>53987.91</v>
+        <v>55278.31</v>
       </c>
       <c r="K36" t="n">
-        <v>54996.2</v>
+        <v>56748.24</v>
       </c>
       <c r="L36" t="n">
-        <v>56004.48</v>
+        <v>58218.17</v>
       </c>
       <c r="M36" t="n">
-        <v>58852.02</v>
+        <v>60203.56</v>
       </c>
       <c r="N36" t="n">
-        <v>61699.56</v>
+        <v>62188.95</v>
       </c>
       <c r="O36" t="n">
-        <v>60868.6</v>
+        <v>63143.42</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3564,7 +3560,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3578,50 +3574,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>58821.16</v>
+        <v>59880.71</v>
       </c>
       <c r="C37" t="n">
-        <v>60013.98</v>
+        <v>60903.95</v>
       </c>
       <c r="D37" t="n">
-        <v>58621.48</v>
+        <v>58928.2</v>
       </c>
       <c r="E37" t="n">
-        <v>59716.18</v>
+        <v>59513.12</v>
       </c>
       <c r="F37" t="n">
-        <v>1240.28</v>
+        <v>-203.06</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0034</v>
       </c>
       <c r="H37" t="n">
-        <v>1392.5</v>
+        <v>1975.75</v>
       </c>
       <c r="I37" t="n">
-        <v>52777.46</v>
+        <v>57228.98</v>
       </c>
       <c r="J37" t="n">
-        <v>55278.31</v>
+        <v>58522.9</v>
       </c>
       <c r="K37" t="n">
-        <v>56748.24</v>
+        <v>59019.93</v>
       </c>
       <c r="L37" t="n">
-        <v>58218.17</v>
+        <v>59516.96</v>
       </c>
       <c r="M37" t="n">
-        <v>60203.56</v>
+        <v>60412.43</v>
       </c>
       <c r="N37" t="n">
-        <v>62188.95</v>
+        <v>61307.9</v>
       </c>
       <c r="O37" t="n">
-        <v>63143.42</v>
+        <v>61406.48</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3629,17 +3625,19 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U37" s="8" t="n">
@@ -3648,64 +3646,64 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>59880.71</v>
+        <v>60241.31</v>
       </c>
       <c r="C38" t="n">
-        <v>60903.95</v>
+        <v>63091.14</v>
       </c>
       <c r="D38" t="n">
-        <v>58928.2</v>
+        <v>60213.02</v>
       </c>
       <c r="E38" t="n">
-        <v>59513.12</v>
+        <v>62713.65</v>
       </c>
       <c r="F38" t="n">
-        <v>-203.06</v>
+        <v>3200.53</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0538</v>
       </c>
       <c r="H38" t="n">
-        <v>1975.75</v>
+        <v>2878.12</v>
       </c>
       <c r="I38" t="n">
-        <v>57228.98</v>
+        <v>56952.45</v>
       </c>
       <c r="J38" t="n">
-        <v>58522.9</v>
+        <v>57335.89</v>
       </c>
       <c r="K38" t="n">
-        <v>59019.93</v>
+        <v>58525.25</v>
       </c>
       <c r="L38" t="n">
-        <v>59516.96</v>
+        <v>59714.6</v>
       </c>
       <c r="M38" t="n">
-        <v>60412.43</v>
+        <v>60501</v>
       </c>
       <c r="N38" t="n">
-        <v>61307.9</v>
+        <v>61287.39</v>
       </c>
       <c r="O38" t="n">
-        <v>61406.48</v>
+        <v>62879.7</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3713,14 +3711,12 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
@@ -3728,70 +3724,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v/>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>60241.31</v>
+        <v>63203.44</v>
       </c>
       <c r="C39" t="n">
-        <v>63091.14</v>
+        <v>63799.32</v>
       </c>
       <c r="D39" t="n">
-        <v>60213.02</v>
+        <v>60937.3</v>
       </c>
       <c r="E39" t="n">
-        <v>62713.65</v>
+        <v>61409.29</v>
       </c>
       <c r="F39" t="n">
-        <v>3200.53</v>
+        <v>-1304.36</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0538</v>
+        <v>-0.0208</v>
       </c>
       <c r="H39" t="n">
-        <v>2878.12</v>
+        <v>2862.02</v>
       </c>
       <c r="I39" t="n">
-        <v>56952.45</v>
+        <v>57334.9</v>
       </c>
       <c r="J39" t="n">
-        <v>57335.89</v>
+        <v>60366.31</v>
       </c>
       <c r="K39" t="n">
-        <v>58525.25</v>
+        <v>61274.59</v>
       </c>
       <c r="L39" t="n">
-        <v>59714.6</v>
+        <v>62182.86</v>
       </c>
       <c r="M39" t="n">
-        <v>60501</v>
+        <v>64152.71</v>
       </c>
       <c r="N39" t="n">
-        <v>61287.39</v>
+        <v>66122.55</v>
       </c>
       <c r="O39" t="n">
-        <v>62879.7</v>
+        <v>65969.25999999999</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3799,83 +3795,83 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>63203.44</v>
+        <v>61299.87</v>
       </c>
       <c r="C40" t="n">
-        <v>63799.32</v>
+        <v>63432.41</v>
       </c>
       <c r="D40" t="n">
-        <v>60937.3</v>
+        <v>59292.25</v>
       </c>
       <c r="E40" t="n">
-        <v>61409.29</v>
+        <v>63339.07</v>
       </c>
       <c r="F40" t="n">
-        <v>-1304.36</v>
+        <v>1929.78</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0314</v>
       </c>
       <c r="H40" t="n">
-        <v>2862.02</v>
+        <v>4140.16</v>
       </c>
       <c r="I40" t="n">
-        <v>57334.9</v>
+        <v>58075.28</v>
       </c>
       <c r="J40" t="n">
-        <v>60366.31</v>
+        <v>58067.76</v>
       </c>
       <c r="K40" t="n">
-        <v>61274.59</v>
+        <v>59978.28</v>
       </c>
       <c r="L40" t="n">
-        <v>62182.86</v>
+        <v>61888.8</v>
       </c>
       <c r="M40" t="n">
-        <v>64152.71</v>
+        <v>62840.3</v>
       </c>
       <c r="N40" t="n">
-        <v>66122.55</v>
+        <v>63791.8</v>
       </c>
       <c r="O40" t="n">
-        <v>65969.25999999999</v>
+        <v>66661.34</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3885,81 +3881,85 @@
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>61299.87</v>
+        <v>63658.95</v>
       </c>
       <c r="C41" t="n">
-        <v>63432.41</v>
+        <v>66505.02</v>
       </c>
       <c r="D41" t="n">
-        <v>59292.25</v>
+        <v>63562.51</v>
       </c>
       <c r="E41" t="n">
-        <v>63339.07</v>
+        <v>66329.5</v>
       </c>
       <c r="F41" t="n">
-        <v>1929.78</v>
+        <v>2990.43</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0314</v>
+        <v>0.0472</v>
       </c>
       <c r="H41" t="n">
-        <v>4140.16</v>
+        <v>2942.51</v>
       </c>
       <c r="I41" t="n">
-        <v>58075.28</v>
+        <v>55152.09</v>
       </c>
       <c r="J41" t="n">
-        <v>58067.76</v>
+        <v>60187.28</v>
       </c>
       <c r="K41" t="n">
-        <v>59978.28</v>
+        <v>61268.99</v>
       </c>
       <c r="L41" t="n">
-        <v>61888.8</v>
+        <v>62350.7</v>
       </c>
       <c r="M41" t="n">
-        <v>62840.3</v>
+        <v>65409.15</v>
       </c>
       <c r="N41" t="n">
-        <v>63791.8</v>
+        <v>68467.60000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>66661.34</v>
+        <v>67572.57000000001</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3967,10 +3967,8 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R41" s="6" t="n">
+        <v/>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
@@ -3979,75 +3977,69 @@
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>63658.95</v>
+        <v>66363.42999999999</v>
       </c>
       <c r="C42" t="n">
-        <v>66505.02</v>
+        <v>68786.49000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>63562.51</v>
+        <v>65551.13</v>
       </c>
       <c r="E42" t="n">
-        <v>66329.5</v>
+        <v>66588.12</v>
       </c>
       <c r="F42" t="n">
-        <v>2990.43</v>
+        <v>258.62</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0472</v>
+        <v>0.0039</v>
       </c>
       <c r="H42" t="n">
-        <v>2942.51</v>
+        <v>3235.36</v>
       </c>
       <c r="I42" t="n">
-        <v>55152.09</v>
+        <v>60620</v>
       </c>
       <c r="J42" t="n">
-        <v>60187.28</v>
+        <v>64034.85</v>
       </c>
       <c r="K42" t="n">
-        <v>61268.99</v>
+        <v>64858.24</v>
       </c>
       <c r="L42" t="n">
-        <v>62350.7</v>
+        <v>65681.63</v>
       </c>
       <c r="M42" t="n">
-        <v>65409.15</v>
+        <v>67800.75999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>68467.60000000001</v>
+        <v>69919.88</v>
       </c>
       <c r="O42" t="n">
-        <v>67572.57000000001</v>
+        <v>69447.53999999999</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4060,12 +4052,12 @@
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U42" s="8" t="n">
@@ -4074,7 +4066,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4084,69 +4076,71 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>66363.42999999999</v>
+        <v>65947.56</v>
       </c>
       <c r="C43" t="n">
-        <v>68786.49000000001</v>
+        <v>67065.94</v>
       </c>
       <c r="D43" t="n">
-        <v>65551.13</v>
+        <v>62335.75</v>
       </c>
       <c r="E43" t="n">
-        <v>66588.12</v>
+        <v>66020.03999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>258.62</v>
+        <v>-568.08</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0039</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>3235.36</v>
+        <v>4730.19</v>
       </c>
       <c r="I43" t="n">
-        <v>60620</v>
+        <v>62315.77</v>
       </c>
       <c r="J43" t="n">
-        <v>64034.85</v>
+        <v>63062.41</v>
       </c>
       <c r="K43" t="n">
-        <v>64858.24</v>
+        <v>64970.44</v>
       </c>
       <c r="L43" t="n">
-        <v>65681.63</v>
+        <v>66878.46000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>67800.75999999999</v>
+        <v>68205.8</v>
       </c>
       <c r="N43" t="n">
-        <v>69919.88</v>
+        <v>69533.13</v>
       </c>
       <c r="O43" t="n">
-        <v>69447.53999999999</v>
+        <v>72021.85000000001</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4154,146 +4148,148 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>65947.56</v>
+        <v>66783.22</v>
       </c>
       <c r="C44" t="n">
-        <v>67065.94</v>
+        <v>71952.99000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>62335.75</v>
+        <v>66783.22</v>
       </c>
       <c r="E44" t="n">
-        <v>66020.03999999999</v>
+        <v>71250.06</v>
       </c>
       <c r="F44" t="n">
-        <v>-568.08</v>
+        <v>5230.02</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>4730.19</v>
+        <v>5169.77</v>
       </c>
       <c r="I44" t="n">
-        <v>62315.77</v>
+        <v>57605.56</v>
       </c>
       <c r="J44" t="n">
-        <v>63062.41</v>
+        <v>61949.45</v>
       </c>
       <c r="K44" t="n">
-        <v>64970.44</v>
+        <v>63654.95</v>
       </c>
       <c r="L44" t="n">
-        <v>66878.46000000001</v>
+        <v>65360.44</v>
       </c>
       <c r="M44" t="n">
-        <v>68205.8</v>
+        <v>68385.13</v>
       </c>
       <c r="N44" t="n">
-        <v>69533.13</v>
+        <v>71409.82000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>72021.85000000001</v>
+        <v>71796.12</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>66783.22</v>
+        <v>71067.14999999999</v>
       </c>
       <c r="C45" t="n">
-        <v>71952.99000000001</v>
+        <v>72831.73</v>
       </c>
       <c r="D45" t="n">
-        <v>66783.22</v>
+        <v>68461.10000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>71250.06</v>
+        <v>69360.88</v>
       </c>
       <c r="F45" t="n">
-        <v>5230.02</v>
+        <v>-1889.18</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.07920000000000001</v>
+        <v>-0.0265</v>
       </c>
       <c r="H45" t="n">
-        <v>5169.77</v>
+        <v>4370.62</v>
       </c>
       <c r="I45" t="n">
-        <v>57605.56</v>
+        <v>61613.45</v>
       </c>
       <c r="J45" t="n">
-        <v>61949.45</v>
+        <v>67021.27</v>
       </c>
       <c r="K45" t="n">
-        <v>63654.95</v>
+        <v>68665.17999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>65360.44</v>
+        <v>70309.08</v>
       </c>
       <c r="M45" t="n">
-        <v>68385.13</v>
+        <v>73834.95</v>
       </c>
       <c r="N45" t="n">
-        <v>71409.82000000001</v>
+        <v>77360.81</v>
       </c>
       <c r="O45" t="n">
-        <v>71796.12</v>
+        <v>77122.77</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4301,83 +4297,83 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
+      <c r="R45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>71067.14999999999</v>
+        <v>69609.88</v>
       </c>
       <c r="C46" t="n">
-        <v>72831.73</v>
+        <v>71962.34</v>
       </c>
       <c r="D46" t="n">
-        <v>68461.10000000001</v>
+        <v>67609.49000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>69360.88</v>
+        <v>69744.07000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>-1889.18</v>
+        <v>383.19</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0265</v>
+        <v>0.0055</v>
       </c>
       <c r="H46" t="n">
-        <v>4370.62</v>
+        <v>4352.85</v>
       </c>
       <c r="I46" t="n">
-        <v>61613.45</v>
+        <v>64090.48</v>
       </c>
       <c r="J46" t="n">
-        <v>67021.27</v>
+        <v>64347.49</v>
       </c>
       <c r="K46" t="n">
-        <v>68665.17999999999</v>
+        <v>67175.57000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>70309.08</v>
+        <v>70003.64999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>73834.95</v>
+        <v>71546.2</v>
       </c>
       <c r="N46" t="n">
-        <v>77360.81</v>
+        <v>73088.74000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>77122.77</v>
+        <v>77202.35000000001</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4385,18 +4381,18 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R46" s="6" t="n">
+        <v/>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4404,64 +4400,64 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>69609.88</v>
+        <v>69973.34</v>
       </c>
       <c r="C47" t="n">
-        <v>71962.34</v>
+        <v>70384.59</v>
       </c>
       <c r="D47" t="n">
-        <v>67609.49000000001</v>
+        <v>66819.05</v>
       </c>
       <c r="E47" t="n">
-        <v>69744.07000000001</v>
+        <v>68557.73</v>
       </c>
       <c r="F47" t="n">
-        <v>383.19</v>
+        <v>-1186.34</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0055</v>
+        <v>-0.017</v>
       </c>
       <c r="H47" t="n">
-        <v>4352.85</v>
+        <v>3565.55</v>
       </c>
       <c r="I47" t="n">
-        <v>64090.48</v>
+        <v>63256.64</v>
       </c>
       <c r="J47" t="n">
-        <v>64347.49</v>
+        <v>65370.29</v>
       </c>
       <c r="K47" t="n">
-        <v>67175.57000000001</v>
+        <v>67567.64</v>
       </c>
       <c r="L47" t="n">
-        <v>70003.64999999999</v>
+        <v>69764.99000000001</v>
       </c>
       <c r="M47" t="n">
-        <v>71546.2</v>
+        <v>71920.5</v>
       </c>
       <c r="N47" t="n">
-        <v>73088.74000000001</v>
+        <v>74076</v>
       </c>
       <c r="O47" t="n">
-        <v>77202.35000000001</v>
+        <v>76315.2</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4469,18 +4465,18 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4488,74 +4484,78 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>69973.34</v>
+        <v>68410.63</v>
       </c>
       <c r="C48" t="n">
-        <v>70384.59</v>
+        <v>69078.21000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>66819.05</v>
+        <v>62704.6</v>
       </c>
       <c r="E48" t="n">
-        <v>68557.73</v>
+        <v>64141.12</v>
       </c>
       <c r="F48" t="n">
-        <v>-1186.34</v>
+        <v>-4416.61</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0644</v>
       </c>
       <c r="H48" t="n">
-        <v>3565.55</v>
+        <v>6373.61</v>
       </c>
       <c r="I48" t="n">
-        <v>63256.64</v>
+        <v>63253.5</v>
       </c>
       <c r="J48" t="n">
-        <v>65370.29</v>
+        <v>64970.13</v>
       </c>
       <c r="K48" t="n">
-        <v>67567.64</v>
+        <v>66774.95</v>
       </c>
       <c r="L48" t="n">
-        <v>69764.99000000001</v>
+        <v>68579.77</v>
       </c>
       <c r="M48" t="n">
-        <v>71920.5</v>
+        <v>70340.5</v>
       </c>
       <c r="N48" t="n">
-        <v>74076</v>
+        <v>72101.23</v>
       </c>
       <c r="O48" t="n">
-        <v>76315.2</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
+        <v>73950.14</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S48" s="7" t="inlineStr">
@@ -4574,85 +4574,77 @@
       </c>
       <c r="W48" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>68410.63</v>
+        <v>64544.05</v>
       </c>
       <c r="C49" t="n">
-        <v>69078.21000000001</v>
+        <v>67592.2</v>
       </c>
       <c r="D49" t="n">
-        <v>62704.6</v>
+        <v>64201.03</v>
       </c>
       <c r="E49" t="n">
-        <v>64141.12</v>
+        <v>64611.15</v>
       </c>
       <c r="F49" t="n">
-        <v>-4416.61</v>
+        <v>470.03</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0644</v>
+        <v>0.0073</v>
       </c>
       <c r="H49" t="n">
-        <v>6373.61</v>
+        <v>3391.17</v>
       </c>
       <c r="I49" t="n">
-        <v>63253.5</v>
+        <v>56330.99</v>
       </c>
       <c r="J49" t="n">
-        <v>64970.13</v>
+        <v>56892.37</v>
       </c>
       <c r="K49" t="n">
-        <v>66774.95</v>
+        <v>60954.32</v>
       </c>
       <c r="L49" t="n">
-        <v>68579.77</v>
+        <v>65016.26</v>
       </c>
       <c r="M49" t="n">
-        <v>70340.5</v>
+        <v>67327.92999999999</v>
       </c>
       <c r="N49" t="n">
-        <v>72101.23</v>
+        <v>69639.59</v>
       </c>
       <c r="O49" t="n">
-        <v>73950.14</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>75451.82000000001</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4660,79 +4652,87 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>64544.05</v>
+        <v>65164.98</v>
       </c>
       <c r="C50" t="n">
-        <v>67592.2</v>
+        <v>65364.73</v>
       </c>
       <c r="D50" t="n">
-        <v>64201.03</v>
+        <v>60448.9</v>
       </c>
       <c r="E50" t="n">
-        <v>64611.15</v>
+        <v>64362.02</v>
       </c>
       <c r="F50" t="n">
-        <v>470.03</v>
+        <v>-249.13</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0073</v>
+        <v>-0.0039</v>
       </c>
       <c r="H50" t="n">
-        <v>3391.17</v>
+        <v>4915.83</v>
       </c>
       <c r="I50" t="n">
-        <v>56330.99</v>
+        <v>60809.86</v>
       </c>
       <c r="J50" t="n">
-        <v>56892.37</v>
+        <v>60577.24</v>
       </c>
       <c r="K50" t="n">
-        <v>60954.32</v>
+        <v>62915.56</v>
       </c>
       <c r="L50" t="n">
-        <v>65016.26</v>
+        <v>65253.88</v>
       </c>
       <c r="M50" t="n">
-        <v>67327.92999999999</v>
+        <v>66306.73</v>
       </c>
       <c r="N50" t="n">
-        <v>69639.59</v>
+        <v>67359.59</v>
       </c>
       <c r="O50" t="n">
-        <v>75451.82000000001</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+        <v>70983.38</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4740,87 +4740,79 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>65164.98</v>
+        <v>63834.95</v>
       </c>
       <c r="C51" t="n">
-        <v>65364.73</v>
+        <v>66302.52</v>
       </c>
       <c r="D51" t="n">
-        <v>60448.9</v>
+        <v>62703.47</v>
       </c>
       <c r="E51" t="n">
-        <v>64362.02</v>
+        <v>65606.71000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>-249.13</v>
+        <v>1244.69</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0193</v>
       </c>
       <c r="H51" t="n">
-        <v>4915.83</v>
+        <v>3599.05</v>
       </c>
       <c r="I51" t="n">
-        <v>60809.86</v>
+        <v>55533.07</v>
       </c>
       <c r="J51" t="n">
-        <v>60577.24</v>
+        <v>60173.79</v>
       </c>
       <c r="K51" t="n">
-        <v>62915.56</v>
+        <v>61904.1</v>
       </c>
       <c r="L51" t="n">
-        <v>65253.88</v>
+        <v>63634.42</v>
       </c>
       <c r="M51" t="n">
-        <v>66306.73</v>
+        <v>66819.94</v>
       </c>
       <c r="N51" t="n">
-        <v>67359.59</v>
+        <v>70005.45</v>
       </c>
       <c r="O51" t="n">
-        <v>70983.38</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+        <v>70280.56</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4828,60 +4820,64 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>63834.95</v>
+        <v>65905.10000000001</v>
       </c>
       <c r="C52" t="n">
-        <v>66302.52</v>
+        <v>69608.24000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>62703.47</v>
+        <v>65848.58</v>
       </c>
       <c r="E52" t="n">
-        <v>65606.71000000001</v>
+        <v>68713.8</v>
       </c>
       <c r="F52" t="n">
-        <v>1244.69</v>
+        <v>3107.09</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0193</v>
+        <v>0.0474</v>
       </c>
       <c r="H52" t="n">
-        <v>3599.05</v>
+        <v>3759.66</v>
       </c>
       <c r="I52" t="n">
-        <v>55533.07</v>
+        <v>59104.41</v>
       </c>
       <c r="J52" t="n">
-        <v>60173.79</v>
+        <v>62559.51</v>
       </c>
       <c r="K52" t="n">
-        <v>61904.1</v>
+        <v>63807.18</v>
       </c>
       <c r="L52" t="n">
-        <v>63634.42</v>
+        <v>65054.85</v>
       </c>
       <c r="M52" t="n">
-        <v>66819.94</v>
+        <v>67406.24000000001</v>
       </c>
       <c r="N52" t="n">
-        <v>70005.45</v>
+        <v>69757.62</v>
       </c>
       <c r="O52" t="n">
-        <v>70280.56</v>
+        <v>69901.58</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4899,16 +4895,18 @@
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4922,153 +4920,145 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>65905.10000000001</v>
+        <v>68882.06</v>
       </c>
       <c r="C53" t="n">
-        <v>69608.24000000001</v>
+        <v>69225.57000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>65848.58</v>
+        <v>65133.98</v>
       </c>
       <c r="E53" t="n">
-        <v>68713.8</v>
+        <v>66016.36</v>
       </c>
       <c r="F53" t="n">
-        <v>3107.09</v>
+        <v>-2697.44</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0474</v>
+        <v>-0.0393</v>
       </c>
       <c r="H53" t="n">
-        <v>3759.66</v>
+        <v>4091.59</v>
       </c>
       <c r="I53" t="n">
-        <v>59104.41</v>
+        <v>62088.91</v>
       </c>
       <c r="J53" t="n">
-        <v>62559.51</v>
+        <v>65446.83</v>
       </c>
       <c r="K53" t="n">
-        <v>63807.18</v>
+        <v>66833.96000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>65054.85</v>
+        <v>68221.10000000001</v>
       </c>
       <c r="M53" t="n">
-        <v>67406.24000000001</v>
+        <v>70593.63</v>
       </c>
       <c r="N53" t="n">
-        <v>69757.62</v>
+        <v>72966.14999999999</v>
       </c>
       <c r="O53" t="n">
-        <v>69901.58</v>
+        <v>73367.91</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
+      <c r="Q53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>68882.06</v>
+        <v>65978.95</v>
       </c>
       <c r="C54" t="n">
-        <v>69225.57000000001</v>
+        <v>66954.69</v>
       </c>
       <c r="D54" t="n">
-        <v>65133.98</v>
+        <v>64609.47</v>
       </c>
       <c r="E54" t="n">
-        <v>66016.36</v>
+        <v>66405.56</v>
       </c>
       <c r="F54" t="n">
-        <v>-2697.44</v>
+        <v>389.2</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0393</v>
+        <v>0.0059</v>
       </c>
       <c r="H54" t="n">
-        <v>4091.59</v>
+        <v>2345.22</v>
       </c>
       <c r="I54" t="n">
-        <v>62088.91</v>
+        <v>61042.39</v>
       </c>
       <c r="J54" t="n">
-        <v>65446.83</v>
+        <v>61343.06</v>
       </c>
       <c r="K54" t="n">
-        <v>66833.96000000001</v>
+        <v>63970.56</v>
       </c>
       <c r="L54" t="n">
-        <v>68221.10000000001</v>
+        <v>66598.07000000001</v>
       </c>
       <c r="M54" t="n">
-        <v>70593.63</v>
+        <v>68062.14999999999</v>
       </c>
       <c r="N54" t="n">
-        <v>72966.14999999999</v>
+        <v>69526.24000000001</v>
       </c>
       <c r="O54" t="n">
-        <v>73367.91</v>
+        <v>73317.16</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5080,73 +5070,81 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>65978.95</v>
+        <v>65668.50999999999</v>
       </c>
       <c r="C55" t="n">
-        <v>66954.69</v>
+        <v>66525.7</v>
       </c>
       <c r="D55" t="n">
-        <v>64609.47</v>
+        <v>63772.8</v>
       </c>
       <c r="E55" t="n">
-        <v>66405.56</v>
+        <v>65020.94</v>
       </c>
       <c r="F55" t="n">
-        <v>389.2</v>
+        <v>-1384.62</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0209</v>
       </c>
       <c r="H55" t="n">
-        <v>2345.22</v>
+        <v>2752.9</v>
       </c>
       <c r="I55" t="n">
-        <v>61042.39</v>
+        <v>62264.25</v>
       </c>
       <c r="J55" t="n">
-        <v>61343.06</v>
+        <v>64372.09</v>
       </c>
       <c r="K55" t="n">
-        <v>63970.56</v>
+        <v>65232.95</v>
       </c>
       <c r="L55" t="n">
-        <v>66598.07000000001</v>
+        <v>66093.82000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>68062.14999999999</v>
+        <v>67578.17</v>
       </c>
       <c r="N55" t="n">
-        <v>69526.24000000001</v>
+        <v>69062.52</v>
       </c>
       <c r="O55" t="n">
-        <v>73317.16</v>
+        <v>69299.91</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5158,72 +5156,66 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>65668.50999999999</v>
+        <v>65600.42</v>
       </c>
       <c r="C56" t="n">
-        <v>66525.7</v>
+        <v>66791.84</v>
       </c>
       <c r="D56" t="n">
-        <v>63772.8</v>
+        <v>63208.63</v>
       </c>
       <c r="E56" t="n">
-        <v>65020.94</v>
+        <v>64011.34</v>
       </c>
       <c r="F56" t="n">
-        <v>-1384.62</v>
+        <v>-1009.6</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0209</v>
+        <v>-0.0155</v>
       </c>
       <c r="H56" t="n">
-        <v>2752.9</v>
+        <v>3583.21</v>
       </c>
       <c r="I56" t="n">
-        <v>62264.25</v>
+        <v>61019.9</v>
       </c>
       <c r="J56" t="n">
-        <v>64372.09</v>
+        <v>62203.88</v>
       </c>
       <c r="K56" t="n">
-        <v>65232.95</v>
+        <v>63644.49</v>
       </c>
       <c r="L56" t="n">
-        <v>66093.82000000001</v>
+        <v>65085.1</v>
       </c>
       <c r="M56" t="n">
-        <v>67578.17</v>
+        <v>66397.39</v>
       </c>
       <c r="N56" t="n">
-        <v>69062.52</v>
+        <v>67709.69</v>
       </c>
       <c r="O56" t="n">
-        <v>69299.91</v>
+        <v>69278.61</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q56" s="6" t="n">
+        <v/>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
@@ -5235,8 +5227,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5244,60 +5238,64 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>65600.42</v>
+        <v>63659.53</v>
       </c>
       <c r="C57" t="n">
-        <v>66791.84</v>
+        <v>65436.57</v>
       </c>
       <c r="D57" t="n">
-        <v>63208.63</v>
+        <v>62726.18</v>
       </c>
       <c r="E57" t="n">
-        <v>64011.34</v>
+        <v>65018.95</v>
       </c>
       <c r="F57" t="n">
-        <v>-1009.6</v>
+        <v>1007.61</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0157</v>
       </c>
       <c r="H57" t="n">
-        <v>3583.21</v>
+        <v>2710.39</v>
       </c>
       <c r="I57" t="n">
-        <v>61019.9</v>
+        <v>59625.41</v>
       </c>
       <c r="J57" t="n">
-        <v>62203.88</v>
+        <v>59933.68</v>
       </c>
       <c r="K57" t="n">
-        <v>63644.49</v>
+        <v>62219.73</v>
       </c>
       <c r="L57" t="n">
-        <v>65085.1</v>
+        <v>64505.79</v>
       </c>
       <c r="M57" t="n">
-        <v>66397.39</v>
+        <v>65802.95</v>
       </c>
       <c r="N57" t="n">
-        <v>67709.69</v>
+        <v>67100.11</v>
       </c>
       <c r="O57" t="n">
-        <v>69278.61</v>
+        <v>70375.06</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5305,20 +5303,16 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5326,7 +5320,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5336,84 +5330,6 @@
           <t>弱警訊</t>
         </is>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>63659.53</v>
-      </c>
-      <c r="C58" t="n">
-        <v>64101</v>
-      </c>
-      <c r="D58" t="n">
-        <v>62726.18</v>
-      </c>
-      <c r="E58" t="n">
-        <v>63923</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-88.34</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0014</v>
-      </c>
-      <c r="H58" t="n">
-        <v>1374.82</v>
-      </c>
-      <c r="I58" t="n">
-        <v>59625.41</v>
-      </c>
-      <c r="J58" t="n">
-        <v>59933.68</v>
-      </c>
-      <c r="K58" t="n">
-        <v>62219.73</v>
-      </c>
-      <c r="L58" t="n">
-        <v>64505.79</v>
-      </c>
-      <c r="M58" t="n">
-        <v>65802.95</v>
-      </c>
-      <c r="N58" t="n">
-        <v>67100.11</v>
-      </c>
-      <c r="O58" t="n">
-        <v>70375.06</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>1063.8</v>
       </c>
       <c r="I2" t="n">
-        <v>40786.36</v>
+        <v>41237</v>
       </c>
       <c r="J2" t="n">
-        <v>40852.95</v>
+        <v>41416.25</v>
       </c>
       <c r="K2" t="n">
-        <v>41860.77</v>
+        <v>42086.09</v>
       </c>
       <c r="L2" t="n">
-        <v>42868.6</v>
+        <v>42755.94</v>
       </c>
       <c r="M2" t="n">
-        <v>43405.8</v>
+        <v>43180.48</v>
       </c>
       <c r="N2" t="n">
-        <v>43943.01</v>
+        <v>43605.03</v>
       </c>
       <c r="O2" t="n">
-        <v>45421.45</v>
+        <v>44520.17</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -693,8 +693,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -659,25 +659,25 @@
         <v>1063.8</v>
       </c>
       <c r="I2" t="n">
-        <v>41237</v>
+        <v>41736.67</v>
       </c>
       <c r="J2" t="n">
-        <v>41416.25</v>
+        <v>42040.84</v>
       </c>
       <c r="K2" t="n">
-        <v>42086.09</v>
+        <v>42335.93</v>
       </c>
       <c r="L2" t="n">
-        <v>42755.94</v>
+        <v>42631.02</v>
       </c>
       <c r="M2" t="n">
-        <v>43180.48</v>
+        <v>42930.65</v>
       </c>
       <c r="N2" t="n">
-        <v>43605.03</v>
+        <v>43230.28</v>
       </c>
       <c r="O2" t="n">
-        <v>44520.17</v>
+        <v>43520.83</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,12 +685,14 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
@@ -711,7 +713,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -774,7 +776,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -858,7 +860,7 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -942,7 +944,7 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1022,7 +1024,7 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1112,7 +1114,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1196,7 +1198,7 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1282,7 +1284,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1364,7 +1366,7 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1446,7 +1448,7 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1534,7 +1536,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1616,7 +1618,7 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1704,7 +1706,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1782,7 +1784,7 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1870,7 +1872,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1952,7 +1954,7 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2040,7 +2042,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2118,7 +2120,7 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2204,7 +2206,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2286,7 +2288,7 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2370,7 +2372,7 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2458,7 +2460,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2542,7 +2544,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2626,7 +2628,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2708,7 +2710,7 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2792,7 +2794,7 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2874,7 +2876,7 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2964,7 +2966,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3044,7 +3046,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3122,7 +3124,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3210,7 +3212,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3294,7 +3296,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3376,7 +3378,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3462,7 +3464,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3546,7 +3548,7 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="10" t="inlineStr">
+      <c r="S36" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3632,7 +3634,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3716,7 +3718,7 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3802,7 +3804,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3886,7 +3888,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3972,7 +3974,7 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4052,7 +4054,7 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="10" t="inlineStr">
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4136,7 +4138,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S43" s="7" t="inlineStr">
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4218,7 +4220,7 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="10" t="inlineStr">
+      <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4304,7 +4306,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S45" s="7" t="inlineStr">
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4386,7 +4388,7 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4472,7 +4474,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S47" s="7" t="inlineStr">
+      <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4560,7 +4562,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S48" s="7" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4638,7 +4640,7 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4728,7 +4730,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4806,7 +4808,7 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="10" t="inlineStr">
+      <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4890,7 +4892,7 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="10" t="inlineStr">
+      <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4980,7 +4982,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5058,7 +5060,7 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -5144,7 +5146,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5224,7 +5226,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5308,7 +5310,7 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -5330,6 +5332,90 @@
       <c r="X57" t="inlineStr">
         <is>
           <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>65476.44</v>
+      </c>
+      <c r="C58" t="n">
+        <v>66249.11</v>
+      </c>
+      <c r="D58" t="n">
+        <v>65407.37</v>
+      </c>
+      <c r="E58" t="n">
+        <v>65513.99</v>
+      </c>
+      <c r="F58" t="n">
+        <v>495.04</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="H58" t="n">
+        <v>841.74</v>
+      </c>
+      <c r="I58" t="n">
+        <v>60015.79</v>
+      </c>
+      <c r="J58" t="n">
+        <v>62777.35</v>
+      </c>
+      <c r="K58" t="n">
+        <v>63663.75</v>
+      </c>
+      <c r="L58" t="n">
+        <v>64550.16</v>
+      </c>
+      <c r="M58" t="n">
+        <v>66374.14</v>
+      </c>
+      <c r="N58" t="n">
+        <v>68198.13</v>
+      </c>
+      <c r="O58" t="n">
+        <v>68146.96000000001</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42977.27</v>
+        <v>42362.71</v>
       </c>
       <c r="C2" t="n">
-        <v>43201.42</v>
+        <v>43220.94</v>
       </c>
       <c r="D2" t="n">
-        <v>42137.62</v>
+        <v>41835.17</v>
       </c>
       <c r="E2" t="n">
-        <v>42718.47</v>
+        <v>43018.75</v>
       </c>
       <c r="F2" t="n">
-        <v>85.18000000000001</v>
+        <v>300.28</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H2" t="n">
-        <v>1063.8</v>
+        <v>1385.77</v>
       </c>
       <c r="I2" t="n">
-        <v>41736.67</v>
+        <v>41073.82</v>
       </c>
       <c r="J2" t="n">
-        <v>42040.84</v>
+        <v>41679.14</v>
       </c>
       <c r="K2" t="n">
-        <v>42335.93</v>
+        <v>42186.57</v>
       </c>
       <c r="L2" t="n">
-        <v>42631.02</v>
+        <v>42694</v>
       </c>
       <c r="M2" t="n">
-        <v>42930.65</v>
+        <v>43250.37</v>
       </c>
       <c r="N2" t="n">
-        <v>43230.28</v>
+        <v>43806.74</v>
       </c>
       <c r="O2" t="n">
-        <v>43520.83</v>
+        <v>44265.22</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,12 +692,12 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U2" s="8" t="n">
@@ -720,50 +720,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42362.71</v>
+        <v>43451.07</v>
       </c>
       <c r="C3" t="n">
-        <v>43220.94</v>
+        <v>44888.02</v>
       </c>
       <c r="D3" t="n">
-        <v>41835.17</v>
+        <v>43343.58</v>
       </c>
       <c r="E3" t="n">
-        <v>43018.75</v>
+        <v>44768.12</v>
       </c>
       <c r="F3" t="n">
-        <v>300.28</v>
+        <v>1749.37</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.007</v>
+        <v>0.0407</v>
       </c>
       <c r="H3" t="n">
-        <v>1385.77</v>
+        <v>1544.44</v>
       </c>
       <c r="I3" t="n">
-        <v>41073.82</v>
+        <v>40449.4</v>
       </c>
       <c r="J3" t="n">
-        <v>41679.14</v>
+        <v>41878.33</v>
       </c>
       <c r="K3" t="n">
-        <v>42186.57</v>
+        <v>42325.87</v>
       </c>
       <c r="L3" t="n">
-        <v>42694</v>
+        <v>42773.4</v>
       </c>
       <c r="M3" t="n">
-        <v>43250.37</v>
+        <v>43711.63</v>
       </c>
       <c r="N3" t="n">
-        <v>43806.74</v>
+        <v>44649.87</v>
       </c>
       <c r="O3" t="n">
-        <v>44265.22</v>
+        <v>44606.71</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -771,10 +771,8 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R3" s="6" t="n">
+        <v/>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
@@ -783,73 +781,73 @@
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43451.07</v>
+        <v>44948.85</v>
       </c>
       <c r="C4" t="n">
-        <v>44888.02</v>
+        <v>45852.75</v>
       </c>
       <c r="D4" t="n">
-        <v>43343.58</v>
+        <v>44495.46</v>
       </c>
       <c r="E4" t="n">
-        <v>44768.12</v>
+        <v>45045.81</v>
       </c>
       <c r="F4" t="n">
-        <v>1749.37</v>
+        <v>277.69</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0407</v>
+        <v>0.0062</v>
       </c>
       <c r="H4" t="n">
-        <v>1544.44</v>
+        <v>1357.29</v>
       </c>
       <c r="I4" t="n">
-        <v>40449.4</v>
+        <v>41799.14</v>
       </c>
       <c r="J4" t="n">
-        <v>41878.33</v>
+        <v>43549.84</v>
       </c>
       <c r="K4" t="n">
-        <v>42325.87</v>
+        <v>43995.9</v>
       </c>
       <c r="L4" t="n">
-        <v>42773.4</v>
+        <v>44441.96</v>
       </c>
       <c r="M4" t="n">
-        <v>43711.63</v>
+        <v>45540.34</v>
       </c>
       <c r="N4" t="n">
-        <v>44649.87</v>
+        <v>46638.72</v>
       </c>
       <c r="O4" t="n">
-        <v>44606.71</v>
+        <v>46432.46</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -867,18 +865,14 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
@@ -890,50 +884,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44948.85</v>
+        <v>45193.77</v>
       </c>
       <c r="C5" t="n">
-        <v>45852.75</v>
+        <v>45824.69</v>
       </c>
       <c r="D5" t="n">
-        <v>44495.46</v>
+        <v>45193.77</v>
       </c>
       <c r="E5" t="n">
-        <v>45045.81</v>
+        <v>45354.99</v>
       </c>
       <c r="F5" t="n">
-        <v>277.69</v>
+        <v>309.18</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0062</v>
+        <v>0.0069</v>
       </c>
       <c r="H5" t="n">
-        <v>1357.29</v>
+        <v>630.92</v>
       </c>
       <c r="I5" t="n">
-        <v>41799.14</v>
+        <v>43138.17</v>
       </c>
       <c r="J5" t="n">
-        <v>43549.84</v>
+        <v>43624.37</v>
       </c>
       <c r="K5" t="n">
-        <v>43995.9</v>
+        <v>44367.16</v>
       </c>
       <c r="L5" t="n">
-        <v>44441.96</v>
+        <v>45109.96</v>
       </c>
       <c r="M5" t="n">
-        <v>45540.34</v>
+        <v>45724.45</v>
       </c>
       <c r="N5" t="n">
-        <v>46638.72</v>
+        <v>46338.95</v>
       </c>
       <c r="O5" t="n">
-        <v>46432.46</v>
+        <v>47210.04</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -946,12 +940,12 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U5" s="8" t="n">
@@ -965,73 +959,83 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45193.77</v>
+        <v>45113.29</v>
       </c>
       <c r="C6" t="n">
-        <v>45824.69</v>
+        <v>45778.66</v>
       </c>
       <c r="D6" t="n">
-        <v>45193.77</v>
+        <v>44357.65</v>
       </c>
       <c r="E6" t="n">
-        <v>45354.99</v>
+        <v>45769.5</v>
       </c>
       <c r="F6" t="n">
-        <v>309.18</v>
+        <v>414.51</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0091</v>
       </c>
       <c r="H6" t="n">
-        <v>630.92</v>
+        <v>1421.01</v>
       </c>
       <c r="I6" t="n">
-        <v>43138.17</v>
+        <v>44562.85</v>
       </c>
       <c r="J6" t="n">
-        <v>43624.37</v>
+        <v>44646.95</v>
       </c>
       <c r="K6" t="n">
-        <v>44367.16</v>
+        <v>45039.53</v>
       </c>
       <c r="L6" t="n">
-        <v>45109.96</v>
+        <v>45432.11</v>
       </c>
       <c r="M6" t="n">
-        <v>45724.45</v>
+        <v>45670.45</v>
       </c>
       <c r="N6" t="n">
-        <v>46338.95</v>
+        <v>45908.79</v>
       </c>
       <c r="O6" t="n">
-        <v>47210.04</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+        <v>46455.61</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U6" s="8" t="n">
@@ -1047,72 +1051,66 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>45113.29</v>
+        <v>46636.07</v>
       </c>
       <c r="C7" t="n">
-        <v>45778.66</v>
+        <v>48597.08</v>
       </c>
       <c r="D7" t="n">
-        <v>44357.65</v>
+        <v>46592.99</v>
       </c>
       <c r="E7" t="n">
-        <v>45769.5</v>
+        <v>48088.8</v>
       </c>
       <c r="F7" t="n">
-        <v>414.51</v>
+        <v>2319.3</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0507</v>
       </c>
       <c r="H7" t="n">
-        <v>1421.01</v>
+        <v>2004.09</v>
       </c>
       <c r="I7" t="n">
-        <v>44562.85</v>
+        <v>42936.64</v>
       </c>
       <c r="J7" t="n">
-        <v>44646.95</v>
+        <v>44699.16</v>
       </c>
       <c r="K7" t="n">
-        <v>45039.53</v>
+        <v>45058.99</v>
       </c>
       <c r="L7" t="n">
-        <v>45432.11</v>
+        <v>45418.83</v>
       </c>
       <c r="M7" t="n">
-        <v>45670.45</v>
+        <v>46480.01</v>
       </c>
       <c r="N7" t="n">
-        <v>45908.79</v>
+        <v>47541.18</v>
       </c>
       <c r="O7" t="n">
-        <v>46455.61</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>47199.67</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
@@ -1121,73 +1119,73 @@
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>46636.07</v>
+        <v>47446.73</v>
       </c>
       <c r="C8" t="n">
-        <v>48597.08</v>
+        <v>48317.34</v>
       </c>
       <c r="D8" t="n">
-        <v>46592.99</v>
+        <v>46544.05</v>
       </c>
       <c r="E8" t="n">
-        <v>48088.8</v>
+        <v>47582.15</v>
       </c>
       <c r="F8" t="n">
-        <v>2319.3</v>
+        <v>-506.65</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0507</v>
+        <v>-0.0105</v>
       </c>
       <c r="H8" t="n">
-        <v>2004.09</v>
+        <v>1773.29</v>
       </c>
       <c r="I8" t="n">
-        <v>42936.64</v>
+        <v>44588.9</v>
       </c>
       <c r="J8" t="n">
-        <v>44699.16</v>
+        <v>46331.59</v>
       </c>
       <c r="K8" t="n">
-        <v>45058.99</v>
+        <v>47086.76</v>
       </c>
       <c r="L8" t="n">
-        <v>45418.83</v>
+        <v>47841.92</v>
       </c>
       <c r="M8" t="n">
-        <v>46480.01</v>
+        <v>49090.85</v>
       </c>
       <c r="N8" t="n">
-        <v>47541.18</v>
+        <v>50339.77</v>
       </c>
       <c r="O8" t="n">
-        <v>47199.67</v>
+        <v>50601.17</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1195,83 +1193,83 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47446.73</v>
+        <v>48332.71</v>
       </c>
       <c r="C9" t="n">
-        <v>48317.34</v>
+        <v>49945.95</v>
       </c>
       <c r="D9" t="n">
-        <v>46544.05</v>
+        <v>48254.83</v>
       </c>
       <c r="E9" t="n">
-        <v>47582.15</v>
+        <v>49299.65</v>
       </c>
       <c r="F9" t="n">
-        <v>-506.65</v>
+        <v>1717.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0105</v>
+        <v>0.0361</v>
       </c>
       <c r="H9" t="n">
-        <v>1773.29</v>
+        <v>1691.12</v>
       </c>
       <c r="I9" t="n">
-        <v>44588.9</v>
+        <v>44770.76</v>
       </c>
       <c r="J9" t="n">
-        <v>46331.59</v>
+        <v>45884.59</v>
       </c>
       <c r="K9" t="n">
-        <v>47086.76</v>
+        <v>46695.5</v>
       </c>
       <c r="L9" t="n">
-        <v>47841.92</v>
+        <v>47506.42</v>
       </c>
       <c r="M9" t="n">
-        <v>49090.85</v>
+        <v>48468.79</v>
       </c>
       <c r="N9" t="n">
-        <v>50339.77</v>
+        <v>49431.16</v>
       </c>
       <c r="O9" t="n">
-        <v>50601.17</v>
+        <v>50090.63</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1279,21 +1277,23 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1303,59 +1303,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48332.71</v>
+        <v>49905.8</v>
       </c>
       <c r="C10" t="n">
-        <v>49945.95</v>
+        <v>52411.34</v>
       </c>
       <c r="D10" t="n">
-        <v>48254.83</v>
+        <v>49838.98</v>
       </c>
       <c r="E10" t="n">
-        <v>49299.65</v>
+        <v>52411.34</v>
       </c>
       <c r="F10" t="n">
-        <v>1717.5</v>
+        <v>3111.69</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0361</v>
+        <v>0.0631</v>
       </c>
       <c r="H10" t="n">
-        <v>1691.12</v>
+        <v>2572.36</v>
       </c>
       <c r="I10" t="n">
-        <v>44770.76</v>
+        <v>46563.71</v>
       </c>
       <c r="J10" t="n">
-        <v>45884.59</v>
+        <v>47708.16</v>
       </c>
       <c r="K10" t="n">
-        <v>46695.5</v>
+        <v>48454.09</v>
       </c>
       <c r="L10" t="n">
-        <v>47506.42</v>
+        <v>49200.02</v>
       </c>
       <c r="M10" t="n">
-        <v>48468.79</v>
+        <v>50145.21</v>
       </c>
       <c r="N10" t="n">
-        <v>49431.16</v>
+        <v>51090.4</v>
       </c>
       <c r="O10" t="n">
-        <v>50090.63</v>
+        <v>51637.07</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1378,11 +1374,13 @@
       </c>
       <c r="U10" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v/>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
@@ -1394,151 +1392,149 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>49905.8</v>
+        <v>52294.31</v>
       </c>
       <c r="C11" t="n">
-        <v>52411.34</v>
+        <v>52636.87</v>
       </c>
       <c r="D11" t="n">
-        <v>49838.98</v>
+        <v>49073.58</v>
       </c>
       <c r="E11" t="n">
-        <v>52411.34</v>
+        <v>50276.37</v>
       </c>
       <c r="F11" t="n">
-        <v>3111.69</v>
+        <v>-2134.97</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0631</v>
+        <v>-0.0407</v>
       </c>
       <c r="H11" t="n">
-        <v>2572.36</v>
+        <v>3563.29</v>
       </c>
       <c r="I11" t="n">
-        <v>46563.71</v>
+        <v>47266.62</v>
       </c>
       <c r="J11" t="n">
-        <v>47708.16</v>
+        <v>50482.07</v>
       </c>
       <c r="K11" t="n">
-        <v>48454.09</v>
+        <v>51125.16</v>
       </c>
       <c r="L11" t="n">
-        <v>49200.02</v>
+        <v>51768.25</v>
       </c>
       <c r="M11" t="n">
-        <v>50145.21</v>
+        <v>53697.52</v>
       </c>
       <c r="N11" t="n">
-        <v>51090.4</v>
+        <v>55626.79</v>
       </c>
       <c r="O11" t="n">
-        <v>51637.07</v>
+        <v>54983.7</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
+      <c r="Q11" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W11" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W11" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52294.31</v>
+        <v>50645.27</v>
       </c>
       <c r="C12" t="n">
-        <v>52636.87</v>
+        <v>51513.16</v>
       </c>
       <c r="D12" t="n">
-        <v>49073.58</v>
+        <v>50246.6</v>
       </c>
       <c r="E12" t="n">
-        <v>50276.37</v>
+        <v>50376.53</v>
       </c>
       <c r="F12" t="n">
-        <v>-2134.97</v>
+        <v>100.16</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0407</v>
+        <v>0.002</v>
       </c>
       <c r="H12" t="n">
-        <v>3563.29</v>
+        <v>1266.56</v>
       </c>
       <c r="I12" t="n">
-        <v>47266.62</v>
+        <v>45510.29</v>
       </c>
       <c r="J12" t="n">
-        <v>50482.07</v>
+        <v>46423.65</v>
       </c>
       <c r="K12" t="n">
-        <v>51125.16</v>
+        <v>48494.72</v>
       </c>
       <c r="L12" t="n">
-        <v>51768.25</v>
+        <v>50565.8</v>
       </c>
       <c r="M12" t="n">
-        <v>53697.52</v>
+        <v>52058.02</v>
       </c>
       <c r="N12" t="n">
-        <v>55626.79</v>
+        <v>53550.24</v>
       </c>
       <c r="O12" t="n">
-        <v>54983.7</v>
+        <v>56200.16</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1557,70 +1553,76 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>50645.27</v>
+        <v>50282.39</v>
       </c>
       <c r="C13" t="n">
-        <v>51513.16</v>
+        <v>50574.82</v>
       </c>
       <c r="D13" t="n">
-        <v>50246.6</v>
+        <v>48235.3</v>
       </c>
       <c r="E13" t="n">
-        <v>50376.53</v>
+        <v>48625.88</v>
       </c>
       <c r="F13" t="n">
-        <v>100.16</v>
+        <v>-1750.65</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0348</v>
       </c>
       <c r="H13" t="n">
-        <v>1266.56</v>
+        <v>2339.52</v>
       </c>
       <c r="I13" t="n">
-        <v>45510.29</v>
+        <v>48980.04</v>
       </c>
       <c r="J13" t="n">
-        <v>46423.65</v>
+        <v>48858.3</v>
       </c>
       <c r="K13" t="n">
-        <v>48494.72</v>
+        <v>49743.25</v>
       </c>
       <c r="L13" t="n">
-        <v>50565.8</v>
+        <v>50628.21</v>
       </c>
       <c r="M13" t="n">
-        <v>52058.02</v>
+        <v>51009.81</v>
       </c>
       <c r="N13" t="n">
-        <v>53550.24</v>
+        <v>51391.42</v>
       </c>
       <c r="O13" t="n">
-        <v>56200.16</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+        <v>52779.72</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1637,86 +1639,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>50282.39</v>
+        <v>49113.82</v>
       </c>
       <c r="C14" t="n">
-        <v>50574.82</v>
+        <v>50322.14</v>
       </c>
       <c r="D14" t="n">
-        <v>48235.3</v>
+        <v>48511.95</v>
       </c>
       <c r="E14" t="n">
-        <v>48625.88</v>
+        <v>50253.91</v>
       </c>
       <c r="F14" t="n">
-        <v>-1750.65</v>
+        <v>1628.03</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0348</v>
+        <v>0.0335</v>
       </c>
       <c r="H14" t="n">
-        <v>2339.52</v>
+        <v>1810.19</v>
       </c>
       <c r="I14" t="n">
-        <v>48980.04</v>
+        <v>45895.78</v>
       </c>
       <c r="J14" t="n">
-        <v>48858.3</v>
+        <v>45896.77</v>
       </c>
       <c r="K14" t="n">
-        <v>49743.25</v>
+        <v>47456.12</v>
       </c>
       <c r="L14" t="n">
-        <v>50628.21</v>
+        <v>49015.47</v>
       </c>
       <c r="M14" t="n">
-        <v>51009.81</v>
+        <v>49795.64</v>
       </c>
       <c r="N14" t="n">
-        <v>51391.42</v>
+        <v>50575.81</v>
       </c>
       <c r="O14" t="n">
-        <v>52779.72</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
+        <v>52914.34</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
@@ -1725,55 +1721,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>49113.82</v>
+        <v>50318.59</v>
       </c>
       <c r="C15" t="n">
-        <v>50322.14</v>
+        <v>51028.42</v>
       </c>
       <c r="D15" t="n">
-        <v>48511.95</v>
+        <v>49215.96</v>
       </c>
       <c r="E15" t="n">
-        <v>50253.91</v>
+        <v>50491.87</v>
       </c>
       <c r="F15" t="n">
-        <v>1628.03</v>
+        <v>237.96</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0335</v>
+        <v>0.0047</v>
       </c>
       <c r="H15" t="n">
-        <v>1810.19</v>
+        <v>1812.46</v>
       </c>
       <c r="I15" t="n">
-        <v>45895.78</v>
+        <v>46701.76</v>
       </c>
       <c r="J15" t="n">
-        <v>45896.77</v>
+        <v>48862.15</v>
       </c>
       <c r="K15" t="n">
-        <v>47456.12</v>
+        <v>49348.81</v>
       </c>
       <c r="L15" t="n">
-        <v>49015.47</v>
+        <v>49835.48</v>
       </c>
       <c r="M15" t="n">
-        <v>49795.64</v>
+        <v>51159.01</v>
       </c>
       <c r="N15" t="n">
-        <v>50575.81</v>
+        <v>52482.53</v>
       </c>
       <c r="O15" t="n">
-        <v>52914.34</v>
+        <v>52132.33</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1781,23 +1781,21 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1809,57 +1807,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>50318.59</v>
+        <v>50643.09</v>
       </c>
       <c r="C16" t="n">
-        <v>51028.42</v>
+        <v>51127.69</v>
       </c>
       <c r="D16" t="n">
-        <v>49215.96</v>
+        <v>49926.27</v>
       </c>
       <c r="E16" t="n">
-        <v>50491.87</v>
+        <v>50836.55</v>
       </c>
       <c r="F16" t="n">
-        <v>237.96</v>
+        <v>344.68</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0047</v>
+        <v>0.0068</v>
       </c>
       <c r="H16" t="n">
-        <v>1812.46</v>
+        <v>1201.42</v>
       </c>
       <c r="I16" t="n">
-        <v>46701.76</v>
+        <v>47403.5</v>
       </c>
       <c r="J16" t="n">
-        <v>48862.15</v>
+        <v>48864.25</v>
       </c>
       <c r="K16" t="n">
-        <v>49348.81</v>
+        <v>49585.64</v>
       </c>
       <c r="L16" t="n">
-        <v>49835.48</v>
+        <v>50307.03</v>
       </c>
       <c r="M16" t="n">
-        <v>51159.01</v>
+        <v>51398.1</v>
       </c>
       <c r="N16" t="n">
-        <v>52482.53</v>
+        <v>52489.17</v>
       </c>
       <c r="O16" t="n">
-        <v>52132.33</v>
+        <v>52840.88</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1867,10 +1865,8 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R16" s="6" t="n">
+        <v/>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
@@ -1900,63 +1896,69 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>50643.09</v>
+        <v>50352.09</v>
       </c>
       <c r="C17" t="n">
-        <v>51127.69</v>
+        <v>50432.1</v>
       </c>
       <c r="D17" t="n">
-        <v>49926.27</v>
+        <v>48643.78</v>
       </c>
       <c r="E17" t="n">
-        <v>50836.55</v>
+        <v>49507.21</v>
       </c>
       <c r="F17" t="n">
-        <v>344.68</v>
+        <v>-1329.34</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0261</v>
       </c>
       <c r="H17" t="n">
-        <v>1201.42</v>
+        <v>1788.32</v>
       </c>
       <c r="I17" t="n">
-        <v>47403.5</v>
+        <v>48724.85</v>
       </c>
       <c r="J17" t="n">
-        <v>48864.25</v>
+        <v>49789.91</v>
       </c>
       <c r="K17" t="n">
-        <v>49585.64</v>
+        <v>50235.84</v>
       </c>
       <c r="L17" t="n">
-        <v>50307.03</v>
+        <v>50681.77</v>
       </c>
       <c r="M17" t="n">
-        <v>51398.1</v>
+        <v>51437.26</v>
       </c>
       <c r="N17" t="n">
-        <v>52489.17</v>
+        <v>52192.76</v>
       </c>
       <c r="O17" t="n">
-        <v>52840.88</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>52329.11</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1973,83 +1975,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50352.09</v>
+        <v>50084.55</v>
       </c>
       <c r="C18" t="n">
-        <v>50432.1</v>
+        <v>50941.89</v>
       </c>
       <c r="D18" t="n">
-        <v>48643.78</v>
+        <v>49982.2</v>
       </c>
       <c r="E18" t="n">
-        <v>49507.21</v>
+        <v>50750.39</v>
       </c>
       <c r="F18" t="n">
-        <v>-1329.34</v>
+        <v>1243.18</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0261</v>
+        <v>0.0251</v>
       </c>
       <c r="H18" t="n">
-        <v>1788.32</v>
+        <v>959.6900000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>48724.85</v>
+        <v>46855.46</v>
       </c>
       <c r="J18" t="n">
-        <v>49789.91</v>
+        <v>47703.53</v>
       </c>
       <c r="K18" t="n">
-        <v>50235.84</v>
+        <v>48613.05</v>
       </c>
       <c r="L18" t="n">
-        <v>50681.77</v>
+        <v>49522.58</v>
       </c>
       <c r="M18" t="n">
-        <v>51437.26</v>
+        <v>50401.37</v>
       </c>
       <c r="N18" t="n">
-        <v>52192.76</v>
+        <v>51280.17</v>
       </c>
       <c r="O18" t="n">
-        <v>52329.11</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q18" s="6" t="inlineStr">
+        <v>52220.42</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
@@ -2061,55 +2055,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>50084.55</v>
+        <v>50691.22</v>
       </c>
       <c r="C19" t="n">
-        <v>50941.89</v>
+        <v>50707.23</v>
       </c>
       <c r="D19" t="n">
-        <v>49982.2</v>
+        <v>50198.97</v>
       </c>
       <c r="E19" t="n">
-        <v>50750.39</v>
+        <v>50339.48</v>
       </c>
       <c r="F19" t="n">
-        <v>1243.18</v>
+        <v>-410.91</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0251</v>
+        <v>-0.0081</v>
       </c>
       <c r="H19" t="n">
-        <v>959.6900000000001</v>
+        <v>508.26</v>
       </c>
       <c r="I19" t="n">
-        <v>46855.46</v>
+        <v>49022.51</v>
       </c>
       <c r="J19" t="n">
-        <v>47703.53</v>
+        <v>49934.87</v>
       </c>
       <c r="K19" t="n">
-        <v>48613.05</v>
+        <v>50270.54</v>
       </c>
       <c r="L19" t="n">
-        <v>49522.58</v>
+        <v>50606.22</v>
       </c>
       <c r="M19" t="n">
-        <v>50401.37</v>
+        <v>51230.24</v>
       </c>
       <c r="N19" t="n">
-        <v>51280.17</v>
+        <v>51854.25</v>
       </c>
       <c r="O19" t="n">
-        <v>52220.42</v>
+        <v>51901.58</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2117,19 +2115,19 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
@@ -2143,57 +2141,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>50691.22</v>
+        <v>51010.28</v>
       </c>
       <c r="C20" t="n">
-        <v>50707.23</v>
+        <v>52523.77</v>
       </c>
       <c r="D20" t="n">
-        <v>50198.97</v>
+        <v>50995.67</v>
       </c>
       <c r="E20" t="n">
-        <v>50339.48</v>
+        <v>51939.89</v>
       </c>
       <c r="F20" t="n">
-        <v>-410.91</v>
+        <v>1600.41</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0081</v>
+        <v>0.0318</v>
       </c>
       <c r="H20" t="n">
-        <v>508.26</v>
+        <v>1528.1</v>
       </c>
       <c r="I20" t="n">
-        <v>49022.51</v>
+        <v>49690.71</v>
       </c>
       <c r="J20" t="n">
-        <v>49934.87</v>
+        <v>49774.41</v>
       </c>
       <c r="K20" t="n">
-        <v>50270.54</v>
+        <v>50085.35</v>
       </c>
       <c r="L20" t="n">
-        <v>50606.22</v>
+        <v>50396.29</v>
       </c>
       <c r="M20" t="n">
-        <v>51230.24</v>
+        <v>50593.61</v>
       </c>
       <c r="N20" t="n">
-        <v>51854.25</v>
+        <v>50790.93</v>
       </c>
       <c r="O20" t="n">
-        <v>51901.58</v>
+        <v>51215.49</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2201,83 +2199,83 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W20" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>51010.28</v>
+        <v>52808.29</v>
       </c>
       <c r="C21" t="n">
-        <v>52523.77</v>
+        <v>54487.32</v>
       </c>
       <c r="D21" t="n">
-        <v>50995.67</v>
+        <v>52741.64</v>
       </c>
       <c r="E21" t="n">
-        <v>51939.89</v>
+        <v>53936.17</v>
       </c>
       <c r="F21" t="n">
-        <v>1600.41</v>
+        <v>1996.28</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0318</v>
+        <v>0.0384</v>
       </c>
       <c r="H21" t="n">
-        <v>1528.1</v>
+        <v>1745.68</v>
       </c>
       <c r="I21" t="n">
-        <v>49690.71</v>
+        <v>49467.57</v>
       </c>
       <c r="J21" t="n">
-        <v>49774.41</v>
+        <v>50501.88</v>
       </c>
       <c r="K21" t="n">
-        <v>50085.35</v>
+        <v>51175.84</v>
       </c>
       <c r="L21" t="n">
-        <v>50396.29</v>
+        <v>51849.81</v>
       </c>
       <c r="M21" t="n">
-        <v>50593.61</v>
+        <v>52703.94</v>
       </c>
       <c r="N21" t="n">
-        <v>50790.93</v>
+        <v>53558.07</v>
       </c>
       <c r="O21" t="n">
-        <v>51215.49</v>
+        <v>54051.87</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2318,151 +2316,151 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52808.29</v>
+        <v>53390.05</v>
       </c>
       <c r="C22" t="n">
-        <v>54487.32</v>
+        <v>54050.84</v>
       </c>
       <c r="D22" t="n">
-        <v>52741.64</v>
+        <v>52194.81</v>
       </c>
       <c r="E22" t="n">
-        <v>53936.17</v>
+        <v>53846.87</v>
       </c>
       <c r="F22" t="n">
-        <v>1996.28</v>
+        <v>-89.3</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0384</v>
+        <v>-0.0017</v>
       </c>
       <c r="H22" t="n">
-        <v>1745.68</v>
+        <v>1856.03</v>
       </c>
       <c r="I22" t="n">
-        <v>49467.57</v>
+        <v>50995.96</v>
       </c>
       <c r="J22" t="n">
-        <v>50501.88</v>
+        <v>52351.34</v>
       </c>
       <c r="K22" t="n">
-        <v>51175.84</v>
+        <v>53063.33</v>
       </c>
       <c r="L22" t="n">
-        <v>51849.81</v>
+        <v>53775.33</v>
       </c>
       <c r="M22" t="n">
-        <v>52703.94</v>
+        <v>54809.01</v>
       </c>
       <c r="N22" t="n">
-        <v>53558.07</v>
+        <v>55842.7</v>
       </c>
       <c r="O22" t="n">
-        <v>54051.87</v>
+        <v>56233</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>53390.05</v>
+        <v>53023.28</v>
       </c>
       <c r="C23" t="n">
-        <v>54050.84</v>
+        <v>53742.69</v>
       </c>
       <c r="D23" t="n">
-        <v>52194.81</v>
+        <v>52637.66</v>
       </c>
       <c r="E23" t="n">
-        <v>53846.87</v>
+        <v>53322.85</v>
       </c>
       <c r="F23" t="n">
-        <v>-89.3</v>
+        <v>-524.02</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0097</v>
       </c>
       <c r="H23" t="n">
-        <v>1856.03</v>
+        <v>1105.03</v>
       </c>
       <c r="I23" t="n">
-        <v>50995.96</v>
+        <v>50338.78</v>
       </c>
       <c r="J23" t="n">
-        <v>52351.34</v>
+        <v>52352.86</v>
       </c>
       <c r="K23" t="n">
-        <v>53063.33</v>
+        <v>52918.86</v>
       </c>
       <c r="L23" t="n">
-        <v>53775.33</v>
+        <v>53484.85</v>
       </c>
       <c r="M23" t="n">
-        <v>54809.01</v>
+        <v>54774.89</v>
       </c>
       <c r="N23" t="n">
-        <v>55842.7</v>
+        <v>56064.93</v>
       </c>
       <c r="O23" t="n">
-        <v>56233</v>
+        <v>55906.87</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q23" s="6" t="n">
+        <v/>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2481,57 +2479,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>53023.28</v>
+        <v>53575.37</v>
       </c>
       <c r="C24" t="n">
-        <v>53742.69</v>
+        <v>54782.83</v>
       </c>
       <c r="D24" t="n">
-        <v>52637.66</v>
+        <v>52655.18</v>
       </c>
       <c r="E24" t="n">
-        <v>53322.85</v>
+        <v>54253.68</v>
       </c>
       <c r="F24" t="n">
-        <v>-524.02</v>
+        <v>930.83</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0175</v>
       </c>
       <c r="H24" t="n">
-        <v>1105.03</v>
+        <v>2127.65</v>
       </c>
       <c r="I24" t="n">
-        <v>50338.78</v>
+        <v>51532.63</v>
       </c>
       <c r="J24" t="n">
-        <v>52352.86</v>
+        <v>52284.16</v>
       </c>
       <c r="K24" t="n">
-        <v>52918.86</v>
+        <v>52770.34</v>
       </c>
       <c r="L24" t="n">
-        <v>53484.85</v>
+        <v>53256.51</v>
       </c>
       <c r="M24" t="n">
-        <v>54774.89</v>
+        <v>53875.37</v>
       </c>
       <c r="N24" t="n">
-        <v>56064.93</v>
+        <v>54494.22</v>
       </c>
       <c r="O24" t="n">
-        <v>55906.87</v>
+        <v>54847.72</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2544,16 +2542,20 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2563,59 +2565,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>53575.37</v>
+        <v>55130.63</v>
       </c>
       <c r="C25" t="n">
-        <v>54782.83</v>
+        <v>58015.08</v>
       </c>
       <c r="D25" t="n">
-        <v>52655.18</v>
+        <v>55018.57</v>
       </c>
       <c r="E25" t="n">
-        <v>54253.68</v>
+        <v>56941.97</v>
       </c>
       <c r="F25" t="n">
-        <v>930.83</v>
+        <v>2688.29</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0496</v>
       </c>
       <c r="H25" t="n">
-        <v>2127.65</v>
+        <v>2996.51</v>
       </c>
       <c r="I25" t="n">
-        <v>51532.63</v>
+        <v>50527.53</v>
       </c>
       <c r="J25" t="n">
-        <v>52284.16</v>
+        <v>52393.37</v>
       </c>
       <c r="K25" t="n">
-        <v>52770.34</v>
+        <v>53189.86</v>
       </c>
       <c r="L25" t="n">
-        <v>53256.51</v>
+        <v>53986.34</v>
       </c>
       <c r="M25" t="n">
-        <v>53875.37</v>
+        <v>55317.5</v>
       </c>
       <c r="N25" t="n">
-        <v>54494.22</v>
+        <v>56648.67</v>
       </c>
       <c r="O25" t="n">
-        <v>54847.72</v>
+        <v>56910.48</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2623,10 +2621,8 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
@@ -2640,11 +2636,13 @@
       </c>
       <c r="U25" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
@@ -2656,50 +2654,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>55130.63</v>
+        <v>57212.97</v>
       </c>
       <c r="C26" t="n">
-        <v>58015.08</v>
+        <v>57709.82</v>
       </c>
       <c r="D26" t="n">
-        <v>55018.57</v>
+        <v>56135.12</v>
       </c>
       <c r="E26" t="n">
-        <v>56941.97</v>
+        <v>56825.7</v>
       </c>
       <c r="F26" t="n">
-        <v>2688.29</v>
+        <v>-116.27</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0496</v>
+        <v>-0.002</v>
       </c>
       <c r="H26" t="n">
-        <v>2996.51</v>
+        <v>1574.7</v>
       </c>
       <c r="I26" t="n">
-        <v>50527.53</v>
+        <v>52022.06</v>
       </c>
       <c r="J26" t="n">
-        <v>52393.37</v>
+        <v>54158.03</v>
       </c>
       <c r="K26" t="n">
-        <v>53189.86</v>
+        <v>55443.71</v>
       </c>
       <c r="L26" t="n">
-        <v>53986.34</v>
+        <v>56729.4</v>
       </c>
       <c r="M26" t="n">
-        <v>55317.5</v>
+        <v>58440.22</v>
       </c>
       <c r="N26" t="n">
-        <v>56648.67</v>
+        <v>60151.05</v>
       </c>
       <c r="O26" t="n">
-        <v>56910.48</v>
+        <v>61011.59</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2712,78 +2710,76 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>57212.97</v>
+        <v>56764.14</v>
       </c>
       <c r="C27" t="n">
-        <v>57709.82</v>
+        <v>59332.43</v>
       </c>
       <c r="D27" t="n">
-        <v>56135.12</v>
+        <v>56732.93</v>
       </c>
       <c r="E27" t="n">
-        <v>56825.7</v>
+        <v>58850.27</v>
       </c>
       <c r="F27" t="n">
-        <v>-116.27</v>
+        <v>2024.57</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0356</v>
       </c>
       <c r="H27" t="n">
-        <v>1574.7</v>
+        <v>2599.5</v>
       </c>
       <c r="I27" t="n">
-        <v>52022.06</v>
+        <v>54560.42</v>
       </c>
       <c r="J27" t="n">
-        <v>54158.03</v>
+        <v>55202.61</v>
       </c>
       <c r="K27" t="n">
-        <v>55443.71</v>
+        <v>56038.35</v>
       </c>
       <c r="L27" t="n">
-        <v>56729.4</v>
+        <v>56874.08</v>
       </c>
       <c r="M27" t="n">
-        <v>58440.22</v>
+        <v>57613.05</v>
       </c>
       <c r="N27" t="n">
-        <v>60151.05</v>
+        <v>58352.01</v>
       </c>
       <c r="O27" t="n">
-        <v>61011.59</v>
+        <v>59284.52</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2796,109 +2792,111 @@
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>56764.14</v>
+        <v>57976.2</v>
       </c>
       <c r="C28" t="n">
-        <v>59332.43</v>
+        <v>58365.21</v>
       </c>
       <c r="D28" t="n">
-        <v>56732.93</v>
+        <v>53618.2</v>
       </c>
       <c r="E28" t="n">
-        <v>58850.27</v>
+        <v>55620.84</v>
       </c>
       <c r="F28" t="n">
-        <v>2024.57</v>
+        <v>-3229.43</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0356</v>
+        <v>-0.0549</v>
       </c>
       <c r="H28" t="n">
-        <v>2599.5</v>
+        <v>4747.01</v>
       </c>
       <c r="I28" t="n">
-        <v>54560.42</v>
+        <v>54133.43</v>
       </c>
       <c r="J28" t="n">
-        <v>55202.61</v>
+        <v>56659.56</v>
       </c>
       <c r="K28" t="n">
-        <v>56038.35</v>
+        <v>57550.52</v>
       </c>
       <c r="L28" t="n">
-        <v>56874.08</v>
+        <v>58441.47</v>
       </c>
       <c r="M28" t="n">
-        <v>57613.05</v>
+        <v>60150.02</v>
       </c>
       <c r="N28" t="n">
-        <v>58352.01</v>
+        <v>61858.56</v>
       </c>
       <c r="O28" t="n">
-        <v>59284.52</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
+        <v>61931.93</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W28" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W28" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr"/>
@@ -2906,64 +2904,60 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>57976.2</v>
+        <v>54608.63</v>
       </c>
       <c r="C29" t="n">
-        <v>58365.21</v>
+        <v>55745.38</v>
       </c>
       <c r="D29" t="n">
-        <v>53618.2</v>
+        <v>51407.66</v>
       </c>
       <c r="E29" t="n">
-        <v>55620.84</v>
+        <v>53819.61</v>
       </c>
       <c r="F29" t="n">
-        <v>-3229.43</v>
+        <v>-1801.23</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0549</v>
+        <v>-0.0324</v>
       </c>
       <c r="H29" t="n">
-        <v>4747.01</v>
+        <v>4337.72</v>
       </c>
       <c r="I29" t="n">
-        <v>54133.43</v>
+        <v>48871.19</v>
       </c>
       <c r="J29" t="n">
-        <v>56659.56</v>
+        <v>50688.4</v>
       </c>
       <c r="K29" t="n">
-        <v>57550.52</v>
+        <v>53247.33</v>
       </c>
       <c r="L29" t="n">
-        <v>58441.47</v>
+        <v>55806.27</v>
       </c>
       <c r="M29" t="n">
-        <v>60150.02</v>
+        <v>57994.35</v>
       </c>
       <c r="N29" t="n">
-        <v>61858.56</v>
+        <v>60182.42</v>
       </c>
       <c r="O29" t="n">
-        <v>61931.93</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q29" s="6" t="inlineStr">
+        <v>63112.22</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
@@ -2990,50 +2984,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>54608.63</v>
+        <v>53627.86</v>
       </c>
       <c r="C30" t="n">
-        <v>55745.38</v>
+        <v>55239.4</v>
       </c>
       <c r="D30" t="n">
-        <v>51407.66</v>
+        <v>53113.95</v>
       </c>
       <c r="E30" t="n">
-        <v>53819.61</v>
+        <v>53372.53</v>
       </c>
       <c r="F30" t="n">
-        <v>-1801.23</v>
+        <v>-447.08</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0324</v>
+        <v>-0.0083</v>
       </c>
       <c r="H30" t="n">
-        <v>4337.72</v>
+        <v>2125.45</v>
       </c>
       <c r="I30" t="n">
-        <v>48871.19</v>
+        <v>47069.94</v>
       </c>
       <c r="J30" t="n">
-        <v>50688.4</v>
+        <v>49603.44</v>
       </c>
       <c r="K30" t="n">
-        <v>53247.33</v>
+        <v>51650.75</v>
       </c>
       <c r="L30" t="n">
-        <v>55806.27</v>
+        <v>53698.06</v>
       </c>
       <c r="M30" t="n">
-        <v>57994.35</v>
+        <v>55988.47</v>
       </c>
       <c r="N30" t="n">
-        <v>60182.42</v>
+        <v>58278.87</v>
       </c>
       <c r="O30" t="n">
-        <v>63112.22</v>
+        <v>60083.1</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3041,14 +3035,12 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R30" s="6" t="n">
+        <v/>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3065,64 +3057,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>53627.86</v>
+        <v>52468.72</v>
       </c>
       <c r="C31" t="n">
-        <v>55239.4</v>
+        <v>54175.8</v>
       </c>
       <c r="D31" t="n">
-        <v>53113.95</v>
+        <v>50688.76</v>
       </c>
       <c r="E31" t="n">
-        <v>53372.53</v>
+        <v>53373.07</v>
       </c>
       <c r="F31" t="n">
-        <v>-447.08</v>
+        <v>0.54</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0083</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2125.45</v>
+        <v>3487.04</v>
       </c>
       <c r="I31" t="n">
-        <v>47069.94</v>
+        <v>50988.5</v>
       </c>
       <c r="J31" t="n">
-        <v>49603.44</v>
+        <v>50845.01</v>
       </c>
       <c r="K31" t="n">
-        <v>51650.75</v>
+        <v>52309.81</v>
       </c>
       <c r="L31" t="n">
-        <v>53698.06</v>
+        <v>53774.6</v>
       </c>
       <c r="M31" t="n">
-        <v>55988.47</v>
+        <v>54435.26</v>
       </c>
       <c r="N31" t="n">
-        <v>58278.87</v>
+        <v>55095.91</v>
       </c>
       <c r="O31" t="n">
-        <v>60083.1</v>
-      </c>
-      <c r="P31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+        <v>57364.85</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
@@ -3152,69 +3154,65 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>52468.72</v>
+        <v>52054.68</v>
       </c>
       <c r="C32" t="n">
-        <v>54175.8</v>
+        <v>54258.48</v>
       </c>
       <c r="D32" t="n">
-        <v>50688.76</v>
+        <v>50558.91</v>
       </c>
       <c r="E32" t="n">
-        <v>53373.07</v>
+        <v>53123.49</v>
       </c>
       <c r="F32" t="n">
-        <v>0.54</v>
+        <v>-249.58</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0</v>
+        <v>-0.0047</v>
       </c>
       <c r="H32" t="n">
-        <v>3487.04</v>
+        <v>3699.57</v>
       </c>
       <c r="I32" t="n">
-        <v>50988.5</v>
+        <v>47201.72</v>
       </c>
       <c r="J32" t="n">
-        <v>50845.01</v>
+        <v>50356.43</v>
       </c>
       <c r="K32" t="n">
-        <v>52309.81</v>
+        <v>51629.55</v>
       </c>
       <c r="L32" t="n">
-        <v>53774.6</v>
+        <v>52902.68</v>
       </c>
       <c r="M32" t="n">
-        <v>54435.26</v>
+        <v>55116.59</v>
       </c>
       <c r="N32" t="n">
-        <v>55095.91</v>
+        <v>57330.5</v>
       </c>
       <c r="O32" t="n">
-        <v>57364.85</v>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>57662.84</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v/>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3240,50 +3238,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>52054.68</v>
+        <v>53205.93</v>
       </c>
       <c r="C33" t="n">
-        <v>54258.48</v>
+        <v>57012.77</v>
       </c>
       <c r="D33" t="n">
-        <v>50558.91</v>
+        <v>53156.94</v>
       </c>
       <c r="E33" t="n">
-        <v>53123.49</v>
+        <v>56924.11</v>
       </c>
       <c r="F33" t="n">
-        <v>-249.58</v>
+        <v>3800.62</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0047</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>3699.57</v>
+        <v>3855.83</v>
       </c>
       <c r="I33" t="n">
-        <v>47201.72</v>
+        <v>46859.34</v>
       </c>
       <c r="J33" t="n">
-        <v>50356.43</v>
+        <v>49781.31</v>
       </c>
       <c r="K33" t="n">
-        <v>51629.55</v>
+        <v>51273.7</v>
       </c>
       <c r="L33" t="n">
-        <v>52902.68</v>
+        <v>52766.09</v>
       </c>
       <c r="M33" t="n">
-        <v>55116.59</v>
+        <v>54973.27</v>
       </c>
       <c r="N33" t="n">
-        <v>57330.5</v>
+        <v>57180.46</v>
       </c>
       <c r="O33" t="n">
-        <v>57662.84</v>
+        <v>57958.05</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3291,21 +3289,23 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R33" s="6" t="n">
+        <v/>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3317,57 +3317,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>53205.93</v>
+        <v>56421.46</v>
       </c>
       <c r="C34" t="n">
-        <v>57012.77</v>
+        <v>59688.1</v>
       </c>
       <c r="D34" t="n">
-        <v>53156.94</v>
+        <v>56232.78</v>
       </c>
       <c r="E34" t="n">
-        <v>56924.11</v>
+        <v>58475.9</v>
       </c>
       <c r="F34" t="n">
-        <v>3800.62</v>
+        <v>1551.79</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0273</v>
       </c>
       <c r="H34" t="n">
-        <v>3855.83</v>
+        <v>3455.32</v>
       </c>
       <c r="I34" t="n">
-        <v>46859.34</v>
+        <v>49301.11</v>
       </c>
       <c r="J34" t="n">
-        <v>49781.31</v>
+        <v>53987.91</v>
       </c>
       <c r="K34" t="n">
-        <v>51273.7</v>
+        <v>54996.2</v>
       </c>
       <c r="L34" t="n">
-        <v>52766.09</v>
+        <v>56004.48</v>
       </c>
       <c r="M34" t="n">
-        <v>54973.27</v>
+        <v>58852.02</v>
       </c>
       <c r="N34" t="n">
-        <v>57180.46</v>
+        <v>61699.56</v>
       </c>
       <c r="O34" t="n">
-        <v>57958.05</v>
+        <v>60868.6</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3385,13 +3385,11 @@
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3410,50 +3408,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>56421.46</v>
+        <v>58821.16</v>
       </c>
       <c r="C35" t="n">
-        <v>59688.1</v>
+        <v>60013.98</v>
       </c>
       <c r="D35" t="n">
-        <v>56232.78</v>
+        <v>58621.48</v>
       </c>
       <c r="E35" t="n">
-        <v>58475.9</v>
+        <v>59716.18</v>
       </c>
       <c r="F35" t="n">
-        <v>1551.79</v>
+        <v>1240.28</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0273</v>
+        <v>0.0212</v>
       </c>
       <c r="H35" t="n">
-        <v>3455.32</v>
+        <v>1392.5</v>
       </c>
       <c r="I35" t="n">
-        <v>49301.11</v>
+        <v>52777.46</v>
       </c>
       <c r="J35" t="n">
-        <v>53987.91</v>
+        <v>55278.31</v>
       </c>
       <c r="K35" t="n">
-        <v>54996.2</v>
+        <v>56748.24</v>
       </c>
       <c r="L35" t="n">
-        <v>56004.48</v>
+        <v>58218.17</v>
       </c>
       <c r="M35" t="n">
-        <v>58852.02</v>
+        <v>60203.56</v>
       </c>
       <c r="N35" t="n">
-        <v>61699.56</v>
+        <v>62188.95</v>
       </c>
       <c r="O35" t="n">
-        <v>60868.6</v>
+        <v>63143.42</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3494,50 +3492,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>58821.16</v>
+        <v>59880.71</v>
       </c>
       <c r="C36" t="n">
-        <v>60013.98</v>
+        <v>60903.95</v>
       </c>
       <c r="D36" t="n">
-        <v>58621.48</v>
+        <v>58928.2</v>
       </c>
       <c r="E36" t="n">
-        <v>59716.18</v>
+        <v>59513.12</v>
       </c>
       <c r="F36" t="n">
-        <v>1240.28</v>
+        <v>-203.06</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0034</v>
       </c>
       <c r="H36" t="n">
-        <v>1392.5</v>
+        <v>1975.75</v>
       </c>
       <c r="I36" t="n">
-        <v>52777.46</v>
+        <v>57228.98</v>
       </c>
       <c r="J36" t="n">
-        <v>55278.31</v>
+        <v>58522.9</v>
       </c>
       <c r="K36" t="n">
-        <v>56748.24</v>
+        <v>59019.93</v>
       </c>
       <c r="L36" t="n">
-        <v>58218.17</v>
+        <v>59516.96</v>
       </c>
       <c r="M36" t="n">
-        <v>60203.56</v>
+        <v>60412.43</v>
       </c>
       <c r="N36" t="n">
-        <v>62188.95</v>
+        <v>61307.9</v>
       </c>
       <c r="O36" t="n">
-        <v>63143.42</v>
+        <v>61406.48</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3545,17 +3543,19 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U36" s="8" t="n">
@@ -3571,57 +3571,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>59880.71</v>
+        <v>60241.31</v>
       </c>
       <c r="C37" t="n">
-        <v>60903.95</v>
+        <v>63091.14</v>
       </c>
       <c r="D37" t="n">
-        <v>58928.2</v>
+        <v>60213.02</v>
       </c>
       <c r="E37" t="n">
-        <v>59513.12</v>
+        <v>62713.65</v>
       </c>
       <c r="F37" t="n">
-        <v>-203.06</v>
+        <v>3200.53</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0538</v>
       </c>
       <c r="H37" t="n">
-        <v>1975.75</v>
+        <v>2878.12</v>
       </c>
       <c r="I37" t="n">
-        <v>57228.98</v>
+        <v>56952.45</v>
       </c>
       <c r="J37" t="n">
-        <v>58522.9</v>
+        <v>57335.89</v>
       </c>
       <c r="K37" t="n">
-        <v>59019.93</v>
+        <v>58525.25</v>
       </c>
       <c r="L37" t="n">
-        <v>59516.96</v>
+        <v>59714.6</v>
       </c>
       <c r="M37" t="n">
-        <v>60412.43</v>
+        <v>60501</v>
       </c>
       <c r="N37" t="n">
-        <v>61307.9</v>
+        <v>61287.39</v>
       </c>
       <c r="O37" t="n">
-        <v>61406.48</v>
+        <v>62879.7</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3629,14 +3629,12 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
@@ -3644,70 +3642,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W37" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W37" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>60241.31</v>
+        <v>63203.44</v>
       </c>
       <c r="C38" t="n">
-        <v>63091.14</v>
+        <v>63799.32</v>
       </c>
       <c r="D38" t="n">
-        <v>60213.02</v>
+        <v>60937.3</v>
       </c>
       <c r="E38" t="n">
-        <v>62713.65</v>
+        <v>61409.29</v>
       </c>
       <c r="F38" t="n">
-        <v>3200.53</v>
+        <v>-1304.36</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0538</v>
+        <v>-0.0208</v>
       </c>
       <c r="H38" t="n">
-        <v>2878.12</v>
+        <v>2862.02</v>
       </c>
       <c r="I38" t="n">
-        <v>56952.45</v>
+        <v>57334.9</v>
       </c>
       <c r="J38" t="n">
-        <v>57335.89</v>
+        <v>60366.31</v>
       </c>
       <c r="K38" t="n">
-        <v>58525.25</v>
+        <v>61274.59</v>
       </c>
       <c r="L38" t="n">
-        <v>59714.6</v>
+        <v>62182.86</v>
       </c>
       <c r="M38" t="n">
-        <v>60501</v>
+        <v>64152.71</v>
       </c>
       <c r="N38" t="n">
-        <v>61287.39</v>
+        <v>66122.55</v>
       </c>
       <c r="O38" t="n">
-        <v>62879.7</v>
+        <v>65969.25999999999</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3715,83 +3713,83 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v/>
+      </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>63203.44</v>
+        <v>61299.87</v>
       </c>
       <c r="C39" t="n">
-        <v>63799.32</v>
+        <v>63432.41</v>
       </c>
       <c r="D39" t="n">
-        <v>60937.3</v>
+        <v>59292.25</v>
       </c>
       <c r="E39" t="n">
-        <v>61409.29</v>
+        <v>63339.07</v>
       </c>
       <c r="F39" t="n">
-        <v>-1304.36</v>
+        <v>1929.78</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0314</v>
       </c>
       <c r="H39" t="n">
-        <v>2862.02</v>
+        <v>4140.16</v>
       </c>
       <c r="I39" t="n">
-        <v>57334.9</v>
+        <v>58075.28</v>
       </c>
       <c r="J39" t="n">
-        <v>60366.31</v>
+        <v>58067.76</v>
       </c>
       <c r="K39" t="n">
-        <v>61274.59</v>
+        <v>59978.28</v>
       </c>
       <c r="L39" t="n">
-        <v>62182.86</v>
+        <v>61888.8</v>
       </c>
       <c r="M39" t="n">
-        <v>64152.71</v>
+        <v>62840.3</v>
       </c>
       <c r="N39" t="n">
-        <v>66122.55</v>
+        <v>63791.8</v>
       </c>
       <c r="O39" t="n">
-        <v>65969.25999999999</v>
+        <v>66661.34</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3801,20 +3799,24 @@
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
@@ -3825,57 +3827,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>61299.87</v>
+        <v>63658.95</v>
       </c>
       <c r="C40" t="n">
-        <v>63432.41</v>
+        <v>66505.02</v>
       </c>
       <c r="D40" t="n">
-        <v>59292.25</v>
+        <v>63562.51</v>
       </c>
       <c r="E40" t="n">
-        <v>63339.07</v>
+        <v>66329.5</v>
       </c>
       <c r="F40" t="n">
-        <v>1929.78</v>
+        <v>2990.43</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0314</v>
+        <v>0.0472</v>
       </c>
       <c r="H40" t="n">
-        <v>4140.16</v>
+        <v>2942.51</v>
       </c>
       <c r="I40" t="n">
-        <v>58075.28</v>
+        <v>55152.09</v>
       </c>
       <c r="J40" t="n">
-        <v>58067.76</v>
+        <v>60187.28</v>
       </c>
       <c r="K40" t="n">
-        <v>59978.28</v>
+        <v>61268.99</v>
       </c>
       <c r="L40" t="n">
-        <v>61888.8</v>
+        <v>62350.7</v>
       </c>
       <c r="M40" t="n">
-        <v>62840.3</v>
+        <v>65409.15</v>
       </c>
       <c r="N40" t="n">
-        <v>63791.8</v>
+        <v>68467.60000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>66661.34</v>
+        <v>67572.57000000001</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3883,10 +3885,8 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
@@ -3895,14 +3895,12 @@
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
@@ -3911,59 +3909,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>63658.95</v>
+        <v>66363.42999999999</v>
       </c>
       <c r="C41" t="n">
-        <v>66505.02</v>
+        <v>68786.49000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>63562.51</v>
+        <v>65551.13</v>
       </c>
       <c r="E41" t="n">
-        <v>66329.5</v>
+        <v>66588.12</v>
       </c>
       <c r="F41" t="n">
-        <v>2990.43</v>
+        <v>258.62</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0472</v>
+        <v>0.0039</v>
       </c>
       <c r="H41" t="n">
-        <v>2942.51</v>
+        <v>3235.36</v>
       </c>
       <c r="I41" t="n">
-        <v>55152.09</v>
+        <v>60620</v>
       </c>
       <c r="J41" t="n">
-        <v>60187.28</v>
+        <v>64034.85</v>
       </c>
       <c r="K41" t="n">
-        <v>61268.99</v>
+        <v>64858.24</v>
       </c>
       <c r="L41" t="n">
-        <v>62350.7</v>
+        <v>65681.63</v>
       </c>
       <c r="M41" t="n">
-        <v>65409.15</v>
+        <v>67800.75999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>68467.60000000001</v>
+        <v>69919.88</v>
       </c>
       <c r="O41" t="n">
-        <v>67572.57000000001</v>
+        <v>69447.53999999999</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3976,12 +3970,12 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U41" s="8" t="n">
@@ -4000,69 +3994,71 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>66363.42999999999</v>
+        <v>65947.56</v>
       </c>
       <c r="C42" t="n">
-        <v>68786.49000000001</v>
+        <v>67065.94</v>
       </c>
       <c r="D42" t="n">
-        <v>65551.13</v>
+        <v>62335.75</v>
       </c>
       <c r="E42" t="n">
-        <v>66588.12</v>
+        <v>66020.03999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>258.62</v>
+        <v>-568.08</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0039</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>3235.36</v>
+        <v>4730.19</v>
       </c>
       <c r="I42" t="n">
-        <v>60620</v>
+        <v>62315.77</v>
       </c>
       <c r="J42" t="n">
-        <v>64034.85</v>
+        <v>63062.41</v>
       </c>
       <c r="K42" t="n">
-        <v>64858.24</v>
+        <v>64970.44</v>
       </c>
       <c r="L42" t="n">
-        <v>65681.63</v>
+        <v>66878.46000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>67800.75999999999</v>
+        <v>68205.8</v>
       </c>
       <c r="N42" t="n">
-        <v>69919.88</v>
+        <v>69533.13</v>
       </c>
       <c r="O42" t="n">
-        <v>69447.53999999999</v>
+        <v>72021.85000000001</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4075,141 +4071,143 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>65947.56</v>
+        <v>66783.22</v>
       </c>
       <c r="C43" t="n">
-        <v>67065.94</v>
+        <v>71952.99000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>62335.75</v>
+        <v>66783.22</v>
       </c>
       <c r="E43" t="n">
-        <v>66020.03999999999</v>
+        <v>71250.06</v>
       </c>
       <c r="F43" t="n">
-        <v>-568.08</v>
+        <v>5230.02</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>4730.19</v>
+        <v>5169.77</v>
       </c>
       <c r="I43" t="n">
-        <v>62315.77</v>
+        <v>57605.56</v>
       </c>
       <c r="J43" t="n">
-        <v>63062.41</v>
+        <v>61949.45</v>
       </c>
       <c r="K43" t="n">
-        <v>64970.44</v>
+        <v>63654.95</v>
       </c>
       <c r="L43" t="n">
-        <v>66878.46000000001</v>
+        <v>65360.44</v>
       </c>
       <c r="M43" t="n">
-        <v>68205.8</v>
+        <v>68385.13</v>
       </c>
       <c r="N43" t="n">
-        <v>69533.13</v>
+        <v>71409.82000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>72021.85000000001</v>
+        <v>71796.12</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v/>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>66783.22</v>
+        <v>71067.14999999999</v>
       </c>
       <c r="C44" t="n">
-        <v>71952.99000000001</v>
+        <v>72831.73</v>
       </c>
       <c r="D44" t="n">
-        <v>66783.22</v>
+        <v>68461.10000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>71250.06</v>
+        <v>69360.88</v>
       </c>
       <c r="F44" t="n">
-        <v>5230.02</v>
+        <v>-1889.18</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.07920000000000001</v>
+        <v>-0.0265</v>
       </c>
       <c r="H44" t="n">
-        <v>5169.77</v>
+        <v>4370.62</v>
       </c>
       <c r="I44" t="n">
-        <v>57605.56</v>
+        <v>61613.45</v>
       </c>
       <c r="J44" t="n">
-        <v>61949.45</v>
+        <v>67021.27</v>
       </c>
       <c r="K44" t="n">
-        <v>63654.95</v>
+        <v>68665.17999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>65360.44</v>
+        <v>70309.08</v>
       </c>
       <c r="M44" t="n">
-        <v>68385.13</v>
+        <v>73834.95</v>
       </c>
       <c r="N44" t="n">
-        <v>71409.82000000001</v>
+        <v>77360.81</v>
       </c>
       <c r="O44" t="n">
-        <v>71796.12</v>
+        <v>77122.77</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4217,83 +4215,83 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v/>
       </c>
       <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>71067.14999999999</v>
+        <v>69609.88</v>
       </c>
       <c r="C45" t="n">
-        <v>72831.73</v>
+        <v>71962.34</v>
       </c>
       <c r="D45" t="n">
-        <v>68461.10000000001</v>
+        <v>67609.49000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>69360.88</v>
+        <v>69744.07000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>-1889.18</v>
+        <v>383.19</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0265</v>
+        <v>0.0055</v>
       </c>
       <c r="H45" t="n">
-        <v>4370.62</v>
+        <v>4352.85</v>
       </c>
       <c r="I45" t="n">
-        <v>61613.45</v>
+        <v>64090.48</v>
       </c>
       <c r="J45" t="n">
-        <v>67021.27</v>
+        <v>64347.49</v>
       </c>
       <c r="K45" t="n">
-        <v>68665.17999999999</v>
+        <v>67175.57000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>70309.08</v>
+        <v>70003.64999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>73834.95</v>
+        <v>71546.2</v>
       </c>
       <c r="N45" t="n">
-        <v>77360.81</v>
+        <v>73088.74000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>77122.77</v>
+        <v>77202.35000000001</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4301,18 +4299,18 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R45" s="6" t="n">
+        <v/>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4327,57 +4325,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>69609.88</v>
+        <v>69973.34</v>
       </c>
       <c r="C46" t="n">
-        <v>71962.34</v>
+        <v>70384.59</v>
       </c>
       <c r="D46" t="n">
-        <v>67609.49000000001</v>
+        <v>66819.05</v>
       </c>
       <c r="E46" t="n">
-        <v>69744.07000000001</v>
+        <v>68557.73</v>
       </c>
       <c r="F46" t="n">
-        <v>383.19</v>
+        <v>-1186.34</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0055</v>
+        <v>-0.017</v>
       </c>
       <c r="H46" t="n">
-        <v>4352.85</v>
+        <v>3565.55</v>
       </c>
       <c r="I46" t="n">
-        <v>64090.48</v>
+        <v>63256.64</v>
       </c>
       <c r="J46" t="n">
-        <v>64347.49</v>
+        <v>65370.29</v>
       </c>
       <c r="K46" t="n">
-        <v>67175.57000000001</v>
+        <v>67567.64</v>
       </c>
       <c r="L46" t="n">
-        <v>70003.64999999999</v>
+        <v>69764.99000000001</v>
       </c>
       <c r="M46" t="n">
-        <v>71546.2</v>
+        <v>71920.5</v>
       </c>
       <c r="N46" t="n">
-        <v>73088.74000000001</v>
+        <v>74076</v>
       </c>
       <c r="O46" t="n">
-        <v>77202.35000000001</v>
+        <v>76315.2</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4385,18 +4383,18 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4411,67 +4409,71 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>69973.34</v>
+        <v>68410.63</v>
       </c>
       <c r="C47" t="n">
-        <v>70384.59</v>
+        <v>69078.21000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>66819.05</v>
+        <v>62704.6</v>
       </c>
       <c r="E47" t="n">
-        <v>68557.73</v>
+        <v>64141.12</v>
       </c>
       <c r="F47" t="n">
-        <v>-1186.34</v>
+        <v>-4416.61</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0644</v>
       </c>
       <c r="H47" t="n">
-        <v>3565.55</v>
+        <v>6373.61</v>
       </c>
       <c r="I47" t="n">
-        <v>63256.64</v>
+        <v>63253.5</v>
       </c>
       <c r="J47" t="n">
-        <v>65370.29</v>
+        <v>64970.13</v>
       </c>
       <c r="K47" t="n">
-        <v>67567.64</v>
+        <v>66774.95</v>
       </c>
       <c r="L47" t="n">
-        <v>69764.99000000001</v>
+        <v>68579.77</v>
       </c>
       <c r="M47" t="n">
-        <v>71920.5</v>
+        <v>70340.5</v>
       </c>
       <c r="N47" t="n">
-        <v>74076</v>
+        <v>72101.23</v>
       </c>
       <c r="O47" t="n">
-        <v>76315.2</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
+        <v>73950.14</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
@@ -4488,87 +4490,79 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W47" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>68410.63</v>
+        <v>64544.05</v>
       </c>
       <c r="C48" t="n">
-        <v>69078.21000000001</v>
+        <v>67592.2</v>
       </c>
       <c r="D48" t="n">
-        <v>62704.6</v>
+        <v>64201.03</v>
       </c>
       <c r="E48" t="n">
-        <v>64141.12</v>
+        <v>64611.15</v>
       </c>
       <c r="F48" t="n">
-        <v>-4416.61</v>
+        <v>470.03</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0644</v>
+        <v>0.0073</v>
       </c>
       <c r="H48" t="n">
-        <v>6373.61</v>
+        <v>3391.17</v>
       </c>
       <c r="I48" t="n">
-        <v>63253.5</v>
+        <v>56330.99</v>
       </c>
       <c r="J48" t="n">
-        <v>64970.13</v>
+        <v>56892.37</v>
       </c>
       <c r="K48" t="n">
-        <v>66774.95</v>
+        <v>60954.32</v>
       </c>
       <c r="L48" t="n">
-        <v>68579.77</v>
+        <v>65016.26</v>
       </c>
       <c r="M48" t="n">
-        <v>70340.5</v>
+        <v>67327.92999999999</v>
       </c>
       <c r="N48" t="n">
-        <v>72101.23</v>
+        <v>69639.59</v>
       </c>
       <c r="O48" t="n">
-        <v>73950.14</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>75451.82000000001</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4581,74 +4575,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>64544.05</v>
+        <v>65164.98</v>
       </c>
       <c r="C49" t="n">
-        <v>67592.2</v>
+        <v>65364.73</v>
       </c>
       <c r="D49" t="n">
-        <v>64201.03</v>
+        <v>60448.9</v>
       </c>
       <c r="E49" t="n">
-        <v>64611.15</v>
+        <v>64362.02</v>
       </c>
       <c r="F49" t="n">
-        <v>470.03</v>
+        <v>-249.13</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0073</v>
+        <v>-0.0039</v>
       </c>
       <c r="H49" t="n">
-        <v>3391.17</v>
+        <v>4915.83</v>
       </c>
       <c r="I49" t="n">
-        <v>56330.99</v>
+        <v>60809.86</v>
       </c>
       <c r="J49" t="n">
-        <v>56892.37</v>
+        <v>60577.24</v>
       </c>
       <c r="K49" t="n">
-        <v>60954.32</v>
+        <v>62915.56</v>
       </c>
       <c r="L49" t="n">
-        <v>65016.26</v>
+        <v>65253.88</v>
       </c>
       <c r="M49" t="n">
-        <v>67327.92999999999</v>
+        <v>66306.73</v>
       </c>
       <c r="N49" t="n">
-        <v>69639.59</v>
+        <v>67359.59</v>
       </c>
       <c r="O49" t="n">
-        <v>75451.82000000001</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+        <v>70983.38</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4661,82 +4663,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>65164.98</v>
+        <v>63834.95</v>
       </c>
       <c r="C50" t="n">
-        <v>65364.73</v>
+        <v>66302.52</v>
       </c>
       <c r="D50" t="n">
-        <v>60448.9</v>
+        <v>62703.47</v>
       </c>
       <c r="E50" t="n">
-        <v>64362.02</v>
+        <v>65606.71000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>-249.13</v>
+        <v>1244.69</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0193</v>
       </c>
       <c r="H50" t="n">
-        <v>4915.83</v>
+        <v>3599.05</v>
       </c>
       <c r="I50" t="n">
-        <v>60809.86</v>
+        <v>55533.07</v>
       </c>
       <c r="J50" t="n">
-        <v>60577.24</v>
+        <v>60173.79</v>
       </c>
       <c r="K50" t="n">
-        <v>62915.56</v>
+        <v>61904.1</v>
       </c>
       <c r="L50" t="n">
-        <v>65253.88</v>
+        <v>63634.42</v>
       </c>
       <c r="M50" t="n">
-        <v>66306.73</v>
+        <v>66819.94</v>
       </c>
       <c r="N50" t="n">
-        <v>67359.59</v>
+        <v>70005.45</v>
       </c>
       <c r="O50" t="n">
-        <v>70983.38</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+        <v>70280.56</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4749,55 +4743,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>63834.95</v>
+        <v>65905.10000000001</v>
       </c>
       <c r="C51" t="n">
-        <v>66302.52</v>
+        <v>69608.24000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>62703.47</v>
+        <v>65848.58</v>
       </c>
       <c r="E51" t="n">
-        <v>65606.71000000001</v>
+        <v>68713.8</v>
       </c>
       <c r="F51" t="n">
-        <v>1244.69</v>
+        <v>3107.09</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0193</v>
+        <v>0.0474</v>
       </c>
       <c r="H51" t="n">
-        <v>3599.05</v>
+        <v>3759.66</v>
       </c>
       <c r="I51" t="n">
-        <v>55533.07</v>
+        <v>59104.41</v>
       </c>
       <c r="J51" t="n">
-        <v>60173.79</v>
+        <v>62559.51</v>
       </c>
       <c r="K51" t="n">
-        <v>61904.1</v>
+        <v>63807.18</v>
       </c>
       <c r="L51" t="n">
-        <v>63634.42</v>
+        <v>65054.85</v>
       </c>
       <c r="M51" t="n">
-        <v>66819.94</v>
+        <v>67406.24000000001</v>
       </c>
       <c r="N51" t="n">
-        <v>70005.45</v>
+        <v>69757.62</v>
       </c>
       <c r="O51" t="n">
-        <v>70280.56</v>
+        <v>69901.58</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4815,11 +4813,13 @@
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4838,75 +4838,75 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>65905.10000000001</v>
+        <v>68882.06</v>
       </c>
       <c r="C52" t="n">
-        <v>69608.24000000001</v>
+        <v>69225.57000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>65848.58</v>
+        <v>65133.98</v>
       </c>
       <c r="E52" t="n">
-        <v>68713.8</v>
+        <v>66016.36</v>
       </c>
       <c r="F52" t="n">
-        <v>3107.09</v>
+        <v>-2697.44</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0474</v>
+        <v>-0.0393</v>
       </c>
       <c r="H52" t="n">
-        <v>3759.66</v>
+        <v>4091.59</v>
       </c>
       <c r="I52" t="n">
-        <v>59104.41</v>
+        <v>62088.91</v>
       </c>
       <c r="J52" t="n">
-        <v>62559.51</v>
+        <v>65446.83</v>
       </c>
       <c r="K52" t="n">
-        <v>63807.18</v>
+        <v>66833.96000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>65054.85</v>
+        <v>68221.10000000001</v>
       </c>
       <c r="M52" t="n">
-        <v>67406.24000000001</v>
+        <v>70593.63</v>
       </c>
       <c r="N52" t="n">
-        <v>69757.62</v>
+        <v>72966.14999999999</v>
       </c>
       <c r="O52" t="n">
-        <v>69901.58</v>
+        <v>73367.91</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
+      <c r="Q52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
@@ -4915,76 +4915,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>68882.06</v>
+        <v>65978.95</v>
       </c>
       <c r="C53" t="n">
-        <v>69225.57000000001</v>
+        <v>66954.69</v>
       </c>
       <c r="D53" t="n">
-        <v>65133.98</v>
+        <v>64609.47</v>
       </c>
       <c r="E53" t="n">
-        <v>66016.36</v>
+        <v>66405.56</v>
       </c>
       <c r="F53" t="n">
-        <v>-2697.44</v>
+        <v>389.2</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0393</v>
+        <v>0.0059</v>
       </c>
       <c r="H53" t="n">
-        <v>4091.59</v>
+        <v>2345.22</v>
       </c>
       <c r="I53" t="n">
-        <v>62088.91</v>
+        <v>61042.39</v>
       </c>
       <c r="J53" t="n">
-        <v>65446.83</v>
+        <v>61343.06</v>
       </c>
       <c r="K53" t="n">
-        <v>66833.96000000001</v>
+        <v>63970.56</v>
       </c>
       <c r="L53" t="n">
-        <v>68221.10000000001</v>
+        <v>66598.07000000001</v>
       </c>
       <c r="M53" t="n">
-        <v>70593.63</v>
+        <v>68062.14999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>72966.14999999999</v>
+        <v>69526.24000000001</v>
       </c>
       <c r="O53" t="n">
-        <v>73367.91</v>
+        <v>73317.16</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -5001,68 +4993,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>65978.95</v>
+        <v>65668.50999999999</v>
       </c>
       <c r="C54" t="n">
-        <v>66954.69</v>
+        <v>66525.7</v>
       </c>
       <c r="D54" t="n">
-        <v>64609.47</v>
+        <v>63772.8</v>
       </c>
       <c r="E54" t="n">
-        <v>66405.56</v>
+        <v>65020.94</v>
       </c>
       <c r="F54" t="n">
-        <v>389.2</v>
+        <v>-1384.62</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0209</v>
       </c>
       <c r="H54" t="n">
-        <v>2345.22</v>
+        <v>2752.9</v>
       </c>
       <c r="I54" t="n">
-        <v>61042.39</v>
+        <v>62264.25</v>
       </c>
       <c r="J54" t="n">
-        <v>61343.06</v>
+        <v>64372.09</v>
       </c>
       <c r="K54" t="n">
-        <v>63970.56</v>
+        <v>65232.95</v>
       </c>
       <c r="L54" t="n">
-        <v>66598.07000000001</v>
+        <v>66093.82000000001</v>
       </c>
       <c r="M54" t="n">
-        <v>68062.14999999999</v>
+        <v>67578.17</v>
       </c>
       <c r="N54" t="n">
-        <v>69526.24000000001</v>
+        <v>69062.52</v>
       </c>
       <c r="O54" t="n">
-        <v>73317.16</v>
+        <v>69299.91</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5079,67 +5079,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>65668.50999999999</v>
+        <v>65600.42</v>
       </c>
       <c r="C55" t="n">
-        <v>66525.7</v>
+        <v>66791.84</v>
       </c>
       <c r="D55" t="n">
-        <v>63772.8</v>
+        <v>63208.63</v>
       </c>
       <c r="E55" t="n">
-        <v>65020.94</v>
+        <v>64011.34</v>
       </c>
       <c r="F55" t="n">
-        <v>-1384.62</v>
+        <v>-1009.6</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0209</v>
+        <v>-0.0155</v>
       </c>
       <c r="H55" t="n">
-        <v>2752.9</v>
+        <v>3583.21</v>
       </c>
       <c r="I55" t="n">
-        <v>62264.25</v>
+        <v>61019.9</v>
       </c>
       <c r="J55" t="n">
-        <v>64372.09</v>
+        <v>62203.88</v>
       </c>
       <c r="K55" t="n">
-        <v>65232.95</v>
+        <v>63644.49</v>
       </c>
       <c r="L55" t="n">
-        <v>66093.82000000001</v>
+        <v>65085.1</v>
       </c>
       <c r="M55" t="n">
-        <v>67578.17</v>
+        <v>66397.39</v>
       </c>
       <c r="N55" t="n">
-        <v>69062.52</v>
+        <v>67709.69</v>
       </c>
       <c r="O55" t="n">
-        <v>69299.91</v>
+        <v>69278.61</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q55" s="6" t="n">
+        <v/>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
@@ -5151,8 +5145,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5165,55 +5161,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>65600.42</v>
+        <v>63659.53</v>
       </c>
       <c r="C56" t="n">
-        <v>66791.84</v>
+        <v>65436.57</v>
       </c>
       <c r="D56" t="n">
-        <v>63208.63</v>
+        <v>62726.18</v>
       </c>
       <c r="E56" t="n">
-        <v>64011.34</v>
+        <v>65018.95</v>
       </c>
       <c r="F56" t="n">
-        <v>-1009.6</v>
+        <v>1007.61</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0157</v>
       </c>
       <c r="H56" t="n">
-        <v>3583.21</v>
+        <v>2710.39</v>
       </c>
       <c r="I56" t="n">
-        <v>61019.9</v>
+        <v>59625.41</v>
       </c>
       <c r="J56" t="n">
-        <v>62203.88</v>
+        <v>59933.68</v>
       </c>
       <c r="K56" t="n">
-        <v>63644.49</v>
+        <v>62219.73</v>
       </c>
       <c r="L56" t="n">
-        <v>65085.1</v>
+        <v>64505.79</v>
       </c>
       <c r="M56" t="n">
-        <v>66397.39</v>
+        <v>65802.95</v>
       </c>
       <c r="N56" t="n">
-        <v>67709.69</v>
+        <v>67100.11</v>
       </c>
       <c r="O56" t="n">
-        <v>69278.61</v>
+        <v>70375.06</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5221,20 +5221,16 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5256,50 +5252,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>63659.53</v>
+        <v>65476.44</v>
       </c>
       <c r="C57" t="n">
-        <v>65436.57</v>
+        <v>66410.27</v>
       </c>
       <c r="D57" t="n">
-        <v>62726.18</v>
+        <v>65407.37</v>
       </c>
       <c r="E57" t="n">
-        <v>65018.95</v>
+        <v>66364.2</v>
       </c>
       <c r="F57" t="n">
-        <v>1007.61</v>
+        <v>1345.25</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0157</v>
+        <v>0.0207</v>
       </c>
       <c r="H57" t="n">
-        <v>2710.39</v>
+        <v>1002.9</v>
       </c>
       <c r="I57" t="n">
-        <v>59625.41</v>
+        <v>60015.79</v>
       </c>
       <c r="J57" t="n">
-        <v>59933.68</v>
+        <v>62777.35</v>
       </c>
       <c r="K57" t="n">
-        <v>62219.73</v>
+        <v>63663.75</v>
       </c>
       <c r="L57" t="n">
-        <v>64505.79</v>
+        <v>64550.16</v>
       </c>
       <c r="M57" t="n">
-        <v>65802.95</v>
+        <v>66374.14</v>
       </c>
       <c r="N57" t="n">
-        <v>67100.11</v>
+        <v>68198.13</v>
       </c>
       <c r="O57" t="n">
-        <v>70375.06</v>
+        <v>68146.96000000001</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5312,11 +5308,13 @@
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5330,90 +5328,6 @@
         </is>
       </c>
       <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>65476.44</v>
-      </c>
-      <c r="C58" t="n">
-        <v>66249.11</v>
-      </c>
-      <c r="D58" t="n">
-        <v>65407.37</v>
-      </c>
-      <c r="E58" t="n">
-        <v>65513.99</v>
-      </c>
-      <c r="F58" t="n">
-        <v>495.04</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0076</v>
-      </c>
-      <c r="H58" t="n">
-        <v>841.74</v>
-      </c>
-      <c r="I58" t="n">
-        <v>60015.79</v>
-      </c>
-      <c r="J58" t="n">
-        <v>62777.35</v>
-      </c>
-      <c r="K58" t="n">
-        <v>63663.75</v>
-      </c>
-      <c r="L58" t="n">
-        <v>64550.16</v>
-      </c>
-      <c r="M58" t="n">
-        <v>66374.14</v>
-      </c>
-      <c r="N58" t="n">
-        <v>68198.13</v>
-      </c>
-      <c r="O58" t="n">
-        <v>68146.96000000001</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
         <is>
           <t>強警訊</t>
         </is>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5333,6 +5336,92 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>66505.94</v>
+      </c>
+      <c r="C58" t="n">
+        <v>67034.74000000001</v>
+      </c>
+      <c r="D58" t="n">
+        <v>65877.62</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>1157.12</v>
+      </c>
+      <c r="I58" t="n">
+        <v>64404.47</v>
+      </c>
+      <c r="J58" t="n">
+        <v>65588.99000000001</v>
+      </c>
+      <c r="K58" t="n">
+        <v>65862.75</v>
+      </c>
+      <c r="L58" t="n">
+        <v>66136.50999999999</v>
+      </c>
+      <c r="M58" t="n">
+        <v>66865.64999999999</v>
+      </c>
+      <c r="N58" t="n">
+        <v>67594.8</v>
+      </c>
+      <c r="O58" t="n">
+        <v>67413.17999999999</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,31 +659,33 @@
         <v>1385.77</v>
       </c>
       <c r="I2" t="n">
-        <v>41073.82</v>
+        <v>41446.45</v>
       </c>
       <c r="J2" t="n">
-        <v>41679.14</v>
+        <v>42144.93</v>
       </c>
       <c r="K2" t="n">
-        <v>42186.57</v>
+        <v>42372.88</v>
       </c>
       <c r="L2" t="n">
-        <v>42694</v>
+        <v>42600.84</v>
       </c>
       <c r="M2" t="n">
-        <v>43250.37</v>
+        <v>43064.05</v>
       </c>
       <c r="N2" t="n">
-        <v>43806.74</v>
+        <v>43527.27</v>
       </c>
       <c r="O2" t="n">
-        <v>44265.22</v>
+        <v>43519.96</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -5349,19 +5348,19 @@
         <v>67034.74000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>65877.62</v>
+        <v>64699.49</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>65481.27</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>-882.9299999999999</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>-0.0133</v>
       </c>
       <c r="H58" t="n">
-        <v>1157.12</v>
+        <v>2335.25</v>
       </c>
       <c r="I58" t="n">
         <v>64404.47</v>
@@ -5384,20 +5383,22 @@
       <c r="O58" t="n">
         <v>67413.17999999999</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
@@ -5418,7 +5419,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>1385.77</v>
       </c>
       <c r="I2" t="n">
-        <v>41446.45</v>
+        <v>41711.57</v>
       </c>
       <c r="J2" t="n">
-        <v>42144.93</v>
+        <v>42244.35</v>
       </c>
       <c r="K2" t="n">
-        <v>42372.88</v>
+        <v>42439.16</v>
       </c>
       <c r="L2" t="n">
-        <v>42600.84</v>
+        <v>42633.98</v>
       </c>
       <c r="M2" t="n">
-        <v>43064.05</v>
+        <v>42997.77</v>
       </c>
       <c r="N2" t="n">
-        <v>43527.27</v>
+        <v>43361.57</v>
       </c>
       <c r="O2" t="n">
-        <v>43519.96</v>
+        <v>43387.4</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5351,13 +5351,13 @@
         <v>64699.49</v>
       </c>
       <c r="E58" t="n">
-        <v>65481.27</v>
+        <v>66753.72</v>
       </c>
       <c r="F58" t="n">
-        <v>-882.9299999999999</v>
+        <v>389.52</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0059</v>
       </c>
       <c r="H58" t="n">
         <v>2335.25</v>
@@ -5388,24 +5388,24 @@
       </c>
       <c r="Q58" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>1385.77</v>
       </c>
       <c r="I2" t="n">
-        <v>41711.57</v>
+        <v>41770.79</v>
       </c>
       <c r="J2" t="n">
-        <v>42244.35</v>
+        <v>42266.56</v>
       </c>
       <c r="K2" t="n">
-        <v>42439.16</v>
+        <v>42453.97</v>
       </c>
       <c r="L2" t="n">
-        <v>42633.98</v>
+        <v>42641.38</v>
       </c>
       <c r="M2" t="n">
-        <v>42997.77</v>
+        <v>42982.97</v>
       </c>
       <c r="N2" t="n">
-        <v>43361.57</v>
+        <v>43324.56</v>
       </c>
       <c r="O2" t="n">
-        <v>43387.4</v>
+        <v>43357.79</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5345,22 +5345,22 @@
         <v>66505.94</v>
       </c>
       <c r="C58" t="n">
-        <v>67034.74000000001</v>
+        <v>68995.3</v>
       </c>
       <c r="D58" t="n">
         <v>64699.49</v>
       </c>
       <c r="E58" t="n">
-        <v>66753.72</v>
+        <v>68956.72</v>
       </c>
       <c r="F58" t="n">
-        <v>389.52</v>
+        <v>2592.52</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0391</v>
       </c>
       <c r="H58" t="n">
-        <v>2335.25</v>
+        <v>4295.81</v>
       </c>
       <c r="I58" t="n">
         <v>64404.47</v>
@@ -5403,23 +5403,27 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,63 +634,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42362.71</v>
+        <v>43451.07</v>
       </c>
       <c r="C2" t="n">
-        <v>43220.94</v>
+        <v>44888.02</v>
       </c>
       <c r="D2" t="n">
-        <v>41835.17</v>
+        <v>43343.58</v>
       </c>
       <c r="E2" t="n">
-        <v>43018.75</v>
+        <v>44768.12</v>
       </c>
       <c r="F2" t="n">
-        <v>300.28</v>
+        <v>1749.37</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.007</v>
+        <v>0.0407</v>
       </c>
       <c r="H2" t="n">
-        <v>1385.77</v>
+        <v>1544.44</v>
       </c>
       <c r="I2" t="n">
-        <v>41770.79</v>
+        <v>40449.4</v>
       </c>
       <c r="J2" t="n">
-        <v>42266.56</v>
+        <v>41878.33</v>
       </c>
       <c r="K2" t="n">
-        <v>42453.97</v>
+        <v>42325.87</v>
       </c>
       <c r="L2" t="n">
-        <v>42641.38</v>
+        <v>42773.4</v>
       </c>
       <c r="M2" t="n">
-        <v>42982.97</v>
+        <v>43711.63</v>
       </c>
       <c r="N2" t="n">
-        <v>43324.56</v>
+        <v>44649.87</v>
       </c>
       <c r="O2" t="n">
-        <v>43357.79</v>
+        <v>44606.71</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -699,73 +695,73 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43451.07</v>
+        <v>44948.85</v>
       </c>
       <c r="C3" t="n">
-        <v>44888.02</v>
+        <v>45852.75</v>
       </c>
       <c r="D3" t="n">
-        <v>43343.58</v>
+        <v>44495.46</v>
       </c>
       <c r="E3" t="n">
-        <v>44768.12</v>
+        <v>45045.81</v>
       </c>
       <c r="F3" t="n">
-        <v>1749.37</v>
+        <v>277.69</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0407</v>
+        <v>0.0062</v>
       </c>
       <c r="H3" t="n">
-        <v>1544.44</v>
+        <v>1357.29</v>
       </c>
       <c r="I3" t="n">
-        <v>40449.4</v>
+        <v>41799.14</v>
       </c>
       <c r="J3" t="n">
-        <v>41878.33</v>
+        <v>43549.84</v>
       </c>
       <c r="K3" t="n">
-        <v>42325.87</v>
+        <v>43995.9</v>
       </c>
       <c r="L3" t="n">
-        <v>42773.4</v>
+        <v>44441.96</v>
       </c>
       <c r="M3" t="n">
-        <v>43711.63</v>
+        <v>45540.34</v>
       </c>
       <c r="N3" t="n">
-        <v>44649.87</v>
+        <v>46638.72</v>
       </c>
       <c r="O3" t="n">
-        <v>44606.71</v>
+        <v>46432.46</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -783,18 +779,14 @@
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
@@ -806,50 +798,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44948.85</v>
+        <v>45193.77</v>
       </c>
       <c r="C4" t="n">
-        <v>45852.75</v>
+        <v>45824.69</v>
       </c>
       <c r="D4" t="n">
-        <v>44495.46</v>
+        <v>45193.77</v>
       </c>
       <c r="E4" t="n">
-        <v>45045.81</v>
+        <v>45354.99</v>
       </c>
       <c r="F4" t="n">
-        <v>277.69</v>
+        <v>309.18</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0062</v>
+        <v>0.0069</v>
       </c>
       <c r="H4" t="n">
-        <v>1357.29</v>
+        <v>630.92</v>
       </c>
       <c r="I4" t="n">
-        <v>41799.14</v>
+        <v>43138.17</v>
       </c>
       <c r="J4" t="n">
-        <v>43549.84</v>
+        <v>43624.37</v>
       </c>
       <c r="K4" t="n">
-        <v>43995.9</v>
+        <v>44367.16</v>
       </c>
       <c r="L4" t="n">
-        <v>44441.96</v>
+        <v>45109.96</v>
       </c>
       <c r="M4" t="n">
-        <v>45540.34</v>
+        <v>45724.45</v>
       </c>
       <c r="N4" t="n">
-        <v>46638.72</v>
+        <v>46338.95</v>
       </c>
       <c r="O4" t="n">
-        <v>46432.46</v>
+        <v>47210.04</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -862,12 +854,12 @@
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U4" s="8" t="n">
@@ -881,73 +873,83 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45193.77</v>
+        <v>45113.29</v>
       </c>
       <c r="C5" t="n">
-        <v>45824.69</v>
+        <v>45778.66</v>
       </c>
       <c r="D5" t="n">
-        <v>45193.77</v>
+        <v>44357.65</v>
       </c>
       <c r="E5" t="n">
-        <v>45354.99</v>
+        <v>45769.5</v>
       </c>
       <c r="F5" t="n">
-        <v>309.18</v>
+        <v>414.51</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0091</v>
       </c>
       <c r="H5" t="n">
-        <v>630.92</v>
+        <v>1421.01</v>
       </c>
       <c r="I5" t="n">
-        <v>43138.17</v>
+        <v>44562.85</v>
       </c>
       <c r="J5" t="n">
-        <v>43624.37</v>
+        <v>44646.95</v>
       </c>
       <c r="K5" t="n">
-        <v>44367.16</v>
+        <v>45039.53</v>
       </c>
       <c r="L5" t="n">
-        <v>45109.96</v>
+        <v>45432.11</v>
       </c>
       <c r="M5" t="n">
-        <v>45724.45</v>
+        <v>45670.45</v>
       </c>
       <c r="N5" t="n">
-        <v>46338.95</v>
+        <v>45908.79</v>
       </c>
       <c r="O5" t="n">
-        <v>47210.04</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+        <v>46455.61</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U5" s="8" t="n">
@@ -963,72 +965,66 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45113.29</v>
+        <v>46636.07</v>
       </c>
       <c r="C6" t="n">
-        <v>45778.66</v>
+        <v>48597.08</v>
       </c>
       <c r="D6" t="n">
-        <v>44357.65</v>
+        <v>46592.99</v>
       </c>
       <c r="E6" t="n">
-        <v>45769.5</v>
+        <v>48088.8</v>
       </c>
       <c r="F6" t="n">
-        <v>414.51</v>
+        <v>2319.3</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0507</v>
       </c>
       <c r="H6" t="n">
-        <v>1421.01</v>
+        <v>2004.09</v>
       </c>
       <c r="I6" t="n">
-        <v>44562.85</v>
+        <v>42936.64</v>
       </c>
       <c r="J6" t="n">
-        <v>44646.95</v>
+        <v>44699.16</v>
       </c>
       <c r="K6" t="n">
-        <v>45039.53</v>
+        <v>45058.99</v>
       </c>
       <c r="L6" t="n">
-        <v>45432.11</v>
+        <v>45418.83</v>
       </c>
       <c r="M6" t="n">
-        <v>45670.45</v>
+        <v>46480.01</v>
       </c>
       <c r="N6" t="n">
-        <v>45908.79</v>
+        <v>47541.18</v>
       </c>
       <c r="O6" t="n">
-        <v>46455.61</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>47199.67</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
@@ -1037,73 +1033,73 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>46636.07</v>
+        <v>47446.73</v>
       </c>
       <c r="C7" t="n">
-        <v>48597.08</v>
+        <v>48317.34</v>
       </c>
       <c r="D7" t="n">
-        <v>46592.99</v>
+        <v>46544.05</v>
       </c>
       <c r="E7" t="n">
-        <v>48088.8</v>
+        <v>47582.15</v>
       </c>
       <c r="F7" t="n">
-        <v>2319.3</v>
+        <v>-506.65</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0507</v>
+        <v>-0.0105</v>
       </c>
       <c r="H7" t="n">
-        <v>2004.09</v>
+        <v>1773.29</v>
       </c>
       <c r="I7" t="n">
-        <v>42936.64</v>
+        <v>44588.9</v>
       </c>
       <c r="J7" t="n">
-        <v>44699.16</v>
+        <v>46331.59</v>
       </c>
       <c r="K7" t="n">
-        <v>45058.99</v>
+        <v>47086.76</v>
       </c>
       <c r="L7" t="n">
-        <v>45418.83</v>
+        <v>47841.92</v>
       </c>
       <c r="M7" t="n">
-        <v>46480.01</v>
+        <v>49090.85</v>
       </c>
       <c r="N7" t="n">
-        <v>47541.18</v>
+        <v>50339.77</v>
       </c>
       <c r="O7" t="n">
-        <v>47199.67</v>
+        <v>50601.17</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1111,83 +1107,83 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>47446.73</v>
+        <v>48332.71</v>
       </c>
       <c r="C8" t="n">
-        <v>48317.34</v>
+        <v>49945.95</v>
       </c>
       <c r="D8" t="n">
-        <v>46544.05</v>
+        <v>48254.83</v>
       </c>
       <c r="E8" t="n">
-        <v>47582.15</v>
+        <v>49299.65</v>
       </c>
       <c r="F8" t="n">
-        <v>-506.65</v>
+        <v>1717.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0105</v>
+        <v>0.0361</v>
       </c>
       <c r="H8" t="n">
-        <v>1773.29</v>
+        <v>1691.12</v>
       </c>
       <c r="I8" t="n">
-        <v>44588.9</v>
+        <v>44770.76</v>
       </c>
       <c r="J8" t="n">
-        <v>46331.59</v>
+        <v>45884.59</v>
       </c>
       <c r="K8" t="n">
-        <v>47086.76</v>
+        <v>46695.5</v>
       </c>
       <c r="L8" t="n">
-        <v>47841.92</v>
+        <v>47506.42</v>
       </c>
       <c r="M8" t="n">
-        <v>49090.85</v>
+        <v>48468.79</v>
       </c>
       <c r="N8" t="n">
-        <v>50339.77</v>
+        <v>49431.16</v>
       </c>
       <c r="O8" t="n">
-        <v>50601.17</v>
+        <v>50090.63</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1195,21 +1191,23 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1219,59 +1217,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>48332.71</v>
+        <v>49905.8</v>
       </c>
       <c r="C9" t="n">
-        <v>49945.95</v>
+        <v>52411.34</v>
       </c>
       <c r="D9" t="n">
-        <v>48254.83</v>
+        <v>49838.98</v>
       </c>
       <c r="E9" t="n">
-        <v>49299.65</v>
+        <v>52411.34</v>
       </c>
       <c r="F9" t="n">
-        <v>1717.5</v>
+        <v>3111.69</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0361</v>
+        <v>0.0631</v>
       </c>
       <c r="H9" t="n">
-        <v>1691.12</v>
+        <v>2572.36</v>
       </c>
       <c r="I9" t="n">
-        <v>44770.76</v>
+        <v>46563.71</v>
       </c>
       <c r="J9" t="n">
-        <v>45884.59</v>
+        <v>47708.16</v>
       </c>
       <c r="K9" t="n">
-        <v>46695.5</v>
+        <v>48454.09</v>
       </c>
       <c r="L9" t="n">
-        <v>47506.42</v>
+        <v>49200.02</v>
       </c>
       <c r="M9" t="n">
-        <v>48468.79</v>
+        <v>50145.21</v>
       </c>
       <c r="N9" t="n">
-        <v>49431.16</v>
+        <v>51090.4</v>
       </c>
       <c r="O9" t="n">
-        <v>50090.63</v>
+        <v>51637.07</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1294,11 +1288,13 @@
       </c>
       <c r="U9" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v/>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
@@ -1310,151 +1306,149 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49905.8</v>
+        <v>52294.31</v>
       </c>
       <c r="C10" t="n">
-        <v>52411.34</v>
+        <v>52636.87</v>
       </c>
       <c r="D10" t="n">
-        <v>49838.98</v>
+        <v>49073.58</v>
       </c>
       <c r="E10" t="n">
-        <v>52411.34</v>
+        <v>50276.37</v>
       </c>
       <c r="F10" t="n">
-        <v>3111.69</v>
+        <v>-2134.97</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0631</v>
+        <v>-0.0407</v>
       </c>
       <c r="H10" t="n">
-        <v>2572.36</v>
+        <v>3563.29</v>
       </c>
       <c r="I10" t="n">
-        <v>46563.71</v>
+        <v>47266.62</v>
       </c>
       <c r="J10" t="n">
-        <v>47708.16</v>
+        <v>50482.07</v>
       </c>
       <c r="K10" t="n">
-        <v>48454.09</v>
+        <v>51125.16</v>
       </c>
       <c r="L10" t="n">
-        <v>49200.02</v>
+        <v>51768.25</v>
       </c>
       <c r="M10" t="n">
-        <v>50145.21</v>
+        <v>53697.52</v>
       </c>
       <c r="N10" t="n">
-        <v>51090.4</v>
+        <v>55626.79</v>
       </c>
       <c r="O10" t="n">
-        <v>51637.07</v>
+        <v>54983.7</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
+      <c r="Q10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W10" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W10" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>52294.31</v>
+        <v>50645.27</v>
       </c>
       <c r="C11" t="n">
-        <v>52636.87</v>
+        <v>51513.16</v>
       </c>
       <c r="D11" t="n">
-        <v>49073.58</v>
+        <v>50246.6</v>
       </c>
       <c r="E11" t="n">
-        <v>50276.37</v>
+        <v>50376.53</v>
       </c>
       <c r="F11" t="n">
-        <v>-2134.97</v>
+        <v>100.16</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0407</v>
+        <v>0.002</v>
       </c>
       <c r="H11" t="n">
-        <v>3563.29</v>
+        <v>1266.56</v>
       </c>
       <c r="I11" t="n">
-        <v>47266.62</v>
+        <v>45510.29</v>
       </c>
       <c r="J11" t="n">
-        <v>50482.07</v>
+        <v>46423.65</v>
       </c>
       <c r="K11" t="n">
-        <v>51125.16</v>
+        <v>48494.72</v>
       </c>
       <c r="L11" t="n">
-        <v>51768.25</v>
+        <v>50565.8</v>
       </c>
       <c r="M11" t="n">
-        <v>53697.52</v>
+        <v>52058.02</v>
       </c>
       <c r="N11" t="n">
-        <v>55626.79</v>
+        <v>53550.24</v>
       </c>
       <c r="O11" t="n">
-        <v>54983.7</v>
+        <v>56200.16</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1473,70 +1467,76 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50645.27</v>
+        <v>50282.39</v>
       </c>
       <c r="C12" t="n">
-        <v>51513.16</v>
+        <v>50574.82</v>
       </c>
       <c r="D12" t="n">
-        <v>50246.6</v>
+        <v>48235.3</v>
       </c>
       <c r="E12" t="n">
-        <v>50376.53</v>
+        <v>48625.88</v>
       </c>
       <c r="F12" t="n">
-        <v>100.16</v>
+        <v>-1750.65</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0348</v>
       </c>
       <c r="H12" t="n">
-        <v>1266.56</v>
+        <v>2339.52</v>
       </c>
       <c r="I12" t="n">
-        <v>45510.29</v>
+        <v>48980.04</v>
       </c>
       <c r="J12" t="n">
-        <v>46423.65</v>
+        <v>48858.3</v>
       </c>
       <c r="K12" t="n">
-        <v>48494.72</v>
+        <v>49743.25</v>
       </c>
       <c r="L12" t="n">
-        <v>50565.8</v>
+        <v>50628.21</v>
       </c>
       <c r="M12" t="n">
-        <v>52058.02</v>
+        <v>51009.81</v>
       </c>
       <c r="N12" t="n">
-        <v>53550.24</v>
+        <v>51391.42</v>
       </c>
       <c r="O12" t="n">
-        <v>56200.16</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+        <v>52779.72</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1553,86 +1553,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>50282.39</v>
+        <v>49113.82</v>
       </c>
       <c r="C13" t="n">
-        <v>50574.82</v>
+        <v>50322.14</v>
       </c>
       <c r="D13" t="n">
-        <v>48235.3</v>
+        <v>48511.95</v>
       </c>
       <c r="E13" t="n">
-        <v>48625.88</v>
+        <v>50253.91</v>
       </c>
       <c r="F13" t="n">
-        <v>-1750.65</v>
+        <v>1628.03</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0348</v>
+        <v>0.0335</v>
       </c>
       <c r="H13" t="n">
-        <v>2339.52</v>
+        <v>1810.19</v>
       </c>
       <c r="I13" t="n">
-        <v>48980.04</v>
+        <v>45895.78</v>
       </c>
       <c r="J13" t="n">
-        <v>48858.3</v>
+        <v>45896.77</v>
       </c>
       <c r="K13" t="n">
-        <v>49743.25</v>
+        <v>47456.12</v>
       </c>
       <c r="L13" t="n">
-        <v>50628.21</v>
+        <v>49015.47</v>
       </c>
       <c r="M13" t="n">
-        <v>51009.81</v>
+        <v>49795.64</v>
       </c>
       <c r="N13" t="n">
-        <v>51391.42</v>
+        <v>50575.81</v>
       </c>
       <c r="O13" t="n">
-        <v>52779.72</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
+        <v>52914.34</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
@@ -1641,55 +1635,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>49113.82</v>
+        <v>50318.59</v>
       </c>
       <c r="C14" t="n">
-        <v>50322.14</v>
+        <v>51028.42</v>
       </c>
       <c r="D14" t="n">
-        <v>48511.95</v>
+        <v>49215.96</v>
       </c>
       <c r="E14" t="n">
-        <v>50253.91</v>
+        <v>50491.87</v>
       </c>
       <c r="F14" t="n">
-        <v>1628.03</v>
+        <v>237.96</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0335</v>
+        <v>0.0047</v>
       </c>
       <c r="H14" t="n">
-        <v>1810.19</v>
+        <v>1812.46</v>
       </c>
       <c r="I14" t="n">
-        <v>45895.78</v>
+        <v>46701.76</v>
       </c>
       <c r="J14" t="n">
-        <v>45896.77</v>
+        <v>48862.15</v>
       </c>
       <c r="K14" t="n">
-        <v>47456.12</v>
+        <v>49348.81</v>
       </c>
       <c r="L14" t="n">
-        <v>49015.47</v>
+        <v>49835.48</v>
       </c>
       <c r="M14" t="n">
-        <v>49795.64</v>
+        <v>51159.01</v>
       </c>
       <c r="N14" t="n">
-        <v>50575.81</v>
+        <v>52482.53</v>
       </c>
       <c r="O14" t="n">
-        <v>52914.34</v>
+        <v>52132.33</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1697,23 +1695,21 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1725,57 +1721,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>50318.59</v>
+        <v>50643.09</v>
       </c>
       <c r="C15" t="n">
-        <v>51028.42</v>
+        <v>51127.69</v>
       </c>
       <c r="D15" t="n">
-        <v>49215.96</v>
+        <v>49926.27</v>
       </c>
       <c r="E15" t="n">
-        <v>50491.87</v>
+        <v>50836.55</v>
       </c>
       <c r="F15" t="n">
-        <v>237.96</v>
+        <v>344.68</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0047</v>
+        <v>0.0068</v>
       </c>
       <c r="H15" t="n">
-        <v>1812.46</v>
+        <v>1201.42</v>
       </c>
       <c r="I15" t="n">
-        <v>46701.76</v>
+        <v>47403.5</v>
       </c>
       <c r="J15" t="n">
-        <v>48862.15</v>
+        <v>48864.25</v>
       </c>
       <c r="K15" t="n">
-        <v>49348.81</v>
+        <v>49585.64</v>
       </c>
       <c r="L15" t="n">
-        <v>49835.48</v>
+        <v>50307.03</v>
       </c>
       <c r="M15" t="n">
-        <v>51159.01</v>
+        <v>51398.1</v>
       </c>
       <c r="N15" t="n">
-        <v>52482.53</v>
+        <v>52489.17</v>
       </c>
       <c r="O15" t="n">
-        <v>52132.33</v>
+        <v>52840.88</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1783,10 +1779,8 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R15" s="6" t="n">
+        <v/>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
@@ -1816,63 +1810,69 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>50643.09</v>
+        <v>50352.09</v>
       </c>
       <c r="C16" t="n">
-        <v>51127.69</v>
+        <v>50432.1</v>
       </c>
       <c r="D16" t="n">
-        <v>49926.27</v>
+        <v>48643.78</v>
       </c>
       <c r="E16" t="n">
-        <v>50836.55</v>
+        <v>49507.21</v>
       </c>
       <c r="F16" t="n">
-        <v>344.68</v>
+        <v>-1329.34</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0261</v>
       </c>
       <c r="H16" t="n">
-        <v>1201.42</v>
+        <v>1788.32</v>
       </c>
       <c r="I16" t="n">
-        <v>47403.5</v>
+        <v>48724.85</v>
       </c>
       <c r="J16" t="n">
-        <v>48864.25</v>
+        <v>49789.91</v>
       </c>
       <c r="K16" t="n">
-        <v>49585.64</v>
+        <v>50235.84</v>
       </c>
       <c r="L16" t="n">
-        <v>50307.03</v>
+        <v>50681.77</v>
       </c>
       <c r="M16" t="n">
-        <v>51398.1</v>
+        <v>51437.26</v>
       </c>
       <c r="N16" t="n">
-        <v>52489.17</v>
+        <v>52192.76</v>
       </c>
       <c r="O16" t="n">
-        <v>52840.88</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>52329.11</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1889,83 +1889,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>50352.09</v>
+        <v>50084.55</v>
       </c>
       <c r="C17" t="n">
-        <v>50432.1</v>
+        <v>50941.89</v>
       </c>
       <c r="D17" t="n">
-        <v>48643.78</v>
+        <v>49982.2</v>
       </c>
       <c r="E17" t="n">
-        <v>49507.21</v>
+        <v>50750.39</v>
       </c>
       <c r="F17" t="n">
-        <v>-1329.34</v>
+        <v>1243.18</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0261</v>
+        <v>0.0251</v>
       </c>
       <c r="H17" t="n">
-        <v>1788.32</v>
+        <v>959.6900000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>48724.85</v>
+        <v>46855.46</v>
       </c>
       <c r="J17" t="n">
-        <v>49789.91</v>
+        <v>47703.53</v>
       </c>
       <c r="K17" t="n">
-        <v>50235.84</v>
+        <v>48613.05</v>
       </c>
       <c r="L17" t="n">
-        <v>50681.77</v>
+        <v>49522.58</v>
       </c>
       <c r="M17" t="n">
-        <v>51437.26</v>
+        <v>50401.37</v>
       </c>
       <c r="N17" t="n">
-        <v>52192.76</v>
+        <v>51280.17</v>
       </c>
       <c r="O17" t="n">
-        <v>52329.11</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
+        <v>52220.42</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
@@ -1977,55 +1969,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50084.55</v>
+        <v>50691.22</v>
       </c>
       <c r="C18" t="n">
-        <v>50941.89</v>
+        <v>50707.23</v>
       </c>
       <c r="D18" t="n">
-        <v>49982.2</v>
+        <v>50198.97</v>
       </c>
       <c r="E18" t="n">
-        <v>50750.39</v>
+        <v>50339.48</v>
       </c>
       <c r="F18" t="n">
-        <v>1243.18</v>
+        <v>-410.91</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0251</v>
+        <v>-0.0081</v>
       </c>
       <c r="H18" t="n">
-        <v>959.6900000000001</v>
+        <v>508.26</v>
       </c>
       <c r="I18" t="n">
-        <v>46855.46</v>
+        <v>49022.51</v>
       </c>
       <c r="J18" t="n">
-        <v>47703.53</v>
+        <v>49934.87</v>
       </c>
       <c r="K18" t="n">
-        <v>48613.05</v>
+        <v>50270.54</v>
       </c>
       <c r="L18" t="n">
-        <v>49522.58</v>
+        <v>50606.22</v>
       </c>
       <c r="M18" t="n">
-        <v>50401.37</v>
+        <v>51230.24</v>
       </c>
       <c r="N18" t="n">
-        <v>51280.17</v>
+        <v>51854.25</v>
       </c>
       <c r="O18" t="n">
-        <v>52220.42</v>
+        <v>51901.58</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2033,19 +2029,19 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
@@ -2059,57 +2055,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>50691.22</v>
+        <v>51010.28</v>
       </c>
       <c r="C19" t="n">
-        <v>50707.23</v>
+        <v>52523.77</v>
       </c>
       <c r="D19" t="n">
-        <v>50198.97</v>
+        <v>50995.67</v>
       </c>
       <c r="E19" t="n">
-        <v>50339.48</v>
+        <v>51939.89</v>
       </c>
       <c r="F19" t="n">
-        <v>-410.91</v>
+        <v>1600.41</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0081</v>
+        <v>0.0318</v>
       </c>
       <c r="H19" t="n">
-        <v>508.26</v>
+        <v>1528.1</v>
       </c>
       <c r="I19" t="n">
-        <v>49022.51</v>
+        <v>49690.71</v>
       </c>
       <c r="J19" t="n">
-        <v>49934.87</v>
+        <v>49774.41</v>
       </c>
       <c r="K19" t="n">
-        <v>50270.54</v>
+        <v>50085.35</v>
       </c>
       <c r="L19" t="n">
-        <v>50606.22</v>
+        <v>50396.29</v>
       </c>
       <c r="M19" t="n">
-        <v>51230.24</v>
+        <v>50593.61</v>
       </c>
       <c r="N19" t="n">
-        <v>51854.25</v>
+        <v>50790.93</v>
       </c>
       <c r="O19" t="n">
-        <v>51901.58</v>
+        <v>51215.49</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2117,83 +2113,83 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W19" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>51010.28</v>
+        <v>52808.29</v>
       </c>
       <c r="C20" t="n">
-        <v>52523.77</v>
+        <v>54487.32</v>
       </c>
       <c r="D20" t="n">
-        <v>50995.67</v>
+        <v>52741.64</v>
       </c>
       <c r="E20" t="n">
-        <v>51939.89</v>
+        <v>53936.17</v>
       </c>
       <c r="F20" t="n">
-        <v>1600.41</v>
+        <v>1996.28</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0318</v>
+        <v>0.0384</v>
       </c>
       <c r="H20" t="n">
-        <v>1528.1</v>
+        <v>1745.68</v>
       </c>
       <c r="I20" t="n">
-        <v>49690.71</v>
+        <v>49467.57</v>
       </c>
       <c r="J20" t="n">
-        <v>49774.41</v>
+        <v>50501.88</v>
       </c>
       <c r="K20" t="n">
-        <v>50085.35</v>
+        <v>51175.84</v>
       </c>
       <c r="L20" t="n">
-        <v>50396.29</v>
+        <v>51849.81</v>
       </c>
       <c r="M20" t="n">
-        <v>50593.61</v>
+        <v>52703.94</v>
       </c>
       <c r="N20" t="n">
-        <v>50790.93</v>
+        <v>53558.07</v>
       </c>
       <c r="O20" t="n">
-        <v>51215.49</v>
+        <v>54051.87</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2234,151 +2230,151 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>52808.29</v>
+        <v>53390.05</v>
       </c>
       <c r="C21" t="n">
-        <v>54487.32</v>
+        <v>54050.84</v>
       </c>
       <c r="D21" t="n">
-        <v>52741.64</v>
+        <v>52194.81</v>
       </c>
       <c r="E21" t="n">
-        <v>53936.17</v>
+        <v>53846.87</v>
       </c>
       <c r="F21" t="n">
-        <v>1996.28</v>
+        <v>-89.3</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0384</v>
+        <v>-0.0017</v>
       </c>
       <c r="H21" t="n">
-        <v>1745.68</v>
+        <v>1856.03</v>
       </c>
       <c r="I21" t="n">
-        <v>49467.57</v>
+        <v>50995.96</v>
       </c>
       <c r="J21" t="n">
-        <v>50501.88</v>
+        <v>52351.34</v>
       </c>
       <c r="K21" t="n">
-        <v>51175.84</v>
+        <v>53063.33</v>
       </c>
       <c r="L21" t="n">
-        <v>51849.81</v>
+        <v>53775.33</v>
       </c>
       <c r="M21" t="n">
-        <v>52703.94</v>
+        <v>54809.01</v>
       </c>
       <c r="N21" t="n">
-        <v>53558.07</v>
+        <v>55842.7</v>
       </c>
       <c r="O21" t="n">
-        <v>54051.87</v>
+        <v>56233</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>53390.05</v>
+        <v>53023.28</v>
       </c>
       <c r="C22" t="n">
-        <v>54050.84</v>
+        <v>53742.69</v>
       </c>
       <c r="D22" t="n">
-        <v>52194.81</v>
+        <v>52637.66</v>
       </c>
       <c r="E22" t="n">
-        <v>53846.87</v>
+        <v>53322.85</v>
       </c>
       <c r="F22" t="n">
-        <v>-89.3</v>
+        <v>-524.02</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0097</v>
       </c>
       <c r="H22" t="n">
-        <v>1856.03</v>
+        <v>1105.03</v>
       </c>
       <c r="I22" t="n">
-        <v>50995.96</v>
+        <v>50338.78</v>
       </c>
       <c r="J22" t="n">
-        <v>52351.34</v>
+        <v>52352.86</v>
       </c>
       <c r="K22" t="n">
-        <v>53063.33</v>
+        <v>52918.86</v>
       </c>
       <c r="L22" t="n">
-        <v>53775.33</v>
+        <v>53484.85</v>
       </c>
       <c r="M22" t="n">
-        <v>54809.01</v>
+        <v>54774.89</v>
       </c>
       <c r="N22" t="n">
-        <v>55842.7</v>
+        <v>56064.93</v>
       </c>
       <c r="O22" t="n">
-        <v>56233</v>
+        <v>55906.87</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q22" s="6" t="n">
+        <v/>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2397,57 +2393,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>53023.28</v>
+        <v>53575.37</v>
       </c>
       <c r="C23" t="n">
-        <v>53742.69</v>
+        <v>54782.83</v>
       </c>
       <c r="D23" t="n">
-        <v>52637.66</v>
+        <v>52655.18</v>
       </c>
       <c r="E23" t="n">
-        <v>53322.85</v>
+        <v>54253.68</v>
       </c>
       <c r="F23" t="n">
-        <v>-524.02</v>
+        <v>930.83</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0175</v>
       </c>
       <c r="H23" t="n">
-        <v>1105.03</v>
+        <v>2127.65</v>
       </c>
       <c r="I23" t="n">
-        <v>50338.78</v>
+        <v>51532.63</v>
       </c>
       <c r="J23" t="n">
-        <v>52352.86</v>
+        <v>52284.16</v>
       </c>
       <c r="K23" t="n">
-        <v>52918.86</v>
+        <v>52770.34</v>
       </c>
       <c r="L23" t="n">
-        <v>53484.85</v>
+        <v>53256.51</v>
       </c>
       <c r="M23" t="n">
-        <v>54774.89</v>
+        <v>53875.37</v>
       </c>
       <c r="N23" t="n">
-        <v>56064.93</v>
+        <v>54494.22</v>
       </c>
       <c r="O23" t="n">
-        <v>55906.87</v>
+        <v>54847.72</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2460,16 +2456,20 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2479,59 +2479,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>53575.37</v>
+        <v>55130.63</v>
       </c>
       <c r="C24" t="n">
-        <v>54782.83</v>
+        <v>58015.08</v>
       </c>
       <c r="D24" t="n">
-        <v>52655.18</v>
+        <v>55018.57</v>
       </c>
       <c r="E24" t="n">
-        <v>54253.68</v>
+        <v>56941.97</v>
       </c>
       <c r="F24" t="n">
-        <v>930.83</v>
+        <v>2688.29</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0496</v>
       </c>
       <c r="H24" t="n">
-        <v>2127.65</v>
+        <v>2996.51</v>
       </c>
       <c r="I24" t="n">
-        <v>51532.63</v>
+        <v>50527.53</v>
       </c>
       <c r="J24" t="n">
-        <v>52284.16</v>
+        <v>52393.37</v>
       </c>
       <c r="K24" t="n">
-        <v>52770.34</v>
+        <v>53189.86</v>
       </c>
       <c r="L24" t="n">
-        <v>53256.51</v>
+        <v>53986.34</v>
       </c>
       <c r="M24" t="n">
-        <v>53875.37</v>
+        <v>55317.5</v>
       </c>
       <c r="N24" t="n">
-        <v>54494.22</v>
+        <v>56648.67</v>
       </c>
       <c r="O24" t="n">
-        <v>54847.72</v>
+        <v>56910.48</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2539,10 +2535,8 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R24" s="6" t="n">
+        <v/>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
@@ -2556,11 +2550,13 @@
       </c>
       <c r="U24" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
@@ -2572,50 +2568,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>55130.63</v>
+        <v>57212.97</v>
       </c>
       <c r="C25" t="n">
-        <v>58015.08</v>
+        <v>57709.82</v>
       </c>
       <c r="D25" t="n">
-        <v>55018.57</v>
+        <v>56135.12</v>
       </c>
       <c r="E25" t="n">
-        <v>56941.97</v>
+        <v>56825.7</v>
       </c>
       <c r="F25" t="n">
-        <v>2688.29</v>
+        <v>-116.27</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0496</v>
+        <v>-0.002</v>
       </c>
       <c r="H25" t="n">
-        <v>2996.51</v>
+        <v>1574.7</v>
       </c>
       <c r="I25" t="n">
-        <v>50527.53</v>
+        <v>52022.06</v>
       </c>
       <c r="J25" t="n">
-        <v>52393.37</v>
+        <v>54158.03</v>
       </c>
       <c r="K25" t="n">
-        <v>53189.86</v>
+        <v>55443.71</v>
       </c>
       <c r="L25" t="n">
-        <v>53986.34</v>
+        <v>56729.4</v>
       </c>
       <c r="M25" t="n">
-        <v>55317.5</v>
+        <v>58440.22</v>
       </c>
       <c r="N25" t="n">
-        <v>56648.67</v>
+        <v>60151.05</v>
       </c>
       <c r="O25" t="n">
-        <v>56910.48</v>
+        <v>61011.59</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2628,78 +2624,76 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>57212.97</v>
+        <v>56764.14</v>
       </c>
       <c r="C26" t="n">
-        <v>57709.82</v>
+        <v>59332.43</v>
       </c>
       <c r="D26" t="n">
-        <v>56135.12</v>
+        <v>56732.93</v>
       </c>
       <c r="E26" t="n">
-        <v>56825.7</v>
+        <v>58850.27</v>
       </c>
       <c r="F26" t="n">
-        <v>-116.27</v>
+        <v>2024.57</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0356</v>
       </c>
       <c r="H26" t="n">
-        <v>1574.7</v>
+        <v>2599.5</v>
       </c>
       <c r="I26" t="n">
-        <v>52022.06</v>
+        <v>54560.42</v>
       </c>
       <c r="J26" t="n">
-        <v>54158.03</v>
+        <v>55202.61</v>
       </c>
       <c r="K26" t="n">
-        <v>55443.71</v>
+        <v>56038.35</v>
       </c>
       <c r="L26" t="n">
-        <v>56729.4</v>
+        <v>56874.08</v>
       </c>
       <c r="M26" t="n">
-        <v>58440.22</v>
+        <v>57613.05</v>
       </c>
       <c r="N26" t="n">
-        <v>60151.05</v>
+        <v>58352.01</v>
       </c>
       <c r="O26" t="n">
-        <v>61011.59</v>
+        <v>59284.52</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2712,109 +2706,111 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>56764.14</v>
+        <v>57976.2</v>
       </c>
       <c r="C27" t="n">
-        <v>59332.43</v>
+        <v>58365.21</v>
       </c>
       <c r="D27" t="n">
-        <v>56732.93</v>
+        <v>53618.2</v>
       </c>
       <c r="E27" t="n">
-        <v>58850.27</v>
+        <v>55620.84</v>
       </c>
       <c r="F27" t="n">
-        <v>2024.57</v>
+        <v>-3229.43</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0356</v>
+        <v>-0.0549</v>
       </c>
       <c r="H27" t="n">
-        <v>2599.5</v>
+        <v>4747.01</v>
       </c>
       <c r="I27" t="n">
-        <v>54560.42</v>
+        <v>54133.43</v>
       </c>
       <c r="J27" t="n">
-        <v>55202.61</v>
+        <v>56659.56</v>
       </c>
       <c r="K27" t="n">
-        <v>56038.35</v>
+        <v>57550.52</v>
       </c>
       <c r="L27" t="n">
-        <v>56874.08</v>
+        <v>58441.47</v>
       </c>
       <c r="M27" t="n">
-        <v>57613.05</v>
+        <v>60150.02</v>
       </c>
       <c r="N27" t="n">
-        <v>58352.01</v>
+        <v>61858.56</v>
       </c>
       <c r="O27" t="n">
-        <v>59284.52</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
+        <v>61931.93</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W27" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W27" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr"/>
@@ -2822,64 +2818,60 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>57976.2</v>
+        <v>54608.63</v>
       </c>
       <c r="C28" t="n">
-        <v>58365.21</v>
+        <v>55745.38</v>
       </c>
       <c r="D28" t="n">
-        <v>53618.2</v>
+        <v>51407.66</v>
       </c>
       <c r="E28" t="n">
-        <v>55620.84</v>
+        <v>53819.61</v>
       </c>
       <c r="F28" t="n">
-        <v>-3229.43</v>
+        <v>-1801.23</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0549</v>
+        <v>-0.0324</v>
       </c>
       <c r="H28" t="n">
-        <v>4747.01</v>
+        <v>4337.72</v>
       </c>
       <c r="I28" t="n">
-        <v>54133.43</v>
+        <v>48871.19</v>
       </c>
       <c r="J28" t="n">
-        <v>56659.56</v>
+        <v>50688.4</v>
       </c>
       <c r="K28" t="n">
-        <v>57550.52</v>
+        <v>53247.33</v>
       </c>
       <c r="L28" t="n">
-        <v>58441.47</v>
+        <v>55806.27</v>
       </c>
       <c r="M28" t="n">
-        <v>60150.02</v>
+        <v>57994.35</v>
       </c>
       <c r="N28" t="n">
-        <v>61858.56</v>
+        <v>60182.42</v>
       </c>
       <c r="O28" t="n">
-        <v>61931.93</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q28" s="6" t="inlineStr">
+        <v>63112.22</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
@@ -2906,50 +2898,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>54608.63</v>
+        <v>53627.86</v>
       </c>
       <c r="C29" t="n">
-        <v>55745.38</v>
+        <v>55239.4</v>
       </c>
       <c r="D29" t="n">
-        <v>51407.66</v>
+        <v>53113.95</v>
       </c>
       <c r="E29" t="n">
-        <v>53819.61</v>
+        <v>53372.53</v>
       </c>
       <c r="F29" t="n">
-        <v>-1801.23</v>
+        <v>-447.08</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0324</v>
+        <v>-0.0083</v>
       </c>
       <c r="H29" t="n">
-        <v>4337.72</v>
+        <v>2125.45</v>
       </c>
       <c r="I29" t="n">
-        <v>48871.19</v>
+        <v>47069.94</v>
       </c>
       <c r="J29" t="n">
-        <v>50688.4</v>
+        <v>49603.44</v>
       </c>
       <c r="K29" t="n">
-        <v>53247.33</v>
+        <v>51650.75</v>
       </c>
       <c r="L29" t="n">
-        <v>55806.27</v>
+        <v>53698.06</v>
       </c>
       <c r="M29" t="n">
-        <v>57994.35</v>
+        <v>55988.47</v>
       </c>
       <c r="N29" t="n">
-        <v>60182.42</v>
+        <v>58278.87</v>
       </c>
       <c r="O29" t="n">
-        <v>63112.22</v>
+        <v>60083.1</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2957,14 +2949,12 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R29" s="6" t="n">
+        <v/>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2981,64 +2971,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>53627.86</v>
+        <v>52468.72</v>
       </c>
       <c r="C30" t="n">
-        <v>55239.4</v>
+        <v>54175.8</v>
       </c>
       <c r="D30" t="n">
-        <v>53113.95</v>
+        <v>50688.76</v>
       </c>
       <c r="E30" t="n">
-        <v>53372.53</v>
+        <v>53373.07</v>
       </c>
       <c r="F30" t="n">
-        <v>-447.08</v>
+        <v>0.54</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0083</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2125.45</v>
+        <v>3487.04</v>
       </c>
       <c r="I30" t="n">
-        <v>47069.94</v>
+        <v>50988.5</v>
       </c>
       <c r="J30" t="n">
-        <v>49603.44</v>
+        <v>50845.01</v>
       </c>
       <c r="K30" t="n">
-        <v>51650.75</v>
+        <v>52309.81</v>
       </c>
       <c r="L30" t="n">
-        <v>53698.06</v>
+        <v>53774.6</v>
       </c>
       <c r="M30" t="n">
-        <v>55988.47</v>
+        <v>54435.26</v>
       </c>
       <c r="N30" t="n">
-        <v>58278.87</v>
+        <v>55095.91</v>
       </c>
       <c r="O30" t="n">
-        <v>60083.1</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+        <v>57364.85</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
@@ -3068,69 +3068,65 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>52468.72</v>
+        <v>52054.68</v>
       </c>
       <c r="C31" t="n">
-        <v>54175.8</v>
+        <v>54258.48</v>
       </c>
       <c r="D31" t="n">
-        <v>50688.76</v>
+        <v>50558.91</v>
       </c>
       <c r="E31" t="n">
-        <v>53373.07</v>
+        <v>53123.49</v>
       </c>
       <c r="F31" t="n">
-        <v>0.54</v>
+        <v>-249.58</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0</v>
+        <v>-0.0047</v>
       </c>
       <c r="H31" t="n">
-        <v>3487.04</v>
+        <v>3699.57</v>
       </c>
       <c r="I31" t="n">
-        <v>50988.5</v>
+        <v>47201.72</v>
       </c>
       <c r="J31" t="n">
-        <v>50845.01</v>
+        <v>50356.43</v>
       </c>
       <c r="K31" t="n">
-        <v>52309.81</v>
+        <v>51629.55</v>
       </c>
       <c r="L31" t="n">
-        <v>53774.6</v>
+        <v>52902.68</v>
       </c>
       <c r="M31" t="n">
-        <v>54435.26</v>
+        <v>55116.59</v>
       </c>
       <c r="N31" t="n">
-        <v>55095.91</v>
+        <v>57330.5</v>
       </c>
       <c r="O31" t="n">
-        <v>57364.85</v>
-      </c>
-      <c r="P31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>57662.84</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v/>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3156,50 +3152,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>52054.68</v>
+        <v>53205.93</v>
       </c>
       <c r="C32" t="n">
-        <v>54258.48</v>
+        <v>57012.77</v>
       </c>
       <c r="D32" t="n">
-        <v>50558.91</v>
+        <v>53156.94</v>
       </c>
       <c r="E32" t="n">
-        <v>53123.49</v>
+        <v>56924.11</v>
       </c>
       <c r="F32" t="n">
-        <v>-249.58</v>
+        <v>3800.62</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0047</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>3699.57</v>
+        <v>3855.83</v>
       </c>
       <c r="I32" t="n">
-        <v>47201.72</v>
+        <v>46859.34</v>
       </c>
       <c r="J32" t="n">
-        <v>50356.43</v>
+        <v>49781.31</v>
       </c>
       <c r="K32" t="n">
-        <v>51629.55</v>
+        <v>51273.7</v>
       </c>
       <c r="L32" t="n">
-        <v>52902.68</v>
+        <v>52766.09</v>
       </c>
       <c r="M32" t="n">
-        <v>55116.59</v>
+        <v>54973.27</v>
       </c>
       <c r="N32" t="n">
-        <v>57330.5</v>
+        <v>57180.46</v>
       </c>
       <c r="O32" t="n">
-        <v>57662.84</v>
+        <v>57958.05</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3207,21 +3203,23 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R32" s="6" t="n">
+        <v/>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3233,57 +3231,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>53205.93</v>
+        <v>56421.46</v>
       </c>
       <c r="C33" t="n">
-        <v>57012.77</v>
+        <v>59688.1</v>
       </c>
       <c r="D33" t="n">
-        <v>53156.94</v>
+        <v>56232.78</v>
       </c>
       <c r="E33" t="n">
-        <v>56924.11</v>
+        <v>58475.9</v>
       </c>
       <c r="F33" t="n">
-        <v>3800.62</v>
+        <v>1551.79</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0273</v>
       </c>
       <c r="H33" t="n">
-        <v>3855.83</v>
+        <v>3455.32</v>
       </c>
       <c r="I33" t="n">
-        <v>46859.34</v>
+        <v>49301.11</v>
       </c>
       <c r="J33" t="n">
-        <v>49781.31</v>
+        <v>53987.91</v>
       </c>
       <c r="K33" t="n">
-        <v>51273.7</v>
+        <v>54996.2</v>
       </c>
       <c r="L33" t="n">
-        <v>52766.09</v>
+        <v>56004.48</v>
       </c>
       <c r="M33" t="n">
-        <v>54973.27</v>
+        <v>58852.02</v>
       </c>
       <c r="N33" t="n">
-        <v>57180.46</v>
+        <v>61699.56</v>
       </c>
       <c r="O33" t="n">
-        <v>57958.05</v>
+        <v>60868.6</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3301,13 +3299,11 @@
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3326,50 +3322,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>56421.46</v>
+        <v>58821.16</v>
       </c>
       <c r="C34" t="n">
-        <v>59688.1</v>
+        <v>60013.98</v>
       </c>
       <c r="D34" t="n">
-        <v>56232.78</v>
+        <v>58621.48</v>
       </c>
       <c r="E34" t="n">
-        <v>58475.9</v>
+        <v>59716.18</v>
       </c>
       <c r="F34" t="n">
-        <v>1551.79</v>
+        <v>1240.28</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0273</v>
+        <v>0.0212</v>
       </c>
       <c r="H34" t="n">
-        <v>3455.32</v>
+        <v>1392.5</v>
       </c>
       <c r="I34" t="n">
-        <v>49301.11</v>
+        <v>52777.46</v>
       </c>
       <c r="J34" t="n">
-        <v>53987.91</v>
+        <v>55278.31</v>
       </c>
       <c r="K34" t="n">
-        <v>54996.2</v>
+        <v>56748.24</v>
       </c>
       <c r="L34" t="n">
-        <v>56004.48</v>
+        <v>58218.17</v>
       </c>
       <c r="M34" t="n">
-        <v>58852.02</v>
+        <v>60203.56</v>
       </c>
       <c r="N34" t="n">
-        <v>61699.56</v>
+        <v>62188.95</v>
       </c>
       <c r="O34" t="n">
-        <v>60868.6</v>
+        <v>63143.42</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3410,50 +3406,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>58821.16</v>
+        <v>59880.71</v>
       </c>
       <c r="C35" t="n">
-        <v>60013.98</v>
+        <v>60903.95</v>
       </c>
       <c r="D35" t="n">
-        <v>58621.48</v>
+        <v>58928.2</v>
       </c>
       <c r="E35" t="n">
-        <v>59716.18</v>
+        <v>59513.12</v>
       </c>
       <c r="F35" t="n">
-        <v>1240.28</v>
+        <v>-203.06</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0034</v>
       </c>
       <c r="H35" t="n">
-        <v>1392.5</v>
+        <v>1975.75</v>
       </c>
       <c r="I35" t="n">
-        <v>52777.46</v>
+        <v>57228.98</v>
       </c>
       <c r="J35" t="n">
-        <v>55278.31</v>
+        <v>58522.9</v>
       </c>
       <c r="K35" t="n">
-        <v>56748.24</v>
+        <v>59019.93</v>
       </c>
       <c r="L35" t="n">
-        <v>58218.17</v>
+        <v>59516.96</v>
       </c>
       <c r="M35" t="n">
-        <v>60203.56</v>
+        <v>60412.43</v>
       </c>
       <c r="N35" t="n">
-        <v>62188.95</v>
+        <v>61307.9</v>
       </c>
       <c r="O35" t="n">
-        <v>63143.42</v>
+        <v>61406.48</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3461,17 +3457,19 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U35" s="8" t="n">
@@ -3487,57 +3485,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>59880.71</v>
+        <v>60241.31</v>
       </c>
       <c r="C36" t="n">
-        <v>60903.95</v>
+        <v>63091.14</v>
       </c>
       <c r="D36" t="n">
-        <v>58928.2</v>
+        <v>60213.02</v>
       </c>
       <c r="E36" t="n">
-        <v>59513.12</v>
+        <v>62713.65</v>
       </c>
       <c r="F36" t="n">
-        <v>-203.06</v>
+        <v>3200.53</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0538</v>
       </c>
       <c r="H36" t="n">
-        <v>1975.75</v>
+        <v>2878.12</v>
       </c>
       <c r="I36" t="n">
-        <v>57228.98</v>
+        <v>56952.45</v>
       </c>
       <c r="J36" t="n">
-        <v>58522.9</v>
+        <v>57335.89</v>
       </c>
       <c r="K36" t="n">
-        <v>59019.93</v>
+        <v>58525.25</v>
       </c>
       <c r="L36" t="n">
-        <v>59516.96</v>
+        <v>59714.6</v>
       </c>
       <c r="M36" t="n">
-        <v>60412.43</v>
+        <v>60501</v>
       </c>
       <c r="N36" t="n">
-        <v>61307.9</v>
+        <v>61287.39</v>
       </c>
       <c r="O36" t="n">
-        <v>61406.48</v>
+        <v>62879.7</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3545,14 +3543,12 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
@@ -3560,70 +3556,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W36" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W36" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>60241.31</v>
+        <v>63203.44</v>
       </c>
       <c r="C37" t="n">
-        <v>63091.14</v>
+        <v>63799.32</v>
       </c>
       <c r="D37" t="n">
-        <v>60213.02</v>
+        <v>60937.3</v>
       </c>
       <c r="E37" t="n">
-        <v>62713.65</v>
+        <v>61409.29</v>
       </c>
       <c r="F37" t="n">
-        <v>3200.53</v>
+        <v>-1304.36</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0538</v>
+        <v>-0.0208</v>
       </c>
       <c r="H37" t="n">
-        <v>2878.12</v>
+        <v>2862.02</v>
       </c>
       <c r="I37" t="n">
-        <v>56952.45</v>
+        <v>57334.9</v>
       </c>
       <c r="J37" t="n">
-        <v>57335.89</v>
+        <v>60366.31</v>
       </c>
       <c r="K37" t="n">
-        <v>58525.25</v>
+        <v>61274.59</v>
       </c>
       <c r="L37" t="n">
-        <v>59714.6</v>
+        <v>62182.86</v>
       </c>
       <c r="M37" t="n">
-        <v>60501</v>
+        <v>64152.71</v>
       </c>
       <c r="N37" t="n">
-        <v>61287.39</v>
+        <v>66122.55</v>
       </c>
       <c r="O37" t="n">
-        <v>62879.7</v>
+        <v>65969.25999999999</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3631,83 +3627,83 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
+      </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>63203.44</v>
+        <v>61299.87</v>
       </c>
       <c r="C38" t="n">
-        <v>63799.32</v>
+        <v>63432.41</v>
       </c>
       <c r="D38" t="n">
-        <v>60937.3</v>
+        <v>59292.25</v>
       </c>
       <c r="E38" t="n">
-        <v>61409.29</v>
+        <v>63339.07</v>
       </c>
       <c r="F38" t="n">
-        <v>-1304.36</v>
+        <v>1929.78</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0314</v>
       </c>
       <c r="H38" t="n">
-        <v>2862.02</v>
+        <v>4140.16</v>
       </c>
       <c r="I38" t="n">
-        <v>57334.9</v>
+        <v>58075.28</v>
       </c>
       <c r="J38" t="n">
-        <v>60366.31</v>
+        <v>58067.76</v>
       </c>
       <c r="K38" t="n">
-        <v>61274.59</v>
+        <v>59978.28</v>
       </c>
       <c r="L38" t="n">
-        <v>62182.86</v>
+        <v>61888.8</v>
       </c>
       <c r="M38" t="n">
-        <v>64152.71</v>
+        <v>62840.3</v>
       </c>
       <c r="N38" t="n">
-        <v>66122.55</v>
+        <v>63791.8</v>
       </c>
       <c r="O38" t="n">
-        <v>65969.25999999999</v>
+        <v>66661.34</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3717,20 +3713,24 @@
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
@@ -3741,57 +3741,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>61299.87</v>
+        <v>63658.95</v>
       </c>
       <c r="C39" t="n">
-        <v>63432.41</v>
+        <v>66505.02</v>
       </c>
       <c r="D39" t="n">
-        <v>59292.25</v>
+        <v>63562.51</v>
       </c>
       <c r="E39" t="n">
-        <v>63339.07</v>
+        <v>66329.5</v>
       </c>
       <c r="F39" t="n">
-        <v>1929.78</v>
+        <v>2990.43</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0314</v>
+        <v>0.0472</v>
       </c>
       <c r="H39" t="n">
-        <v>4140.16</v>
+        <v>2942.51</v>
       </c>
       <c r="I39" t="n">
-        <v>58075.28</v>
+        <v>55152.09</v>
       </c>
       <c r="J39" t="n">
-        <v>58067.76</v>
+        <v>60187.28</v>
       </c>
       <c r="K39" t="n">
-        <v>59978.28</v>
+        <v>61268.99</v>
       </c>
       <c r="L39" t="n">
-        <v>61888.8</v>
+        <v>62350.7</v>
       </c>
       <c r="M39" t="n">
-        <v>62840.3</v>
+        <v>65409.15</v>
       </c>
       <c r="N39" t="n">
-        <v>63791.8</v>
+        <v>68467.60000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>66661.34</v>
+        <v>67572.57000000001</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3799,10 +3799,8 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
@@ -3811,14 +3809,12 @@
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
@@ -3827,59 +3823,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>63658.95</v>
+        <v>66363.42999999999</v>
       </c>
       <c r="C40" t="n">
-        <v>66505.02</v>
+        <v>68786.49000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>63562.51</v>
+        <v>65551.13</v>
       </c>
       <c r="E40" t="n">
-        <v>66329.5</v>
+        <v>66588.12</v>
       </c>
       <c r="F40" t="n">
-        <v>2990.43</v>
+        <v>258.62</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0472</v>
+        <v>0.0039</v>
       </c>
       <c r="H40" t="n">
-        <v>2942.51</v>
+        <v>3235.36</v>
       </c>
       <c r="I40" t="n">
-        <v>55152.09</v>
+        <v>60620</v>
       </c>
       <c r="J40" t="n">
-        <v>60187.28</v>
+        <v>64034.85</v>
       </c>
       <c r="K40" t="n">
-        <v>61268.99</v>
+        <v>64858.24</v>
       </c>
       <c r="L40" t="n">
-        <v>62350.7</v>
+        <v>65681.63</v>
       </c>
       <c r="M40" t="n">
-        <v>65409.15</v>
+        <v>67800.75999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>68467.60000000001</v>
+        <v>69919.88</v>
       </c>
       <c r="O40" t="n">
-        <v>67572.57000000001</v>
+        <v>69447.53999999999</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3892,12 +3884,12 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U40" s="8" t="n">
@@ -3916,69 +3908,71 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>66363.42999999999</v>
+        <v>65947.56</v>
       </c>
       <c r="C41" t="n">
-        <v>68786.49000000001</v>
+        <v>67065.94</v>
       </c>
       <c r="D41" t="n">
-        <v>65551.13</v>
+        <v>62335.75</v>
       </c>
       <c r="E41" t="n">
-        <v>66588.12</v>
+        <v>66020.03999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>258.62</v>
+        <v>-568.08</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0039</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>3235.36</v>
+        <v>4730.19</v>
       </c>
       <c r="I41" t="n">
-        <v>60620</v>
+        <v>62315.77</v>
       </c>
       <c r="J41" t="n">
-        <v>64034.85</v>
+        <v>63062.41</v>
       </c>
       <c r="K41" t="n">
-        <v>64858.24</v>
+        <v>64970.44</v>
       </c>
       <c r="L41" t="n">
-        <v>65681.63</v>
+        <v>66878.46000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>67800.75999999999</v>
+        <v>68205.8</v>
       </c>
       <c r="N41" t="n">
-        <v>69919.88</v>
+        <v>69533.13</v>
       </c>
       <c r="O41" t="n">
-        <v>69447.53999999999</v>
+        <v>72021.85000000001</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3991,141 +3985,143 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>65947.56</v>
+        <v>66783.22</v>
       </c>
       <c r="C42" t="n">
-        <v>67065.94</v>
+        <v>71952.99000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>62335.75</v>
+        <v>66783.22</v>
       </c>
       <c r="E42" t="n">
-        <v>66020.03999999999</v>
+        <v>71250.06</v>
       </c>
       <c r="F42" t="n">
-        <v>-568.08</v>
+        <v>5230.02</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>4730.19</v>
+        <v>5169.77</v>
       </c>
       <c r="I42" t="n">
-        <v>62315.77</v>
+        <v>57605.56</v>
       </c>
       <c r="J42" t="n">
-        <v>63062.41</v>
+        <v>61949.45</v>
       </c>
       <c r="K42" t="n">
-        <v>64970.44</v>
+        <v>63654.95</v>
       </c>
       <c r="L42" t="n">
-        <v>66878.46000000001</v>
+        <v>65360.44</v>
       </c>
       <c r="M42" t="n">
-        <v>68205.8</v>
+        <v>68385.13</v>
       </c>
       <c r="N42" t="n">
-        <v>69533.13</v>
+        <v>71409.82000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>72021.85000000001</v>
+        <v>71796.12</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v/>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>66783.22</v>
+        <v>71067.14999999999</v>
       </c>
       <c r="C43" t="n">
-        <v>71952.99000000001</v>
+        <v>72831.73</v>
       </c>
       <c r="D43" t="n">
-        <v>66783.22</v>
+        <v>68461.10000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>71250.06</v>
+        <v>69360.88</v>
       </c>
       <c r="F43" t="n">
-        <v>5230.02</v>
+        <v>-1889.18</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.07920000000000001</v>
+        <v>-0.0265</v>
       </c>
       <c r="H43" t="n">
-        <v>5169.77</v>
+        <v>4370.62</v>
       </c>
       <c r="I43" t="n">
-        <v>57605.56</v>
+        <v>61613.45</v>
       </c>
       <c r="J43" t="n">
-        <v>61949.45</v>
+        <v>67021.27</v>
       </c>
       <c r="K43" t="n">
-        <v>63654.95</v>
+        <v>68665.17999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>65360.44</v>
+        <v>70309.08</v>
       </c>
       <c r="M43" t="n">
-        <v>68385.13</v>
+        <v>73834.95</v>
       </c>
       <c r="N43" t="n">
-        <v>71409.82000000001</v>
+        <v>77360.81</v>
       </c>
       <c r="O43" t="n">
-        <v>71796.12</v>
+        <v>77122.77</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4133,83 +4129,83 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
+      <c r="R43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v/>
       </c>
       <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>71067.14999999999</v>
+        <v>69609.88</v>
       </c>
       <c r="C44" t="n">
-        <v>72831.73</v>
+        <v>71962.34</v>
       </c>
       <c r="D44" t="n">
-        <v>68461.10000000001</v>
+        <v>67609.49000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>69360.88</v>
+        <v>69744.07000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>-1889.18</v>
+        <v>383.19</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0265</v>
+        <v>0.0055</v>
       </c>
       <c r="H44" t="n">
-        <v>4370.62</v>
+        <v>4352.85</v>
       </c>
       <c r="I44" t="n">
-        <v>61613.45</v>
+        <v>64090.48</v>
       </c>
       <c r="J44" t="n">
-        <v>67021.27</v>
+        <v>64347.49</v>
       </c>
       <c r="K44" t="n">
-        <v>68665.17999999999</v>
+        <v>67175.57000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>70309.08</v>
+        <v>70003.64999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>73834.95</v>
+        <v>71546.2</v>
       </c>
       <c r="N44" t="n">
-        <v>77360.81</v>
+        <v>73088.74000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>77122.77</v>
+        <v>77202.35000000001</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4217,18 +4213,18 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4243,57 +4239,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>69609.88</v>
+        <v>69973.34</v>
       </c>
       <c r="C45" t="n">
-        <v>71962.34</v>
+        <v>70384.59</v>
       </c>
       <c r="D45" t="n">
-        <v>67609.49000000001</v>
+        <v>66819.05</v>
       </c>
       <c r="E45" t="n">
-        <v>69744.07000000001</v>
+        <v>68557.73</v>
       </c>
       <c r="F45" t="n">
-        <v>383.19</v>
+        <v>-1186.34</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0055</v>
+        <v>-0.017</v>
       </c>
       <c r="H45" t="n">
-        <v>4352.85</v>
+        <v>3565.55</v>
       </c>
       <c r="I45" t="n">
-        <v>64090.48</v>
+        <v>63256.64</v>
       </c>
       <c r="J45" t="n">
-        <v>64347.49</v>
+        <v>65370.29</v>
       </c>
       <c r="K45" t="n">
-        <v>67175.57000000001</v>
+        <v>67567.64</v>
       </c>
       <c r="L45" t="n">
-        <v>70003.64999999999</v>
+        <v>69764.99000000001</v>
       </c>
       <c r="M45" t="n">
-        <v>71546.2</v>
+        <v>71920.5</v>
       </c>
       <c r="N45" t="n">
-        <v>73088.74000000001</v>
+        <v>74076</v>
       </c>
       <c r="O45" t="n">
-        <v>77202.35000000001</v>
+        <v>76315.2</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4301,18 +4297,18 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4327,67 +4323,71 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>69973.34</v>
+        <v>68410.63</v>
       </c>
       <c r="C46" t="n">
-        <v>70384.59</v>
+        <v>69078.21000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>66819.05</v>
+        <v>62704.6</v>
       </c>
       <c r="E46" t="n">
-        <v>68557.73</v>
+        <v>64141.12</v>
       </c>
       <c r="F46" t="n">
-        <v>-1186.34</v>
+        <v>-4416.61</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0644</v>
       </c>
       <c r="H46" t="n">
-        <v>3565.55</v>
+        <v>6373.61</v>
       </c>
       <c r="I46" t="n">
-        <v>63256.64</v>
+        <v>63253.5</v>
       </c>
       <c r="J46" t="n">
-        <v>65370.29</v>
+        <v>64970.13</v>
       </c>
       <c r="K46" t="n">
-        <v>67567.64</v>
+        <v>66774.95</v>
       </c>
       <c r="L46" t="n">
-        <v>69764.99000000001</v>
+        <v>68579.77</v>
       </c>
       <c r="M46" t="n">
-        <v>71920.5</v>
+        <v>70340.5</v>
       </c>
       <c r="N46" t="n">
-        <v>74076</v>
+        <v>72101.23</v>
       </c>
       <c r="O46" t="n">
-        <v>76315.2</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
+        <v>73950.14</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
@@ -4404,87 +4404,79 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W46" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>68410.63</v>
+        <v>64544.05</v>
       </c>
       <c r="C47" t="n">
-        <v>69078.21000000001</v>
+        <v>67592.2</v>
       </c>
       <c r="D47" t="n">
-        <v>62704.6</v>
+        <v>64201.03</v>
       </c>
       <c r="E47" t="n">
-        <v>64141.12</v>
+        <v>64611.15</v>
       </c>
       <c r="F47" t="n">
-        <v>-4416.61</v>
+        <v>470.03</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0644</v>
+        <v>0.0073</v>
       </c>
       <c r="H47" t="n">
-        <v>6373.61</v>
+        <v>3391.17</v>
       </c>
       <c r="I47" t="n">
-        <v>63253.5</v>
+        <v>56330.99</v>
       </c>
       <c r="J47" t="n">
-        <v>64970.13</v>
+        <v>56892.37</v>
       </c>
       <c r="K47" t="n">
-        <v>66774.95</v>
+        <v>60954.32</v>
       </c>
       <c r="L47" t="n">
-        <v>68579.77</v>
+        <v>65016.26</v>
       </c>
       <c r="M47" t="n">
-        <v>70340.5</v>
+        <v>67327.92999999999</v>
       </c>
       <c r="N47" t="n">
-        <v>72101.23</v>
+        <v>69639.59</v>
       </c>
       <c r="O47" t="n">
-        <v>73950.14</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>75451.82000000001</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4497,74 +4489,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>64544.05</v>
+        <v>65164.98</v>
       </c>
       <c r="C48" t="n">
-        <v>67592.2</v>
+        <v>65364.73</v>
       </c>
       <c r="D48" t="n">
-        <v>64201.03</v>
+        <v>60448.9</v>
       </c>
       <c r="E48" t="n">
-        <v>64611.15</v>
+        <v>64362.02</v>
       </c>
       <c r="F48" t="n">
-        <v>470.03</v>
+        <v>-249.13</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0073</v>
+        <v>-0.0039</v>
       </c>
       <c r="H48" t="n">
-        <v>3391.17</v>
+        <v>4915.83</v>
       </c>
       <c r="I48" t="n">
-        <v>56330.99</v>
+        <v>60809.86</v>
       </c>
       <c r="J48" t="n">
-        <v>56892.37</v>
+        <v>60577.24</v>
       </c>
       <c r="K48" t="n">
-        <v>60954.32</v>
+        <v>62915.56</v>
       </c>
       <c r="L48" t="n">
-        <v>65016.26</v>
+        <v>65253.88</v>
       </c>
       <c r="M48" t="n">
-        <v>67327.92999999999</v>
+        <v>66306.73</v>
       </c>
       <c r="N48" t="n">
-        <v>69639.59</v>
+        <v>67359.59</v>
       </c>
       <c r="O48" t="n">
-        <v>75451.82000000001</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+        <v>70983.38</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4577,82 +4577,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>65164.98</v>
+        <v>63834.95</v>
       </c>
       <c r="C49" t="n">
-        <v>65364.73</v>
+        <v>66302.52</v>
       </c>
       <c r="D49" t="n">
-        <v>60448.9</v>
+        <v>62703.47</v>
       </c>
       <c r="E49" t="n">
-        <v>64362.02</v>
+        <v>65606.71000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>-249.13</v>
+        <v>1244.69</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0193</v>
       </c>
       <c r="H49" t="n">
-        <v>4915.83</v>
+        <v>3599.05</v>
       </c>
       <c r="I49" t="n">
-        <v>60809.86</v>
+        <v>55533.07</v>
       </c>
       <c r="J49" t="n">
-        <v>60577.24</v>
+        <v>60173.79</v>
       </c>
       <c r="K49" t="n">
-        <v>62915.56</v>
+        <v>61904.1</v>
       </c>
       <c r="L49" t="n">
-        <v>65253.88</v>
+        <v>63634.42</v>
       </c>
       <c r="M49" t="n">
-        <v>66306.73</v>
+        <v>66819.94</v>
       </c>
       <c r="N49" t="n">
-        <v>67359.59</v>
+        <v>70005.45</v>
       </c>
       <c r="O49" t="n">
-        <v>70983.38</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+        <v>70280.56</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4665,55 +4657,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>63834.95</v>
+        <v>65905.10000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>66302.52</v>
+        <v>69608.24000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>62703.47</v>
+        <v>65848.58</v>
       </c>
       <c r="E50" t="n">
-        <v>65606.71000000001</v>
+        <v>68713.8</v>
       </c>
       <c r="F50" t="n">
-        <v>1244.69</v>
+        <v>3107.09</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0193</v>
+        <v>0.0474</v>
       </c>
       <c r="H50" t="n">
-        <v>3599.05</v>
+        <v>3759.66</v>
       </c>
       <c r="I50" t="n">
-        <v>55533.07</v>
+        <v>59104.41</v>
       </c>
       <c r="J50" t="n">
-        <v>60173.79</v>
+        <v>62559.51</v>
       </c>
       <c r="K50" t="n">
-        <v>61904.1</v>
+        <v>63807.18</v>
       </c>
       <c r="L50" t="n">
-        <v>63634.42</v>
+        <v>65054.85</v>
       </c>
       <c r="M50" t="n">
-        <v>66819.94</v>
+        <v>67406.24000000001</v>
       </c>
       <c r="N50" t="n">
-        <v>70005.45</v>
+        <v>69757.62</v>
       </c>
       <c r="O50" t="n">
-        <v>70280.56</v>
+        <v>69901.58</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4731,11 +4727,13 @@
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4754,75 +4752,75 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>65905.10000000001</v>
+        <v>68882.06</v>
       </c>
       <c r="C51" t="n">
-        <v>69608.24000000001</v>
+        <v>69225.57000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>65848.58</v>
+        <v>65133.98</v>
       </c>
       <c r="E51" t="n">
-        <v>68713.8</v>
+        <v>66016.36</v>
       </c>
       <c r="F51" t="n">
-        <v>3107.09</v>
+        <v>-2697.44</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0474</v>
+        <v>-0.0393</v>
       </c>
       <c r="H51" t="n">
-        <v>3759.66</v>
+        <v>4091.59</v>
       </c>
       <c r="I51" t="n">
-        <v>59104.41</v>
+        <v>62088.91</v>
       </c>
       <c r="J51" t="n">
-        <v>62559.51</v>
+        <v>65446.83</v>
       </c>
       <c r="K51" t="n">
-        <v>63807.18</v>
+        <v>66833.96000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>65054.85</v>
+        <v>68221.10000000001</v>
       </c>
       <c r="M51" t="n">
-        <v>67406.24000000001</v>
+        <v>70593.63</v>
       </c>
       <c r="N51" t="n">
-        <v>69757.62</v>
+        <v>72966.14999999999</v>
       </c>
       <c r="O51" t="n">
-        <v>69901.58</v>
+        <v>73367.91</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
+      <c r="Q51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
@@ -4831,76 +4829,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>68882.06</v>
+        <v>65978.95</v>
       </c>
       <c r="C52" t="n">
-        <v>69225.57000000001</v>
+        <v>66954.69</v>
       </c>
       <c r="D52" t="n">
-        <v>65133.98</v>
+        <v>64609.47</v>
       </c>
       <c r="E52" t="n">
-        <v>66016.36</v>
+        <v>66405.56</v>
       </c>
       <c r="F52" t="n">
-        <v>-2697.44</v>
+        <v>389.2</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0393</v>
+        <v>0.0059</v>
       </c>
       <c r="H52" t="n">
-        <v>4091.59</v>
+        <v>2345.22</v>
       </c>
       <c r="I52" t="n">
-        <v>62088.91</v>
+        <v>61042.39</v>
       </c>
       <c r="J52" t="n">
-        <v>65446.83</v>
+        <v>61343.06</v>
       </c>
       <c r="K52" t="n">
-        <v>66833.96000000001</v>
+        <v>63970.56</v>
       </c>
       <c r="L52" t="n">
-        <v>68221.10000000001</v>
+        <v>66598.07000000001</v>
       </c>
       <c r="M52" t="n">
-        <v>70593.63</v>
+        <v>68062.14999999999</v>
       </c>
       <c r="N52" t="n">
-        <v>72966.14999999999</v>
+        <v>69526.24000000001</v>
       </c>
       <c r="O52" t="n">
-        <v>73367.91</v>
+        <v>73317.16</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4917,68 +4907,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>65978.95</v>
+        <v>65668.50999999999</v>
       </c>
       <c r="C53" t="n">
-        <v>66954.69</v>
+        <v>66525.7</v>
       </c>
       <c r="D53" t="n">
-        <v>64609.47</v>
+        <v>63772.8</v>
       </c>
       <c r="E53" t="n">
-        <v>66405.56</v>
+        <v>65020.94</v>
       </c>
       <c r="F53" t="n">
-        <v>389.2</v>
+        <v>-1384.62</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0209</v>
       </c>
       <c r="H53" t="n">
-        <v>2345.22</v>
+        <v>2752.9</v>
       </c>
       <c r="I53" t="n">
-        <v>61042.39</v>
+        <v>62264.25</v>
       </c>
       <c r="J53" t="n">
-        <v>61343.06</v>
+        <v>64372.09</v>
       </c>
       <c r="K53" t="n">
-        <v>63970.56</v>
+        <v>65232.95</v>
       </c>
       <c r="L53" t="n">
-        <v>66598.07000000001</v>
+        <v>66093.82000000001</v>
       </c>
       <c r="M53" t="n">
-        <v>68062.14999999999</v>
+        <v>67578.17</v>
       </c>
       <c r="N53" t="n">
-        <v>69526.24000000001</v>
+        <v>69062.52</v>
       </c>
       <c r="O53" t="n">
-        <v>73317.16</v>
+        <v>69299.91</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4995,67 +4993,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>65668.50999999999</v>
+        <v>65600.42</v>
       </c>
       <c r="C54" t="n">
-        <v>66525.7</v>
+        <v>66791.84</v>
       </c>
       <c r="D54" t="n">
-        <v>63772.8</v>
+        <v>63208.63</v>
       </c>
       <c r="E54" t="n">
-        <v>65020.94</v>
+        <v>64011.34</v>
       </c>
       <c r="F54" t="n">
-        <v>-1384.62</v>
+        <v>-1009.6</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0209</v>
+        <v>-0.0155</v>
       </c>
       <c r="H54" t="n">
-        <v>2752.9</v>
+        <v>3583.21</v>
       </c>
       <c r="I54" t="n">
-        <v>62264.25</v>
+        <v>61019.9</v>
       </c>
       <c r="J54" t="n">
-        <v>64372.09</v>
+        <v>62203.88</v>
       </c>
       <c r="K54" t="n">
-        <v>65232.95</v>
+        <v>63644.49</v>
       </c>
       <c r="L54" t="n">
-        <v>66093.82000000001</v>
+        <v>65085.1</v>
       </c>
       <c r="M54" t="n">
-        <v>67578.17</v>
+        <v>66397.39</v>
       </c>
       <c r="N54" t="n">
-        <v>69062.52</v>
+        <v>67709.69</v>
       </c>
       <c r="O54" t="n">
-        <v>69299.91</v>
+        <v>69278.61</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q54" s="6" t="n">
+        <v/>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
@@ -5067,8 +5059,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5081,55 +5075,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>65600.42</v>
+        <v>63659.53</v>
       </c>
       <c r="C55" t="n">
-        <v>66791.84</v>
+        <v>65436.57</v>
       </c>
       <c r="D55" t="n">
-        <v>63208.63</v>
+        <v>62726.18</v>
       </c>
       <c r="E55" t="n">
-        <v>64011.34</v>
+        <v>65018.95</v>
       </c>
       <c r="F55" t="n">
-        <v>-1009.6</v>
+        <v>1007.61</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0157</v>
       </c>
       <c r="H55" t="n">
-        <v>3583.21</v>
+        <v>2710.39</v>
       </c>
       <c r="I55" t="n">
-        <v>61019.9</v>
+        <v>59625.41</v>
       </c>
       <c r="J55" t="n">
-        <v>62203.88</v>
+        <v>59933.68</v>
       </c>
       <c r="K55" t="n">
-        <v>63644.49</v>
+        <v>62219.73</v>
       </c>
       <c r="L55" t="n">
-        <v>65085.1</v>
+        <v>64505.79</v>
       </c>
       <c r="M55" t="n">
-        <v>66397.39</v>
+        <v>65802.95</v>
       </c>
       <c r="N55" t="n">
-        <v>67709.69</v>
+        <v>67100.11</v>
       </c>
       <c r="O55" t="n">
-        <v>69278.61</v>
+        <v>70375.06</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5137,20 +5135,16 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5172,50 +5166,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>63659.53</v>
+        <v>65476.44</v>
       </c>
       <c r="C56" t="n">
-        <v>65436.57</v>
+        <v>66410.27</v>
       </c>
       <c r="D56" t="n">
-        <v>62726.18</v>
+        <v>65407.37</v>
       </c>
       <c r="E56" t="n">
-        <v>65018.95</v>
+        <v>66364.2</v>
       </c>
       <c r="F56" t="n">
-        <v>1007.61</v>
+        <v>1345.25</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0157</v>
+        <v>0.0207</v>
       </c>
       <c r="H56" t="n">
-        <v>2710.39</v>
+        <v>1002.9</v>
       </c>
       <c r="I56" t="n">
-        <v>59625.41</v>
+        <v>60015.79</v>
       </c>
       <c r="J56" t="n">
-        <v>59933.68</v>
+        <v>62777.35</v>
       </c>
       <c r="K56" t="n">
-        <v>62219.73</v>
+        <v>63663.75</v>
       </c>
       <c r="L56" t="n">
-        <v>64505.79</v>
+        <v>64550.16</v>
       </c>
       <c r="M56" t="n">
-        <v>65802.95</v>
+        <v>66374.14</v>
       </c>
       <c r="N56" t="n">
-        <v>67100.11</v>
+        <v>68198.13</v>
       </c>
       <c r="O56" t="n">
-        <v>70375.06</v>
+        <v>68146.96000000001</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5228,11 +5222,13 @@
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5247,66 +5243,70 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>65476.44</v>
+        <v>66505.94</v>
       </c>
       <c r="C57" t="n">
-        <v>66410.27</v>
+        <v>68995.3</v>
       </c>
       <c r="D57" t="n">
-        <v>65407.37</v>
+        <v>64699.49</v>
       </c>
       <c r="E57" t="n">
-        <v>66364.2</v>
+        <v>68309.46000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>1345.25</v>
+        <v>1945.26</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0207</v>
+        <v>0.0293</v>
       </c>
       <c r="H57" t="n">
-        <v>1002.9</v>
+        <v>4295.81</v>
       </c>
       <c r="I57" t="n">
-        <v>60015.79</v>
+        <v>64404.47</v>
       </c>
       <c r="J57" t="n">
-        <v>62777.35</v>
+        <v>65588.99000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>63663.75</v>
+        <v>65862.75</v>
       </c>
       <c r="L57" t="n">
-        <v>64550.16</v>
+        <v>66136.50999999999</v>
       </c>
       <c r="M57" t="n">
-        <v>66374.14</v>
+        <v>66865.64999999999</v>
       </c>
       <c r="N57" t="n">
-        <v>68198.13</v>
+        <v>67594.8</v>
       </c>
       <c r="O57" t="n">
-        <v>68146.96000000001</v>
+        <v>67413.17999999999</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
@@ -5315,113 +5315,25 @@
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W57" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>66505.94</v>
-      </c>
-      <c r="C58" t="n">
-        <v>68995.3</v>
-      </c>
-      <c r="D58" t="n">
-        <v>64699.49</v>
-      </c>
-      <c r="E58" t="n">
-        <v>68956.72</v>
-      </c>
-      <c r="F58" t="n">
-        <v>2592.52</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0391</v>
-      </c>
-      <c r="H58" t="n">
-        <v>4295.81</v>
-      </c>
-      <c r="I58" t="n">
-        <v>64404.47</v>
-      </c>
-      <c r="J58" t="n">
-        <v>65588.99000000001</v>
-      </c>
-      <c r="K58" t="n">
-        <v>65862.75</v>
-      </c>
-      <c r="L58" t="n">
-        <v>66136.50999999999</v>
-      </c>
-      <c r="M58" t="n">
-        <v>66865.64999999999</v>
-      </c>
-      <c r="N58" t="n">
-        <v>67594.8</v>
-      </c>
-      <c r="O58" t="n">
-        <v>67413.17999999999</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5339,6 +5342,86 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>69113.74000000001</v>
+      </c>
+      <c r="C58" t="n">
+        <v>70072.13</v>
+      </c>
+      <c r="D58" t="n">
+        <v>69050.23</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>1021.91</v>
+      </c>
+      <c r="I58" t="n">
+        <v>60403.68</v>
+      </c>
+      <c r="J58" t="n">
+        <v>64744.69</v>
+      </c>
+      <c r="K58" t="n">
+        <v>66161.56</v>
+      </c>
+      <c r="L58" t="n">
+        <v>67578.42999999999</v>
+      </c>
+      <c r="M58" t="n">
+        <v>70457.37</v>
+      </c>
+      <c r="N58" t="n">
+        <v>73336.3</v>
+      </c>
+      <c r="O58" t="n">
+        <v>73291.11</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,25 +659,25 @@
         <v>1544.44</v>
       </c>
       <c r="I2" t="n">
-        <v>40449.4</v>
+        <v>40505.46</v>
       </c>
       <c r="J2" t="n">
-        <v>41878.33</v>
+        <v>41899.35</v>
       </c>
       <c r="K2" t="n">
-        <v>42325.87</v>
+        <v>42339.88</v>
       </c>
       <c r="L2" t="n">
-        <v>42773.4</v>
+        <v>42780.41</v>
       </c>
       <c r="M2" t="n">
-        <v>43711.63</v>
+        <v>43697.62</v>
       </c>
       <c r="N2" t="n">
-        <v>44649.87</v>
+        <v>44614.83</v>
       </c>
       <c r="O2" t="n">
-        <v>44606.71</v>
+        <v>44578.68</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5352,22 +5349,22 @@
         <v>69113.74000000001</v>
       </c>
       <c r="C58" t="n">
-        <v>70072.13</v>
+        <v>70798.62</v>
       </c>
       <c r="D58" t="n">
         <v>69050.23</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>70683.98</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>2374.52</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.0348</v>
       </c>
       <c r="H58" t="n">
-        <v>1021.91</v>
+        <v>1748.39</v>
       </c>
       <c r="I58" t="n">
         <v>60403.68</v>
@@ -5390,24 +5387,24 @@
       <c r="O58" t="n">
         <v>73291.11</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>1544.44</v>
       </c>
       <c r="I2" t="n">
-        <v>40505.46</v>
+        <v>40912.24</v>
       </c>
       <c r="J2" t="n">
-        <v>41899.35</v>
+        <v>42051.89</v>
       </c>
       <c r="K2" t="n">
-        <v>42339.88</v>
+        <v>42441.57</v>
       </c>
       <c r="L2" t="n">
-        <v>42780.41</v>
+        <v>42831.26</v>
       </c>
       <c r="M2" t="n">
-        <v>43697.62</v>
+        <v>43595.93</v>
       </c>
       <c r="N2" t="n">
-        <v>44614.83</v>
+        <v>44360.59</v>
       </c>
       <c r="O2" t="n">
-        <v>44578.68</v>
+        <v>44375.29</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -700,12 +700,12 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W2" s="9" t="inlineStr">

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -5355,13 +5355,13 @@
         <v>69050.23</v>
       </c>
       <c r="E58" t="n">
-        <v>70683.98</v>
+        <v>70035.71000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>2374.52</v>
+        <v>1726.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0348</v>
+        <v>0.0253</v>
       </c>
       <c r="H58" t="n">
         <v>1748.39</v>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>1544.44</v>
       </c>
       <c r="I2" t="n">
-        <v>40912.24</v>
+        <v>42346.14</v>
       </c>
       <c r="J2" t="n">
-        <v>42051.89</v>
+        <v>42589.6</v>
       </c>
       <c r="K2" t="n">
-        <v>42441.57</v>
+        <v>42800.05</v>
       </c>
       <c r="L2" t="n">
-        <v>42831.26</v>
+        <v>43010.5</v>
       </c>
       <c r="M2" t="n">
-        <v>43595.93</v>
+        <v>43237.45</v>
       </c>
       <c r="N2" t="n">
-        <v>44360.59</v>
+        <v>43464.41</v>
       </c>
       <c r="O2" t="n">
-        <v>44375.29</v>
+        <v>43658.34</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5352,19 +5352,19 @@
         <v>70798.62</v>
       </c>
       <c r="D58" t="n">
-        <v>69050.23</v>
+        <v>69042.11</v>
       </c>
       <c r="E58" t="n">
-        <v>70035.71000000001</v>
+        <v>69042.11</v>
       </c>
       <c r="F58" t="n">
-        <v>1726.25</v>
+        <v>732.65</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0253</v>
+        <v>0.0107</v>
       </c>
       <c r="H58" t="n">
-        <v>1748.39</v>
+        <v>1756.51</v>
       </c>
       <c r="I58" t="n">
         <v>60403.68</v>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43451.07</v>
+        <v>44948.85</v>
       </c>
       <c r="C2" t="n">
-        <v>44888.02</v>
+        <v>45852.75</v>
       </c>
       <c r="D2" t="n">
-        <v>43343.58</v>
+        <v>44495.46</v>
       </c>
       <c r="E2" t="n">
-        <v>44768.12</v>
+        <v>45045.81</v>
       </c>
       <c r="F2" t="n">
-        <v>1749.37</v>
+        <v>277.69</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0407</v>
+        <v>0.0062</v>
       </c>
       <c r="H2" t="n">
-        <v>1544.44</v>
+        <v>1357.29</v>
       </c>
       <c r="I2" t="n">
-        <v>42346.14</v>
+        <v>41799.14</v>
       </c>
       <c r="J2" t="n">
-        <v>42589.6</v>
+        <v>43549.84</v>
       </c>
       <c r="K2" t="n">
-        <v>42800.05</v>
+        <v>43995.9</v>
       </c>
       <c r="L2" t="n">
-        <v>43010.5</v>
+        <v>44441.96</v>
       </c>
       <c r="M2" t="n">
-        <v>43237.45</v>
+        <v>45540.34</v>
       </c>
       <c r="N2" t="n">
-        <v>43464.41</v>
+        <v>46638.72</v>
       </c>
       <c r="O2" t="n">
-        <v>43658.34</v>
+        <v>46432.46</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,18 +695,14 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -718,50 +714,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44948.85</v>
+        <v>45193.77</v>
       </c>
       <c r="C3" t="n">
-        <v>45852.75</v>
+        <v>45824.69</v>
       </c>
       <c r="D3" t="n">
-        <v>44495.46</v>
+        <v>45193.77</v>
       </c>
       <c r="E3" t="n">
-        <v>45045.81</v>
+        <v>45354.99</v>
       </c>
       <c r="F3" t="n">
-        <v>277.69</v>
+        <v>309.18</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0062</v>
+        <v>0.0069</v>
       </c>
       <c r="H3" t="n">
-        <v>1357.29</v>
+        <v>630.92</v>
       </c>
       <c r="I3" t="n">
-        <v>41799.14</v>
+        <v>43138.17</v>
       </c>
       <c r="J3" t="n">
-        <v>43549.84</v>
+        <v>43624.37</v>
       </c>
       <c r="K3" t="n">
-        <v>43995.9</v>
+        <v>44367.16</v>
       </c>
       <c r="L3" t="n">
-        <v>44441.96</v>
+        <v>45109.96</v>
       </c>
       <c r="M3" t="n">
-        <v>45540.34</v>
+        <v>45724.45</v>
       </c>
       <c r="N3" t="n">
-        <v>46638.72</v>
+        <v>46338.95</v>
       </c>
       <c r="O3" t="n">
-        <v>46432.46</v>
+        <v>47210.04</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -774,12 +770,12 @@
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U3" s="8" t="n">
@@ -793,73 +789,83 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45193.77</v>
+        <v>45113.29</v>
       </c>
       <c r="C4" t="n">
-        <v>45824.69</v>
+        <v>45778.66</v>
       </c>
       <c r="D4" t="n">
-        <v>45193.77</v>
+        <v>44357.65</v>
       </c>
       <c r="E4" t="n">
-        <v>45354.99</v>
+        <v>45769.5</v>
       </c>
       <c r="F4" t="n">
-        <v>309.18</v>
+        <v>414.51</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0091</v>
       </c>
       <c r="H4" t="n">
-        <v>630.92</v>
+        <v>1421.01</v>
       </c>
       <c r="I4" t="n">
-        <v>43138.17</v>
+        <v>44562.85</v>
       </c>
       <c r="J4" t="n">
-        <v>43624.37</v>
+        <v>44646.95</v>
       </c>
       <c r="K4" t="n">
-        <v>44367.16</v>
+        <v>45039.53</v>
       </c>
       <c r="L4" t="n">
-        <v>45109.96</v>
+        <v>45432.11</v>
       </c>
       <c r="M4" t="n">
-        <v>45724.45</v>
+        <v>45670.45</v>
       </c>
       <c r="N4" t="n">
-        <v>46338.95</v>
+        <v>45908.79</v>
       </c>
       <c r="O4" t="n">
-        <v>47210.04</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+        <v>46455.61</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U4" s="8" t="n">
@@ -875,72 +881,66 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45113.29</v>
+        <v>46636.07</v>
       </c>
       <c r="C5" t="n">
-        <v>45778.66</v>
+        <v>48597.08</v>
       </c>
       <c r="D5" t="n">
-        <v>44357.65</v>
+        <v>46592.99</v>
       </c>
       <c r="E5" t="n">
-        <v>45769.5</v>
+        <v>48088.8</v>
       </c>
       <c r="F5" t="n">
-        <v>414.51</v>
+        <v>2319.3</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0507</v>
       </c>
       <c r="H5" t="n">
-        <v>1421.01</v>
+        <v>2004.09</v>
       </c>
       <c r="I5" t="n">
-        <v>44562.85</v>
+        <v>42936.64</v>
       </c>
       <c r="J5" t="n">
-        <v>44646.95</v>
+        <v>44699.16</v>
       </c>
       <c r="K5" t="n">
-        <v>45039.53</v>
+        <v>45058.99</v>
       </c>
       <c r="L5" t="n">
-        <v>45432.11</v>
+        <v>45418.83</v>
       </c>
       <c r="M5" t="n">
-        <v>45670.45</v>
+        <v>46480.01</v>
       </c>
       <c r="N5" t="n">
-        <v>45908.79</v>
+        <v>47541.18</v>
       </c>
       <c r="O5" t="n">
-        <v>46455.61</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>47199.67</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
@@ -949,73 +949,73 @@
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46636.07</v>
+        <v>47446.73</v>
       </c>
       <c r="C6" t="n">
-        <v>48597.08</v>
+        <v>48317.34</v>
       </c>
       <c r="D6" t="n">
-        <v>46592.99</v>
+        <v>46544.05</v>
       </c>
       <c r="E6" t="n">
-        <v>48088.8</v>
+        <v>47582.15</v>
       </c>
       <c r="F6" t="n">
-        <v>2319.3</v>
+        <v>-506.65</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0507</v>
+        <v>-0.0105</v>
       </c>
       <c r="H6" t="n">
-        <v>2004.09</v>
+        <v>1773.29</v>
       </c>
       <c r="I6" t="n">
-        <v>42936.64</v>
+        <v>44588.9</v>
       </c>
       <c r="J6" t="n">
-        <v>44699.16</v>
+        <v>46331.59</v>
       </c>
       <c r="K6" t="n">
-        <v>45058.99</v>
+        <v>47086.76</v>
       </c>
       <c r="L6" t="n">
-        <v>45418.83</v>
+        <v>47841.92</v>
       </c>
       <c r="M6" t="n">
-        <v>46480.01</v>
+        <v>49090.85</v>
       </c>
       <c r="N6" t="n">
-        <v>47541.18</v>
+        <v>50339.77</v>
       </c>
       <c r="O6" t="n">
-        <v>47199.67</v>
+        <v>50601.17</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1023,83 +1023,83 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47446.73</v>
+        <v>48332.71</v>
       </c>
       <c r="C7" t="n">
-        <v>48317.34</v>
+        <v>49945.95</v>
       </c>
       <c r="D7" t="n">
-        <v>46544.05</v>
+        <v>48254.83</v>
       </c>
       <c r="E7" t="n">
-        <v>47582.15</v>
+        <v>49299.65</v>
       </c>
       <c r="F7" t="n">
-        <v>-506.65</v>
+        <v>1717.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0105</v>
+        <v>0.0361</v>
       </c>
       <c r="H7" t="n">
-        <v>1773.29</v>
+        <v>1691.12</v>
       </c>
       <c r="I7" t="n">
-        <v>44588.9</v>
+        <v>44770.76</v>
       </c>
       <c r="J7" t="n">
-        <v>46331.59</v>
+        <v>45884.59</v>
       </c>
       <c r="K7" t="n">
-        <v>47086.76</v>
+        <v>46695.5</v>
       </c>
       <c r="L7" t="n">
-        <v>47841.92</v>
+        <v>47506.42</v>
       </c>
       <c r="M7" t="n">
-        <v>49090.85</v>
+        <v>48468.79</v>
       </c>
       <c r="N7" t="n">
-        <v>50339.77</v>
+        <v>49431.16</v>
       </c>
       <c r="O7" t="n">
-        <v>50601.17</v>
+        <v>50090.63</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1107,21 +1107,23 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1131,59 +1133,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>48332.71</v>
+        <v>49905.8</v>
       </c>
       <c r="C8" t="n">
-        <v>49945.95</v>
+        <v>52411.34</v>
       </c>
       <c r="D8" t="n">
-        <v>48254.83</v>
+        <v>49838.98</v>
       </c>
       <c r="E8" t="n">
-        <v>49299.65</v>
+        <v>52411.34</v>
       </c>
       <c r="F8" t="n">
-        <v>1717.5</v>
+        <v>3111.69</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0361</v>
+        <v>0.0631</v>
       </c>
       <c r="H8" t="n">
-        <v>1691.12</v>
+        <v>2572.36</v>
       </c>
       <c r="I8" t="n">
-        <v>44770.76</v>
+        <v>46563.71</v>
       </c>
       <c r="J8" t="n">
-        <v>45884.59</v>
+        <v>47708.16</v>
       </c>
       <c r="K8" t="n">
-        <v>46695.5</v>
+        <v>48454.09</v>
       </c>
       <c r="L8" t="n">
-        <v>47506.42</v>
+        <v>49200.02</v>
       </c>
       <c r="M8" t="n">
-        <v>48468.79</v>
+        <v>50145.21</v>
       </c>
       <c r="N8" t="n">
-        <v>49431.16</v>
+        <v>51090.4</v>
       </c>
       <c r="O8" t="n">
-        <v>50090.63</v>
+        <v>51637.07</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1206,11 +1204,13 @@
       </c>
       <c r="U8" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
@@ -1222,151 +1222,149 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>49905.8</v>
+        <v>52294.31</v>
       </c>
       <c r="C9" t="n">
-        <v>52411.34</v>
+        <v>52636.87</v>
       </c>
       <c r="D9" t="n">
-        <v>49838.98</v>
+        <v>49073.58</v>
       </c>
       <c r="E9" t="n">
-        <v>52411.34</v>
+        <v>50276.37</v>
       </c>
       <c r="F9" t="n">
-        <v>3111.69</v>
+        <v>-2134.97</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0631</v>
+        <v>-0.0407</v>
       </c>
       <c r="H9" t="n">
-        <v>2572.36</v>
+        <v>3563.29</v>
       </c>
       <c r="I9" t="n">
-        <v>46563.71</v>
+        <v>47266.62</v>
       </c>
       <c r="J9" t="n">
-        <v>47708.16</v>
+        <v>50482.07</v>
       </c>
       <c r="K9" t="n">
-        <v>48454.09</v>
+        <v>51125.16</v>
       </c>
       <c r="L9" t="n">
-        <v>49200.02</v>
+        <v>51768.25</v>
       </c>
       <c r="M9" t="n">
-        <v>50145.21</v>
+        <v>53697.52</v>
       </c>
       <c r="N9" t="n">
-        <v>51090.4</v>
+        <v>55626.79</v>
       </c>
       <c r="O9" t="n">
-        <v>51637.07</v>
+        <v>54983.7</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
+      <c r="Q9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W9" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W9" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52294.31</v>
+        <v>50645.27</v>
       </c>
       <c r="C10" t="n">
-        <v>52636.87</v>
+        <v>51513.16</v>
       </c>
       <c r="D10" t="n">
-        <v>49073.58</v>
+        <v>50246.6</v>
       </c>
       <c r="E10" t="n">
-        <v>50276.37</v>
+        <v>50376.53</v>
       </c>
       <c r="F10" t="n">
-        <v>-2134.97</v>
+        <v>100.16</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0407</v>
+        <v>0.002</v>
       </c>
       <c r="H10" t="n">
-        <v>3563.29</v>
+        <v>1266.56</v>
       </c>
       <c r="I10" t="n">
-        <v>47266.62</v>
+        <v>45510.29</v>
       </c>
       <c r="J10" t="n">
-        <v>50482.07</v>
+        <v>46423.65</v>
       </c>
       <c r="K10" t="n">
-        <v>51125.16</v>
+        <v>48494.72</v>
       </c>
       <c r="L10" t="n">
-        <v>51768.25</v>
+        <v>50565.8</v>
       </c>
       <c r="M10" t="n">
-        <v>53697.52</v>
+        <v>52058.02</v>
       </c>
       <c r="N10" t="n">
-        <v>55626.79</v>
+        <v>53550.24</v>
       </c>
       <c r="O10" t="n">
-        <v>54983.7</v>
+        <v>56200.16</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1385,70 +1383,76 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50645.27</v>
+        <v>50282.39</v>
       </c>
       <c r="C11" t="n">
-        <v>51513.16</v>
+        <v>50574.82</v>
       </c>
       <c r="D11" t="n">
-        <v>50246.6</v>
+        <v>48235.3</v>
       </c>
       <c r="E11" t="n">
-        <v>50376.53</v>
+        <v>48625.88</v>
       </c>
       <c r="F11" t="n">
-        <v>100.16</v>
+        <v>-1750.65</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0348</v>
       </c>
       <c r="H11" t="n">
-        <v>1266.56</v>
+        <v>2339.52</v>
       </c>
       <c r="I11" t="n">
-        <v>45510.29</v>
+        <v>48980.04</v>
       </c>
       <c r="J11" t="n">
-        <v>46423.65</v>
+        <v>48858.3</v>
       </c>
       <c r="K11" t="n">
-        <v>48494.72</v>
+        <v>49743.25</v>
       </c>
       <c r="L11" t="n">
-        <v>50565.8</v>
+        <v>50628.21</v>
       </c>
       <c r="M11" t="n">
-        <v>52058.02</v>
+        <v>51009.81</v>
       </c>
       <c r="N11" t="n">
-        <v>53550.24</v>
+        <v>51391.42</v>
       </c>
       <c r="O11" t="n">
-        <v>56200.16</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+        <v>52779.72</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1465,86 +1469,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50282.39</v>
+        <v>49113.82</v>
       </c>
       <c r="C12" t="n">
-        <v>50574.82</v>
+        <v>50322.14</v>
       </c>
       <c r="D12" t="n">
-        <v>48235.3</v>
+        <v>48511.95</v>
       </c>
       <c r="E12" t="n">
-        <v>48625.88</v>
+        <v>50253.91</v>
       </c>
       <c r="F12" t="n">
-        <v>-1750.65</v>
+        <v>1628.03</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0348</v>
+        <v>0.0335</v>
       </c>
       <c r="H12" t="n">
-        <v>2339.52</v>
+        <v>1810.19</v>
       </c>
       <c r="I12" t="n">
-        <v>48980.04</v>
+        <v>45895.78</v>
       </c>
       <c r="J12" t="n">
-        <v>48858.3</v>
+        <v>45896.77</v>
       </c>
       <c r="K12" t="n">
-        <v>49743.25</v>
+        <v>47456.12</v>
       </c>
       <c r="L12" t="n">
-        <v>50628.21</v>
+        <v>49015.47</v>
       </c>
       <c r="M12" t="n">
-        <v>51009.81</v>
+        <v>49795.64</v>
       </c>
       <c r="N12" t="n">
-        <v>51391.42</v>
+        <v>50575.81</v>
       </c>
       <c r="O12" t="n">
-        <v>52779.72</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
+        <v>52914.34</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
@@ -1553,55 +1551,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>49113.82</v>
+        <v>50318.59</v>
       </c>
       <c r="C13" t="n">
-        <v>50322.14</v>
+        <v>51028.42</v>
       </c>
       <c r="D13" t="n">
-        <v>48511.95</v>
+        <v>49215.96</v>
       </c>
       <c r="E13" t="n">
-        <v>50253.91</v>
+        <v>50491.87</v>
       </c>
       <c r="F13" t="n">
-        <v>1628.03</v>
+        <v>237.96</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0335</v>
+        <v>0.0047</v>
       </c>
       <c r="H13" t="n">
-        <v>1810.19</v>
+        <v>1812.46</v>
       </c>
       <c r="I13" t="n">
-        <v>45895.78</v>
+        <v>46701.76</v>
       </c>
       <c r="J13" t="n">
-        <v>45896.77</v>
+        <v>48862.15</v>
       </c>
       <c r="K13" t="n">
-        <v>47456.12</v>
+        <v>49348.81</v>
       </c>
       <c r="L13" t="n">
-        <v>49015.47</v>
+        <v>49835.48</v>
       </c>
       <c r="M13" t="n">
-        <v>49795.64</v>
+        <v>51159.01</v>
       </c>
       <c r="N13" t="n">
-        <v>50575.81</v>
+        <v>52482.53</v>
       </c>
       <c r="O13" t="n">
-        <v>52914.34</v>
+        <v>52132.33</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1609,23 +1611,21 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1637,57 +1637,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>50318.59</v>
+        <v>50643.09</v>
       </c>
       <c r="C14" t="n">
-        <v>51028.42</v>
+        <v>51127.69</v>
       </c>
       <c r="D14" t="n">
-        <v>49215.96</v>
+        <v>49926.27</v>
       </c>
       <c r="E14" t="n">
-        <v>50491.87</v>
+        <v>50836.55</v>
       </c>
       <c r="F14" t="n">
-        <v>237.96</v>
+        <v>344.68</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0047</v>
+        <v>0.0068</v>
       </c>
       <c r="H14" t="n">
-        <v>1812.46</v>
+        <v>1201.42</v>
       </c>
       <c r="I14" t="n">
-        <v>46701.76</v>
+        <v>47403.5</v>
       </c>
       <c r="J14" t="n">
-        <v>48862.15</v>
+        <v>48864.25</v>
       </c>
       <c r="K14" t="n">
-        <v>49348.81</v>
+        <v>49585.64</v>
       </c>
       <c r="L14" t="n">
-        <v>49835.48</v>
+        <v>50307.03</v>
       </c>
       <c r="M14" t="n">
-        <v>51159.01</v>
+        <v>51398.1</v>
       </c>
       <c r="N14" t="n">
-        <v>52482.53</v>
+        <v>52489.17</v>
       </c>
       <c r="O14" t="n">
-        <v>52132.33</v>
+        <v>52840.88</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1695,10 +1695,8 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R14" s="6" t="n">
+        <v/>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
@@ -1728,63 +1726,69 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>50643.09</v>
+        <v>50352.09</v>
       </c>
       <c r="C15" t="n">
-        <v>51127.69</v>
+        <v>50432.1</v>
       </c>
       <c r="D15" t="n">
-        <v>49926.27</v>
+        <v>48643.78</v>
       </c>
       <c r="E15" t="n">
-        <v>50836.55</v>
+        <v>49507.21</v>
       </c>
       <c r="F15" t="n">
-        <v>344.68</v>
+        <v>-1329.34</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0261</v>
       </c>
       <c r="H15" t="n">
-        <v>1201.42</v>
+        <v>1788.32</v>
       </c>
       <c r="I15" t="n">
-        <v>47403.5</v>
+        <v>48724.85</v>
       </c>
       <c r="J15" t="n">
-        <v>48864.25</v>
+        <v>49789.91</v>
       </c>
       <c r="K15" t="n">
-        <v>49585.64</v>
+        <v>50235.84</v>
       </c>
       <c r="L15" t="n">
-        <v>50307.03</v>
+        <v>50681.77</v>
       </c>
       <c r="M15" t="n">
-        <v>51398.1</v>
+        <v>51437.26</v>
       </c>
       <c r="N15" t="n">
-        <v>52489.17</v>
+        <v>52192.76</v>
       </c>
       <c r="O15" t="n">
-        <v>52840.88</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>52329.11</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1801,83 +1805,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>50352.09</v>
+        <v>50084.55</v>
       </c>
       <c r="C16" t="n">
-        <v>50432.1</v>
+        <v>50941.89</v>
       </c>
       <c r="D16" t="n">
-        <v>48643.78</v>
+        <v>49982.2</v>
       </c>
       <c r="E16" t="n">
-        <v>49507.21</v>
+        <v>50750.39</v>
       </c>
       <c r="F16" t="n">
-        <v>-1329.34</v>
+        <v>1243.18</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0261</v>
+        <v>0.0251</v>
       </c>
       <c r="H16" t="n">
-        <v>1788.32</v>
+        <v>959.6900000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>48724.85</v>
+        <v>46855.46</v>
       </c>
       <c r="J16" t="n">
-        <v>49789.91</v>
+        <v>47703.53</v>
       </c>
       <c r="K16" t="n">
-        <v>50235.84</v>
+        <v>48613.05</v>
       </c>
       <c r="L16" t="n">
-        <v>50681.77</v>
+        <v>49522.58</v>
       </c>
       <c r="M16" t="n">
-        <v>51437.26</v>
+        <v>50401.37</v>
       </c>
       <c r="N16" t="n">
-        <v>52192.76</v>
+        <v>51280.17</v>
       </c>
       <c r="O16" t="n">
-        <v>52329.11</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
+        <v>52220.42</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
@@ -1889,55 +1885,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>50084.55</v>
+        <v>50691.22</v>
       </c>
       <c r="C17" t="n">
-        <v>50941.89</v>
+        <v>50707.23</v>
       </c>
       <c r="D17" t="n">
-        <v>49982.2</v>
+        <v>50198.97</v>
       </c>
       <c r="E17" t="n">
-        <v>50750.39</v>
+        <v>50339.48</v>
       </c>
       <c r="F17" t="n">
-        <v>1243.18</v>
+        <v>-410.91</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0251</v>
+        <v>-0.0081</v>
       </c>
       <c r="H17" t="n">
-        <v>959.6900000000001</v>
+        <v>508.26</v>
       </c>
       <c r="I17" t="n">
-        <v>46855.46</v>
+        <v>49022.51</v>
       </c>
       <c r="J17" t="n">
-        <v>47703.53</v>
+        <v>49934.87</v>
       </c>
       <c r="K17" t="n">
-        <v>48613.05</v>
+        <v>50270.54</v>
       </c>
       <c r="L17" t="n">
-        <v>49522.58</v>
+        <v>50606.22</v>
       </c>
       <c r="M17" t="n">
-        <v>50401.37</v>
+        <v>51230.24</v>
       </c>
       <c r="N17" t="n">
-        <v>51280.17</v>
+        <v>51854.25</v>
       </c>
       <c r="O17" t="n">
-        <v>52220.42</v>
+        <v>51901.58</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1945,19 +1945,19 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50691.22</v>
+        <v>51010.28</v>
       </c>
       <c r="C18" t="n">
-        <v>50707.23</v>
+        <v>52523.77</v>
       </c>
       <c r="D18" t="n">
-        <v>50198.97</v>
+        <v>50995.67</v>
       </c>
       <c r="E18" t="n">
-        <v>50339.48</v>
+        <v>51939.89</v>
       </c>
       <c r="F18" t="n">
-        <v>-410.91</v>
+        <v>1600.41</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0081</v>
+        <v>0.0318</v>
       </c>
       <c r="H18" t="n">
-        <v>508.26</v>
+        <v>1528.1</v>
       </c>
       <c r="I18" t="n">
-        <v>49022.51</v>
+        <v>49690.71</v>
       </c>
       <c r="J18" t="n">
-        <v>49934.87</v>
+        <v>49774.41</v>
       </c>
       <c r="K18" t="n">
-        <v>50270.54</v>
+        <v>50085.35</v>
       </c>
       <c r="L18" t="n">
-        <v>50606.22</v>
+        <v>50396.29</v>
       </c>
       <c r="M18" t="n">
-        <v>51230.24</v>
+        <v>50593.61</v>
       </c>
       <c r="N18" t="n">
-        <v>51854.25</v>
+        <v>50790.93</v>
       </c>
       <c r="O18" t="n">
-        <v>51901.58</v>
+        <v>51215.49</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2029,83 +2029,83 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W18" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>51010.28</v>
+        <v>52808.29</v>
       </c>
       <c r="C19" t="n">
-        <v>52523.77</v>
+        <v>54487.32</v>
       </c>
       <c r="D19" t="n">
-        <v>50995.67</v>
+        <v>52741.64</v>
       </c>
       <c r="E19" t="n">
-        <v>51939.89</v>
+        <v>53936.17</v>
       </c>
       <c r="F19" t="n">
-        <v>1600.41</v>
+        <v>1996.28</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0318</v>
+        <v>0.0384</v>
       </c>
       <c r="H19" t="n">
-        <v>1528.1</v>
+        <v>1745.68</v>
       </c>
       <c r="I19" t="n">
-        <v>49690.71</v>
+        <v>49467.57</v>
       </c>
       <c r="J19" t="n">
-        <v>49774.41</v>
+        <v>50501.88</v>
       </c>
       <c r="K19" t="n">
-        <v>50085.35</v>
+        <v>51175.84</v>
       </c>
       <c r="L19" t="n">
-        <v>50396.29</v>
+        <v>51849.81</v>
       </c>
       <c r="M19" t="n">
-        <v>50593.61</v>
+        <v>52703.94</v>
       </c>
       <c r="N19" t="n">
-        <v>50790.93</v>
+        <v>53558.07</v>
       </c>
       <c r="O19" t="n">
-        <v>51215.49</v>
+        <v>54051.87</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2146,151 +2146,151 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>52808.29</v>
+        <v>53390.05</v>
       </c>
       <c r="C20" t="n">
-        <v>54487.32</v>
+        <v>54050.84</v>
       </c>
       <c r="D20" t="n">
-        <v>52741.64</v>
+        <v>52194.81</v>
       </c>
       <c r="E20" t="n">
-        <v>53936.17</v>
+        <v>53846.87</v>
       </c>
       <c r="F20" t="n">
-        <v>1996.28</v>
+        <v>-89.3</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0384</v>
+        <v>-0.0017</v>
       </c>
       <c r="H20" t="n">
-        <v>1745.68</v>
+        <v>1856.03</v>
       </c>
       <c r="I20" t="n">
-        <v>49467.57</v>
+        <v>50995.96</v>
       </c>
       <c r="J20" t="n">
-        <v>50501.88</v>
+        <v>52351.34</v>
       </c>
       <c r="K20" t="n">
-        <v>51175.84</v>
+        <v>53063.33</v>
       </c>
       <c r="L20" t="n">
-        <v>51849.81</v>
+        <v>53775.33</v>
       </c>
       <c r="M20" t="n">
-        <v>52703.94</v>
+        <v>54809.01</v>
       </c>
       <c r="N20" t="n">
-        <v>53558.07</v>
+        <v>55842.7</v>
       </c>
       <c r="O20" t="n">
-        <v>54051.87</v>
+        <v>56233</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>53390.05</v>
+        <v>53023.28</v>
       </c>
       <c r="C21" t="n">
-        <v>54050.84</v>
+        <v>53742.69</v>
       </c>
       <c r="D21" t="n">
-        <v>52194.81</v>
+        <v>52637.66</v>
       </c>
       <c r="E21" t="n">
-        <v>53846.87</v>
+        <v>53322.85</v>
       </c>
       <c r="F21" t="n">
-        <v>-89.3</v>
+        <v>-524.02</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0097</v>
       </c>
       <c r="H21" t="n">
-        <v>1856.03</v>
+        <v>1105.03</v>
       </c>
       <c r="I21" t="n">
-        <v>50995.96</v>
+        <v>50338.78</v>
       </c>
       <c r="J21" t="n">
-        <v>52351.34</v>
+        <v>52352.86</v>
       </c>
       <c r="K21" t="n">
-        <v>53063.33</v>
+        <v>52918.86</v>
       </c>
       <c r="L21" t="n">
-        <v>53775.33</v>
+        <v>53484.85</v>
       </c>
       <c r="M21" t="n">
-        <v>54809.01</v>
+        <v>54774.89</v>
       </c>
       <c r="N21" t="n">
-        <v>55842.7</v>
+        <v>56064.93</v>
       </c>
       <c r="O21" t="n">
-        <v>56233</v>
+        <v>55906.87</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q21" s="6" t="n">
+        <v/>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2309,57 +2309,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>53023.28</v>
+        <v>53575.37</v>
       </c>
       <c r="C22" t="n">
-        <v>53742.69</v>
+        <v>54782.83</v>
       </c>
       <c r="D22" t="n">
-        <v>52637.66</v>
+        <v>52655.18</v>
       </c>
       <c r="E22" t="n">
-        <v>53322.85</v>
+        <v>54253.68</v>
       </c>
       <c r="F22" t="n">
-        <v>-524.02</v>
+        <v>930.83</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0175</v>
       </c>
       <c r="H22" t="n">
-        <v>1105.03</v>
+        <v>2127.65</v>
       </c>
       <c r="I22" t="n">
-        <v>50338.78</v>
+        <v>51532.63</v>
       </c>
       <c r="J22" t="n">
-        <v>52352.86</v>
+        <v>52284.16</v>
       </c>
       <c r="K22" t="n">
-        <v>52918.86</v>
+        <v>52770.34</v>
       </c>
       <c r="L22" t="n">
-        <v>53484.85</v>
+        <v>53256.51</v>
       </c>
       <c r="M22" t="n">
-        <v>54774.89</v>
+        <v>53875.37</v>
       </c>
       <c r="N22" t="n">
-        <v>56064.93</v>
+        <v>54494.22</v>
       </c>
       <c r="O22" t="n">
-        <v>55906.87</v>
+        <v>54847.72</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2372,16 +2372,20 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2391,59 +2395,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>53575.37</v>
+        <v>55130.63</v>
       </c>
       <c r="C23" t="n">
-        <v>54782.83</v>
+        <v>58015.08</v>
       </c>
       <c r="D23" t="n">
-        <v>52655.18</v>
+        <v>55018.57</v>
       </c>
       <c r="E23" t="n">
-        <v>54253.68</v>
+        <v>56941.97</v>
       </c>
       <c r="F23" t="n">
-        <v>930.83</v>
+        <v>2688.29</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0496</v>
       </c>
       <c r="H23" t="n">
-        <v>2127.65</v>
+        <v>2996.51</v>
       </c>
       <c r="I23" t="n">
-        <v>51532.63</v>
+        <v>50527.53</v>
       </c>
       <c r="J23" t="n">
-        <v>52284.16</v>
+        <v>52393.37</v>
       </c>
       <c r="K23" t="n">
-        <v>52770.34</v>
+        <v>53189.86</v>
       </c>
       <c r="L23" t="n">
-        <v>53256.51</v>
+        <v>53986.34</v>
       </c>
       <c r="M23" t="n">
-        <v>53875.37</v>
+        <v>55317.5</v>
       </c>
       <c r="N23" t="n">
-        <v>54494.22</v>
+        <v>56648.67</v>
       </c>
       <c r="O23" t="n">
-        <v>54847.72</v>
+        <v>56910.48</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2451,10 +2451,8 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
@@ -2468,11 +2466,13 @@
       </c>
       <c r="U23" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
@@ -2484,50 +2484,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>55130.63</v>
+        <v>57212.97</v>
       </c>
       <c r="C24" t="n">
-        <v>58015.08</v>
+        <v>57709.82</v>
       </c>
       <c r="D24" t="n">
-        <v>55018.57</v>
+        <v>56135.12</v>
       </c>
       <c r="E24" t="n">
-        <v>56941.97</v>
+        <v>56825.7</v>
       </c>
       <c r="F24" t="n">
-        <v>2688.29</v>
+        <v>-116.27</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0496</v>
+        <v>-0.002</v>
       </c>
       <c r="H24" t="n">
-        <v>2996.51</v>
+        <v>1574.7</v>
       </c>
       <c r="I24" t="n">
-        <v>50527.53</v>
+        <v>52022.06</v>
       </c>
       <c r="J24" t="n">
-        <v>52393.37</v>
+        <v>54158.03</v>
       </c>
       <c r="K24" t="n">
-        <v>53189.86</v>
+        <v>55443.71</v>
       </c>
       <c r="L24" t="n">
-        <v>53986.34</v>
+        <v>56729.4</v>
       </c>
       <c r="M24" t="n">
-        <v>55317.5</v>
+        <v>58440.22</v>
       </c>
       <c r="N24" t="n">
-        <v>56648.67</v>
+        <v>60151.05</v>
       </c>
       <c r="O24" t="n">
-        <v>56910.48</v>
+        <v>61011.59</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2540,78 +2540,76 @@
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>57212.97</v>
+        <v>56764.14</v>
       </c>
       <c r="C25" t="n">
-        <v>57709.82</v>
+        <v>59332.43</v>
       </c>
       <c r="D25" t="n">
-        <v>56135.12</v>
+        <v>56732.93</v>
       </c>
       <c r="E25" t="n">
-        <v>56825.7</v>
+        <v>58850.27</v>
       </c>
       <c r="F25" t="n">
-        <v>-116.27</v>
+        <v>2024.57</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0356</v>
       </c>
       <c r="H25" t="n">
-        <v>1574.7</v>
+        <v>2599.5</v>
       </c>
       <c r="I25" t="n">
-        <v>52022.06</v>
+        <v>54560.42</v>
       </c>
       <c r="J25" t="n">
-        <v>54158.03</v>
+        <v>55202.61</v>
       </c>
       <c r="K25" t="n">
-        <v>55443.71</v>
+        <v>56038.35</v>
       </c>
       <c r="L25" t="n">
-        <v>56729.4</v>
+        <v>56874.08</v>
       </c>
       <c r="M25" t="n">
-        <v>58440.22</v>
+        <v>57613.05</v>
       </c>
       <c r="N25" t="n">
-        <v>60151.05</v>
+        <v>58352.01</v>
       </c>
       <c r="O25" t="n">
-        <v>61011.59</v>
+        <v>59284.52</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2624,109 +2622,111 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>56764.14</v>
+        <v>57976.2</v>
       </c>
       <c r="C26" t="n">
-        <v>59332.43</v>
+        <v>58365.21</v>
       </c>
       <c r="D26" t="n">
-        <v>56732.93</v>
+        <v>53618.2</v>
       </c>
       <c r="E26" t="n">
-        <v>58850.27</v>
+        <v>55620.84</v>
       </c>
       <c r="F26" t="n">
-        <v>2024.57</v>
+        <v>-3229.43</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0356</v>
+        <v>-0.0549</v>
       </c>
       <c r="H26" t="n">
-        <v>2599.5</v>
+        <v>4747.01</v>
       </c>
       <c r="I26" t="n">
-        <v>54560.42</v>
+        <v>54133.43</v>
       </c>
       <c r="J26" t="n">
-        <v>55202.61</v>
+        <v>56659.56</v>
       </c>
       <c r="K26" t="n">
-        <v>56038.35</v>
+        <v>57550.52</v>
       </c>
       <c r="L26" t="n">
-        <v>56874.08</v>
+        <v>58441.47</v>
       </c>
       <c r="M26" t="n">
-        <v>57613.05</v>
+        <v>60150.02</v>
       </c>
       <c r="N26" t="n">
-        <v>58352.01</v>
+        <v>61858.56</v>
       </c>
       <c r="O26" t="n">
-        <v>59284.52</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
+        <v>61931.93</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W26" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W26" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr"/>
@@ -2734,64 +2734,60 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>57976.2</v>
+        <v>54608.63</v>
       </c>
       <c r="C27" t="n">
-        <v>58365.21</v>
+        <v>55745.38</v>
       </c>
       <c r="D27" t="n">
-        <v>53618.2</v>
+        <v>51407.66</v>
       </c>
       <c r="E27" t="n">
-        <v>55620.84</v>
+        <v>53819.61</v>
       </c>
       <c r="F27" t="n">
-        <v>-3229.43</v>
+        <v>-1801.23</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0549</v>
+        <v>-0.0324</v>
       </c>
       <c r="H27" t="n">
-        <v>4747.01</v>
+        <v>4337.72</v>
       </c>
       <c r="I27" t="n">
-        <v>54133.43</v>
+        <v>48871.19</v>
       </c>
       <c r="J27" t="n">
-        <v>56659.56</v>
+        <v>50688.4</v>
       </c>
       <c r="K27" t="n">
-        <v>57550.52</v>
+        <v>53247.33</v>
       </c>
       <c r="L27" t="n">
-        <v>58441.47</v>
+        <v>55806.27</v>
       </c>
       <c r="M27" t="n">
-        <v>60150.02</v>
+        <v>57994.35</v>
       </c>
       <c r="N27" t="n">
-        <v>61858.56</v>
+        <v>60182.42</v>
       </c>
       <c r="O27" t="n">
-        <v>61931.93</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q27" s="6" t="inlineStr">
+        <v>63112.22</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
@@ -2818,50 +2814,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>54608.63</v>
+        <v>53627.86</v>
       </c>
       <c r="C28" t="n">
-        <v>55745.38</v>
+        <v>55239.4</v>
       </c>
       <c r="D28" t="n">
-        <v>51407.66</v>
+        <v>53113.95</v>
       </c>
       <c r="E28" t="n">
-        <v>53819.61</v>
+        <v>53372.53</v>
       </c>
       <c r="F28" t="n">
-        <v>-1801.23</v>
+        <v>-447.08</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0324</v>
+        <v>-0.0083</v>
       </c>
       <c r="H28" t="n">
-        <v>4337.72</v>
+        <v>2125.45</v>
       </c>
       <c r="I28" t="n">
-        <v>48871.19</v>
+        <v>47069.94</v>
       </c>
       <c r="J28" t="n">
-        <v>50688.4</v>
+        <v>49603.44</v>
       </c>
       <c r="K28" t="n">
-        <v>53247.33</v>
+        <v>51650.75</v>
       </c>
       <c r="L28" t="n">
-        <v>55806.27</v>
+        <v>53698.06</v>
       </c>
       <c r="M28" t="n">
-        <v>57994.35</v>
+        <v>55988.47</v>
       </c>
       <c r="N28" t="n">
-        <v>60182.42</v>
+        <v>58278.87</v>
       </c>
       <c r="O28" t="n">
-        <v>63112.22</v>
+        <v>60083.1</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2869,14 +2865,12 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R28" s="6" t="n">
+        <v/>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2893,64 +2887,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>53627.86</v>
+        <v>52468.72</v>
       </c>
       <c r="C29" t="n">
-        <v>55239.4</v>
+        <v>54175.8</v>
       </c>
       <c r="D29" t="n">
-        <v>53113.95</v>
+        <v>50688.76</v>
       </c>
       <c r="E29" t="n">
-        <v>53372.53</v>
+        <v>53373.07</v>
       </c>
       <c r="F29" t="n">
-        <v>-447.08</v>
+        <v>0.54</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0083</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2125.45</v>
+        <v>3487.04</v>
       </c>
       <c r="I29" t="n">
-        <v>47069.94</v>
+        <v>50988.5</v>
       </c>
       <c r="J29" t="n">
-        <v>49603.44</v>
+        <v>50845.01</v>
       </c>
       <c r="K29" t="n">
-        <v>51650.75</v>
+        <v>52309.81</v>
       </c>
       <c r="L29" t="n">
-        <v>53698.06</v>
+        <v>53774.6</v>
       </c>
       <c r="M29" t="n">
-        <v>55988.47</v>
+        <v>54435.26</v>
       </c>
       <c r="N29" t="n">
-        <v>58278.87</v>
+        <v>55095.91</v>
       </c>
       <c r="O29" t="n">
-        <v>60083.1</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+        <v>57364.85</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
@@ -2980,69 +2984,65 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>52468.72</v>
+        <v>52054.68</v>
       </c>
       <c r="C30" t="n">
-        <v>54175.8</v>
+        <v>54258.48</v>
       </c>
       <c r="D30" t="n">
-        <v>50688.76</v>
+        <v>50558.91</v>
       </c>
       <c r="E30" t="n">
-        <v>53373.07</v>
+        <v>53123.49</v>
       </c>
       <c r="F30" t="n">
-        <v>0.54</v>
+        <v>-249.58</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0</v>
+        <v>-0.0047</v>
       </c>
       <c r="H30" t="n">
-        <v>3487.04</v>
+        <v>3699.57</v>
       </c>
       <c r="I30" t="n">
-        <v>50988.5</v>
+        <v>47201.72</v>
       </c>
       <c r="J30" t="n">
-        <v>50845.01</v>
+        <v>50356.43</v>
       </c>
       <c r="K30" t="n">
-        <v>52309.81</v>
+        <v>51629.55</v>
       </c>
       <c r="L30" t="n">
-        <v>53774.6</v>
+        <v>52902.68</v>
       </c>
       <c r="M30" t="n">
-        <v>54435.26</v>
+        <v>55116.59</v>
       </c>
       <c r="N30" t="n">
-        <v>55095.91</v>
+        <v>57330.5</v>
       </c>
       <c r="O30" t="n">
-        <v>57364.85</v>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>57662.84</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3068,50 +3068,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>52054.68</v>
+        <v>53205.93</v>
       </c>
       <c r="C31" t="n">
-        <v>54258.48</v>
+        <v>57012.77</v>
       </c>
       <c r="D31" t="n">
-        <v>50558.91</v>
+        <v>53156.94</v>
       </c>
       <c r="E31" t="n">
-        <v>53123.49</v>
+        <v>56924.11</v>
       </c>
       <c r="F31" t="n">
-        <v>-249.58</v>
+        <v>3800.62</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0047</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>3699.57</v>
+        <v>3855.83</v>
       </c>
       <c r="I31" t="n">
-        <v>47201.72</v>
+        <v>46859.34</v>
       </c>
       <c r="J31" t="n">
-        <v>50356.43</v>
+        <v>49781.31</v>
       </c>
       <c r="K31" t="n">
-        <v>51629.55</v>
+        <v>51273.7</v>
       </c>
       <c r="L31" t="n">
-        <v>52902.68</v>
+        <v>52766.09</v>
       </c>
       <c r="M31" t="n">
-        <v>55116.59</v>
+        <v>54973.27</v>
       </c>
       <c r="N31" t="n">
-        <v>57330.5</v>
+        <v>57180.46</v>
       </c>
       <c r="O31" t="n">
-        <v>57662.84</v>
+        <v>57958.05</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3119,21 +3119,23 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R31" s="6" t="n">
+        <v/>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3145,57 +3147,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>53205.93</v>
+        <v>56421.46</v>
       </c>
       <c r="C32" t="n">
-        <v>57012.77</v>
+        <v>59688.1</v>
       </c>
       <c r="D32" t="n">
-        <v>53156.94</v>
+        <v>56232.78</v>
       </c>
       <c r="E32" t="n">
-        <v>56924.11</v>
+        <v>58475.9</v>
       </c>
       <c r="F32" t="n">
-        <v>3800.62</v>
+        <v>1551.79</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0273</v>
       </c>
       <c r="H32" t="n">
-        <v>3855.83</v>
+        <v>3455.32</v>
       </c>
       <c r="I32" t="n">
-        <v>46859.34</v>
+        <v>49301.11</v>
       </c>
       <c r="J32" t="n">
-        <v>49781.31</v>
+        <v>53987.91</v>
       </c>
       <c r="K32" t="n">
-        <v>51273.7</v>
+        <v>54996.2</v>
       </c>
       <c r="L32" t="n">
-        <v>52766.09</v>
+        <v>56004.48</v>
       </c>
       <c r="M32" t="n">
-        <v>54973.27</v>
+        <v>58852.02</v>
       </c>
       <c r="N32" t="n">
-        <v>57180.46</v>
+        <v>61699.56</v>
       </c>
       <c r="O32" t="n">
-        <v>57958.05</v>
+        <v>60868.6</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3213,13 +3215,11 @@
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3238,50 +3238,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>56421.46</v>
+        <v>58821.16</v>
       </c>
       <c r="C33" t="n">
-        <v>59688.1</v>
+        <v>60013.98</v>
       </c>
       <c r="D33" t="n">
-        <v>56232.78</v>
+        <v>58621.48</v>
       </c>
       <c r="E33" t="n">
-        <v>58475.9</v>
+        <v>59716.18</v>
       </c>
       <c r="F33" t="n">
-        <v>1551.79</v>
+        <v>1240.28</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0273</v>
+        <v>0.0212</v>
       </c>
       <c r="H33" t="n">
-        <v>3455.32</v>
+        <v>1392.5</v>
       </c>
       <c r="I33" t="n">
-        <v>49301.11</v>
+        <v>52777.46</v>
       </c>
       <c r="J33" t="n">
-        <v>53987.91</v>
+        <v>55278.31</v>
       </c>
       <c r="K33" t="n">
-        <v>54996.2</v>
+        <v>56748.24</v>
       </c>
       <c r="L33" t="n">
-        <v>56004.48</v>
+        <v>58218.17</v>
       </c>
       <c r="M33" t="n">
-        <v>58852.02</v>
+        <v>60203.56</v>
       </c>
       <c r="N33" t="n">
-        <v>61699.56</v>
+        <v>62188.95</v>
       </c>
       <c r="O33" t="n">
-        <v>60868.6</v>
+        <v>63143.42</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3322,50 +3322,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>58821.16</v>
+        <v>59880.71</v>
       </c>
       <c r="C34" t="n">
-        <v>60013.98</v>
+        <v>60903.95</v>
       </c>
       <c r="D34" t="n">
-        <v>58621.48</v>
+        <v>58928.2</v>
       </c>
       <c r="E34" t="n">
-        <v>59716.18</v>
+        <v>59513.12</v>
       </c>
       <c r="F34" t="n">
-        <v>1240.28</v>
+        <v>-203.06</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0034</v>
       </c>
       <c r="H34" t="n">
-        <v>1392.5</v>
+        <v>1975.75</v>
       </c>
       <c r="I34" t="n">
-        <v>52777.46</v>
+        <v>57228.98</v>
       </c>
       <c r="J34" t="n">
-        <v>55278.31</v>
+        <v>58522.9</v>
       </c>
       <c r="K34" t="n">
-        <v>56748.24</v>
+        <v>59019.93</v>
       </c>
       <c r="L34" t="n">
-        <v>58218.17</v>
+        <v>59516.96</v>
       </c>
       <c r="M34" t="n">
-        <v>60203.56</v>
+        <v>60412.43</v>
       </c>
       <c r="N34" t="n">
-        <v>62188.95</v>
+        <v>61307.9</v>
       </c>
       <c r="O34" t="n">
-        <v>63143.42</v>
+        <v>61406.48</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3373,17 +3373,19 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U34" s="8" t="n">
@@ -3399,57 +3401,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>59880.71</v>
+        <v>60241.31</v>
       </c>
       <c r="C35" t="n">
-        <v>60903.95</v>
+        <v>63091.14</v>
       </c>
       <c r="D35" t="n">
-        <v>58928.2</v>
+        <v>60213.02</v>
       </c>
       <c r="E35" t="n">
-        <v>59513.12</v>
+        <v>62713.65</v>
       </c>
       <c r="F35" t="n">
-        <v>-203.06</v>
+        <v>3200.53</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0538</v>
       </c>
       <c r="H35" t="n">
-        <v>1975.75</v>
+        <v>2878.12</v>
       </c>
       <c r="I35" t="n">
-        <v>57228.98</v>
+        <v>56952.45</v>
       </c>
       <c r="J35" t="n">
-        <v>58522.9</v>
+        <v>57335.89</v>
       </c>
       <c r="K35" t="n">
-        <v>59019.93</v>
+        <v>58525.25</v>
       </c>
       <c r="L35" t="n">
-        <v>59516.96</v>
+        <v>59714.6</v>
       </c>
       <c r="M35" t="n">
-        <v>60412.43</v>
+        <v>60501</v>
       </c>
       <c r="N35" t="n">
-        <v>61307.9</v>
+        <v>61287.39</v>
       </c>
       <c r="O35" t="n">
-        <v>61406.48</v>
+        <v>62879.7</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3457,14 +3459,12 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
@@ -3472,70 +3472,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W35" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W35" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>60241.31</v>
+        <v>63203.44</v>
       </c>
       <c r="C36" t="n">
-        <v>63091.14</v>
+        <v>63799.32</v>
       </c>
       <c r="D36" t="n">
-        <v>60213.02</v>
+        <v>60937.3</v>
       </c>
       <c r="E36" t="n">
-        <v>62713.65</v>
+        <v>61409.29</v>
       </c>
       <c r="F36" t="n">
-        <v>3200.53</v>
+        <v>-1304.36</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0538</v>
+        <v>-0.0208</v>
       </c>
       <c r="H36" t="n">
-        <v>2878.12</v>
+        <v>2862.02</v>
       </c>
       <c r="I36" t="n">
-        <v>56952.45</v>
+        <v>57334.9</v>
       </c>
       <c r="J36" t="n">
-        <v>57335.89</v>
+        <v>60366.31</v>
       </c>
       <c r="K36" t="n">
-        <v>58525.25</v>
+        <v>61274.59</v>
       </c>
       <c r="L36" t="n">
-        <v>59714.6</v>
+        <v>62182.86</v>
       </c>
       <c r="M36" t="n">
-        <v>60501</v>
+        <v>64152.71</v>
       </c>
       <c r="N36" t="n">
-        <v>61287.39</v>
+        <v>66122.55</v>
       </c>
       <c r="O36" t="n">
-        <v>62879.7</v>
+        <v>65969.25999999999</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3543,83 +3543,83 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
+      </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>63203.44</v>
+        <v>61299.87</v>
       </c>
       <c r="C37" t="n">
-        <v>63799.32</v>
+        <v>63432.41</v>
       </c>
       <c r="D37" t="n">
-        <v>60937.3</v>
+        <v>59292.25</v>
       </c>
       <c r="E37" t="n">
-        <v>61409.29</v>
+        <v>63339.07</v>
       </c>
       <c r="F37" t="n">
-        <v>-1304.36</v>
+        <v>1929.78</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0314</v>
       </c>
       <c r="H37" t="n">
-        <v>2862.02</v>
+        <v>4140.16</v>
       </c>
       <c r="I37" t="n">
-        <v>57334.9</v>
+        <v>58075.28</v>
       </c>
       <c r="J37" t="n">
-        <v>60366.31</v>
+        <v>58067.76</v>
       </c>
       <c r="K37" t="n">
-        <v>61274.59</v>
+        <v>59978.28</v>
       </c>
       <c r="L37" t="n">
-        <v>62182.86</v>
+        <v>61888.8</v>
       </c>
       <c r="M37" t="n">
-        <v>64152.71</v>
+        <v>62840.3</v>
       </c>
       <c r="N37" t="n">
-        <v>66122.55</v>
+        <v>63791.8</v>
       </c>
       <c r="O37" t="n">
-        <v>65969.25999999999</v>
+        <v>66661.34</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3629,20 +3629,24 @@
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
@@ -3653,57 +3657,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>61299.87</v>
+        <v>63658.95</v>
       </c>
       <c r="C38" t="n">
-        <v>63432.41</v>
+        <v>66505.02</v>
       </c>
       <c r="D38" t="n">
-        <v>59292.25</v>
+        <v>63562.51</v>
       </c>
       <c r="E38" t="n">
-        <v>63339.07</v>
+        <v>66329.5</v>
       </c>
       <c r="F38" t="n">
-        <v>1929.78</v>
+        <v>2990.43</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0314</v>
+        <v>0.0472</v>
       </c>
       <c r="H38" t="n">
-        <v>4140.16</v>
+        <v>2942.51</v>
       </c>
       <c r="I38" t="n">
-        <v>58075.28</v>
+        <v>55152.09</v>
       </c>
       <c r="J38" t="n">
-        <v>58067.76</v>
+        <v>60187.28</v>
       </c>
       <c r="K38" t="n">
-        <v>59978.28</v>
+        <v>61268.99</v>
       </c>
       <c r="L38" t="n">
-        <v>61888.8</v>
+        <v>62350.7</v>
       </c>
       <c r="M38" t="n">
-        <v>62840.3</v>
+        <v>65409.15</v>
       </c>
       <c r="N38" t="n">
-        <v>63791.8</v>
+        <v>68467.60000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>66661.34</v>
+        <v>67572.57000000001</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3711,10 +3715,8 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
@@ -3723,14 +3725,12 @@
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
@@ -3739,59 +3739,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>63658.95</v>
+        <v>66363.42999999999</v>
       </c>
       <c r="C39" t="n">
-        <v>66505.02</v>
+        <v>68786.49000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>63562.51</v>
+        <v>65551.13</v>
       </c>
       <c r="E39" t="n">
-        <v>66329.5</v>
+        <v>66588.12</v>
       </c>
       <c r="F39" t="n">
-        <v>2990.43</v>
+        <v>258.62</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0472</v>
+        <v>0.0039</v>
       </c>
       <c r="H39" t="n">
-        <v>2942.51</v>
+        <v>3235.36</v>
       </c>
       <c r="I39" t="n">
-        <v>55152.09</v>
+        <v>60620</v>
       </c>
       <c r="J39" t="n">
-        <v>60187.28</v>
+        <v>64034.85</v>
       </c>
       <c r="K39" t="n">
-        <v>61268.99</v>
+        <v>64858.24</v>
       </c>
       <c r="L39" t="n">
-        <v>62350.7</v>
+        <v>65681.63</v>
       </c>
       <c r="M39" t="n">
-        <v>65409.15</v>
+        <v>67800.75999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>68467.60000000001</v>
+        <v>69919.88</v>
       </c>
       <c r="O39" t="n">
-        <v>67572.57000000001</v>
+        <v>69447.53999999999</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3804,12 +3800,12 @@
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U39" s="8" t="n">
@@ -3828,69 +3824,71 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>66363.42999999999</v>
+        <v>65947.56</v>
       </c>
       <c r="C40" t="n">
-        <v>68786.49000000001</v>
+        <v>67065.94</v>
       </c>
       <c r="D40" t="n">
-        <v>65551.13</v>
+        <v>62335.75</v>
       </c>
       <c r="E40" t="n">
-        <v>66588.12</v>
+        <v>66020.03999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>258.62</v>
+        <v>-568.08</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0039</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>3235.36</v>
+        <v>4730.19</v>
       </c>
       <c r="I40" t="n">
-        <v>60620</v>
+        <v>62315.77</v>
       </c>
       <c r="J40" t="n">
-        <v>64034.85</v>
+        <v>63062.41</v>
       </c>
       <c r="K40" t="n">
-        <v>64858.24</v>
+        <v>64970.44</v>
       </c>
       <c r="L40" t="n">
-        <v>65681.63</v>
+        <v>66878.46000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>67800.75999999999</v>
+        <v>68205.8</v>
       </c>
       <c r="N40" t="n">
-        <v>69919.88</v>
+        <v>69533.13</v>
       </c>
       <c r="O40" t="n">
-        <v>69447.53999999999</v>
+        <v>72021.85000000001</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3903,141 +3901,143 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>65947.56</v>
+        <v>66783.22</v>
       </c>
       <c r="C41" t="n">
-        <v>67065.94</v>
+        <v>71952.99000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>62335.75</v>
+        <v>66783.22</v>
       </c>
       <c r="E41" t="n">
-        <v>66020.03999999999</v>
+        <v>71250.06</v>
       </c>
       <c r="F41" t="n">
-        <v>-568.08</v>
+        <v>5230.02</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>4730.19</v>
+        <v>5169.77</v>
       </c>
       <c r="I41" t="n">
-        <v>62315.77</v>
+        <v>57605.56</v>
       </c>
       <c r="J41" t="n">
-        <v>63062.41</v>
+        <v>61949.45</v>
       </c>
       <c r="K41" t="n">
-        <v>64970.44</v>
+        <v>63654.95</v>
       </c>
       <c r="L41" t="n">
-        <v>66878.46000000001</v>
+        <v>65360.44</v>
       </c>
       <c r="M41" t="n">
-        <v>68205.8</v>
+        <v>68385.13</v>
       </c>
       <c r="N41" t="n">
-        <v>69533.13</v>
+        <v>71409.82000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>72021.85000000001</v>
+        <v>71796.12</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v/>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>66783.22</v>
+        <v>71067.14999999999</v>
       </c>
       <c r="C42" t="n">
-        <v>71952.99000000001</v>
+        <v>72831.73</v>
       </c>
       <c r="D42" t="n">
-        <v>66783.22</v>
+        <v>68461.10000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>71250.06</v>
+        <v>69360.88</v>
       </c>
       <c r="F42" t="n">
-        <v>5230.02</v>
+        <v>-1889.18</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.07920000000000001</v>
+        <v>-0.0265</v>
       </c>
       <c r="H42" t="n">
-        <v>5169.77</v>
+        <v>4370.62</v>
       </c>
       <c r="I42" t="n">
-        <v>57605.56</v>
+        <v>61613.45</v>
       </c>
       <c r="J42" t="n">
-        <v>61949.45</v>
+        <v>67021.27</v>
       </c>
       <c r="K42" t="n">
-        <v>63654.95</v>
+        <v>68665.17999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>65360.44</v>
+        <v>70309.08</v>
       </c>
       <c r="M42" t="n">
-        <v>68385.13</v>
+        <v>73834.95</v>
       </c>
       <c r="N42" t="n">
-        <v>71409.82000000001</v>
+        <v>77360.81</v>
       </c>
       <c r="O42" t="n">
-        <v>71796.12</v>
+        <v>77122.77</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4045,83 +4045,83 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
+      <c r="R42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v/>
       </c>
       <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>71067.14999999999</v>
+        <v>69609.88</v>
       </c>
       <c r="C43" t="n">
-        <v>72831.73</v>
+        <v>71962.34</v>
       </c>
       <c r="D43" t="n">
-        <v>68461.10000000001</v>
+        <v>67609.49000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>69360.88</v>
+        <v>69744.07000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>-1889.18</v>
+        <v>383.19</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0265</v>
+        <v>0.0055</v>
       </c>
       <c r="H43" t="n">
-        <v>4370.62</v>
+        <v>4352.85</v>
       </c>
       <c r="I43" t="n">
-        <v>61613.45</v>
+        <v>64090.48</v>
       </c>
       <c r="J43" t="n">
-        <v>67021.27</v>
+        <v>64347.49</v>
       </c>
       <c r="K43" t="n">
-        <v>68665.17999999999</v>
+        <v>67175.57000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>70309.08</v>
+        <v>70003.64999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>73834.95</v>
+        <v>71546.2</v>
       </c>
       <c r="N43" t="n">
-        <v>77360.81</v>
+        <v>73088.74000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>77122.77</v>
+        <v>77202.35000000001</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4129,18 +4129,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R43" s="6" t="n">
+        <v/>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>69609.88</v>
+        <v>69973.34</v>
       </c>
       <c r="C44" t="n">
-        <v>71962.34</v>
+        <v>70384.59</v>
       </c>
       <c r="D44" t="n">
-        <v>67609.49000000001</v>
+        <v>66819.05</v>
       </c>
       <c r="E44" t="n">
-        <v>69744.07000000001</v>
+        <v>68557.73</v>
       </c>
       <c r="F44" t="n">
-        <v>383.19</v>
+        <v>-1186.34</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0055</v>
+        <v>-0.017</v>
       </c>
       <c r="H44" t="n">
-        <v>4352.85</v>
+        <v>3565.55</v>
       </c>
       <c r="I44" t="n">
-        <v>64090.48</v>
+        <v>63256.64</v>
       </c>
       <c r="J44" t="n">
-        <v>64347.49</v>
+        <v>65370.29</v>
       </c>
       <c r="K44" t="n">
-        <v>67175.57000000001</v>
+        <v>67567.64</v>
       </c>
       <c r="L44" t="n">
-        <v>70003.64999999999</v>
+        <v>69764.99000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>71546.2</v>
+        <v>71920.5</v>
       </c>
       <c r="N44" t="n">
-        <v>73088.74000000001</v>
+        <v>74076</v>
       </c>
       <c r="O44" t="n">
-        <v>77202.35000000001</v>
+        <v>76315.2</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4213,18 +4213,18 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4239,67 +4239,71 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>69973.34</v>
+        <v>68410.63</v>
       </c>
       <c r="C45" t="n">
-        <v>70384.59</v>
+        <v>69078.21000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>66819.05</v>
+        <v>62704.6</v>
       </c>
       <c r="E45" t="n">
-        <v>68557.73</v>
+        <v>64141.12</v>
       </c>
       <c r="F45" t="n">
-        <v>-1186.34</v>
+        <v>-4416.61</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0644</v>
       </c>
       <c r="H45" t="n">
-        <v>3565.55</v>
+        <v>6373.61</v>
       </c>
       <c r="I45" t="n">
-        <v>63256.64</v>
+        <v>63253.5</v>
       </c>
       <c r="J45" t="n">
-        <v>65370.29</v>
+        <v>64970.13</v>
       </c>
       <c r="K45" t="n">
-        <v>67567.64</v>
+        <v>66774.95</v>
       </c>
       <c r="L45" t="n">
-        <v>69764.99000000001</v>
+        <v>68579.77</v>
       </c>
       <c r="M45" t="n">
-        <v>71920.5</v>
+        <v>70340.5</v>
       </c>
       <c r="N45" t="n">
-        <v>74076</v>
+        <v>72101.23</v>
       </c>
       <c r="O45" t="n">
-        <v>76315.2</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
+        <v>73950.14</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
@@ -4316,87 +4320,79 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W45" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>68410.63</v>
+        <v>64544.05</v>
       </c>
       <c r="C46" t="n">
-        <v>69078.21000000001</v>
+        <v>67592.2</v>
       </c>
       <c r="D46" t="n">
-        <v>62704.6</v>
+        <v>64201.03</v>
       </c>
       <c r="E46" t="n">
-        <v>64141.12</v>
+        <v>64611.15</v>
       </c>
       <c r="F46" t="n">
-        <v>-4416.61</v>
+        <v>470.03</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0644</v>
+        <v>0.0073</v>
       </c>
       <c r="H46" t="n">
-        <v>6373.61</v>
+        <v>3391.17</v>
       </c>
       <c r="I46" t="n">
-        <v>63253.5</v>
+        <v>56330.99</v>
       </c>
       <c r="J46" t="n">
-        <v>64970.13</v>
+        <v>56892.37</v>
       </c>
       <c r="K46" t="n">
-        <v>66774.95</v>
+        <v>60954.32</v>
       </c>
       <c r="L46" t="n">
-        <v>68579.77</v>
+        <v>65016.26</v>
       </c>
       <c r="M46" t="n">
-        <v>70340.5</v>
+        <v>67327.92999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>72101.23</v>
+        <v>69639.59</v>
       </c>
       <c r="O46" t="n">
-        <v>73950.14</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>75451.82000000001</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4409,74 +4405,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>64544.05</v>
+        <v>65164.98</v>
       </c>
       <c r="C47" t="n">
-        <v>67592.2</v>
+        <v>65364.73</v>
       </c>
       <c r="D47" t="n">
-        <v>64201.03</v>
+        <v>60448.9</v>
       </c>
       <c r="E47" t="n">
-        <v>64611.15</v>
+        <v>64362.02</v>
       </c>
       <c r="F47" t="n">
-        <v>470.03</v>
+        <v>-249.13</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0073</v>
+        <v>-0.0039</v>
       </c>
       <c r="H47" t="n">
-        <v>3391.17</v>
+        <v>4915.83</v>
       </c>
       <c r="I47" t="n">
-        <v>56330.99</v>
+        <v>60809.86</v>
       </c>
       <c r="J47" t="n">
-        <v>56892.37</v>
+        <v>60577.24</v>
       </c>
       <c r="K47" t="n">
-        <v>60954.32</v>
+        <v>62915.56</v>
       </c>
       <c r="L47" t="n">
-        <v>65016.26</v>
+        <v>65253.88</v>
       </c>
       <c r="M47" t="n">
-        <v>67327.92999999999</v>
+        <v>66306.73</v>
       </c>
       <c r="N47" t="n">
-        <v>69639.59</v>
+        <v>67359.59</v>
       </c>
       <c r="O47" t="n">
-        <v>75451.82000000001</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+        <v>70983.38</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4489,82 +4493,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>65164.98</v>
+        <v>63834.95</v>
       </c>
       <c r="C48" t="n">
-        <v>65364.73</v>
+        <v>66302.52</v>
       </c>
       <c r="D48" t="n">
-        <v>60448.9</v>
+        <v>62703.47</v>
       </c>
       <c r="E48" t="n">
-        <v>64362.02</v>
+        <v>65606.71000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>-249.13</v>
+        <v>1244.69</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0193</v>
       </c>
       <c r="H48" t="n">
-        <v>4915.83</v>
+        <v>3599.05</v>
       </c>
       <c r="I48" t="n">
-        <v>60809.86</v>
+        <v>55533.07</v>
       </c>
       <c r="J48" t="n">
-        <v>60577.24</v>
+        <v>60173.79</v>
       </c>
       <c r="K48" t="n">
-        <v>62915.56</v>
+        <v>61904.1</v>
       </c>
       <c r="L48" t="n">
-        <v>65253.88</v>
+        <v>63634.42</v>
       </c>
       <c r="M48" t="n">
-        <v>66306.73</v>
+        <v>66819.94</v>
       </c>
       <c r="N48" t="n">
-        <v>67359.59</v>
+        <v>70005.45</v>
       </c>
       <c r="O48" t="n">
-        <v>70983.38</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+        <v>70280.56</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4577,55 +4573,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>63834.95</v>
+        <v>65905.10000000001</v>
       </c>
       <c r="C49" t="n">
-        <v>66302.52</v>
+        <v>69608.24000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>62703.47</v>
+        <v>65848.58</v>
       </c>
       <c r="E49" t="n">
-        <v>65606.71000000001</v>
+        <v>68713.8</v>
       </c>
       <c r="F49" t="n">
-        <v>1244.69</v>
+        <v>3107.09</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0193</v>
+        <v>0.0474</v>
       </c>
       <c r="H49" t="n">
-        <v>3599.05</v>
+        <v>3759.66</v>
       </c>
       <c r="I49" t="n">
-        <v>55533.07</v>
+        <v>59104.41</v>
       </c>
       <c r="J49" t="n">
-        <v>60173.79</v>
+        <v>62559.51</v>
       </c>
       <c r="K49" t="n">
-        <v>61904.1</v>
+        <v>63807.18</v>
       </c>
       <c r="L49" t="n">
-        <v>63634.42</v>
+        <v>65054.85</v>
       </c>
       <c r="M49" t="n">
-        <v>66819.94</v>
+        <v>67406.24000000001</v>
       </c>
       <c r="N49" t="n">
-        <v>70005.45</v>
+        <v>69757.62</v>
       </c>
       <c r="O49" t="n">
-        <v>70280.56</v>
+        <v>69901.58</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4643,11 +4643,13 @@
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4666,75 +4668,75 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>65905.10000000001</v>
+        <v>68882.06</v>
       </c>
       <c r="C50" t="n">
-        <v>69608.24000000001</v>
+        <v>69225.57000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>65848.58</v>
+        <v>65133.98</v>
       </c>
       <c r="E50" t="n">
-        <v>68713.8</v>
+        <v>66016.36</v>
       </c>
       <c r="F50" t="n">
-        <v>3107.09</v>
+        <v>-2697.44</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0474</v>
+        <v>-0.0393</v>
       </c>
       <c r="H50" t="n">
-        <v>3759.66</v>
+        <v>4091.59</v>
       </c>
       <c r="I50" t="n">
-        <v>59104.41</v>
+        <v>62088.91</v>
       </c>
       <c r="J50" t="n">
-        <v>62559.51</v>
+        <v>65446.83</v>
       </c>
       <c r="K50" t="n">
-        <v>63807.18</v>
+        <v>66833.96000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>65054.85</v>
+        <v>68221.10000000001</v>
       </c>
       <c r="M50" t="n">
-        <v>67406.24000000001</v>
+        <v>70593.63</v>
       </c>
       <c r="N50" t="n">
-        <v>69757.62</v>
+        <v>72966.14999999999</v>
       </c>
       <c r="O50" t="n">
-        <v>69901.58</v>
+        <v>73367.91</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
+      <c r="Q50" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
@@ -4743,76 +4745,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>68882.06</v>
+        <v>65978.95</v>
       </c>
       <c r="C51" t="n">
-        <v>69225.57000000001</v>
+        <v>66954.69</v>
       </c>
       <c r="D51" t="n">
-        <v>65133.98</v>
+        <v>64609.47</v>
       </c>
       <c r="E51" t="n">
-        <v>66016.36</v>
+        <v>66405.56</v>
       </c>
       <c r="F51" t="n">
-        <v>-2697.44</v>
+        <v>389.2</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0393</v>
+        <v>0.0059</v>
       </c>
       <c r="H51" t="n">
-        <v>4091.59</v>
+        <v>2345.22</v>
       </c>
       <c r="I51" t="n">
-        <v>62088.91</v>
+        <v>61042.39</v>
       </c>
       <c r="J51" t="n">
-        <v>65446.83</v>
+        <v>61343.06</v>
       </c>
       <c r="K51" t="n">
-        <v>66833.96000000001</v>
+        <v>63970.56</v>
       </c>
       <c r="L51" t="n">
-        <v>68221.10000000001</v>
+        <v>66598.07000000001</v>
       </c>
       <c r="M51" t="n">
-        <v>70593.63</v>
+        <v>68062.14999999999</v>
       </c>
       <c r="N51" t="n">
-        <v>72966.14999999999</v>
+        <v>69526.24000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>73367.91</v>
+        <v>73317.16</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4829,68 +4823,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>65978.95</v>
+        <v>65668.50999999999</v>
       </c>
       <c r="C52" t="n">
-        <v>66954.69</v>
+        <v>66525.7</v>
       </c>
       <c r="D52" t="n">
-        <v>64609.47</v>
+        <v>63772.8</v>
       </c>
       <c r="E52" t="n">
-        <v>66405.56</v>
+        <v>65020.94</v>
       </c>
       <c r="F52" t="n">
-        <v>389.2</v>
+        <v>-1384.62</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0209</v>
       </c>
       <c r="H52" t="n">
-        <v>2345.22</v>
+        <v>2752.9</v>
       </c>
       <c r="I52" t="n">
-        <v>61042.39</v>
+        <v>62264.25</v>
       </c>
       <c r="J52" t="n">
-        <v>61343.06</v>
+        <v>64372.09</v>
       </c>
       <c r="K52" t="n">
-        <v>63970.56</v>
+        <v>65232.95</v>
       </c>
       <c r="L52" t="n">
-        <v>66598.07000000001</v>
+        <v>66093.82000000001</v>
       </c>
       <c r="M52" t="n">
-        <v>68062.14999999999</v>
+        <v>67578.17</v>
       </c>
       <c r="N52" t="n">
-        <v>69526.24000000001</v>
+        <v>69062.52</v>
       </c>
       <c r="O52" t="n">
-        <v>73317.16</v>
+        <v>69299.91</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4907,67 +4909,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>65668.50999999999</v>
+        <v>65600.42</v>
       </c>
       <c r="C53" t="n">
-        <v>66525.7</v>
+        <v>66791.84</v>
       </c>
       <c r="D53" t="n">
-        <v>63772.8</v>
+        <v>63208.63</v>
       </c>
       <c r="E53" t="n">
-        <v>65020.94</v>
+        <v>64011.34</v>
       </c>
       <c r="F53" t="n">
-        <v>-1384.62</v>
+        <v>-1009.6</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0209</v>
+        <v>-0.0155</v>
       </c>
       <c r="H53" t="n">
-        <v>2752.9</v>
+        <v>3583.21</v>
       </c>
       <c r="I53" t="n">
-        <v>62264.25</v>
+        <v>61019.9</v>
       </c>
       <c r="J53" t="n">
-        <v>64372.09</v>
+        <v>62203.88</v>
       </c>
       <c r="K53" t="n">
-        <v>65232.95</v>
+        <v>63644.49</v>
       </c>
       <c r="L53" t="n">
-        <v>66093.82000000001</v>
+        <v>65085.1</v>
       </c>
       <c r="M53" t="n">
-        <v>67578.17</v>
+        <v>66397.39</v>
       </c>
       <c r="N53" t="n">
-        <v>69062.52</v>
+        <v>67709.69</v>
       </c>
       <c r="O53" t="n">
-        <v>69299.91</v>
+        <v>69278.61</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q53" s="6" t="n">
+        <v/>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
@@ -4979,8 +4975,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4993,55 +4991,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>65600.42</v>
+        <v>63659.53</v>
       </c>
       <c r="C54" t="n">
-        <v>66791.84</v>
+        <v>65436.57</v>
       </c>
       <c r="D54" t="n">
-        <v>63208.63</v>
+        <v>62726.18</v>
       </c>
       <c r="E54" t="n">
-        <v>64011.34</v>
+        <v>65018.95</v>
       </c>
       <c r="F54" t="n">
-        <v>-1009.6</v>
+        <v>1007.61</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0157</v>
       </c>
       <c r="H54" t="n">
-        <v>3583.21</v>
+        <v>2710.39</v>
       </c>
       <c r="I54" t="n">
-        <v>61019.9</v>
+        <v>59625.41</v>
       </c>
       <c r="J54" t="n">
-        <v>62203.88</v>
+        <v>59933.68</v>
       </c>
       <c r="K54" t="n">
-        <v>63644.49</v>
+        <v>62219.73</v>
       </c>
       <c r="L54" t="n">
-        <v>65085.1</v>
+        <v>64505.79</v>
       </c>
       <c r="M54" t="n">
-        <v>66397.39</v>
+        <v>65802.95</v>
       </c>
       <c r="N54" t="n">
-        <v>67709.69</v>
+        <v>67100.11</v>
       </c>
       <c r="O54" t="n">
-        <v>69278.61</v>
+        <v>70375.06</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5049,20 +5051,16 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5084,50 +5082,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>63659.53</v>
+        <v>65476.44</v>
       </c>
       <c r="C55" t="n">
-        <v>65436.57</v>
+        <v>66410.27</v>
       </c>
       <c r="D55" t="n">
-        <v>62726.18</v>
+        <v>65407.37</v>
       </c>
       <c r="E55" t="n">
-        <v>65018.95</v>
+        <v>66364.2</v>
       </c>
       <c r="F55" t="n">
-        <v>1007.61</v>
+        <v>1345.25</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0157</v>
+        <v>0.0207</v>
       </c>
       <c r="H55" t="n">
-        <v>2710.39</v>
+        <v>1002.9</v>
       </c>
       <c r="I55" t="n">
-        <v>59625.41</v>
+        <v>60015.79</v>
       </c>
       <c r="J55" t="n">
-        <v>59933.68</v>
+        <v>62777.35</v>
       </c>
       <c r="K55" t="n">
-        <v>62219.73</v>
+        <v>63663.75</v>
       </c>
       <c r="L55" t="n">
-        <v>64505.79</v>
+        <v>64550.16</v>
       </c>
       <c r="M55" t="n">
-        <v>65802.95</v>
+        <v>66374.14</v>
       </c>
       <c r="N55" t="n">
-        <v>67100.11</v>
+        <v>68198.13</v>
       </c>
       <c r="O55" t="n">
-        <v>70375.06</v>
+        <v>68146.96000000001</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5140,11 +5138,13 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5159,66 +5159,70 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>65476.44</v>
+        <v>66505.94</v>
       </c>
       <c r="C56" t="n">
-        <v>66410.27</v>
+        <v>68995.3</v>
       </c>
       <c r="D56" t="n">
-        <v>65407.37</v>
+        <v>64699.49</v>
       </c>
       <c r="E56" t="n">
-        <v>66364.2</v>
+        <v>68309.46000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>1345.25</v>
+        <v>1945.26</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0207</v>
+        <v>0.0293</v>
       </c>
       <c r="H56" t="n">
-        <v>1002.9</v>
+        <v>4295.81</v>
       </c>
       <c r="I56" t="n">
-        <v>60015.79</v>
+        <v>64404.47</v>
       </c>
       <c r="J56" t="n">
-        <v>62777.35</v>
+        <v>65588.99000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>63663.75</v>
+        <v>65862.75</v>
       </c>
       <c r="L56" t="n">
-        <v>64550.16</v>
+        <v>66136.50999999999</v>
       </c>
       <c r="M56" t="n">
-        <v>66374.14</v>
+        <v>66865.64999999999</v>
       </c>
       <c r="N56" t="n">
-        <v>68198.13</v>
+        <v>67594.8</v>
       </c>
       <c r="O56" t="n">
-        <v>68146.96000000001</v>
+        <v>67413.17999999999</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
@@ -5227,86 +5231,86 @@
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W56" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W56" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>66505.94</v>
+        <v>69113.74000000001</v>
       </c>
       <c r="C57" t="n">
-        <v>68995.3</v>
+        <v>70798.62</v>
       </c>
       <c r="D57" t="n">
-        <v>64699.49</v>
+        <v>68150.02</v>
       </c>
       <c r="E57" t="n">
-        <v>68309.46000000001</v>
+        <v>69030.92</v>
       </c>
       <c r="F57" t="n">
-        <v>1945.26</v>
+        <v>721.46</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0293</v>
+        <v>0.0106</v>
       </c>
       <c r="H57" t="n">
-        <v>4295.81</v>
+        <v>2648.59</v>
       </c>
       <c r="I57" t="n">
-        <v>64404.47</v>
+        <v>60403.68</v>
       </c>
       <c r="J57" t="n">
-        <v>65588.99000000001</v>
+        <v>64744.69</v>
       </c>
       <c r="K57" t="n">
-        <v>65862.75</v>
+        <v>66161.56</v>
       </c>
       <c r="L57" t="n">
-        <v>66136.50999999999</v>
+        <v>67578.42999999999</v>
       </c>
       <c r="M57" t="n">
-        <v>66865.64999999999</v>
+        <v>70457.37</v>
       </c>
       <c r="N57" t="n">
-        <v>67594.8</v>
+        <v>73336.3</v>
       </c>
       <c r="O57" t="n">
-        <v>67413.17999999999</v>
+        <v>73291.11</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
@@ -5315,109 +5319,21 @@
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>69113.74000000001</v>
-      </c>
-      <c r="C58" t="n">
-        <v>70798.62</v>
-      </c>
-      <c r="D58" t="n">
-        <v>69042.11</v>
-      </c>
-      <c r="E58" t="n">
-        <v>69042.11</v>
-      </c>
-      <c r="F58" t="n">
-        <v>732.65</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0107</v>
-      </c>
-      <c r="H58" t="n">
-        <v>1756.51</v>
-      </c>
-      <c r="I58" t="n">
-        <v>60403.68</v>
-      </c>
-      <c r="J58" t="n">
-        <v>64744.69</v>
-      </c>
-      <c r="K58" t="n">
-        <v>66161.56</v>
-      </c>
-      <c r="L58" t="n">
-        <v>67578.42999999999</v>
-      </c>
-      <c r="M58" t="n">
-        <v>70457.37</v>
-      </c>
-      <c r="N58" t="n">
-        <v>73336.3</v>
-      </c>
-      <c r="O58" t="n">
-        <v>73291.11</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -659,25 +662,25 @@
         <v>1357.29</v>
       </c>
       <c r="I2" t="n">
-        <v>41799.14</v>
+        <v>42017.46</v>
       </c>
       <c r="J2" t="n">
-        <v>43549.84</v>
+        <v>43631.71</v>
       </c>
       <c r="K2" t="n">
-        <v>43995.9</v>
+        <v>44050.48</v>
       </c>
       <c r="L2" t="n">
-        <v>44441.96</v>
+        <v>44469.25</v>
       </c>
       <c r="M2" t="n">
-        <v>45540.34</v>
+        <v>45485.76</v>
       </c>
       <c r="N2" t="n">
-        <v>46638.72</v>
+        <v>46502.27</v>
       </c>
       <c r="O2" t="n">
-        <v>46432.46</v>
+        <v>46323.3</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5334,6 +5337,92 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>68564.85000000001</v>
+      </c>
+      <c r="C58" t="n">
+        <v>68710.99000000001</v>
+      </c>
+      <c r="D58" t="n">
+        <v>67058.56</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>1652.43</v>
+      </c>
+      <c r="I58" t="n">
+        <v>65501.43</v>
+      </c>
+      <c r="J58" t="n">
+        <v>66160.63</v>
+      </c>
+      <c r="K58" t="n">
+        <v>67706.62</v>
+      </c>
+      <c r="L58" t="n">
+        <v>69252.62</v>
+      </c>
+      <c r="M58" t="n">
+        <v>70355.22</v>
+      </c>
+      <c r="N58" t="n">
+        <v>71457.82000000001</v>
+      </c>
+      <c r="O58" t="n">
+        <v>73447.21000000001</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,25 +659,25 @@
         <v>1357.29</v>
       </c>
       <c r="I2" t="n">
-        <v>42017.46</v>
+        <v>42130.02</v>
       </c>
       <c r="J2" t="n">
-        <v>43631.71</v>
+        <v>43673.92</v>
       </c>
       <c r="K2" t="n">
-        <v>44050.48</v>
+        <v>44078.62</v>
       </c>
       <c r="L2" t="n">
-        <v>44469.25</v>
+        <v>44483.32</v>
       </c>
       <c r="M2" t="n">
-        <v>45485.76</v>
+        <v>45457.62</v>
       </c>
       <c r="N2" t="n">
-        <v>46502.27</v>
+        <v>46431.92</v>
       </c>
       <c r="O2" t="n">
-        <v>46323.3</v>
+        <v>46267.02</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5354,13 +5351,13 @@
         <v>67058.56</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>67777.52</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>-1253.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>-0.0182</v>
       </c>
       <c r="H58" t="n">
         <v>1652.43</v>
@@ -5386,22 +5383,20 @@
       <c r="O58" t="n">
         <v>73447.21000000001</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5420,7 +5415,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>1357.29</v>
       </c>
       <c r="I2" t="n">
-        <v>42130.02</v>
+        <v>42853.06</v>
       </c>
       <c r="J2" t="n">
-        <v>43673.92</v>
+        <v>43945.06</v>
       </c>
       <c r="K2" t="n">
-        <v>44078.62</v>
+        <v>44259.38</v>
       </c>
       <c r="L2" t="n">
-        <v>44483.32</v>
+        <v>44573.7</v>
       </c>
       <c r="M2" t="n">
-        <v>45457.62</v>
+        <v>45276.86</v>
       </c>
       <c r="N2" t="n">
-        <v>46431.92</v>
+        <v>45980.02</v>
       </c>
       <c r="O2" t="n">
-        <v>46267.02</v>
+        <v>45905.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5351,13 +5351,13 @@
         <v>67058.56</v>
       </c>
       <c r="E58" t="n">
-        <v>67777.52</v>
+        <v>67744.28999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>-1253.4</v>
+        <v>-1286.63</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0182</v>
+        <v>-0.0186</v>
       </c>
       <c r="H58" t="n">
         <v>1652.43</v>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>1357.29</v>
       </c>
       <c r="I2" t="n">
-        <v>42853.06</v>
+        <v>44209.12</v>
       </c>
       <c r="J2" t="n">
-        <v>43945.06</v>
+        <v>44453.58</v>
       </c>
       <c r="K2" t="n">
-        <v>44259.38</v>
+        <v>44598.4</v>
       </c>
       <c r="L2" t="n">
-        <v>44573.7</v>
+        <v>44743.21</v>
       </c>
       <c r="M2" t="n">
-        <v>45276.86</v>
+        <v>44937.85</v>
       </c>
       <c r="N2" t="n">
-        <v>45980.02</v>
+        <v>45132.48</v>
       </c>
       <c r="O2" t="n">
-        <v>45905.5</v>
+        <v>45227.47</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,8 +685,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -695,21 +697,29 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5348,19 +5358,19 @@
         <v>68710.99000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>67058.56</v>
+        <v>64092.74</v>
       </c>
       <c r="E58" t="n">
-        <v>67744.28999999999</v>
+        <v>64425.95</v>
       </c>
       <c r="F58" t="n">
-        <v>-1286.63</v>
+        <v>-4604.97</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0186</v>
+        <v>-0.0667</v>
       </c>
       <c r="H58" t="n">
-        <v>1652.43</v>
+        <v>4618.25</v>
       </c>
       <c r="I58" t="n">
         <v>65501.43</v>
@@ -5383,15 +5393,19 @@
       <c r="O58" t="n">
         <v>73447.21000000001</v>
       </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
@@ -5408,16 +5422,12 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44948.85</v>
+        <v>45193.77</v>
       </c>
       <c r="C2" t="n">
-        <v>45852.75</v>
+        <v>45824.69</v>
       </c>
       <c r="D2" t="n">
-        <v>44495.46</v>
+        <v>45193.77</v>
       </c>
       <c r="E2" t="n">
-        <v>45045.81</v>
+        <v>45354.99</v>
       </c>
       <c r="F2" t="n">
-        <v>277.69</v>
+        <v>309.18</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0062</v>
+        <v>0.0069</v>
       </c>
       <c r="H2" t="n">
-        <v>1357.29</v>
+        <v>630.92</v>
       </c>
       <c r="I2" t="n">
-        <v>44209.12</v>
+        <v>43138.17</v>
       </c>
       <c r="J2" t="n">
-        <v>44453.58</v>
+        <v>43624.37</v>
       </c>
       <c r="K2" t="n">
-        <v>44598.4</v>
+        <v>44367.16</v>
       </c>
       <c r="L2" t="n">
-        <v>44743.21</v>
+        <v>45109.96</v>
       </c>
       <c r="M2" t="n">
-        <v>44937.85</v>
+        <v>45724.45</v>
       </c>
       <c r="N2" t="n">
-        <v>45132.48</v>
+        <v>46338.95</v>
       </c>
       <c r="O2" t="n">
-        <v>45227.47</v>
+        <v>47210.04</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,14 +685,12 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
@@ -700,15 +698,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -724,68 +718,74 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45193.77</v>
+        <v>45113.29</v>
       </c>
       <c r="C3" t="n">
-        <v>45824.69</v>
+        <v>45778.66</v>
       </c>
       <c r="D3" t="n">
-        <v>45193.77</v>
+        <v>44357.65</v>
       </c>
       <c r="E3" t="n">
-        <v>45354.99</v>
+        <v>45769.5</v>
       </c>
       <c r="F3" t="n">
-        <v>309.18</v>
+        <v>414.51</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0091</v>
       </c>
       <c r="H3" t="n">
-        <v>630.92</v>
+        <v>1421.01</v>
       </c>
       <c r="I3" t="n">
-        <v>43138.17</v>
+        <v>44562.85</v>
       </c>
       <c r="J3" t="n">
-        <v>43624.37</v>
+        <v>44646.95</v>
       </c>
       <c r="K3" t="n">
-        <v>44367.16</v>
+        <v>45039.53</v>
       </c>
       <c r="L3" t="n">
-        <v>45109.96</v>
+        <v>45432.11</v>
       </c>
       <c r="M3" t="n">
-        <v>45724.45</v>
+        <v>45670.45</v>
       </c>
       <c r="N3" t="n">
-        <v>46338.95</v>
+        <v>45908.79</v>
       </c>
       <c r="O3" t="n">
-        <v>47210.04</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+        <v>46455.61</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U3" s="8" t="n">
@@ -801,72 +801,66 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45113.29</v>
+        <v>46636.07</v>
       </c>
       <c r="C4" t="n">
-        <v>45778.66</v>
+        <v>48597.08</v>
       </c>
       <c r="D4" t="n">
-        <v>44357.65</v>
+        <v>46592.99</v>
       </c>
       <c r="E4" t="n">
-        <v>45769.5</v>
+        <v>48088.8</v>
       </c>
       <c r="F4" t="n">
-        <v>414.51</v>
+        <v>2319.3</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0507</v>
       </c>
       <c r="H4" t="n">
-        <v>1421.01</v>
+        <v>2004.09</v>
       </c>
       <c r="I4" t="n">
-        <v>44562.85</v>
+        <v>42936.64</v>
       </c>
       <c r="J4" t="n">
-        <v>44646.95</v>
+        <v>44699.16</v>
       </c>
       <c r="K4" t="n">
-        <v>45039.53</v>
+        <v>45058.99</v>
       </c>
       <c r="L4" t="n">
-        <v>45432.11</v>
+        <v>45418.83</v>
       </c>
       <c r="M4" t="n">
-        <v>45670.45</v>
+        <v>46480.01</v>
       </c>
       <c r="N4" t="n">
-        <v>45908.79</v>
+        <v>47541.18</v>
       </c>
       <c r="O4" t="n">
-        <v>46455.61</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>47199.67</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
@@ -875,73 +869,73 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46636.07</v>
+        <v>47446.73</v>
       </c>
       <c r="C5" t="n">
-        <v>48597.08</v>
+        <v>48317.34</v>
       </c>
       <c r="D5" t="n">
-        <v>46592.99</v>
+        <v>46544.05</v>
       </c>
       <c r="E5" t="n">
-        <v>48088.8</v>
+        <v>47582.15</v>
       </c>
       <c r="F5" t="n">
-        <v>2319.3</v>
+        <v>-506.65</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0507</v>
+        <v>-0.0105</v>
       </c>
       <c r="H5" t="n">
-        <v>2004.09</v>
+        <v>1773.29</v>
       </c>
       <c r="I5" t="n">
-        <v>42936.64</v>
+        <v>44588.9</v>
       </c>
       <c r="J5" t="n">
-        <v>44699.16</v>
+        <v>46331.59</v>
       </c>
       <c r="K5" t="n">
-        <v>45058.99</v>
+        <v>47086.76</v>
       </c>
       <c r="L5" t="n">
-        <v>45418.83</v>
+        <v>47841.92</v>
       </c>
       <c r="M5" t="n">
-        <v>46480.01</v>
+        <v>49090.85</v>
       </c>
       <c r="N5" t="n">
-        <v>47541.18</v>
+        <v>50339.77</v>
       </c>
       <c r="O5" t="n">
-        <v>47199.67</v>
+        <v>50601.17</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -949,83 +943,83 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47446.73</v>
+        <v>48332.71</v>
       </c>
       <c r="C6" t="n">
-        <v>48317.34</v>
+        <v>49945.95</v>
       </c>
       <c r="D6" t="n">
-        <v>46544.05</v>
+        <v>48254.83</v>
       </c>
       <c r="E6" t="n">
-        <v>47582.15</v>
+        <v>49299.65</v>
       </c>
       <c r="F6" t="n">
-        <v>-506.65</v>
+        <v>1717.5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0105</v>
+        <v>0.0361</v>
       </c>
       <c r="H6" t="n">
-        <v>1773.29</v>
+        <v>1691.12</v>
       </c>
       <c r="I6" t="n">
-        <v>44588.9</v>
+        <v>44770.76</v>
       </c>
       <c r="J6" t="n">
-        <v>46331.59</v>
+        <v>45884.59</v>
       </c>
       <c r="K6" t="n">
-        <v>47086.76</v>
+        <v>46695.5</v>
       </c>
       <c r="L6" t="n">
-        <v>47841.92</v>
+        <v>47506.42</v>
       </c>
       <c r="M6" t="n">
-        <v>49090.85</v>
+        <v>48468.79</v>
       </c>
       <c r="N6" t="n">
-        <v>50339.77</v>
+        <v>49431.16</v>
       </c>
       <c r="O6" t="n">
-        <v>50601.17</v>
+        <v>50090.63</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1033,21 +1027,23 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1057,59 +1053,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>48332.71</v>
+        <v>49905.8</v>
       </c>
       <c r="C7" t="n">
-        <v>49945.95</v>
+        <v>52411.34</v>
       </c>
       <c r="D7" t="n">
-        <v>48254.83</v>
+        <v>49838.98</v>
       </c>
       <c r="E7" t="n">
-        <v>49299.65</v>
+        <v>52411.34</v>
       </c>
       <c r="F7" t="n">
-        <v>1717.5</v>
+        <v>3111.69</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0361</v>
+        <v>0.0631</v>
       </c>
       <c r="H7" t="n">
-        <v>1691.12</v>
+        <v>2572.36</v>
       </c>
       <c r="I7" t="n">
-        <v>44770.76</v>
+        <v>46563.71</v>
       </c>
       <c r="J7" t="n">
-        <v>45884.59</v>
+        <v>47708.16</v>
       </c>
       <c r="K7" t="n">
-        <v>46695.5</v>
+        <v>48454.09</v>
       </c>
       <c r="L7" t="n">
-        <v>47506.42</v>
+        <v>49200.02</v>
       </c>
       <c r="M7" t="n">
-        <v>48468.79</v>
+        <v>50145.21</v>
       </c>
       <c r="N7" t="n">
-        <v>49431.16</v>
+        <v>51090.4</v>
       </c>
       <c r="O7" t="n">
-        <v>50090.63</v>
+        <v>51637.07</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1132,11 +1124,13 @@
       </c>
       <c r="U7" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
@@ -1148,151 +1142,149 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>49905.8</v>
+        <v>52294.31</v>
       </c>
       <c r="C8" t="n">
-        <v>52411.34</v>
+        <v>52636.87</v>
       </c>
       <c r="D8" t="n">
-        <v>49838.98</v>
+        <v>49073.58</v>
       </c>
       <c r="E8" t="n">
-        <v>52411.34</v>
+        <v>50276.37</v>
       </c>
       <c r="F8" t="n">
-        <v>3111.69</v>
+        <v>-2134.97</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0631</v>
+        <v>-0.0407</v>
       </c>
       <c r="H8" t="n">
-        <v>2572.36</v>
+        <v>3563.29</v>
       </c>
       <c r="I8" t="n">
-        <v>46563.71</v>
+        <v>47266.62</v>
       </c>
       <c r="J8" t="n">
-        <v>47708.16</v>
+        <v>50482.07</v>
       </c>
       <c r="K8" t="n">
-        <v>48454.09</v>
+        <v>51125.16</v>
       </c>
       <c r="L8" t="n">
-        <v>49200.02</v>
+        <v>51768.25</v>
       </c>
       <c r="M8" t="n">
-        <v>50145.21</v>
+        <v>53697.52</v>
       </c>
       <c r="N8" t="n">
-        <v>51090.4</v>
+        <v>55626.79</v>
       </c>
       <c r="O8" t="n">
-        <v>51637.07</v>
+        <v>54983.7</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
+      <c r="Q8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W8" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W8" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52294.31</v>
+        <v>50645.27</v>
       </c>
       <c r="C9" t="n">
-        <v>52636.87</v>
+        <v>51513.16</v>
       </c>
       <c r="D9" t="n">
-        <v>49073.58</v>
+        <v>50246.6</v>
       </c>
       <c r="E9" t="n">
-        <v>50276.37</v>
+        <v>50376.53</v>
       </c>
       <c r="F9" t="n">
-        <v>-2134.97</v>
+        <v>100.16</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0407</v>
+        <v>0.002</v>
       </c>
       <c r="H9" t="n">
-        <v>3563.29</v>
+        <v>1266.56</v>
       </c>
       <c r="I9" t="n">
-        <v>47266.62</v>
+        <v>45510.29</v>
       </c>
       <c r="J9" t="n">
-        <v>50482.07</v>
+        <v>46423.65</v>
       </c>
       <c r="K9" t="n">
-        <v>51125.16</v>
+        <v>48494.72</v>
       </c>
       <c r="L9" t="n">
-        <v>51768.25</v>
+        <v>50565.8</v>
       </c>
       <c r="M9" t="n">
-        <v>53697.52</v>
+        <v>52058.02</v>
       </c>
       <c r="N9" t="n">
-        <v>55626.79</v>
+        <v>53550.24</v>
       </c>
       <c r="O9" t="n">
-        <v>54983.7</v>
+        <v>56200.16</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1311,70 +1303,76 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50645.27</v>
+        <v>50282.39</v>
       </c>
       <c r="C10" t="n">
-        <v>51513.16</v>
+        <v>50574.82</v>
       </c>
       <c r="D10" t="n">
-        <v>50246.6</v>
+        <v>48235.3</v>
       </c>
       <c r="E10" t="n">
-        <v>50376.53</v>
+        <v>48625.88</v>
       </c>
       <c r="F10" t="n">
-        <v>100.16</v>
+        <v>-1750.65</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0348</v>
       </c>
       <c r="H10" t="n">
-        <v>1266.56</v>
+        <v>2339.52</v>
       </c>
       <c r="I10" t="n">
-        <v>45510.29</v>
+        <v>48980.04</v>
       </c>
       <c r="J10" t="n">
-        <v>46423.65</v>
+        <v>48858.3</v>
       </c>
       <c r="K10" t="n">
-        <v>48494.72</v>
+        <v>49743.25</v>
       </c>
       <c r="L10" t="n">
-        <v>50565.8</v>
+        <v>50628.21</v>
       </c>
       <c r="M10" t="n">
-        <v>52058.02</v>
+        <v>51009.81</v>
       </c>
       <c r="N10" t="n">
-        <v>53550.24</v>
+        <v>51391.42</v>
       </c>
       <c r="O10" t="n">
-        <v>56200.16</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+        <v>52779.72</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1391,86 +1389,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50282.39</v>
+        <v>49113.82</v>
       </c>
       <c r="C11" t="n">
-        <v>50574.82</v>
+        <v>50322.14</v>
       </c>
       <c r="D11" t="n">
-        <v>48235.3</v>
+        <v>48511.95</v>
       </c>
       <c r="E11" t="n">
-        <v>48625.88</v>
+        <v>50253.91</v>
       </c>
       <c r="F11" t="n">
-        <v>-1750.65</v>
+        <v>1628.03</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0348</v>
+        <v>0.0335</v>
       </c>
       <c r="H11" t="n">
-        <v>2339.52</v>
+        <v>1810.19</v>
       </c>
       <c r="I11" t="n">
-        <v>48980.04</v>
+        <v>45895.78</v>
       </c>
       <c r="J11" t="n">
-        <v>48858.3</v>
+        <v>45896.77</v>
       </c>
       <c r="K11" t="n">
-        <v>49743.25</v>
+        <v>47456.12</v>
       </c>
       <c r="L11" t="n">
-        <v>50628.21</v>
+        <v>49015.47</v>
       </c>
       <c r="M11" t="n">
-        <v>51009.81</v>
+        <v>49795.64</v>
       </c>
       <c r="N11" t="n">
-        <v>51391.42</v>
+        <v>50575.81</v>
       </c>
       <c r="O11" t="n">
-        <v>52779.72</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
+        <v>52914.34</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
@@ -1479,55 +1471,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49113.82</v>
+        <v>50318.59</v>
       </c>
       <c r="C12" t="n">
-        <v>50322.14</v>
+        <v>51028.42</v>
       </c>
       <c r="D12" t="n">
-        <v>48511.95</v>
+        <v>49215.96</v>
       </c>
       <c r="E12" t="n">
-        <v>50253.91</v>
+        <v>50491.87</v>
       </c>
       <c r="F12" t="n">
-        <v>1628.03</v>
+        <v>237.96</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0335</v>
+        <v>0.0047</v>
       </c>
       <c r="H12" t="n">
-        <v>1810.19</v>
+        <v>1812.46</v>
       </c>
       <c r="I12" t="n">
-        <v>45895.78</v>
+        <v>46701.76</v>
       </c>
       <c r="J12" t="n">
-        <v>45896.77</v>
+        <v>48862.15</v>
       </c>
       <c r="K12" t="n">
-        <v>47456.12</v>
+        <v>49348.81</v>
       </c>
       <c r="L12" t="n">
-        <v>49015.47</v>
+        <v>49835.48</v>
       </c>
       <c r="M12" t="n">
-        <v>49795.64</v>
+        <v>51159.01</v>
       </c>
       <c r="N12" t="n">
-        <v>50575.81</v>
+        <v>52482.53</v>
       </c>
       <c r="O12" t="n">
-        <v>52914.34</v>
+        <v>52132.33</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1535,23 +1531,21 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1563,57 +1557,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>50318.59</v>
+        <v>50643.09</v>
       </c>
       <c r="C13" t="n">
-        <v>51028.42</v>
+        <v>51127.69</v>
       </c>
       <c r="D13" t="n">
-        <v>49215.96</v>
+        <v>49926.27</v>
       </c>
       <c r="E13" t="n">
-        <v>50491.87</v>
+        <v>50836.55</v>
       </c>
       <c r="F13" t="n">
-        <v>237.96</v>
+        <v>344.68</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0047</v>
+        <v>0.0068</v>
       </c>
       <c r="H13" t="n">
-        <v>1812.46</v>
+        <v>1201.42</v>
       </c>
       <c r="I13" t="n">
-        <v>46701.76</v>
+        <v>47403.5</v>
       </c>
       <c r="J13" t="n">
-        <v>48862.15</v>
+        <v>48864.25</v>
       </c>
       <c r="K13" t="n">
-        <v>49348.81</v>
+        <v>49585.64</v>
       </c>
       <c r="L13" t="n">
-        <v>49835.48</v>
+        <v>50307.03</v>
       </c>
       <c r="M13" t="n">
-        <v>51159.01</v>
+        <v>51398.1</v>
       </c>
       <c r="N13" t="n">
-        <v>52482.53</v>
+        <v>52489.17</v>
       </c>
       <c r="O13" t="n">
-        <v>52132.33</v>
+        <v>52840.88</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1621,10 +1615,8 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R13" s="6" t="n">
+        <v/>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
@@ -1654,63 +1646,69 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>50643.09</v>
+        <v>50352.09</v>
       </c>
       <c r="C14" t="n">
-        <v>51127.69</v>
+        <v>50432.1</v>
       </c>
       <c r="D14" t="n">
-        <v>49926.27</v>
+        <v>48643.78</v>
       </c>
       <c r="E14" t="n">
-        <v>50836.55</v>
+        <v>49507.21</v>
       </c>
       <c r="F14" t="n">
-        <v>344.68</v>
+        <v>-1329.34</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0261</v>
       </c>
       <c r="H14" t="n">
-        <v>1201.42</v>
+        <v>1788.32</v>
       </c>
       <c r="I14" t="n">
-        <v>47403.5</v>
+        <v>48724.85</v>
       </c>
       <c r="J14" t="n">
-        <v>48864.25</v>
+        <v>49789.91</v>
       </c>
       <c r="K14" t="n">
-        <v>49585.64</v>
+        <v>50235.84</v>
       </c>
       <c r="L14" t="n">
-        <v>50307.03</v>
+        <v>50681.77</v>
       </c>
       <c r="M14" t="n">
-        <v>51398.1</v>
+        <v>51437.26</v>
       </c>
       <c r="N14" t="n">
-        <v>52489.17</v>
+        <v>52192.76</v>
       </c>
       <c r="O14" t="n">
-        <v>52840.88</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>52329.11</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1727,83 +1725,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>50352.09</v>
+        <v>50084.55</v>
       </c>
       <c r="C15" t="n">
-        <v>50432.1</v>
+        <v>50941.89</v>
       </c>
       <c r="D15" t="n">
-        <v>48643.78</v>
+        <v>49982.2</v>
       </c>
       <c r="E15" t="n">
-        <v>49507.21</v>
+        <v>50750.39</v>
       </c>
       <c r="F15" t="n">
-        <v>-1329.34</v>
+        <v>1243.18</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0261</v>
+        <v>0.0251</v>
       </c>
       <c r="H15" t="n">
-        <v>1788.32</v>
+        <v>959.6900000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>48724.85</v>
+        <v>46855.46</v>
       </c>
       <c r="J15" t="n">
-        <v>49789.91</v>
+        <v>47703.53</v>
       </c>
       <c r="K15" t="n">
-        <v>50235.84</v>
+        <v>48613.05</v>
       </c>
       <c r="L15" t="n">
-        <v>50681.77</v>
+        <v>49522.58</v>
       </c>
       <c r="M15" t="n">
-        <v>51437.26</v>
+        <v>50401.37</v>
       </c>
       <c r="N15" t="n">
-        <v>52192.76</v>
+        <v>51280.17</v>
       </c>
       <c r="O15" t="n">
-        <v>52329.11</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
+        <v>52220.42</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
@@ -1815,55 +1805,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>50084.55</v>
+        <v>50691.22</v>
       </c>
       <c r="C16" t="n">
-        <v>50941.89</v>
+        <v>50707.23</v>
       </c>
       <c r="D16" t="n">
-        <v>49982.2</v>
+        <v>50198.97</v>
       </c>
       <c r="E16" t="n">
-        <v>50750.39</v>
+        <v>50339.48</v>
       </c>
       <c r="F16" t="n">
-        <v>1243.18</v>
+        <v>-410.91</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0251</v>
+        <v>-0.0081</v>
       </c>
       <c r="H16" t="n">
-        <v>959.6900000000001</v>
+        <v>508.26</v>
       </c>
       <c r="I16" t="n">
-        <v>46855.46</v>
+        <v>49022.51</v>
       </c>
       <c r="J16" t="n">
-        <v>47703.53</v>
+        <v>49934.87</v>
       </c>
       <c r="K16" t="n">
-        <v>48613.05</v>
+        <v>50270.54</v>
       </c>
       <c r="L16" t="n">
-        <v>49522.58</v>
+        <v>50606.22</v>
       </c>
       <c r="M16" t="n">
-        <v>50401.37</v>
+        <v>51230.24</v>
       </c>
       <c r="N16" t="n">
-        <v>51280.17</v>
+        <v>51854.25</v>
       </c>
       <c r="O16" t="n">
-        <v>52220.42</v>
+        <v>51901.58</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1871,19 +1865,19 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
@@ -1897,57 +1891,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>50691.22</v>
+        <v>51010.28</v>
       </c>
       <c r="C17" t="n">
-        <v>50707.23</v>
+        <v>52523.77</v>
       </c>
       <c r="D17" t="n">
-        <v>50198.97</v>
+        <v>50995.67</v>
       </c>
       <c r="E17" t="n">
-        <v>50339.48</v>
+        <v>51939.89</v>
       </c>
       <c r="F17" t="n">
-        <v>-410.91</v>
+        <v>1600.41</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0081</v>
+        <v>0.0318</v>
       </c>
       <c r="H17" t="n">
-        <v>508.26</v>
+        <v>1528.1</v>
       </c>
       <c r="I17" t="n">
-        <v>49022.51</v>
+        <v>49690.71</v>
       </c>
       <c r="J17" t="n">
-        <v>49934.87</v>
+        <v>49774.41</v>
       </c>
       <c r="K17" t="n">
-        <v>50270.54</v>
+        <v>50085.35</v>
       </c>
       <c r="L17" t="n">
-        <v>50606.22</v>
+        <v>50396.29</v>
       </c>
       <c r="M17" t="n">
-        <v>51230.24</v>
+        <v>50593.61</v>
       </c>
       <c r="N17" t="n">
-        <v>51854.25</v>
+        <v>50790.93</v>
       </c>
       <c r="O17" t="n">
-        <v>51901.58</v>
+        <v>51215.49</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1955,83 +1949,83 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W17" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W17" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51010.28</v>
+        <v>52808.29</v>
       </c>
       <c r="C18" t="n">
-        <v>52523.77</v>
+        <v>54487.32</v>
       </c>
       <c r="D18" t="n">
-        <v>50995.67</v>
+        <v>52741.64</v>
       </c>
       <c r="E18" t="n">
-        <v>51939.89</v>
+        <v>53936.17</v>
       </c>
       <c r="F18" t="n">
-        <v>1600.41</v>
+        <v>1996.28</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0318</v>
+        <v>0.0384</v>
       </c>
       <c r="H18" t="n">
-        <v>1528.1</v>
+        <v>1745.68</v>
       </c>
       <c r="I18" t="n">
-        <v>49690.71</v>
+        <v>49467.57</v>
       </c>
       <c r="J18" t="n">
-        <v>49774.41</v>
+        <v>50501.88</v>
       </c>
       <c r="K18" t="n">
-        <v>50085.35</v>
+        <v>51175.84</v>
       </c>
       <c r="L18" t="n">
-        <v>50396.29</v>
+        <v>51849.81</v>
       </c>
       <c r="M18" t="n">
-        <v>50593.61</v>
+        <v>52703.94</v>
       </c>
       <c r="N18" t="n">
-        <v>50790.93</v>
+        <v>53558.07</v>
       </c>
       <c r="O18" t="n">
-        <v>51215.49</v>
+        <v>54051.87</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2072,151 +2066,151 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>52808.29</v>
+        <v>53390.05</v>
       </c>
       <c r="C19" t="n">
-        <v>54487.32</v>
+        <v>54050.84</v>
       </c>
       <c r="D19" t="n">
-        <v>52741.64</v>
+        <v>52194.81</v>
       </c>
       <c r="E19" t="n">
-        <v>53936.17</v>
+        <v>53846.87</v>
       </c>
       <c r="F19" t="n">
-        <v>1996.28</v>
+        <v>-89.3</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0384</v>
+        <v>-0.0017</v>
       </c>
       <c r="H19" t="n">
-        <v>1745.68</v>
+        <v>1856.03</v>
       </c>
       <c r="I19" t="n">
-        <v>49467.57</v>
+        <v>50995.96</v>
       </c>
       <c r="J19" t="n">
-        <v>50501.88</v>
+        <v>52351.34</v>
       </c>
       <c r="K19" t="n">
-        <v>51175.84</v>
+        <v>53063.33</v>
       </c>
       <c r="L19" t="n">
-        <v>51849.81</v>
+        <v>53775.33</v>
       </c>
       <c r="M19" t="n">
-        <v>52703.94</v>
+        <v>54809.01</v>
       </c>
       <c r="N19" t="n">
-        <v>53558.07</v>
+        <v>55842.7</v>
       </c>
       <c r="O19" t="n">
-        <v>54051.87</v>
+        <v>56233</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>53390.05</v>
+        <v>53023.28</v>
       </c>
       <c r="C20" t="n">
-        <v>54050.84</v>
+        <v>53742.69</v>
       </c>
       <c r="D20" t="n">
-        <v>52194.81</v>
+        <v>52637.66</v>
       </c>
       <c r="E20" t="n">
-        <v>53846.87</v>
+        <v>53322.85</v>
       </c>
       <c r="F20" t="n">
-        <v>-89.3</v>
+        <v>-524.02</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0097</v>
       </c>
       <c r="H20" t="n">
-        <v>1856.03</v>
+        <v>1105.03</v>
       </c>
       <c r="I20" t="n">
-        <v>50995.96</v>
+        <v>50338.78</v>
       </c>
       <c r="J20" t="n">
-        <v>52351.34</v>
+        <v>52352.86</v>
       </c>
       <c r="K20" t="n">
-        <v>53063.33</v>
+        <v>52918.86</v>
       </c>
       <c r="L20" t="n">
-        <v>53775.33</v>
+        <v>53484.85</v>
       </c>
       <c r="M20" t="n">
-        <v>54809.01</v>
+        <v>54774.89</v>
       </c>
       <c r="N20" t="n">
-        <v>55842.7</v>
+        <v>56064.93</v>
       </c>
       <c r="O20" t="n">
-        <v>56233</v>
+        <v>55906.87</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q20" s="6" t="n">
+        <v/>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2235,57 +2229,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>53023.28</v>
+        <v>53575.37</v>
       </c>
       <c r="C21" t="n">
-        <v>53742.69</v>
+        <v>54782.83</v>
       </c>
       <c r="D21" t="n">
-        <v>52637.66</v>
+        <v>52655.18</v>
       </c>
       <c r="E21" t="n">
-        <v>53322.85</v>
+        <v>54253.68</v>
       </c>
       <c r="F21" t="n">
-        <v>-524.02</v>
+        <v>930.83</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0175</v>
       </c>
       <c r="H21" t="n">
-        <v>1105.03</v>
+        <v>2127.65</v>
       </c>
       <c r="I21" t="n">
-        <v>50338.78</v>
+        <v>51532.63</v>
       </c>
       <c r="J21" t="n">
-        <v>52352.86</v>
+        <v>52284.16</v>
       </c>
       <c r="K21" t="n">
-        <v>52918.86</v>
+        <v>52770.34</v>
       </c>
       <c r="L21" t="n">
-        <v>53484.85</v>
+        <v>53256.51</v>
       </c>
       <c r="M21" t="n">
-        <v>54774.89</v>
+        <v>53875.37</v>
       </c>
       <c r="N21" t="n">
-        <v>56064.93</v>
+        <v>54494.22</v>
       </c>
       <c r="O21" t="n">
-        <v>55906.87</v>
+        <v>54847.72</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2298,16 +2292,20 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2317,59 +2315,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>53575.37</v>
+        <v>55130.63</v>
       </c>
       <c r="C22" t="n">
-        <v>54782.83</v>
+        <v>58015.08</v>
       </c>
       <c r="D22" t="n">
-        <v>52655.18</v>
+        <v>55018.57</v>
       </c>
       <c r="E22" t="n">
-        <v>54253.68</v>
+        <v>56941.97</v>
       </c>
       <c r="F22" t="n">
-        <v>930.83</v>
+        <v>2688.29</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0496</v>
       </c>
       <c r="H22" t="n">
-        <v>2127.65</v>
+        <v>2996.51</v>
       </c>
       <c r="I22" t="n">
-        <v>51532.63</v>
+        <v>50527.53</v>
       </c>
       <c r="J22" t="n">
-        <v>52284.16</v>
+        <v>52393.37</v>
       </c>
       <c r="K22" t="n">
-        <v>52770.34</v>
+        <v>53189.86</v>
       </c>
       <c r="L22" t="n">
-        <v>53256.51</v>
+        <v>53986.34</v>
       </c>
       <c r="M22" t="n">
-        <v>53875.37</v>
+        <v>55317.5</v>
       </c>
       <c r="N22" t="n">
-        <v>54494.22</v>
+        <v>56648.67</v>
       </c>
       <c r="O22" t="n">
-        <v>54847.72</v>
+        <v>56910.48</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2377,10 +2371,8 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
@@ -2394,11 +2386,13 @@
       </c>
       <c r="U22" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
@@ -2410,50 +2404,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>55130.63</v>
+        <v>57212.97</v>
       </c>
       <c r="C23" t="n">
-        <v>58015.08</v>
+        <v>57709.82</v>
       </c>
       <c r="D23" t="n">
-        <v>55018.57</v>
+        <v>56135.12</v>
       </c>
       <c r="E23" t="n">
-        <v>56941.97</v>
+        <v>56825.7</v>
       </c>
       <c r="F23" t="n">
-        <v>2688.29</v>
+        <v>-116.27</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0496</v>
+        <v>-0.002</v>
       </c>
       <c r="H23" t="n">
-        <v>2996.51</v>
+        <v>1574.7</v>
       </c>
       <c r="I23" t="n">
-        <v>50527.53</v>
+        <v>52022.06</v>
       </c>
       <c r="J23" t="n">
-        <v>52393.37</v>
+        <v>54158.03</v>
       </c>
       <c r="K23" t="n">
-        <v>53189.86</v>
+        <v>55443.71</v>
       </c>
       <c r="L23" t="n">
-        <v>53986.34</v>
+        <v>56729.4</v>
       </c>
       <c r="M23" t="n">
-        <v>55317.5</v>
+        <v>58440.22</v>
       </c>
       <c r="N23" t="n">
-        <v>56648.67</v>
+        <v>60151.05</v>
       </c>
       <c r="O23" t="n">
-        <v>56910.48</v>
+        <v>61011.59</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2466,78 +2460,76 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>57212.97</v>
+        <v>56764.14</v>
       </c>
       <c r="C24" t="n">
-        <v>57709.82</v>
+        <v>59332.43</v>
       </c>
       <c r="D24" t="n">
-        <v>56135.12</v>
+        <v>56732.93</v>
       </c>
       <c r="E24" t="n">
-        <v>56825.7</v>
+        <v>58850.27</v>
       </c>
       <c r="F24" t="n">
-        <v>-116.27</v>
+        <v>2024.57</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0356</v>
       </c>
       <c r="H24" t="n">
-        <v>1574.7</v>
+        <v>2599.5</v>
       </c>
       <c r="I24" t="n">
-        <v>52022.06</v>
+        <v>54560.42</v>
       </c>
       <c r="J24" t="n">
-        <v>54158.03</v>
+        <v>55202.61</v>
       </c>
       <c r="K24" t="n">
-        <v>55443.71</v>
+        <v>56038.35</v>
       </c>
       <c r="L24" t="n">
-        <v>56729.4</v>
+        <v>56874.08</v>
       </c>
       <c r="M24" t="n">
-        <v>58440.22</v>
+        <v>57613.05</v>
       </c>
       <c r="N24" t="n">
-        <v>60151.05</v>
+        <v>58352.01</v>
       </c>
       <c r="O24" t="n">
-        <v>61011.59</v>
+        <v>59284.52</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2550,109 +2542,111 @@
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>56764.14</v>
+        <v>57976.2</v>
       </c>
       <c r="C25" t="n">
-        <v>59332.43</v>
+        <v>58365.21</v>
       </c>
       <c r="D25" t="n">
-        <v>56732.93</v>
+        <v>53618.2</v>
       </c>
       <c r="E25" t="n">
-        <v>58850.27</v>
+        <v>55620.84</v>
       </c>
       <c r="F25" t="n">
-        <v>2024.57</v>
+        <v>-3229.43</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0356</v>
+        <v>-0.0549</v>
       </c>
       <c r="H25" t="n">
-        <v>2599.5</v>
+        <v>4747.01</v>
       </c>
       <c r="I25" t="n">
-        <v>54560.42</v>
+        <v>54133.43</v>
       </c>
       <c r="J25" t="n">
-        <v>55202.61</v>
+        <v>56659.56</v>
       </c>
       <c r="K25" t="n">
-        <v>56038.35</v>
+        <v>57550.52</v>
       </c>
       <c r="L25" t="n">
-        <v>56874.08</v>
+        <v>58441.47</v>
       </c>
       <c r="M25" t="n">
-        <v>57613.05</v>
+        <v>60150.02</v>
       </c>
       <c r="N25" t="n">
-        <v>58352.01</v>
+        <v>61858.56</v>
       </c>
       <c r="O25" t="n">
-        <v>59284.52</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
+        <v>61931.93</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W25" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W25" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
@@ -2660,64 +2654,60 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>57976.2</v>
+        <v>54608.63</v>
       </c>
       <c r="C26" t="n">
-        <v>58365.21</v>
+        <v>55745.38</v>
       </c>
       <c r="D26" t="n">
-        <v>53618.2</v>
+        <v>51407.66</v>
       </c>
       <c r="E26" t="n">
-        <v>55620.84</v>
+        <v>53819.61</v>
       </c>
       <c r="F26" t="n">
-        <v>-3229.43</v>
+        <v>-1801.23</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0549</v>
+        <v>-0.0324</v>
       </c>
       <c r="H26" t="n">
-        <v>4747.01</v>
+        <v>4337.72</v>
       </c>
       <c r="I26" t="n">
-        <v>54133.43</v>
+        <v>48871.19</v>
       </c>
       <c r="J26" t="n">
-        <v>56659.56</v>
+        <v>50688.4</v>
       </c>
       <c r="K26" t="n">
-        <v>57550.52</v>
+        <v>53247.33</v>
       </c>
       <c r="L26" t="n">
-        <v>58441.47</v>
+        <v>55806.27</v>
       </c>
       <c r="M26" t="n">
-        <v>60150.02</v>
+        <v>57994.35</v>
       </c>
       <c r="N26" t="n">
-        <v>61858.56</v>
+        <v>60182.42</v>
       </c>
       <c r="O26" t="n">
-        <v>61931.93</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q26" s="6" t="inlineStr">
+        <v>63112.22</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
@@ -2744,50 +2734,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>54608.63</v>
+        <v>53627.86</v>
       </c>
       <c r="C27" t="n">
-        <v>55745.38</v>
+        <v>55239.4</v>
       </c>
       <c r="D27" t="n">
-        <v>51407.66</v>
+        <v>53113.95</v>
       </c>
       <c r="E27" t="n">
-        <v>53819.61</v>
+        <v>53372.53</v>
       </c>
       <c r="F27" t="n">
-        <v>-1801.23</v>
+        <v>-447.08</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0324</v>
+        <v>-0.0083</v>
       </c>
       <c r="H27" t="n">
-        <v>4337.72</v>
+        <v>2125.45</v>
       </c>
       <c r="I27" t="n">
-        <v>48871.19</v>
+        <v>47069.94</v>
       </c>
       <c r="J27" t="n">
-        <v>50688.4</v>
+        <v>49603.44</v>
       </c>
       <c r="K27" t="n">
-        <v>53247.33</v>
+        <v>51650.75</v>
       </c>
       <c r="L27" t="n">
-        <v>55806.27</v>
+        <v>53698.06</v>
       </c>
       <c r="M27" t="n">
-        <v>57994.35</v>
+        <v>55988.47</v>
       </c>
       <c r="N27" t="n">
-        <v>60182.42</v>
+        <v>58278.87</v>
       </c>
       <c r="O27" t="n">
-        <v>63112.22</v>
+        <v>60083.1</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2795,14 +2785,12 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2819,64 +2807,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>53627.86</v>
+        <v>52468.72</v>
       </c>
       <c r="C28" t="n">
-        <v>55239.4</v>
+        <v>54175.8</v>
       </c>
       <c r="D28" t="n">
-        <v>53113.95</v>
+        <v>50688.76</v>
       </c>
       <c r="E28" t="n">
-        <v>53372.53</v>
+        <v>53373.07</v>
       </c>
       <c r="F28" t="n">
-        <v>-447.08</v>
+        <v>0.54</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0083</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2125.45</v>
+        <v>3487.04</v>
       </c>
       <c r="I28" t="n">
-        <v>47069.94</v>
+        <v>50988.5</v>
       </c>
       <c r="J28" t="n">
-        <v>49603.44</v>
+        <v>50845.01</v>
       </c>
       <c r="K28" t="n">
-        <v>51650.75</v>
+        <v>52309.81</v>
       </c>
       <c r="L28" t="n">
-        <v>53698.06</v>
+        <v>53774.6</v>
       </c>
       <c r="M28" t="n">
-        <v>55988.47</v>
+        <v>54435.26</v>
       </c>
       <c r="N28" t="n">
-        <v>58278.87</v>
+        <v>55095.91</v>
       </c>
       <c r="O28" t="n">
-        <v>60083.1</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+        <v>57364.85</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
@@ -2906,69 +2904,65 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>52468.72</v>
+        <v>52054.68</v>
       </c>
       <c r="C29" t="n">
-        <v>54175.8</v>
+        <v>54258.48</v>
       </c>
       <c r="D29" t="n">
-        <v>50688.76</v>
+        <v>50558.91</v>
       </c>
       <c r="E29" t="n">
-        <v>53373.07</v>
+        <v>53123.49</v>
       </c>
       <c r="F29" t="n">
-        <v>0.54</v>
+        <v>-249.58</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0</v>
+        <v>-0.0047</v>
       </c>
       <c r="H29" t="n">
-        <v>3487.04</v>
+        <v>3699.57</v>
       </c>
       <c r="I29" t="n">
-        <v>50988.5</v>
+        <v>47201.72</v>
       </c>
       <c r="J29" t="n">
-        <v>50845.01</v>
+        <v>50356.43</v>
       </c>
       <c r="K29" t="n">
-        <v>52309.81</v>
+        <v>51629.55</v>
       </c>
       <c r="L29" t="n">
-        <v>53774.6</v>
+        <v>52902.68</v>
       </c>
       <c r="M29" t="n">
-        <v>54435.26</v>
+        <v>55116.59</v>
       </c>
       <c r="N29" t="n">
-        <v>55095.91</v>
+        <v>57330.5</v>
       </c>
       <c r="O29" t="n">
-        <v>57364.85</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>57662.84</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2994,50 +2988,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>52054.68</v>
+        <v>53205.93</v>
       </c>
       <c r="C30" t="n">
-        <v>54258.48</v>
+        <v>57012.77</v>
       </c>
       <c r="D30" t="n">
-        <v>50558.91</v>
+        <v>53156.94</v>
       </c>
       <c r="E30" t="n">
-        <v>53123.49</v>
+        <v>56924.11</v>
       </c>
       <c r="F30" t="n">
-        <v>-249.58</v>
+        <v>3800.62</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0047</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>3699.57</v>
+        <v>3855.83</v>
       </c>
       <c r="I30" t="n">
-        <v>47201.72</v>
+        <v>46859.34</v>
       </c>
       <c r="J30" t="n">
-        <v>50356.43</v>
+        <v>49781.31</v>
       </c>
       <c r="K30" t="n">
-        <v>51629.55</v>
+        <v>51273.7</v>
       </c>
       <c r="L30" t="n">
-        <v>52902.68</v>
+        <v>52766.09</v>
       </c>
       <c r="M30" t="n">
-        <v>55116.59</v>
+        <v>54973.27</v>
       </c>
       <c r="N30" t="n">
-        <v>57330.5</v>
+        <v>57180.46</v>
       </c>
       <c r="O30" t="n">
-        <v>57662.84</v>
+        <v>57958.05</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3045,21 +3039,23 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R30" s="6" t="n">
+        <v/>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3071,57 +3067,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>53205.93</v>
+        <v>56421.46</v>
       </c>
       <c r="C31" t="n">
-        <v>57012.77</v>
+        <v>59688.1</v>
       </c>
       <c r="D31" t="n">
-        <v>53156.94</v>
+        <v>56232.78</v>
       </c>
       <c r="E31" t="n">
-        <v>56924.11</v>
+        <v>58475.9</v>
       </c>
       <c r="F31" t="n">
-        <v>3800.62</v>
+        <v>1551.79</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0273</v>
       </c>
       <c r="H31" t="n">
-        <v>3855.83</v>
+        <v>3455.32</v>
       </c>
       <c r="I31" t="n">
-        <v>46859.34</v>
+        <v>49301.11</v>
       </c>
       <c r="J31" t="n">
-        <v>49781.31</v>
+        <v>53987.91</v>
       </c>
       <c r="K31" t="n">
-        <v>51273.7</v>
+        <v>54996.2</v>
       </c>
       <c r="L31" t="n">
-        <v>52766.09</v>
+        <v>56004.48</v>
       </c>
       <c r="M31" t="n">
-        <v>54973.27</v>
+        <v>58852.02</v>
       </c>
       <c r="N31" t="n">
-        <v>57180.46</v>
+        <v>61699.56</v>
       </c>
       <c r="O31" t="n">
-        <v>57958.05</v>
+        <v>60868.6</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3139,13 +3135,11 @@
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3164,50 +3158,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>56421.46</v>
+        <v>58821.16</v>
       </c>
       <c r="C32" t="n">
-        <v>59688.1</v>
+        <v>60013.98</v>
       </c>
       <c r="D32" t="n">
-        <v>56232.78</v>
+        <v>58621.48</v>
       </c>
       <c r="E32" t="n">
-        <v>58475.9</v>
+        <v>59716.18</v>
       </c>
       <c r="F32" t="n">
-        <v>1551.79</v>
+        <v>1240.28</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0273</v>
+        <v>0.0212</v>
       </c>
       <c r="H32" t="n">
-        <v>3455.32</v>
+        <v>1392.5</v>
       </c>
       <c r="I32" t="n">
-        <v>49301.11</v>
+        <v>52777.46</v>
       </c>
       <c r="J32" t="n">
-        <v>53987.91</v>
+        <v>55278.31</v>
       </c>
       <c r="K32" t="n">
-        <v>54996.2</v>
+        <v>56748.24</v>
       </c>
       <c r="L32" t="n">
-        <v>56004.48</v>
+        <v>58218.17</v>
       </c>
       <c r="M32" t="n">
-        <v>58852.02</v>
+        <v>60203.56</v>
       </c>
       <c r="N32" t="n">
-        <v>61699.56</v>
+        <v>62188.95</v>
       </c>
       <c r="O32" t="n">
-        <v>60868.6</v>
+        <v>63143.42</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3248,50 +3242,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>58821.16</v>
+        <v>59880.71</v>
       </c>
       <c r="C33" t="n">
-        <v>60013.98</v>
+        <v>60903.95</v>
       </c>
       <c r="D33" t="n">
-        <v>58621.48</v>
+        <v>58928.2</v>
       </c>
       <c r="E33" t="n">
-        <v>59716.18</v>
+        <v>59513.12</v>
       </c>
       <c r="F33" t="n">
-        <v>1240.28</v>
+        <v>-203.06</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0034</v>
       </c>
       <c r="H33" t="n">
-        <v>1392.5</v>
+        <v>1975.75</v>
       </c>
       <c r="I33" t="n">
-        <v>52777.46</v>
+        <v>57228.98</v>
       </c>
       <c r="J33" t="n">
-        <v>55278.31</v>
+        <v>58522.9</v>
       </c>
       <c r="K33" t="n">
-        <v>56748.24</v>
+        <v>59019.93</v>
       </c>
       <c r="L33" t="n">
-        <v>58218.17</v>
+        <v>59516.96</v>
       </c>
       <c r="M33" t="n">
-        <v>60203.56</v>
+        <v>60412.43</v>
       </c>
       <c r="N33" t="n">
-        <v>62188.95</v>
+        <v>61307.9</v>
       </c>
       <c r="O33" t="n">
-        <v>63143.42</v>
+        <v>61406.48</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3299,17 +3293,19 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U33" s="8" t="n">
@@ -3325,57 +3321,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>59880.71</v>
+        <v>60241.31</v>
       </c>
       <c r="C34" t="n">
-        <v>60903.95</v>
+        <v>63091.14</v>
       </c>
       <c r="D34" t="n">
-        <v>58928.2</v>
+        <v>60213.02</v>
       </c>
       <c r="E34" t="n">
-        <v>59513.12</v>
+        <v>62713.65</v>
       </c>
       <c r="F34" t="n">
-        <v>-203.06</v>
+        <v>3200.53</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0538</v>
       </c>
       <c r="H34" t="n">
-        <v>1975.75</v>
+        <v>2878.12</v>
       </c>
       <c r="I34" t="n">
-        <v>57228.98</v>
+        <v>56952.45</v>
       </c>
       <c r="J34" t="n">
-        <v>58522.9</v>
+        <v>57335.89</v>
       </c>
       <c r="K34" t="n">
-        <v>59019.93</v>
+        <v>58525.25</v>
       </c>
       <c r="L34" t="n">
-        <v>59516.96</v>
+        <v>59714.6</v>
       </c>
       <c r="M34" t="n">
-        <v>60412.43</v>
+        <v>60501</v>
       </c>
       <c r="N34" t="n">
-        <v>61307.9</v>
+        <v>61287.39</v>
       </c>
       <c r="O34" t="n">
-        <v>61406.48</v>
+        <v>62879.7</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3383,14 +3379,12 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
@@ -3398,70 +3392,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W34" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W34" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>60241.31</v>
+        <v>63203.44</v>
       </c>
       <c r="C35" t="n">
-        <v>63091.14</v>
+        <v>63799.32</v>
       </c>
       <c r="D35" t="n">
-        <v>60213.02</v>
+        <v>60937.3</v>
       </c>
       <c r="E35" t="n">
-        <v>62713.65</v>
+        <v>61409.29</v>
       </c>
       <c r="F35" t="n">
-        <v>3200.53</v>
+        <v>-1304.36</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0538</v>
+        <v>-0.0208</v>
       </c>
       <c r="H35" t="n">
-        <v>2878.12</v>
+        <v>2862.02</v>
       </c>
       <c r="I35" t="n">
-        <v>56952.45</v>
+        <v>57334.9</v>
       </c>
       <c r="J35" t="n">
-        <v>57335.89</v>
+        <v>60366.31</v>
       </c>
       <c r="K35" t="n">
-        <v>58525.25</v>
+        <v>61274.59</v>
       </c>
       <c r="L35" t="n">
-        <v>59714.6</v>
+        <v>62182.86</v>
       </c>
       <c r="M35" t="n">
-        <v>60501</v>
+        <v>64152.71</v>
       </c>
       <c r="N35" t="n">
-        <v>61287.39</v>
+        <v>66122.55</v>
       </c>
       <c r="O35" t="n">
-        <v>62879.7</v>
+        <v>65969.25999999999</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3469,83 +3463,83 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
+      </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>63203.44</v>
+        <v>61299.87</v>
       </c>
       <c r="C36" t="n">
-        <v>63799.32</v>
+        <v>63432.41</v>
       </c>
       <c r="D36" t="n">
-        <v>60937.3</v>
+        <v>59292.25</v>
       </c>
       <c r="E36" t="n">
-        <v>61409.29</v>
+        <v>63339.07</v>
       </c>
       <c r="F36" t="n">
-        <v>-1304.36</v>
+        <v>1929.78</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0314</v>
       </c>
       <c r="H36" t="n">
-        <v>2862.02</v>
+        <v>4140.16</v>
       </c>
       <c r="I36" t="n">
-        <v>57334.9</v>
+        <v>58075.28</v>
       </c>
       <c r="J36" t="n">
-        <v>60366.31</v>
+        <v>58067.76</v>
       </c>
       <c r="K36" t="n">
-        <v>61274.59</v>
+        <v>59978.28</v>
       </c>
       <c r="L36" t="n">
-        <v>62182.86</v>
+        <v>61888.8</v>
       </c>
       <c r="M36" t="n">
-        <v>64152.71</v>
+        <v>62840.3</v>
       </c>
       <c r="N36" t="n">
-        <v>66122.55</v>
+        <v>63791.8</v>
       </c>
       <c r="O36" t="n">
-        <v>65969.25999999999</v>
+        <v>66661.34</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3555,20 +3549,24 @@
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
@@ -3579,57 +3577,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>61299.87</v>
+        <v>63658.95</v>
       </c>
       <c r="C37" t="n">
-        <v>63432.41</v>
+        <v>66505.02</v>
       </c>
       <c r="D37" t="n">
-        <v>59292.25</v>
+        <v>63562.51</v>
       </c>
       <c r="E37" t="n">
-        <v>63339.07</v>
+        <v>66329.5</v>
       </c>
       <c r="F37" t="n">
-        <v>1929.78</v>
+        <v>2990.43</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0314</v>
+        <v>0.0472</v>
       </c>
       <c r="H37" t="n">
-        <v>4140.16</v>
+        <v>2942.51</v>
       </c>
       <c r="I37" t="n">
-        <v>58075.28</v>
+        <v>55152.09</v>
       </c>
       <c r="J37" t="n">
-        <v>58067.76</v>
+        <v>60187.28</v>
       </c>
       <c r="K37" t="n">
-        <v>59978.28</v>
+        <v>61268.99</v>
       </c>
       <c r="L37" t="n">
-        <v>61888.8</v>
+        <v>62350.7</v>
       </c>
       <c r="M37" t="n">
-        <v>62840.3</v>
+        <v>65409.15</v>
       </c>
       <c r="N37" t="n">
-        <v>63791.8</v>
+        <v>68467.60000000001</v>
       </c>
       <c r="O37" t="n">
-        <v>66661.34</v>
+        <v>67572.57000000001</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3637,10 +3635,8 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R37" s="6" t="n">
+        <v/>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
@@ -3649,14 +3645,12 @@
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
@@ -3665,59 +3659,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>63658.95</v>
+        <v>66363.42999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>66505.02</v>
+        <v>68786.49000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>63562.51</v>
+        <v>65551.13</v>
       </c>
       <c r="E38" t="n">
-        <v>66329.5</v>
+        <v>66588.12</v>
       </c>
       <c r="F38" t="n">
-        <v>2990.43</v>
+        <v>258.62</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0472</v>
+        <v>0.0039</v>
       </c>
       <c r="H38" t="n">
-        <v>2942.51</v>
+        <v>3235.36</v>
       </c>
       <c r="I38" t="n">
-        <v>55152.09</v>
+        <v>60620</v>
       </c>
       <c r="J38" t="n">
-        <v>60187.28</v>
+        <v>64034.85</v>
       </c>
       <c r="K38" t="n">
-        <v>61268.99</v>
+        <v>64858.24</v>
       </c>
       <c r="L38" t="n">
-        <v>62350.7</v>
+        <v>65681.63</v>
       </c>
       <c r="M38" t="n">
-        <v>65409.15</v>
+        <v>67800.75999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>68467.60000000001</v>
+        <v>69919.88</v>
       </c>
       <c r="O38" t="n">
-        <v>67572.57000000001</v>
+        <v>69447.53999999999</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3730,12 +3720,12 @@
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U38" s="8" t="n">
@@ -3754,69 +3744,71 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>66363.42999999999</v>
+        <v>65947.56</v>
       </c>
       <c r="C39" t="n">
-        <v>68786.49000000001</v>
+        <v>67065.94</v>
       </c>
       <c r="D39" t="n">
-        <v>65551.13</v>
+        <v>62335.75</v>
       </c>
       <c r="E39" t="n">
-        <v>66588.12</v>
+        <v>66020.03999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>258.62</v>
+        <v>-568.08</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0039</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>3235.36</v>
+        <v>4730.19</v>
       </c>
       <c r="I39" t="n">
-        <v>60620</v>
+        <v>62315.77</v>
       </c>
       <c r="J39" t="n">
-        <v>64034.85</v>
+        <v>63062.41</v>
       </c>
       <c r="K39" t="n">
-        <v>64858.24</v>
+        <v>64970.44</v>
       </c>
       <c r="L39" t="n">
-        <v>65681.63</v>
+        <v>66878.46000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>67800.75999999999</v>
+        <v>68205.8</v>
       </c>
       <c r="N39" t="n">
-        <v>69919.88</v>
+        <v>69533.13</v>
       </c>
       <c r="O39" t="n">
-        <v>69447.53999999999</v>
+        <v>72021.85000000001</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3829,141 +3821,143 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>65947.56</v>
+        <v>66783.22</v>
       </c>
       <c r="C40" t="n">
-        <v>67065.94</v>
+        <v>71952.99000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>62335.75</v>
+        <v>66783.22</v>
       </c>
       <c r="E40" t="n">
-        <v>66020.03999999999</v>
+        <v>71250.06</v>
       </c>
       <c r="F40" t="n">
-        <v>-568.08</v>
+        <v>5230.02</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>4730.19</v>
+        <v>5169.77</v>
       </c>
       <c r="I40" t="n">
-        <v>62315.77</v>
+        <v>57605.56</v>
       </c>
       <c r="J40" t="n">
-        <v>63062.41</v>
+        <v>61949.45</v>
       </c>
       <c r="K40" t="n">
-        <v>64970.44</v>
+        <v>63654.95</v>
       </c>
       <c r="L40" t="n">
-        <v>66878.46000000001</v>
+        <v>65360.44</v>
       </c>
       <c r="M40" t="n">
-        <v>68205.8</v>
+        <v>68385.13</v>
       </c>
       <c r="N40" t="n">
-        <v>69533.13</v>
+        <v>71409.82000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>72021.85000000001</v>
+        <v>71796.12</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V40" s="8" t="n">
-        <v/>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>66783.22</v>
+        <v>71067.14999999999</v>
       </c>
       <c r="C41" t="n">
-        <v>71952.99000000001</v>
+        <v>72831.73</v>
       </c>
       <c r="D41" t="n">
-        <v>66783.22</v>
+        <v>68461.10000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>71250.06</v>
+        <v>69360.88</v>
       </c>
       <c r="F41" t="n">
-        <v>5230.02</v>
+        <v>-1889.18</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.07920000000000001</v>
+        <v>-0.0265</v>
       </c>
       <c r="H41" t="n">
-        <v>5169.77</v>
+        <v>4370.62</v>
       </c>
       <c r="I41" t="n">
-        <v>57605.56</v>
+        <v>61613.45</v>
       </c>
       <c r="J41" t="n">
-        <v>61949.45</v>
+        <v>67021.27</v>
       </c>
       <c r="K41" t="n">
-        <v>63654.95</v>
+        <v>68665.17999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>65360.44</v>
+        <v>70309.08</v>
       </c>
       <c r="M41" t="n">
-        <v>68385.13</v>
+        <v>73834.95</v>
       </c>
       <c r="N41" t="n">
-        <v>71409.82000000001</v>
+        <v>77360.81</v>
       </c>
       <c r="O41" t="n">
-        <v>71796.12</v>
+        <v>77122.77</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3971,83 +3965,83 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
+      <c r="R41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v/>
       </c>
       <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>71067.14999999999</v>
+        <v>69609.88</v>
       </c>
       <c r="C42" t="n">
-        <v>72831.73</v>
+        <v>71962.34</v>
       </c>
       <c r="D42" t="n">
-        <v>68461.10000000001</v>
+        <v>67609.49000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>69360.88</v>
+        <v>69744.07000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>-1889.18</v>
+        <v>383.19</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0265</v>
+        <v>0.0055</v>
       </c>
       <c r="H42" t="n">
-        <v>4370.62</v>
+        <v>4352.85</v>
       </c>
       <c r="I42" t="n">
-        <v>61613.45</v>
+        <v>64090.48</v>
       </c>
       <c r="J42" t="n">
-        <v>67021.27</v>
+        <v>64347.49</v>
       </c>
       <c r="K42" t="n">
-        <v>68665.17999999999</v>
+        <v>67175.57000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>70309.08</v>
+        <v>70003.64999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>73834.95</v>
+        <v>71546.2</v>
       </c>
       <c r="N42" t="n">
-        <v>77360.81</v>
+        <v>73088.74000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>77122.77</v>
+        <v>77202.35000000001</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4055,18 +4049,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R42" s="6" t="n">
+        <v/>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4081,57 +4075,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>69609.88</v>
+        <v>69973.34</v>
       </c>
       <c r="C43" t="n">
-        <v>71962.34</v>
+        <v>70384.59</v>
       </c>
       <c r="D43" t="n">
-        <v>67609.49000000001</v>
+        <v>66819.05</v>
       </c>
       <c r="E43" t="n">
-        <v>69744.07000000001</v>
+        <v>68557.73</v>
       </c>
       <c r="F43" t="n">
-        <v>383.19</v>
+        <v>-1186.34</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0055</v>
+        <v>-0.017</v>
       </c>
       <c r="H43" t="n">
-        <v>4352.85</v>
+        <v>3565.55</v>
       </c>
       <c r="I43" t="n">
-        <v>64090.48</v>
+        <v>63256.64</v>
       </c>
       <c r="J43" t="n">
-        <v>64347.49</v>
+        <v>65370.29</v>
       </c>
       <c r="K43" t="n">
-        <v>67175.57000000001</v>
+        <v>67567.64</v>
       </c>
       <c r="L43" t="n">
-        <v>70003.64999999999</v>
+        <v>69764.99000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>71546.2</v>
+        <v>71920.5</v>
       </c>
       <c r="N43" t="n">
-        <v>73088.74000000001</v>
+        <v>74076</v>
       </c>
       <c r="O43" t="n">
-        <v>77202.35000000001</v>
+        <v>76315.2</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4139,18 +4133,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4165,67 +4159,71 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>69973.34</v>
+        <v>68410.63</v>
       </c>
       <c r="C44" t="n">
-        <v>70384.59</v>
+        <v>69078.21000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>66819.05</v>
+        <v>62704.6</v>
       </c>
       <c r="E44" t="n">
-        <v>68557.73</v>
+        <v>64141.12</v>
       </c>
       <c r="F44" t="n">
-        <v>-1186.34</v>
+        <v>-4416.61</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0644</v>
       </c>
       <c r="H44" t="n">
-        <v>3565.55</v>
+        <v>6373.61</v>
       </c>
       <c r="I44" t="n">
-        <v>63256.64</v>
+        <v>63253.5</v>
       </c>
       <c r="J44" t="n">
-        <v>65370.29</v>
+        <v>64970.13</v>
       </c>
       <c r="K44" t="n">
-        <v>67567.64</v>
+        <v>66774.95</v>
       </c>
       <c r="L44" t="n">
-        <v>69764.99000000001</v>
+        <v>68579.77</v>
       </c>
       <c r="M44" t="n">
-        <v>71920.5</v>
+        <v>70340.5</v>
       </c>
       <c r="N44" t="n">
-        <v>74076</v>
+        <v>72101.23</v>
       </c>
       <c r="O44" t="n">
-        <v>76315.2</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
+        <v>73950.14</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
@@ -4242,87 +4240,79 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W44" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>68410.63</v>
+        <v>64544.05</v>
       </c>
       <c r="C45" t="n">
-        <v>69078.21000000001</v>
+        <v>67592.2</v>
       </c>
       <c r="D45" t="n">
-        <v>62704.6</v>
+        <v>64201.03</v>
       </c>
       <c r="E45" t="n">
-        <v>64141.12</v>
+        <v>64611.15</v>
       </c>
       <c r="F45" t="n">
-        <v>-4416.61</v>
+        <v>470.03</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0644</v>
+        <v>0.0073</v>
       </c>
       <c r="H45" t="n">
-        <v>6373.61</v>
+        <v>3391.17</v>
       </c>
       <c r="I45" t="n">
-        <v>63253.5</v>
+        <v>56330.99</v>
       </c>
       <c r="J45" t="n">
-        <v>64970.13</v>
+        <v>56892.37</v>
       </c>
       <c r="K45" t="n">
-        <v>66774.95</v>
+        <v>60954.32</v>
       </c>
       <c r="L45" t="n">
-        <v>68579.77</v>
+        <v>65016.26</v>
       </c>
       <c r="M45" t="n">
-        <v>70340.5</v>
+        <v>67327.92999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>72101.23</v>
+        <v>69639.59</v>
       </c>
       <c r="O45" t="n">
-        <v>73950.14</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>75451.82000000001</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4335,74 +4325,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>64544.05</v>
+        <v>65164.98</v>
       </c>
       <c r="C46" t="n">
-        <v>67592.2</v>
+        <v>65364.73</v>
       </c>
       <c r="D46" t="n">
-        <v>64201.03</v>
+        <v>60448.9</v>
       </c>
       <c r="E46" t="n">
-        <v>64611.15</v>
+        <v>64362.02</v>
       </c>
       <c r="F46" t="n">
-        <v>470.03</v>
+        <v>-249.13</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0073</v>
+        <v>-0.0039</v>
       </c>
       <c r="H46" t="n">
-        <v>3391.17</v>
+        <v>4915.83</v>
       </c>
       <c r="I46" t="n">
-        <v>56330.99</v>
+        <v>60809.86</v>
       </c>
       <c r="J46" t="n">
-        <v>56892.37</v>
+        <v>60577.24</v>
       </c>
       <c r="K46" t="n">
-        <v>60954.32</v>
+        <v>62915.56</v>
       </c>
       <c r="L46" t="n">
-        <v>65016.26</v>
+        <v>65253.88</v>
       </c>
       <c r="M46" t="n">
-        <v>67327.92999999999</v>
+        <v>66306.73</v>
       </c>
       <c r="N46" t="n">
-        <v>69639.59</v>
+        <v>67359.59</v>
       </c>
       <c r="O46" t="n">
-        <v>75451.82000000001</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+        <v>70983.38</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4415,82 +4413,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>65164.98</v>
+        <v>63834.95</v>
       </c>
       <c r="C47" t="n">
-        <v>65364.73</v>
+        <v>66302.52</v>
       </c>
       <c r="D47" t="n">
-        <v>60448.9</v>
+        <v>62703.47</v>
       </c>
       <c r="E47" t="n">
-        <v>64362.02</v>
+        <v>65606.71000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>-249.13</v>
+        <v>1244.69</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0193</v>
       </c>
       <c r="H47" t="n">
-        <v>4915.83</v>
+        <v>3599.05</v>
       </c>
       <c r="I47" t="n">
-        <v>60809.86</v>
+        <v>55533.07</v>
       </c>
       <c r="J47" t="n">
-        <v>60577.24</v>
+        <v>60173.79</v>
       </c>
       <c r="K47" t="n">
-        <v>62915.56</v>
+        <v>61904.1</v>
       </c>
       <c r="L47" t="n">
-        <v>65253.88</v>
+        <v>63634.42</v>
       </c>
       <c r="M47" t="n">
-        <v>66306.73</v>
+        <v>66819.94</v>
       </c>
       <c r="N47" t="n">
-        <v>67359.59</v>
+        <v>70005.45</v>
       </c>
       <c r="O47" t="n">
-        <v>70983.38</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+        <v>70280.56</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4503,55 +4493,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>63834.95</v>
+        <v>65905.10000000001</v>
       </c>
       <c r="C48" t="n">
-        <v>66302.52</v>
+        <v>69608.24000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>62703.47</v>
+        <v>65848.58</v>
       </c>
       <c r="E48" t="n">
-        <v>65606.71000000001</v>
+        <v>68713.8</v>
       </c>
       <c r="F48" t="n">
-        <v>1244.69</v>
+        <v>3107.09</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0193</v>
+        <v>0.0474</v>
       </c>
       <c r="H48" t="n">
-        <v>3599.05</v>
+        <v>3759.66</v>
       </c>
       <c r="I48" t="n">
-        <v>55533.07</v>
+        <v>59104.41</v>
       </c>
       <c r="J48" t="n">
-        <v>60173.79</v>
+        <v>62559.51</v>
       </c>
       <c r="K48" t="n">
-        <v>61904.1</v>
+        <v>63807.18</v>
       </c>
       <c r="L48" t="n">
-        <v>63634.42</v>
+        <v>65054.85</v>
       </c>
       <c r="M48" t="n">
-        <v>66819.94</v>
+        <v>67406.24000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>70005.45</v>
+        <v>69757.62</v>
       </c>
       <c r="O48" t="n">
-        <v>70280.56</v>
+        <v>69901.58</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4569,11 +4563,13 @@
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4592,75 +4588,75 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>65905.10000000001</v>
+        <v>68882.06</v>
       </c>
       <c r="C49" t="n">
-        <v>69608.24000000001</v>
+        <v>69225.57000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>65848.58</v>
+        <v>65133.98</v>
       </c>
       <c r="E49" t="n">
-        <v>68713.8</v>
+        <v>66016.36</v>
       </c>
       <c r="F49" t="n">
-        <v>3107.09</v>
+        <v>-2697.44</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0474</v>
+        <v>-0.0393</v>
       </c>
       <c r="H49" t="n">
-        <v>3759.66</v>
+        <v>4091.59</v>
       </c>
       <c r="I49" t="n">
-        <v>59104.41</v>
+        <v>62088.91</v>
       </c>
       <c r="J49" t="n">
-        <v>62559.51</v>
+        <v>65446.83</v>
       </c>
       <c r="K49" t="n">
-        <v>63807.18</v>
+        <v>66833.96000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>65054.85</v>
+        <v>68221.10000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>67406.24000000001</v>
+        <v>70593.63</v>
       </c>
       <c r="N49" t="n">
-        <v>69757.62</v>
+        <v>72966.14999999999</v>
       </c>
       <c r="O49" t="n">
-        <v>69901.58</v>
+        <v>73367.91</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
+      <c r="Q49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
@@ -4669,76 +4665,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>68882.06</v>
+        <v>65978.95</v>
       </c>
       <c r="C50" t="n">
-        <v>69225.57000000001</v>
+        <v>66954.69</v>
       </c>
       <c r="D50" t="n">
-        <v>65133.98</v>
+        <v>64609.47</v>
       </c>
       <c r="E50" t="n">
-        <v>66016.36</v>
+        <v>66405.56</v>
       </c>
       <c r="F50" t="n">
-        <v>-2697.44</v>
+        <v>389.2</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0393</v>
+        <v>0.0059</v>
       </c>
       <c r="H50" t="n">
-        <v>4091.59</v>
+        <v>2345.22</v>
       </c>
       <c r="I50" t="n">
-        <v>62088.91</v>
+        <v>61042.39</v>
       </c>
       <c r="J50" t="n">
-        <v>65446.83</v>
+        <v>61343.06</v>
       </c>
       <c r="K50" t="n">
-        <v>66833.96000000001</v>
+        <v>63970.56</v>
       </c>
       <c r="L50" t="n">
-        <v>68221.10000000001</v>
+        <v>66598.07000000001</v>
       </c>
       <c r="M50" t="n">
-        <v>70593.63</v>
+        <v>68062.14999999999</v>
       </c>
       <c r="N50" t="n">
-        <v>72966.14999999999</v>
+        <v>69526.24000000001</v>
       </c>
       <c r="O50" t="n">
-        <v>73367.91</v>
+        <v>73317.16</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4755,68 +4743,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>65978.95</v>
+        <v>65668.50999999999</v>
       </c>
       <c r="C51" t="n">
-        <v>66954.69</v>
+        <v>66525.7</v>
       </c>
       <c r="D51" t="n">
-        <v>64609.47</v>
+        <v>63772.8</v>
       </c>
       <c r="E51" t="n">
-        <v>66405.56</v>
+        <v>65020.94</v>
       </c>
       <c r="F51" t="n">
-        <v>389.2</v>
+        <v>-1384.62</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0209</v>
       </c>
       <c r="H51" t="n">
-        <v>2345.22</v>
+        <v>2752.9</v>
       </c>
       <c r="I51" t="n">
-        <v>61042.39</v>
+        <v>62264.25</v>
       </c>
       <c r="J51" t="n">
-        <v>61343.06</v>
+        <v>64372.09</v>
       </c>
       <c r="K51" t="n">
-        <v>63970.56</v>
+        <v>65232.95</v>
       </c>
       <c r="L51" t="n">
-        <v>66598.07000000001</v>
+        <v>66093.82000000001</v>
       </c>
       <c r="M51" t="n">
-        <v>68062.14999999999</v>
+        <v>67578.17</v>
       </c>
       <c r="N51" t="n">
-        <v>69526.24000000001</v>
+        <v>69062.52</v>
       </c>
       <c r="O51" t="n">
-        <v>73317.16</v>
+        <v>69299.91</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4833,67 +4829,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>65668.50999999999</v>
+        <v>65600.42</v>
       </c>
       <c r="C52" t="n">
-        <v>66525.7</v>
+        <v>66791.84</v>
       </c>
       <c r="D52" t="n">
-        <v>63772.8</v>
+        <v>63208.63</v>
       </c>
       <c r="E52" t="n">
-        <v>65020.94</v>
+        <v>64011.34</v>
       </c>
       <c r="F52" t="n">
-        <v>-1384.62</v>
+        <v>-1009.6</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0209</v>
+        <v>-0.0155</v>
       </c>
       <c r="H52" t="n">
-        <v>2752.9</v>
+        <v>3583.21</v>
       </c>
       <c r="I52" t="n">
-        <v>62264.25</v>
+        <v>61019.9</v>
       </c>
       <c r="J52" t="n">
-        <v>64372.09</v>
+        <v>62203.88</v>
       </c>
       <c r="K52" t="n">
-        <v>65232.95</v>
+        <v>63644.49</v>
       </c>
       <c r="L52" t="n">
-        <v>66093.82000000001</v>
+        <v>65085.1</v>
       </c>
       <c r="M52" t="n">
-        <v>67578.17</v>
+        <v>66397.39</v>
       </c>
       <c r="N52" t="n">
-        <v>69062.52</v>
+        <v>67709.69</v>
       </c>
       <c r="O52" t="n">
-        <v>69299.91</v>
+        <v>69278.61</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q52" s="6" t="n">
+        <v/>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
@@ -4905,8 +4895,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4919,55 +4911,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>65600.42</v>
+        <v>63659.53</v>
       </c>
       <c r="C53" t="n">
-        <v>66791.84</v>
+        <v>65436.57</v>
       </c>
       <c r="D53" t="n">
-        <v>63208.63</v>
+        <v>62726.18</v>
       </c>
       <c r="E53" t="n">
-        <v>64011.34</v>
+        <v>65018.95</v>
       </c>
       <c r="F53" t="n">
-        <v>-1009.6</v>
+        <v>1007.61</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0157</v>
       </c>
       <c r="H53" t="n">
-        <v>3583.21</v>
+        <v>2710.39</v>
       </c>
       <c r="I53" t="n">
-        <v>61019.9</v>
+        <v>59625.41</v>
       </c>
       <c r="J53" t="n">
-        <v>62203.88</v>
+        <v>59933.68</v>
       </c>
       <c r="K53" t="n">
-        <v>63644.49</v>
+        <v>62219.73</v>
       </c>
       <c r="L53" t="n">
-        <v>65085.1</v>
+        <v>64505.79</v>
       </c>
       <c r="M53" t="n">
-        <v>66397.39</v>
+        <v>65802.95</v>
       </c>
       <c r="N53" t="n">
-        <v>67709.69</v>
+        <v>67100.11</v>
       </c>
       <c r="O53" t="n">
-        <v>69278.61</v>
+        <v>70375.06</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4975,20 +4971,16 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -5010,50 +5002,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>63659.53</v>
+        <v>65476.44</v>
       </c>
       <c r="C54" t="n">
-        <v>65436.57</v>
+        <v>66410.27</v>
       </c>
       <c r="D54" t="n">
-        <v>62726.18</v>
+        <v>65407.37</v>
       </c>
       <c r="E54" t="n">
-        <v>65018.95</v>
+        <v>66364.2</v>
       </c>
       <c r="F54" t="n">
-        <v>1007.61</v>
+        <v>1345.25</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0157</v>
+        <v>0.0207</v>
       </c>
       <c r="H54" t="n">
-        <v>2710.39</v>
+        <v>1002.9</v>
       </c>
       <c r="I54" t="n">
-        <v>59625.41</v>
+        <v>60015.79</v>
       </c>
       <c r="J54" t="n">
-        <v>59933.68</v>
+        <v>62777.35</v>
       </c>
       <c r="K54" t="n">
-        <v>62219.73</v>
+        <v>63663.75</v>
       </c>
       <c r="L54" t="n">
-        <v>64505.79</v>
+        <v>64550.16</v>
       </c>
       <c r="M54" t="n">
-        <v>65802.95</v>
+        <v>66374.14</v>
       </c>
       <c r="N54" t="n">
-        <v>67100.11</v>
+        <v>68198.13</v>
       </c>
       <c r="O54" t="n">
-        <v>70375.06</v>
+        <v>68146.96000000001</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5066,11 +5058,13 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5085,66 +5079,70 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>65476.44</v>
+        <v>66505.94</v>
       </c>
       <c r="C55" t="n">
-        <v>66410.27</v>
+        <v>68995.3</v>
       </c>
       <c r="D55" t="n">
-        <v>65407.37</v>
+        <v>64699.49</v>
       </c>
       <c r="E55" t="n">
-        <v>66364.2</v>
+        <v>68309.46000000001</v>
       </c>
       <c r="F55" t="n">
-        <v>1345.25</v>
+        <v>1945.26</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0207</v>
+        <v>0.0293</v>
       </c>
       <c r="H55" t="n">
-        <v>1002.9</v>
+        <v>4295.81</v>
       </c>
       <c r="I55" t="n">
-        <v>60015.79</v>
+        <v>64404.47</v>
       </c>
       <c r="J55" t="n">
-        <v>62777.35</v>
+        <v>65588.99000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>63663.75</v>
+        <v>65862.75</v>
       </c>
       <c r="L55" t="n">
-        <v>64550.16</v>
+        <v>66136.50999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>66374.14</v>
+        <v>66865.64999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>68198.13</v>
+        <v>67594.8</v>
       </c>
       <c r="O55" t="n">
-        <v>68146.96000000001</v>
+        <v>67413.17999999999</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
@@ -5153,86 +5151,86 @@
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W55" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W55" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>66505.94</v>
+        <v>69113.74000000001</v>
       </c>
       <c r="C56" t="n">
-        <v>68995.3</v>
+        <v>70798.62</v>
       </c>
       <c r="D56" t="n">
-        <v>64699.49</v>
+        <v>68150.02</v>
       </c>
       <c r="E56" t="n">
-        <v>68309.46000000001</v>
+        <v>69030.92</v>
       </c>
       <c r="F56" t="n">
-        <v>1945.26</v>
+        <v>721.46</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0293</v>
+        <v>0.0106</v>
       </c>
       <c r="H56" t="n">
-        <v>4295.81</v>
+        <v>2648.59</v>
       </c>
       <c r="I56" t="n">
-        <v>64404.47</v>
+        <v>60403.68</v>
       </c>
       <c r="J56" t="n">
-        <v>65588.99000000001</v>
+        <v>64744.69</v>
       </c>
       <c r="K56" t="n">
-        <v>65862.75</v>
+        <v>66161.56</v>
       </c>
       <c r="L56" t="n">
-        <v>66136.50999999999</v>
+        <v>67578.42999999999</v>
       </c>
       <c r="M56" t="n">
-        <v>66865.64999999999</v>
+        <v>70457.37</v>
       </c>
       <c r="N56" t="n">
-        <v>67594.8</v>
+        <v>73336.3</v>
       </c>
       <c r="O56" t="n">
-        <v>67413.17999999999</v>
+        <v>73291.11</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
@@ -5241,193 +5239,105 @@
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
       </c>
       <c r="W56" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>69113.74000000001</v>
+        <v>68564.85000000001</v>
       </c>
       <c r="C57" t="n">
-        <v>70798.62</v>
+        <v>68710.99000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>68150.02</v>
+        <v>64092.74</v>
       </c>
       <c r="E57" t="n">
-        <v>69030.92</v>
+        <v>65324.29</v>
       </c>
       <c r="F57" t="n">
-        <v>721.46</v>
+        <v>-3706.63</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0106</v>
+        <v>-0.0537</v>
       </c>
       <c r="H57" t="n">
-        <v>2648.59</v>
+        <v>4618.25</v>
       </c>
       <c r="I57" t="n">
-        <v>60403.68</v>
+        <v>65501.43</v>
       </c>
       <c r="J57" t="n">
-        <v>64744.69</v>
+        <v>66160.63</v>
       </c>
       <c r="K57" t="n">
-        <v>66161.56</v>
+        <v>67706.62</v>
       </c>
       <c r="L57" t="n">
-        <v>67578.42999999999</v>
+        <v>69252.62</v>
       </c>
       <c r="M57" t="n">
-        <v>70457.37</v>
+        <v>70355.22</v>
       </c>
       <c r="N57" t="n">
-        <v>73336.3</v>
+        <v>71457.82000000001</v>
       </c>
       <c r="O57" t="n">
-        <v>73291.11</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
+        <v>73447.21000000001</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W57" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>68564.85000000001</v>
-      </c>
-      <c r="C58" t="n">
-        <v>68710.99000000001</v>
-      </c>
-      <c r="D58" t="n">
-        <v>64092.74</v>
-      </c>
-      <c r="E58" t="n">
-        <v>64425.95</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-4604.97</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0667</v>
-      </c>
-      <c r="H58" t="n">
-        <v>4618.25</v>
-      </c>
-      <c r="I58" t="n">
-        <v>65501.43</v>
-      </c>
-      <c r="J58" t="n">
-        <v>66160.63</v>
-      </c>
-      <c r="K58" t="n">
-        <v>67706.62</v>
-      </c>
-      <c r="L58" t="n">
-        <v>69252.62</v>
-      </c>
-      <c r="M58" t="n">
-        <v>70355.22</v>
-      </c>
-      <c r="N58" t="n">
-        <v>71457.82000000001</v>
-      </c>
-      <c r="O58" t="n">
-        <v>73447.21000000001</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5339,6 +5342,86 @@
       </c>
       <c r="X57" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>64819.56</v>
+      </c>
+      <c r="C58" t="n">
+        <v>64819.56</v>
+      </c>
+      <c r="D58" t="n">
+        <v>63831.78</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>987.78</v>
+      </c>
+      <c r="I58" t="n">
+        <v>59474.48</v>
+      </c>
+      <c r="J58" t="n">
+        <v>60167.25</v>
+      </c>
+      <c r="K58" t="n">
+        <v>63015.16</v>
+      </c>
+      <c r="L58" t="n">
+        <v>65863.08</v>
+      </c>
+      <c r="M58" t="n">
+        <v>67633.42</v>
+      </c>
+      <c r="N58" t="n">
+        <v>69403.75</v>
+      </c>
+      <c r="O58" t="n">
+        <v>73329.25</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -5349,13 +5349,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>64819.56</v>
+        <v>64755.49</v>
       </c>
       <c r="C58" t="n">
-        <v>64819.56</v>
+        <v>64822.22</v>
       </c>
       <c r="D58" t="n">
-        <v>63831.78</v>
+        <v>64058.77</v>
       </c>
       <c r="E58" t="n">
         <v/>
@@ -5367,7 +5367,7 @@
         <v/>
       </c>
       <c r="H58" t="n">
-        <v>987.78</v>
+        <v>763.45</v>
       </c>
       <c r="I58" t="n">
         <v>59474.48</v>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5349,25 +5346,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>64755.49</v>
+        <v>64819.56</v>
       </c>
       <c r="C58" t="n">
-        <v>64822.22</v>
+        <v>65067.8</v>
       </c>
       <c r="D58" t="n">
-        <v>64058.77</v>
+        <v>63831.78</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>64916.7</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>-407.59</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>-0.0062</v>
       </c>
       <c r="H58" t="n">
-        <v>763.45</v>
+        <v>1236.02</v>
       </c>
       <c r="I58" t="n">
         <v>59474.48</v>
@@ -5390,10 +5387,8 @@
       <c r="O58" t="n">
         <v>73329.25</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5401,9 +5396,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -5352,19 +5352,19 @@
         <v>65067.8</v>
       </c>
       <c r="D58" t="n">
-        <v>63831.78</v>
+        <v>63807.15</v>
       </c>
       <c r="E58" t="n">
-        <v>64916.7</v>
+        <v>64075.42</v>
       </c>
       <c r="F58" t="n">
-        <v>-407.59</v>
+        <v>-1248.87</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0191</v>
       </c>
       <c r="H58" t="n">
-        <v>1236.02</v>
+        <v>1260.65</v>
       </c>
       <c r="I58" t="n">
         <v>59474.48</v>
@@ -5393,12 +5393,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -5349,22 +5349,22 @@
         <v>64819.56</v>
       </c>
       <c r="C58" t="n">
-        <v>65067.8</v>
+        <v>65404.63</v>
       </c>
       <c r="D58" t="n">
         <v>63807.15</v>
       </c>
       <c r="E58" t="n">
-        <v>64075.42</v>
+        <v>64621.24</v>
       </c>
       <c r="F58" t="n">
-        <v>-1248.87</v>
+        <v>-703.05</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0191</v>
+        <v>-0.0108</v>
       </c>
       <c r="H58" t="n">
-        <v>1260.65</v>
+        <v>1597.48</v>
       </c>
       <c r="I58" t="n">
         <v>59474.48</v>
@@ -5393,14 +5393,12 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,68 +634,74 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45193.77</v>
+        <v>45113.29</v>
       </c>
       <c r="C2" t="n">
-        <v>45824.69</v>
+        <v>45778.66</v>
       </c>
       <c r="D2" t="n">
-        <v>45193.77</v>
+        <v>44357.65</v>
       </c>
       <c r="E2" t="n">
-        <v>45354.99</v>
+        <v>45769.5</v>
       </c>
       <c r="F2" t="n">
-        <v>309.18</v>
+        <v>414.51</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0091</v>
       </c>
       <c r="H2" t="n">
-        <v>630.92</v>
+        <v>1421.01</v>
       </c>
       <c r="I2" t="n">
-        <v>43138.17</v>
+        <v>44562.85</v>
       </c>
       <c r="J2" t="n">
-        <v>43624.37</v>
+        <v>44646.95</v>
       </c>
       <c r="K2" t="n">
-        <v>44367.16</v>
+        <v>45039.53</v>
       </c>
       <c r="L2" t="n">
-        <v>45109.96</v>
+        <v>45432.11</v>
       </c>
       <c r="M2" t="n">
-        <v>45724.45</v>
+        <v>45670.45</v>
       </c>
       <c r="N2" t="n">
-        <v>46338.95</v>
+        <v>45908.79</v>
       </c>
       <c r="O2" t="n">
-        <v>47210.04</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+        <v>46455.61</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U2" s="8" t="n">
@@ -711,72 +717,66 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45113.29</v>
+        <v>46636.07</v>
       </c>
       <c r="C3" t="n">
-        <v>45778.66</v>
+        <v>48597.08</v>
       </c>
       <c r="D3" t="n">
-        <v>44357.65</v>
+        <v>46592.99</v>
       </c>
       <c r="E3" t="n">
-        <v>45769.5</v>
+        <v>48088.8</v>
       </c>
       <c r="F3" t="n">
-        <v>414.51</v>
+        <v>2319.3</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0507</v>
       </c>
       <c r="H3" t="n">
-        <v>1421.01</v>
+        <v>2004.09</v>
       </c>
       <c r="I3" t="n">
-        <v>44562.85</v>
+        <v>42936.64</v>
       </c>
       <c r="J3" t="n">
-        <v>44646.95</v>
+        <v>44699.16</v>
       </c>
       <c r="K3" t="n">
-        <v>45039.53</v>
+        <v>45058.99</v>
       </c>
       <c r="L3" t="n">
-        <v>45432.11</v>
+        <v>45418.83</v>
       </c>
       <c r="M3" t="n">
-        <v>45670.45</v>
+        <v>46480.01</v>
       </c>
       <c r="N3" t="n">
-        <v>45908.79</v>
+        <v>47541.18</v>
       </c>
       <c r="O3" t="n">
-        <v>46455.61</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>47199.67</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
@@ -785,73 +785,73 @@
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46636.07</v>
+        <v>47446.73</v>
       </c>
       <c r="C4" t="n">
-        <v>48597.08</v>
+        <v>48317.34</v>
       </c>
       <c r="D4" t="n">
-        <v>46592.99</v>
+        <v>46544.05</v>
       </c>
       <c r="E4" t="n">
-        <v>48088.8</v>
+        <v>47582.15</v>
       </c>
       <c r="F4" t="n">
-        <v>2319.3</v>
+        <v>-506.65</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0507</v>
+        <v>-0.0105</v>
       </c>
       <c r="H4" t="n">
-        <v>2004.09</v>
+        <v>1773.29</v>
       </c>
       <c r="I4" t="n">
-        <v>42936.64</v>
+        <v>44588.9</v>
       </c>
       <c r="J4" t="n">
-        <v>44699.16</v>
+        <v>46331.59</v>
       </c>
       <c r="K4" t="n">
-        <v>45058.99</v>
+        <v>47086.76</v>
       </c>
       <c r="L4" t="n">
-        <v>45418.83</v>
+        <v>47841.92</v>
       </c>
       <c r="M4" t="n">
-        <v>46480.01</v>
+        <v>49090.85</v>
       </c>
       <c r="N4" t="n">
-        <v>47541.18</v>
+        <v>50339.77</v>
       </c>
       <c r="O4" t="n">
-        <v>47199.67</v>
+        <v>50601.17</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -859,83 +859,83 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47446.73</v>
+        <v>48332.71</v>
       </c>
       <c r="C5" t="n">
-        <v>48317.34</v>
+        <v>49945.95</v>
       </c>
       <c r="D5" t="n">
-        <v>46544.05</v>
+        <v>48254.83</v>
       </c>
       <c r="E5" t="n">
-        <v>47582.15</v>
+        <v>49299.65</v>
       </c>
       <c r="F5" t="n">
-        <v>-506.65</v>
+        <v>1717.5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0105</v>
+        <v>0.0361</v>
       </c>
       <c r="H5" t="n">
-        <v>1773.29</v>
+        <v>1691.12</v>
       </c>
       <c r="I5" t="n">
-        <v>44588.9</v>
+        <v>44770.76</v>
       </c>
       <c r="J5" t="n">
-        <v>46331.59</v>
+        <v>45884.59</v>
       </c>
       <c r="K5" t="n">
-        <v>47086.76</v>
+        <v>46695.5</v>
       </c>
       <c r="L5" t="n">
-        <v>47841.92</v>
+        <v>47506.42</v>
       </c>
       <c r="M5" t="n">
-        <v>49090.85</v>
+        <v>48468.79</v>
       </c>
       <c r="N5" t="n">
-        <v>50339.77</v>
+        <v>49431.16</v>
       </c>
       <c r="O5" t="n">
-        <v>50601.17</v>
+        <v>50090.63</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -943,21 +943,23 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -967,59 +969,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48332.71</v>
+        <v>49905.8</v>
       </c>
       <c r="C6" t="n">
-        <v>49945.95</v>
+        <v>52411.34</v>
       </c>
       <c r="D6" t="n">
-        <v>48254.83</v>
+        <v>49838.98</v>
       </c>
       <c r="E6" t="n">
-        <v>49299.65</v>
+        <v>52411.34</v>
       </c>
       <c r="F6" t="n">
-        <v>1717.5</v>
+        <v>3111.69</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0361</v>
+        <v>0.0631</v>
       </c>
       <c r="H6" t="n">
-        <v>1691.12</v>
+        <v>2572.36</v>
       </c>
       <c r="I6" t="n">
-        <v>44770.76</v>
+        <v>46563.71</v>
       </c>
       <c r="J6" t="n">
-        <v>45884.59</v>
+        <v>47708.16</v>
       </c>
       <c r="K6" t="n">
-        <v>46695.5</v>
+        <v>48454.09</v>
       </c>
       <c r="L6" t="n">
-        <v>47506.42</v>
+        <v>49200.02</v>
       </c>
       <c r="M6" t="n">
-        <v>48468.79</v>
+        <v>50145.21</v>
       </c>
       <c r="N6" t="n">
-        <v>49431.16</v>
+        <v>51090.4</v>
       </c>
       <c r="O6" t="n">
-        <v>50090.63</v>
+        <v>51637.07</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1042,11 +1040,13 @@
       </c>
       <c r="U6" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
@@ -1058,151 +1058,149 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>49905.8</v>
+        <v>52294.31</v>
       </c>
       <c r="C7" t="n">
-        <v>52411.34</v>
+        <v>52636.87</v>
       </c>
       <c r="D7" t="n">
-        <v>49838.98</v>
+        <v>49073.58</v>
       </c>
       <c r="E7" t="n">
-        <v>52411.34</v>
+        <v>50276.37</v>
       </c>
       <c r="F7" t="n">
-        <v>3111.69</v>
+        <v>-2134.97</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0631</v>
+        <v>-0.0407</v>
       </c>
       <c r="H7" t="n">
-        <v>2572.36</v>
+        <v>3563.29</v>
       </c>
       <c r="I7" t="n">
-        <v>46563.71</v>
+        <v>47266.62</v>
       </c>
       <c r="J7" t="n">
-        <v>47708.16</v>
+        <v>50482.07</v>
       </c>
       <c r="K7" t="n">
-        <v>48454.09</v>
+        <v>51125.16</v>
       </c>
       <c r="L7" t="n">
-        <v>49200.02</v>
+        <v>51768.25</v>
       </c>
       <c r="M7" t="n">
-        <v>50145.21</v>
+        <v>53697.52</v>
       </c>
       <c r="N7" t="n">
-        <v>51090.4</v>
+        <v>55626.79</v>
       </c>
       <c r="O7" t="n">
-        <v>51637.07</v>
+        <v>54983.7</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
+      <c r="Q7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W7" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W7" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52294.31</v>
+        <v>50645.27</v>
       </c>
       <c r="C8" t="n">
-        <v>52636.87</v>
+        <v>51513.16</v>
       </c>
       <c r="D8" t="n">
-        <v>49073.58</v>
+        <v>50246.6</v>
       </c>
       <c r="E8" t="n">
-        <v>50276.37</v>
+        <v>50376.53</v>
       </c>
       <c r="F8" t="n">
-        <v>-2134.97</v>
+        <v>100.16</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0407</v>
+        <v>0.002</v>
       </c>
       <c r="H8" t="n">
-        <v>3563.29</v>
+        <v>1266.56</v>
       </c>
       <c r="I8" t="n">
-        <v>47266.62</v>
+        <v>45510.29</v>
       </c>
       <c r="J8" t="n">
-        <v>50482.07</v>
+        <v>46423.65</v>
       </c>
       <c r="K8" t="n">
-        <v>51125.16</v>
+        <v>48494.72</v>
       </c>
       <c r="L8" t="n">
-        <v>51768.25</v>
+        <v>50565.8</v>
       </c>
       <c r="M8" t="n">
-        <v>53697.52</v>
+        <v>52058.02</v>
       </c>
       <c r="N8" t="n">
-        <v>55626.79</v>
+        <v>53550.24</v>
       </c>
       <c r="O8" t="n">
-        <v>54983.7</v>
+        <v>56200.16</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1221,70 +1219,76 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50645.27</v>
+        <v>50282.39</v>
       </c>
       <c r="C9" t="n">
-        <v>51513.16</v>
+        <v>50574.82</v>
       </c>
       <c r="D9" t="n">
-        <v>50246.6</v>
+        <v>48235.3</v>
       </c>
       <c r="E9" t="n">
-        <v>50376.53</v>
+        <v>48625.88</v>
       </c>
       <c r="F9" t="n">
-        <v>100.16</v>
+        <v>-1750.65</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0348</v>
       </c>
       <c r="H9" t="n">
-        <v>1266.56</v>
+        <v>2339.52</v>
       </c>
       <c r="I9" t="n">
-        <v>45510.29</v>
+        <v>48980.04</v>
       </c>
       <c r="J9" t="n">
-        <v>46423.65</v>
+        <v>48858.3</v>
       </c>
       <c r="K9" t="n">
-        <v>48494.72</v>
+        <v>49743.25</v>
       </c>
       <c r="L9" t="n">
-        <v>50565.8</v>
+        <v>50628.21</v>
       </c>
       <c r="M9" t="n">
-        <v>52058.02</v>
+        <v>51009.81</v>
       </c>
       <c r="N9" t="n">
-        <v>53550.24</v>
+        <v>51391.42</v>
       </c>
       <c r="O9" t="n">
-        <v>56200.16</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+        <v>52779.72</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1301,86 +1305,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50282.39</v>
+        <v>49113.82</v>
       </c>
       <c r="C10" t="n">
-        <v>50574.82</v>
+        <v>50322.14</v>
       </c>
       <c r="D10" t="n">
-        <v>48235.3</v>
+        <v>48511.95</v>
       </c>
       <c r="E10" t="n">
-        <v>48625.88</v>
+        <v>50253.91</v>
       </c>
       <c r="F10" t="n">
-        <v>-1750.65</v>
+        <v>1628.03</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0348</v>
+        <v>0.0335</v>
       </c>
       <c r="H10" t="n">
-        <v>2339.52</v>
+        <v>1810.19</v>
       </c>
       <c r="I10" t="n">
-        <v>48980.04</v>
+        <v>45895.78</v>
       </c>
       <c r="J10" t="n">
-        <v>48858.3</v>
+        <v>45896.77</v>
       </c>
       <c r="K10" t="n">
-        <v>49743.25</v>
+        <v>47456.12</v>
       </c>
       <c r="L10" t="n">
-        <v>50628.21</v>
+        <v>49015.47</v>
       </c>
       <c r="M10" t="n">
-        <v>51009.81</v>
+        <v>49795.64</v>
       </c>
       <c r="N10" t="n">
-        <v>51391.42</v>
+        <v>50575.81</v>
       </c>
       <c r="O10" t="n">
-        <v>52779.72</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
+        <v>52914.34</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
@@ -1389,55 +1387,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>49113.82</v>
+        <v>50318.59</v>
       </c>
       <c r="C11" t="n">
-        <v>50322.14</v>
+        <v>51028.42</v>
       </c>
       <c r="D11" t="n">
-        <v>48511.95</v>
+        <v>49215.96</v>
       </c>
       <c r="E11" t="n">
-        <v>50253.91</v>
+        <v>50491.87</v>
       </c>
       <c r="F11" t="n">
-        <v>1628.03</v>
+        <v>237.96</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0335</v>
+        <v>0.0047</v>
       </c>
       <c r="H11" t="n">
-        <v>1810.19</v>
+        <v>1812.46</v>
       </c>
       <c r="I11" t="n">
-        <v>45895.78</v>
+        <v>46701.76</v>
       </c>
       <c r="J11" t="n">
-        <v>45896.77</v>
+        <v>48862.15</v>
       </c>
       <c r="K11" t="n">
-        <v>47456.12</v>
+        <v>49348.81</v>
       </c>
       <c r="L11" t="n">
-        <v>49015.47</v>
+        <v>49835.48</v>
       </c>
       <c r="M11" t="n">
-        <v>49795.64</v>
+        <v>51159.01</v>
       </c>
       <c r="N11" t="n">
-        <v>50575.81</v>
+        <v>52482.53</v>
       </c>
       <c r="O11" t="n">
-        <v>52914.34</v>
+        <v>52132.33</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1445,23 +1447,21 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1473,57 +1473,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50318.59</v>
+        <v>50643.09</v>
       </c>
       <c r="C12" t="n">
-        <v>51028.42</v>
+        <v>51127.69</v>
       </c>
       <c r="D12" t="n">
-        <v>49215.96</v>
+        <v>49926.27</v>
       </c>
       <c r="E12" t="n">
-        <v>50491.87</v>
+        <v>50836.55</v>
       </c>
       <c r="F12" t="n">
-        <v>237.96</v>
+        <v>344.68</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0047</v>
+        <v>0.0068</v>
       </c>
       <c r="H12" t="n">
-        <v>1812.46</v>
+        <v>1201.42</v>
       </c>
       <c r="I12" t="n">
-        <v>46701.76</v>
+        <v>47403.5</v>
       </c>
       <c r="J12" t="n">
-        <v>48862.15</v>
+        <v>48864.25</v>
       </c>
       <c r="K12" t="n">
-        <v>49348.81</v>
+        <v>49585.64</v>
       </c>
       <c r="L12" t="n">
-        <v>49835.48</v>
+        <v>50307.03</v>
       </c>
       <c r="M12" t="n">
-        <v>51159.01</v>
+        <v>51398.1</v>
       </c>
       <c r="N12" t="n">
-        <v>52482.53</v>
+        <v>52489.17</v>
       </c>
       <c r="O12" t="n">
-        <v>52132.33</v>
+        <v>52840.88</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1531,10 +1531,8 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R12" s="6" t="n">
+        <v/>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
@@ -1564,63 +1562,69 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>50643.09</v>
+        <v>50352.09</v>
       </c>
       <c r="C13" t="n">
-        <v>51127.69</v>
+        <v>50432.1</v>
       </c>
       <c r="D13" t="n">
-        <v>49926.27</v>
+        <v>48643.78</v>
       </c>
       <c r="E13" t="n">
-        <v>50836.55</v>
+        <v>49507.21</v>
       </c>
       <c r="F13" t="n">
-        <v>344.68</v>
+        <v>-1329.34</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0261</v>
       </c>
       <c r="H13" t="n">
-        <v>1201.42</v>
+        <v>1788.32</v>
       </c>
       <c r="I13" t="n">
-        <v>47403.5</v>
+        <v>48724.85</v>
       </c>
       <c r="J13" t="n">
-        <v>48864.25</v>
+        <v>49789.91</v>
       </c>
       <c r="K13" t="n">
-        <v>49585.64</v>
+        <v>50235.84</v>
       </c>
       <c r="L13" t="n">
-        <v>50307.03</v>
+        <v>50681.77</v>
       </c>
       <c r="M13" t="n">
-        <v>51398.1</v>
+        <v>51437.26</v>
       </c>
       <c r="N13" t="n">
-        <v>52489.17</v>
+        <v>52192.76</v>
       </c>
       <c r="O13" t="n">
-        <v>52840.88</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>52329.11</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1637,83 +1641,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>50352.09</v>
+        <v>50084.55</v>
       </c>
       <c r="C14" t="n">
-        <v>50432.1</v>
+        <v>50941.89</v>
       </c>
       <c r="D14" t="n">
-        <v>48643.78</v>
+        <v>49982.2</v>
       </c>
       <c r="E14" t="n">
-        <v>49507.21</v>
+        <v>50750.39</v>
       </c>
       <c r="F14" t="n">
-        <v>-1329.34</v>
+        <v>1243.18</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0261</v>
+        <v>0.0251</v>
       </c>
       <c r="H14" t="n">
-        <v>1788.32</v>
+        <v>959.6900000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>48724.85</v>
+        <v>46855.46</v>
       </c>
       <c r="J14" t="n">
-        <v>49789.91</v>
+        <v>47703.53</v>
       </c>
       <c r="K14" t="n">
-        <v>50235.84</v>
+        <v>48613.05</v>
       </c>
       <c r="L14" t="n">
-        <v>50681.77</v>
+        <v>49522.58</v>
       </c>
       <c r="M14" t="n">
-        <v>51437.26</v>
+        <v>50401.37</v>
       </c>
       <c r="N14" t="n">
-        <v>52192.76</v>
+        <v>51280.17</v>
       </c>
       <c r="O14" t="n">
-        <v>52329.11</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
+        <v>52220.42</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
@@ -1725,55 +1721,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>50084.55</v>
+        <v>50691.22</v>
       </c>
       <c r="C15" t="n">
-        <v>50941.89</v>
+        <v>50707.23</v>
       </c>
       <c r="D15" t="n">
-        <v>49982.2</v>
+        <v>50198.97</v>
       </c>
       <c r="E15" t="n">
-        <v>50750.39</v>
+        <v>50339.48</v>
       </c>
       <c r="F15" t="n">
-        <v>1243.18</v>
+        <v>-410.91</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0251</v>
+        <v>-0.0081</v>
       </c>
       <c r="H15" t="n">
-        <v>959.6900000000001</v>
+        <v>508.26</v>
       </c>
       <c r="I15" t="n">
-        <v>46855.46</v>
+        <v>49022.51</v>
       </c>
       <c r="J15" t="n">
-        <v>47703.53</v>
+        <v>49934.87</v>
       </c>
       <c r="K15" t="n">
-        <v>48613.05</v>
+        <v>50270.54</v>
       </c>
       <c r="L15" t="n">
-        <v>49522.58</v>
+        <v>50606.22</v>
       </c>
       <c r="M15" t="n">
-        <v>50401.37</v>
+        <v>51230.24</v>
       </c>
       <c r="N15" t="n">
-        <v>51280.17</v>
+        <v>51854.25</v>
       </c>
       <c r="O15" t="n">
-        <v>52220.42</v>
+        <v>51901.58</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1781,19 +1781,19 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
@@ -1807,57 +1807,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>50691.22</v>
+        <v>51010.28</v>
       </c>
       <c r="C16" t="n">
-        <v>50707.23</v>
+        <v>52523.77</v>
       </c>
       <c r="D16" t="n">
-        <v>50198.97</v>
+        <v>50995.67</v>
       </c>
       <c r="E16" t="n">
-        <v>50339.48</v>
+        <v>51939.89</v>
       </c>
       <c r="F16" t="n">
-        <v>-410.91</v>
+        <v>1600.41</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0081</v>
+        <v>0.0318</v>
       </c>
       <c r="H16" t="n">
-        <v>508.26</v>
+        <v>1528.1</v>
       </c>
       <c r="I16" t="n">
-        <v>49022.51</v>
+        <v>49690.71</v>
       </c>
       <c r="J16" t="n">
-        <v>49934.87</v>
+        <v>49774.41</v>
       </c>
       <c r="K16" t="n">
-        <v>50270.54</v>
+        <v>50085.35</v>
       </c>
       <c r="L16" t="n">
-        <v>50606.22</v>
+        <v>50396.29</v>
       </c>
       <c r="M16" t="n">
-        <v>51230.24</v>
+        <v>50593.61</v>
       </c>
       <c r="N16" t="n">
-        <v>51854.25</v>
+        <v>50790.93</v>
       </c>
       <c r="O16" t="n">
-        <v>51901.58</v>
+        <v>51215.49</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1865,83 +1865,83 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W16" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>51010.28</v>
+        <v>52808.29</v>
       </c>
       <c r="C17" t="n">
-        <v>52523.77</v>
+        <v>54487.32</v>
       </c>
       <c r="D17" t="n">
-        <v>50995.67</v>
+        <v>52741.64</v>
       </c>
       <c r="E17" t="n">
-        <v>51939.89</v>
+        <v>53936.17</v>
       </c>
       <c r="F17" t="n">
-        <v>1600.41</v>
+        <v>1996.28</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0318</v>
+        <v>0.0384</v>
       </c>
       <c r="H17" t="n">
-        <v>1528.1</v>
+        <v>1745.68</v>
       </c>
       <c r="I17" t="n">
-        <v>49690.71</v>
+        <v>49467.57</v>
       </c>
       <c r="J17" t="n">
-        <v>49774.41</v>
+        <v>50501.88</v>
       </c>
       <c r="K17" t="n">
-        <v>50085.35</v>
+        <v>51175.84</v>
       </c>
       <c r="L17" t="n">
-        <v>50396.29</v>
+        <v>51849.81</v>
       </c>
       <c r="M17" t="n">
-        <v>50593.61</v>
+        <v>52703.94</v>
       </c>
       <c r="N17" t="n">
-        <v>50790.93</v>
+        <v>53558.07</v>
       </c>
       <c r="O17" t="n">
-        <v>51215.49</v>
+        <v>54051.87</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1982,151 +1982,151 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52808.29</v>
+        <v>53390.05</v>
       </c>
       <c r="C18" t="n">
-        <v>54487.32</v>
+        <v>54050.84</v>
       </c>
       <c r="D18" t="n">
-        <v>52741.64</v>
+        <v>52194.81</v>
       </c>
       <c r="E18" t="n">
-        <v>53936.17</v>
+        <v>53846.87</v>
       </c>
       <c r="F18" t="n">
-        <v>1996.28</v>
+        <v>-89.3</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0384</v>
+        <v>-0.0017</v>
       </c>
       <c r="H18" t="n">
-        <v>1745.68</v>
+        <v>1856.03</v>
       </c>
       <c r="I18" t="n">
-        <v>49467.57</v>
+        <v>50995.96</v>
       </c>
       <c r="J18" t="n">
-        <v>50501.88</v>
+        <v>52351.34</v>
       </c>
       <c r="K18" t="n">
-        <v>51175.84</v>
+        <v>53063.33</v>
       </c>
       <c r="L18" t="n">
-        <v>51849.81</v>
+        <v>53775.33</v>
       </c>
       <c r="M18" t="n">
-        <v>52703.94</v>
+        <v>54809.01</v>
       </c>
       <c r="N18" t="n">
-        <v>53558.07</v>
+        <v>55842.7</v>
       </c>
       <c r="O18" t="n">
-        <v>54051.87</v>
+        <v>56233</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>53390.05</v>
+        <v>53023.28</v>
       </c>
       <c r="C19" t="n">
-        <v>54050.84</v>
+        <v>53742.69</v>
       </c>
       <c r="D19" t="n">
-        <v>52194.81</v>
+        <v>52637.66</v>
       </c>
       <c r="E19" t="n">
-        <v>53846.87</v>
+        <v>53322.85</v>
       </c>
       <c r="F19" t="n">
-        <v>-89.3</v>
+        <v>-524.02</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0097</v>
       </c>
       <c r="H19" t="n">
-        <v>1856.03</v>
+        <v>1105.03</v>
       </c>
       <c r="I19" t="n">
-        <v>50995.96</v>
+        <v>50338.78</v>
       </c>
       <c r="J19" t="n">
-        <v>52351.34</v>
+        <v>52352.86</v>
       </c>
       <c r="K19" t="n">
-        <v>53063.33</v>
+        <v>52918.86</v>
       </c>
       <c r="L19" t="n">
-        <v>53775.33</v>
+        <v>53484.85</v>
       </c>
       <c r="M19" t="n">
-        <v>54809.01</v>
+        <v>54774.89</v>
       </c>
       <c r="N19" t="n">
-        <v>55842.7</v>
+        <v>56064.93</v>
       </c>
       <c r="O19" t="n">
-        <v>56233</v>
+        <v>55906.87</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q19" s="6" t="n">
+        <v/>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2145,57 +2145,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>53023.28</v>
+        <v>53575.37</v>
       </c>
       <c r="C20" t="n">
-        <v>53742.69</v>
+        <v>54782.83</v>
       </c>
       <c r="D20" t="n">
-        <v>52637.66</v>
+        <v>52655.18</v>
       </c>
       <c r="E20" t="n">
-        <v>53322.85</v>
+        <v>54253.68</v>
       </c>
       <c r="F20" t="n">
-        <v>-524.02</v>
+        <v>930.83</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0175</v>
       </c>
       <c r="H20" t="n">
-        <v>1105.03</v>
+        <v>2127.65</v>
       </c>
       <c r="I20" t="n">
-        <v>50338.78</v>
+        <v>51532.63</v>
       </c>
       <c r="J20" t="n">
-        <v>52352.86</v>
+        <v>52284.16</v>
       </c>
       <c r="K20" t="n">
-        <v>52918.86</v>
+        <v>52770.34</v>
       </c>
       <c r="L20" t="n">
-        <v>53484.85</v>
+        <v>53256.51</v>
       </c>
       <c r="M20" t="n">
-        <v>54774.89</v>
+        <v>53875.37</v>
       </c>
       <c r="N20" t="n">
-        <v>56064.93</v>
+        <v>54494.22</v>
       </c>
       <c r="O20" t="n">
-        <v>55906.87</v>
+        <v>54847.72</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2208,16 +2208,20 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2227,59 +2231,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>53575.37</v>
+        <v>55130.63</v>
       </c>
       <c r="C21" t="n">
-        <v>54782.83</v>
+        <v>58015.08</v>
       </c>
       <c r="D21" t="n">
-        <v>52655.18</v>
+        <v>55018.57</v>
       </c>
       <c r="E21" t="n">
-        <v>54253.68</v>
+        <v>56941.97</v>
       </c>
       <c r="F21" t="n">
-        <v>930.83</v>
+        <v>2688.29</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0496</v>
       </c>
       <c r="H21" t="n">
-        <v>2127.65</v>
+        <v>2996.51</v>
       </c>
       <c r="I21" t="n">
-        <v>51532.63</v>
+        <v>50527.53</v>
       </c>
       <c r="J21" t="n">
-        <v>52284.16</v>
+        <v>52393.37</v>
       </c>
       <c r="K21" t="n">
-        <v>52770.34</v>
+        <v>53189.86</v>
       </c>
       <c r="L21" t="n">
-        <v>53256.51</v>
+        <v>53986.34</v>
       </c>
       <c r="M21" t="n">
-        <v>53875.37</v>
+        <v>55317.5</v>
       </c>
       <c r="N21" t="n">
-        <v>54494.22</v>
+        <v>56648.67</v>
       </c>
       <c r="O21" t="n">
-        <v>54847.72</v>
+        <v>56910.48</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2287,10 +2287,8 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R21" s="6" t="n">
+        <v/>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
@@ -2304,11 +2302,13 @@
       </c>
       <c r="U21" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
@@ -2320,50 +2320,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>55130.63</v>
+        <v>57212.97</v>
       </c>
       <c r="C22" t="n">
-        <v>58015.08</v>
+        <v>57709.82</v>
       </c>
       <c r="D22" t="n">
-        <v>55018.57</v>
+        <v>56135.12</v>
       </c>
       <c r="E22" t="n">
-        <v>56941.97</v>
+        <v>56825.7</v>
       </c>
       <c r="F22" t="n">
-        <v>2688.29</v>
+        <v>-116.27</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0496</v>
+        <v>-0.002</v>
       </c>
       <c r="H22" t="n">
-        <v>2996.51</v>
+        <v>1574.7</v>
       </c>
       <c r="I22" t="n">
-        <v>50527.53</v>
+        <v>52022.06</v>
       </c>
       <c r="J22" t="n">
-        <v>52393.37</v>
+        <v>54158.03</v>
       </c>
       <c r="K22" t="n">
-        <v>53189.86</v>
+        <v>55443.71</v>
       </c>
       <c r="L22" t="n">
-        <v>53986.34</v>
+        <v>56729.4</v>
       </c>
       <c r="M22" t="n">
-        <v>55317.5</v>
+        <v>58440.22</v>
       </c>
       <c r="N22" t="n">
-        <v>56648.67</v>
+        <v>60151.05</v>
       </c>
       <c r="O22" t="n">
-        <v>56910.48</v>
+        <v>61011.59</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2376,78 +2376,76 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>57212.97</v>
+        <v>56764.14</v>
       </c>
       <c r="C23" t="n">
-        <v>57709.82</v>
+        <v>59332.43</v>
       </c>
       <c r="D23" t="n">
-        <v>56135.12</v>
+        <v>56732.93</v>
       </c>
       <c r="E23" t="n">
-        <v>56825.7</v>
+        <v>58850.27</v>
       </c>
       <c r="F23" t="n">
-        <v>-116.27</v>
+        <v>2024.57</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0356</v>
       </c>
       <c r="H23" t="n">
-        <v>1574.7</v>
+        <v>2599.5</v>
       </c>
       <c r="I23" t="n">
-        <v>52022.06</v>
+        <v>54560.42</v>
       </c>
       <c r="J23" t="n">
-        <v>54158.03</v>
+        <v>55202.61</v>
       </c>
       <c r="K23" t="n">
-        <v>55443.71</v>
+        <v>56038.35</v>
       </c>
       <c r="L23" t="n">
-        <v>56729.4</v>
+        <v>56874.08</v>
       </c>
       <c r="M23" t="n">
-        <v>58440.22</v>
+        <v>57613.05</v>
       </c>
       <c r="N23" t="n">
-        <v>60151.05</v>
+        <v>58352.01</v>
       </c>
       <c r="O23" t="n">
-        <v>61011.59</v>
+        <v>59284.52</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2460,109 +2458,111 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>56764.14</v>
+        <v>57976.2</v>
       </c>
       <c r="C24" t="n">
-        <v>59332.43</v>
+        <v>58365.21</v>
       </c>
       <c r="D24" t="n">
-        <v>56732.93</v>
+        <v>53618.2</v>
       </c>
       <c r="E24" t="n">
-        <v>58850.27</v>
+        <v>55620.84</v>
       </c>
       <c r="F24" t="n">
-        <v>2024.57</v>
+        <v>-3229.43</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0356</v>
+        <v>-0.0549</v>
       </c>
       <c r="H24" t="n">
-        <v>2599.5</v>
+        <v>4747.01</v>
       </c>
       <c r="I24" t="n">
-        <v>54560.42</v>
+        <v>54133.43</v>
       </c>
       <c r="J24" t="n">
-        <v>55202.61</v>
+        <v>56659.56</v>
       </c>
       <c r="K24" t="n">
-        <v>56038.35</v>
+        <v>57550.52</v>
       </c>
       <c r="L24" t="n">
-        <v>56874.08</v>
+        <v>58441.47</v>
       </c>
       <c r="M24" t="n">
-        <v>57613.05</v>
+        <v>60150.02</v>
       </c>
       <c r="N24" t="n">
-        <v>58352.01</v>
+        <v>61858.56</v>
       </c>
       <c r="O24" t="n">
-        <v>59284.52</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
+        <v>61931.93</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W24" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W24" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
@@ -2570,64 +2570,60 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>57976.2</v>
+        <v>54608.63</v>
       </c>
       <c r="C25" t="n">
-        <v>58365.21</v>
+        <v>55745.38</v>
       </c>
       <c r="D25" t="n">
-        <v>53618.2</v>
+        <v>51407.66</v>
       </c>
       <c r="E25" t="n">
-        <v>55620.84</v>
+        <v>53819.61</v>
       </c>
       <c r="F25" t="n">
-        <v>-3229.43</v>
+        <v>-1801.23</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0549</v>
+        <v>-0.0324</v>
       </c>
       <c r="H25" t="n">
-        <v>4747.01</v>
+        <v>4337.72</v>
       </c>
       <c r="I25" t="n">
-        <v>54133.43</v>
+        <v>48871.19</v>
       </c>
       <c r="J25" t="n">
-        <v>56659.56</v>
+        <v>50688.4</v>
       </c>
       <c r="K25" t="n">
-        <v>57550.52</v>
+        <v>53247.33</v>
       </c>
       <c r="L25" t="n">
-        <v>58441.47</v>
+        <v>55806.27</v>
       </c>
       <c r="M25" t="n">
-        <v>60150.02</v>
+        <v>57994.35</v>
       </c>
       <c r="N25" t="n">
-        <v>61858.56</v>
+        <v>60182.42</v>
       </c>
       <c r="O25" t="n">
-        <v>61931.93</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q25" s="6" t="inlineStr">
+        <v>63112.22</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
@@ -2654,50 +2650,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>54608.63</v>
+        <v>53627.86</v>
       </c>
       <c r="C26" t="n">
-        <v>55745.38</v>
+        <v>55239.4</v>
       </c>
       <c r="D26" t="n">
-        <v>51407.66</v>
+        <v>53113.95</v>
       </c>
       <c r="E26" t="n">
-        <v>53819.61</v>
+        <v>53372.53</v>
       </c>
       <c r="F26" t="n">
-        <v>-1801.23</v>
+        <v>-447.08</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0324</v>
+        <v>-0.0083</v>
       </c>
       <c r="H26" t="n">
-        <v>4337.72</v>
+        <v>2125.45</v>
       </c>
       <c r="I26" t="n">
-        <v>48871.19</v>
+        <v>47069.94</v>
       </c>
       <c r="J26" t="n">
-        <v>50688.4</v>
+        <v>49603.44</v>
       </c>
       <c r="K26" t="n">
-        <v>53247.33</v>
+        <v>51650.75</v>
       </c>
       <c r="L26" t="n">
-        <v>55806.27</v>
+        <v>53698.06</v>
       </c>
       <c r="M26" t="n">
-        <v>57994.35</v>
+        <v>55988.47</v>
       </c>
       <c r="N26" t="n">
-        <v>60182.42</v>
+        <v>58278.87</v>
       </c>
       <c r="O26" t="n">
-        <v>63112.22</v>
+        <v>60083.1</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2705,14 +2701,12 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2729,64 +2723,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>53627.86</v>
+        <v>52468.72</v>
       </c>
       <c r="C27" t="n">
-        <v>55239.4</v>
+        <v>54175.8</v>
       </c>
       <c r="D27" t="n">
-        <v>53113.95</v>
+        <v>50688.76</v>
       </c>
       <c r="E27" t="n">
-        <v>53372.53</v>
+        <v>53373.07</v>
       </c>
       <c r="F27" t="n">
-        <v>-447.08</v>
+        <v>0.54</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0083</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2125.45</v>
+        <v>3487.04</v>
       </c>
       <c r="I27" t="n">
-        <v>47069.94</v>
+        <v>50988.5</v>
       </c>
       <c r="J27" t="n">
-        <v>49603.44</v>
+        <v>50845.01</v>
       </c>
       <c r="K27" t="n">
-        <v>51650.75</v>
+        <v>52309.81</v>
       </c>
       <c r="L27" t="n">
-        <v>53698.06</v>
+        <v>53774.6</v>
       </c>
       <c r="M27" t="n">
-        <v>55988.47</v>
+        <v>54435.26</v>
       </c>
       <c r="N27" t="n">
-        <v>58278.87</v>
+        <v>55095.91</v>
       </c>
       <c r="O27" t="n">
-        <v>60083.1</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+        <v>57364.85</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
@@ -2816,69 +2820,65 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>52468.72</v>
+        <v>52054.68</v>
       </c>
       <c r="C28" t="n">
-        <v>54175.8</v>
+        <v>54258.48</v>
       </c>
       <c r="D28" t="n">
-        <v>50688.76</v>
+        <v>50558.91</v>
       </c>
       <c r="E28" t="n">
-        <v>53373.07</v>
+        <v>53123.49</v>
       </c>
       <c r="F28" t="n">
-        <v>0.54</v>
+        <v>-249.58</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0</v>
+        <v>-0.0047</v>
       </c>
       <c r="H28" t="n">
-        <v>3487.04</v>
+        <v>3699.57</v>
       </c>
       <c r="I28" t="n">
-        <v>50988.5</v>
+        <v>47201.72</v>
       </c>
       <c r="J28" t="n">
-        <v>50845.01</v>
+        <v>50356.43</v>
       </c>
       <c r="K28" t="n">
-        <v>52309.81</v>
+        <v>51629.55</v>
       </c>
       <c r="L28" t="n">
-        <v>53774.6</v>
+        <v>52902.68</v>
       </c>
       <c r="M28" t="n">
-        <v>54435.26</v>
+        <v>55116.59</v>
       </c>
       <c r="N28" t="n">
-        <v>55095.91</v>
+        <v>57330.5</v>
       </c>
       <c r="O28" t="n">
-        <v>57364.85</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>57662.84</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2904,50 +2904,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>52054.68</v>
+        <v>53205.93</v>
       </c>
       <c r="C29" t="n">
-        <v>54258.48</v>
+        <v>57012.77</v>
       </c>
       <c r="D29" t="n">
-        <v>50558.91</v>
+        <v>53156.94</v>
       </c>
       <c r="E29" t="n">
-        <v>53123.49</v>
+        <v>56924.11</v>
       </c>
       <c r="F29" t="n">
-        <v>-249.58</v>
+        <v>3800.62</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0047</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>3699.57</v>
+        <v>3855.83</v>
       </c>
       <c r="I29" t="n">
-        <v>47201.72</v>
+        <v>46859.34</v>
       </c>
       <c r="J29" t="n">
-        <v>50356.43</v>
+        <v>49781.31</v>
       </c>
       <c r="K29" t="n">
-        <v>51629.55</v>
+        <v>51273.7</v>
       </c>
       <c r="L29" t="n">
-        <v>52902.68</v>
+        <v>52766.09</v>
       </c>
       <c r="M29" t="n">
-        <v>55116.59</v>
+        <v>54973.27</v>
       </c>
       <c r="N29" t="n">
-        <v>57330.5</v>
+        <v>57180.46</v>
       </c>
       <c r="O29" t="n">
-        <v>57662.84</v>
+        <v>57958.05</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2955,21 +2955,23 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R29" s="6" t="n">
+        <v/>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2981,57 +2983,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>53205.93</v>
+        <v>56421.46</v>
       </c>
       <c r="C30" t="n">
-        <v>57012.77</v>
+        <v>59688.1</v>
       </c>
       <c r="D30" t="n">
-        <v>53156.94</v>
+        <v>56232.78</v>
       </c>
       <c r="E30" t="n">
-        <v>56924.11</v>
+        <v>58475.9</v>
       </c>
       <c r="F30" t="n">
-        <v>3800.62</v>
+        <v>1551.79</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0273</v>
       </c>
       <c r="H30" t="n">
-        <v>3855.83</v>
+        <v>3455.32</v>
       </c>
       <c r="I30" t="n">
-        <v>46859.34</v>
+        <v>49301.11</v>
       </c>
       <c r="J30" t="n">
-        <v>49781.31</v>
+        <v>53987.91</v>
       </c>
       <c r="K30" t="n">
-        <v>51273.7</v>
+        <v>54996.2</v>
       </c>
       <c r="L30" t="n">
-        <v>52766.09</v>
+        <v>56004.48</v>
       </c>
       <c r="M30" t="n">
-        <v>54973.27</v>
+        <v>58852.02</v>
       </c>
       <c r="N30" t="n">
-        <v>57180.46</v>
+        <v>61699.56</v>
       </c>
       <c r="O30" t="n">
-        <v>57958.05</v>
+        <v>60868.6</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3049,13 +3051,11 @@
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3074,50 +3074,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>56421.46</v>
+        <v>58821.16</v>
       </c>
       <c r="C31" t="n">
-        <v>59688.1</v>
+        <v>60013.98</v>
       </c>
       <c r="D31" t="n">
-        <v>56232.78</v>
+        <v>58621.48</v>
       </c>
       <c r="E31" t="n">
-        <v>58475.9</v>
+        <v>59716.18</v>
       </c>
       <c r="F31" t="n">
-        <v>1551.79</v>
+        <v>1240.28</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0273</v>
+        <v>0.0212</v>
       </c>
       <c r="H31" t="n">
-        <v>3455.32</v>
+        <v>1392.5</v>
       </c>
       <c r="I31" t="n">
-        <v>49301.11</v>
+        <v>52777.46</v>
       </c>
       <c r="J31" t="n">
-        <v>53987.91</v>
+        <v>55278.31</v>
       </c>
       <c r="K31" t="n">
-        <v>54996.2</v>
+        <v>56748.24</v>
       </c>
       <c r="L31" t="n">
-        <v>56004.48</v>
+        <v>58218.17</v>
       </c>
       <c r="M31" t="n">
-        <v>58852.02</v>
+        <v>60203.56</v>
       </c>
       <c r="N31" t="n">
-        <v>61699.56</v>
+        <v>62188.95</v>
       </c>
       <c r="O31" t="n">
-        <v>60868.6</v>
+        <v>63143.42</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3158,50 +3158,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>58821.16</v>
+        <v>59880.71</v>
       </c>
       <c r="C32" t="n">
-        <v>60013.98</v>
+        <v>60903.95</v>
       </c>
       <c r="D32" t="n">
-        <v>58621.48</v>
+        <v>58928.2</v>
       </c>
       <c r="E32" t="n">
-        <v>59716.18</v>
+        <v>59513.12</v>
       </c>
       <c r="F32" t="n">
-        <v>1240.28</v>
+        <v>-203.06</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0034</v>
       </c>
       <c r="H32" t="n">
-        <v>1392.5</v>
+        <v>1975.75</v>
       </c>
       <c r="I32" t="n">
-        <v>52777.46</v>
+        <v>57228.98</v>
       </c>
       <c r="J32" t="n">
-        <v>55278.31</v>
+        <v>58522.9</v>
       </c>
       <c r="K32" t="n">
-        <v>56748.24</v>
+        <v>59019.93</v>
       </c>
       <c r="L32" t="n">
-        <v>58218.17</v>
+        <v>59516.96</v>
       </c>
       <c r="M32" t="n">
-        <v>60203.56</v>
+        <v>60412.43</v>
       </c>
       <c r="N32" t="n">
-        <v>62188.95</v>
+        <v>61307.9</v>
       </c>
       <c r="O32" t="n">
-        <v>63143.42</v>
+        <v>61406.48</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3209,17 +3209,19 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U32" s="8" t="n">
@@ -3235,57 +3237,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>59880.71</v>
+        <v>60241.31</v>
       </c>
       <c r="C33" t="n">
-        <v>60903.95</v>
+        <v>63091.14</v>
       </c>
       <c r="D33" t="n">
-        <v>58928.2</v>
+        <v>60213.02</v>
       </c>
       <c r="E33" t="n">
-        <v>59513.12</v>
+        <v>62713.65</v>
       </c>
       <c r="F33" t="n">
-        <v>-203.06</v>
+        <v>3200.53</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0538</v>
       </c>
       <c r="H33" t="n">
-        <v>1975.75</v>
+        <v>2878.12</v>
       </c>
       <c r="I33" t="n">
-        <v>57228.98</v>
+        <v>56952.45</v>
       </c>
       <c r="J33" t="n">
-        <v>58522.9</v>
+        <v>57335.89</v>
       </c>
       <c r="K33" t="n">
-        <v>59019.93</v>
+        <v>58525.25</v>
       </c>
       <c r="L33" t="n">
-        <v>59516.96</v>
+        <v>59714.6</v>
       </c>
       <c r="M33" t="n">
-        <v>60412.43</v>
+        <v>60501</v>
       </c>
       <c r="N33" t="n">
-        <v>61307.9</v>
+        <v>61287.39</v>
       </c>
       <c r="O33" t="n">
-        <v>61406.48</v>
+        <v>62879.7</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3293,14 +3295,12 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
@@ -3308,70 +3308,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W33" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W33" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>60241.31</v>
+        <v>63203.44</v>
       </c>
       <c r="C34" t="n">
-        <v>63091.14</v>
+        <v>63799.32</v>
       </c>
       <c r="D34" t="n">
-        <v>60213.02</v>
+        <v>60937.3</v>
       </c>
       <c r="E34" t="n">
-        <v>62713.65</v>
+        <v>61409.29</v>
       </c>
       <c r="F34" t="n">
-        <v>3200.53</v>
+        <v>-1304.36</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0538</v>
+        <v>-0.0208</v>
       </c>
       <c r="H34" t="n">
-        <v>2878.12</v>
+        <v>2862.02</v>
       </c>
       <c r="I34" t="n">
-        <v>56952.45</v>
+        <v>57334.9</v>
       </c>
       <c r="J34" t="n">
-        <v>57335.89</v>
+        <v>60366.31</v>
       </c>
       <c r="K34" t="n">
-        <v>58525.25</v>
+        <v>61274.59</v>
       </c>
       <c r="L34" t="n">
-        <v>59714.6</v>
+        <v>62182.86</v>
       </c>
       <c r="M34" t="n">
-        <v>60501</v>
+        <v>64152.71</v>
       </c>
       <c r="N34" t="n">
-        <v>61287.39</v>
+        <v>66122.55</v>
       </c>
       <c r="O34" t="n">
-        <v>62879.7</v>
+        <v>65969.25999999999</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3379,83 +3379,83 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
+      <c r="R34" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
+      </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>63203.44</v>
+        <v>61299.87</v>
       </c>
       <c r="C35" t="n">
-        <v>63799.32</v>
+        <v>63432.41</v>
       </c>
       <c r="D35" t="n">
-        <v>60937.3</v>
+        <v>59292.25</v>
       </c>
       <c r="E35" t="n">
-        <v>61409.29</v>
+        <v>63339.07</v>
       </c>
       <c r="F35" t="n">
-        <v>-1304.36</v>
+        <v>1929.78</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0314</v>
       </c>
       <c r="H35" t="n">
-        <v>2862.02</v>
+        <v>4140.16</v>
       </c>
       <c r="I35" t="n">
-        <v>57334.9</v>
+        <v>58075.28</v>
       </c>
       <c r="J35" t="n">
-        <v>60366.31</v>
+        <v>58067.76</v>
       </c>
       <c r="K35" t="n">
-        <v>61274.59</v>
+        <v>59978.28</v>
       </c>
       <c r="L35" t="n">
-        <v>62182.86</v>
+        <v>61888.8</v>
       </c>
       <c r="M35" t="n">
-        <v>64152.71</v>
+        <v>62840.3</v>
       </c>
       <c r="N35" t="n">
-        <v>66122.55</v>
+        <v>63791.8</v>
       </c>
       <c r="O35" t="n">
-        <v>65969.25999999999</v>
+        <v>66661.34</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3465,20 +3465,24 @@
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
@@ -3489,57 +3493,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>61299.87</v>
+        <v>63658.95</v>
       </c>
       <c r="C36" t="n">
-        <v>63432.41</v>
+        <v>66505.02</v>
       </c>
       <c r="D36" t="n">
-        <v>59292.25</v>
+        <v>63562.51</v>
       </c>
       <c r="E36" t="n">
-        <v>63339.07</v>
+        <v>66329.5</v>
       </c>
       <c r="F36" t="n">
-        <v>1929.78</v>
+        <v>2990.43</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0314</v>
+        <v>0.0472</v>
       </c>
       <c r="H36" t="n">
-        <v>4140.16</v>
+        <v>2942.51</v>
       </c>
       <c r="I36" t="n">
-        <v>58075.28</v>
+        <v>55152.09</v>
       </c>
       <c r="J36" t="n">
-        <v>58067.76</v>
+        <v>60187.28</v>
       </c>
       <c r="K36" t="n">
-        <v>59978.28</v>
+        <v>61268.99</v>
       </c>
       <c r="L36" t="n">
-        <v>61888.8</v>
+        <v>62350.7</v>
       </c>
       <c r="M36" t="n">
-        <v>62840.3</v>
+        <v>65409.15</v>
       </c>
       <c r="N36" t="n">
-        <v>63791.8</v>
+        <v>68467.60000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>66661.34</v>
+        <v>67572.57000000001</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3547,10 +3551,8 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R36" s="6" t="n">
+        <v/>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
@@ -3559,14 +3561,12 @@
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
@@ -3575,59 +3575,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>63658.95</v>
+        <v>66363.42999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>66505.02</v>
+        <v>68786.49000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>63562.51</v>
+        <v>65551.13</v>
       </c>
       <c r="E37" t="n">
-        <v>66329.5</v>
+        <v>66588.12</v>
       </c>
       <c r="F37" t="n">
-        <v>2990.43</v>
+        <v>258.62</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0472</v>
+        <v>0.0039</v>
       </c>
       <c r="H37" t="n">
-        <v>2942.51</v>
+        <v>3235.36</v>
       </c>
       <c r="I37" t="n">
-        <v>55152.09</v>
+        <v>60620</v>
       </c>
       <c r="J37" t="n">
-        <v>60187.28</v>
+        <v>64034.85</v>
       </c>
       <c r="K37" t="n">
-        <v>61268.99</v>
+        <v>64858.24</v>
       </c>
       <c r="L37" t="n">
-        <v>62350.7</v>
+        <v>65681.63</v>
       </c>
       <c r="M37" t="n">
-        <v>65409.15</v>
+        <v>67800.75999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>68467.60000000001</v>
+        <v>69919.88</v>
       </c>
       <c r="O37" t="n">
-        <v>67572.57000000001</v>
+        <v>69447.53999999999</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3640,12 +3636,12 @@
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U37" s="8" t="n">
@@ -3664,69 +3660,71 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>66363.42999999999</v>
+        <v>65947.56</v>
       </c>
       <c r="C38" t="n">
-        <v>68786.49000000001</v>
+        <v>67065.94</v>
       </c>
       <c r="D38" t="n">
-        <v>65551.13</v>
+        <v>62335.75</v>
       </c>
       <c r="E38" t="n">
-        <v>66588.12</v>
+        <v>66020.03999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>258.62</v>
+        <v>-568.08</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0039</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>3235.36</v>
+        <v>4730.19</v>
       </c>
       <c r="I38" t="n">
-        <v>60620</v>
+        <v>62315.77</v>
       </c>
       <c r="J38" t="n">
-        <v>64034.85</v>
+        <v>63062.41</v>
       </c>
       <c r="K38" t="n">
-        <v>64858.24</v>
+        <v>64970.44</v>
       </c>
       <c r="L38" t="n">
-        <v>65681.63</v>
+        <v>66878.46000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>67800.75999999999</v>
+        <v>68205.8</v>
       </c>
       <c r="N38" t="n">
-        <v>69919.88</v>
+        <v>69533.13</v>
       </c>
       <c r="O38" t="n">
-        <v>69447.53999999999</v>
+        <v>72021.85000000001</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3739,141 +3737,143 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>65947.56</v>
+        <v>66783.22</v>
       </c>
       <c r="C39" t="n">
-        <v>67065.94</v>
+        <v>71952.99000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>62335.75</v>
+        <v>66783.22</v>
       </c>
       <c r="E39" t="n">
-        <v>66020.03999999999</v>
+        <v>71250.06</v>
       </c>
       <c r="F39" t="n">
-        <v>-568.08</v>
+        <v>5230.02</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>4730.19</v>
+        <v>5169.77</v>
       </c>
       <c r="I39" t="n">
-        <v>62315.77</v>
+        <v>57605.56</v>
       </c>
       <c r="J39" t="n">
-        <v>63062.41</v>
+        <v>61949.45</v>
       </c>
       <c r="K39" t="n">
-        <v>64970.44</v>
+        <v>63654.95</v>
       </c>
       <c r="L39" t="n">
-        <v>66878.46000000001</v>
+        <v>65360.44</v>
       </c>
       <c r="M39" t="n">
-        <v>68205.8</v>
+        <v>68385.13</v>
       </c>
       <c r="N39" t="n">
-        <v>69533.13</v>
+        <v>71409.82000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>72021.85000000001</v>
+        <v>71796.12</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v/>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>66783.22</v>
+        <v>71067.14999999999</v>
       </c>
       <c r="C40" t="n">
-        <v>71952.99000000001</v>
+        <v>72831.73</v>
       </c>
       <c r="D40" t="n">
-        <v>66783.22</v>
+        <v>68461.10000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>71250.06</v>
+        <v>69360.88</v>
       </c>
       <c r="F40" t="n">
-        <v>5230.02</v>
+        <v>-1889.18</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.07920000000000001</v>
+        <v>-0.0265</v>
       </c>
       <c r="H40" t="n">
-        <v>5169.77</v>
+        <v>4370.62</v>
       </c>
       <c r="I40" t="n">
-        <v>57605.56</v>
+        <v>61613.45</v>
       </c>
       <c r="J40" t="n">
-        <v>61949.45</v>
+        <v>67021.27</v>
       </c>
       <c r="K40" t="n">
-        <v>63654.95</v>
+        <v>68665.17999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>65360.44</v>
+        <v>70309.08</v>
       </c>
       <c r="M40" t="n">
-        <v>68385.13</v>
+        <v>73834.95</v>
       </c>
       <c r="N40" t="n">
-        <v>71409.82000000001</v>
+        <v>77360.81</v>
       </c>
       <c r="O40" t="n">
-        <v>71796.12</v>
+        <v>77122.77</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3881,83 +3881,83 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v/>
       </c>
       <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>71067.14999999999</v>
+        <v>69609.88</v>
       </c>
       <c r="C41" t="n">
-        <v>72831.73</v>
+        <v>71962.34</v>
       </c>
       <c r="D41" t="n">
-        <v>68461.10000000001</v>
+        <v>67609.49000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>69360.88</v>
+        <v>69744.07000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>-1889.18</v>
+        <v>383.19</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0265</v>
+        <v>0.0055</v>
       </c>
       <c r="H41" t="n">
-        <v>4370.62</v>
+        <v>4352.85</v>
       </c>
       <c r="I41" t="n">
-        <v>61613.45</v>
+        <v>64090.48</v>
       </c>
       <c r="J41" t="n">
-        <v>67021.27</v>
+        <v>64347.49</v>
       </c>
       <c r="K41" t="n">
-        <v>68665.17999999999</v>
+        <v>67175.57000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>70309.08</v>
+        <v>70003.64999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>73834.95</v>
+        <v>71546.2</v>
       </c>
       <c r="N41" t="n">
-        <v>77360.81</v>
+        <v>73088.74000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>77122.77</v>
+        <v>77202.35000000001</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3965,18 +3965,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R41" s="6" t="n">
+        <v/>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3991,57 +3991,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>69609.88</v>
+        <v>69973.34</v>
       </c>
       <c r="C42" t="n">
-        <v>71962.34</v>
+        <v>70384.59</v>
       </c>
       <c r="D42" t="n">
-        <v>67609.49000000001</v>
+        <v>66819.05</v>
       </c>
       <c r="E42" t="n">
-        <v>69744.07000000001</v>
+        <v>68557.73</v>
       </c>
       <c r="F42" t="n">
-        <v>383.19</v>
+        <v>-1186.34</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0055</v>
+        <v>-0.017</v>
       </c>
       <c r="H42" t="n">
-        <v>4352.85</v>
+        <v>3565.55</v>
       </c>
       <c r="I42" t="n">
-        <v>64090.48</v>
+        <v>63256.64</v>
       </c>
       <c r="J42" t="n">
-        <v>64347.49</v>
+        <v>65370.29</v>
       </c>
       <c r="K42" t="n">
-        <v>67175.57000000001</v>
+        <v>67567.64</v>
       </c>
       <c r="L42" t="n">
-        <v>70003.64999999999</v>
+        <v>69764.99000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>71546.2</v>
+        <v>71920.5</v>
       </c>
       <c r="N42" t="n">
-        <v>73088.74000000001</v>
+        <v>74076</v>
       </c>
       <c r="O42" t="n">
-        <v>77202.35000000001</v>
+        <v>76315.2</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4049,18 +4049,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4075,67 +4075,71 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>69973.34</v>
+        <v>68410.63</v>
       </c>
       <c r="C43" t="n">
-        <v>70384.59</v>
+        <v>69078.21000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>66819.05</v>
+        <v>62704.6</v>
       </c>
       <c r="E43" t="n">
-        <v>68557.73</v>
+        <v>64141.12</v>
       </c>
       <c r="F43" t="n">
-        <v>-1186.34</v>
+        <v>-4416.61</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0644</v>
       </c>
       <c r="H43" t="n">
-        <v>3565.55</v>
+        <v>6373.61</v>
       </c>
       <c r="I43" t="n">
-        <v>63256.64</v>
+        <v>63253.5</v>
       </c>
       <c r="J43" t="n">
-        <v>65370.29</v>
+        <v>64970.13</v>
       </c>
       <c r="K43" t="n">
-        <v>67567.64</v>
+        <v>66774.95</v>
       </c>
       <c r="L43" t="n">
-        <v>69764.99000000001</v>
+        <v>68579.77</v>
       </c>
       <c r="M43" t="n">
-        <v>71920.5</v>
+        <v>70340.5</v>
       </c>
       <c r="N43" t="n">
-        <v>74076</v>
+        <v>72101.23</v>
       </c>
       <c r="O43" t="n">
-        <v>76315.2</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
+        <v>73950.14</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
@@ -4152,87 +4156,79 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W43" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>68410.63</v>
+        <v>64544.05</v>
       </c>
       <c r="C44" t="n">
-        <v>69078.21000000001</v>
+        <v>67592.2</v>
       </c>
       <c r="D44" t="n">
-        <v>62704.6</v>
+        <v>64201.03</v>
       </c>
       <c r="E44" t="n">
-        <v>64141.12</v>
+        <v>64611.15</v>
       </c>
       <c r="F44" t="n">
-        <v>-4416.61</v>
+        <v>470.03</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0644</v>
+        <v>0.0073</v>
       </c>
       <c r="H44" t="n">
-        <v>6373.61</v>
+        <v>3391.17</v>
       </c>
       <c r="I44" t="n">
-        <v>63253.5</v>
+        <v>56330.99</v>
       </c>
       <c r="J44" t="n">
-        <v>64970.13</v>
+        <v>56892.37</v>
       </c>
       <c r="K44" t="n">
-        <v>66774.95</v>
+        <v>60954.32</v>
       </c>
       <c r="L44" t="n">
-        <v>68579.77</v>
+        <v>65016.26</v>
       </c>
       <c r="M44" t="n">
-        <v>70340.5</v>
+        <v>67327.92999999999</v>
       </c>
       <c r="N44" t="n">
-        <v>72101.23</v>
+        <v>69639.59</v>
       </c>
       <c r="O44" t="n">
-        <v>73950.14</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>75451.82000000001</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4245,74 +4241,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>64544.05</v>
+        <v>65164.98</v>
       </c>
       <c r="C45" t="n">
-        <v>67592.2</v>
+        <v>65364.73</v>
       </c>
       <c r="D45" t="n">
-        <v>64201.03</v>
+        <v>60448.9</v>
       </c>
       <c r="E45" t="n">
-        <v>64611.15</v>
+        <v>64362.02</v>
       </c>
       <c r="F45" t="n">
-        <v>470.03</v>
+        <v>-249.13</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0073</v>
+        <v>-0.0039</v>
       </c>
       <c r="H45" t="n">
-        <v>3391.17</v>
+        <v>4915.83</v>
       </c>
       <c r="I45" t="n">
-        <v>56330.99</v>
+        <v>60809.86</v>
       </c>
       <c r="J45" t="n">
-        <v>56892.37</v>
+        <v>60577.24</v>
       </c>
       <c r="K45" t="n">
-        <v>60954.32</v>
+        <v>62915.56</v>
       </c>
       <c r="L45" t="n">
-        <v>65016.26</v>
+        <v>65253.88</v>
       </c>
       <c r="M45" t="n">
-        <v>67327.92999999999</v>
+        <v>66306.73</v>
       </c>
       <c r="N45" t="n">
-        <v>69639.59</v>
+        <v>67359.59</v>
       </c>
       <c r="O45" t="n">
-        <v>75451.82000000001</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+        <v>70983.38</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4325,82 +4329,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>65164.98</v>
+        <v>63834.95</v>
       </c>
       <c r="C46" t="n">
-        <v>65364.73</v>
+        <v>66302.52</v>
       </c>
       <c r="D46" t="n">
-        <v>60448.9</v>
+        <v>62703.47</v>
       </c>
       <c r="E46" t="n">
-        <v>64362.02</v>
+        <v>65606.71000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>-249.13</v>
+        <v>1244.69</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0193</v>
       </c>
       <c r="H46" t="n">
-        <v>4915.83</v>
+        <v>3599.05</v>
       </c>
       <c r="I46" t="n">
-        <v>60809.86</v>
+        <v>55533.07</v>
       </c>
       <c r="J46" t="n">
-        <v>60577.24</v>
+        <v>60173.79</v>
       </c>
       <c r="K46" t="n">
-        <v>62915.56</v>
+        <v>61904.1</v>
       </c>
       <c r="L46" t="n">
-        <v>65253.88</v>
+        <v>63634.42</v>
       </c>
       <c r="M46" t="n">
-        <v>66306.73</v>
+        <v>66819.94</v>
       </c>
       <c r="N46" t="n">
-        <v>67359.59</v>
+        <v>70005.45</v>
       </c>
       <c r="O46" t="n">
-        <v>70983.38</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+        <v>70280.56</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4413,55 +4409,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>63834.95</v>
+        <v>65905.10000000001</v>
       </c>
       <c r="C47" t="n">
-        <v>66302.52</v>
+        <v>69608.24000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>62703.47</v>
+        <v>65848.58</v>
       </c>
       <c r="E47" t="n">
-        <v>65606.71000000001</v>
+        <v>68713.8</v>
       </c>
       <c r="F47" t="n">
-        <v>1244.69</v>
+        <v>3107.09</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0193</v>
+        <v>0.0474</v>
       </c>
       <c r="H47" t="n">
-        <v>3599.05</v>
+        <v>3759.66</v>
       </c>
       <c r="I47" t="n">
-        <v>55533.07</v>
+        <v>59104.41</v>
       </c>
       <c r="J47" t="n">
-        <v>60173.79</v>
+        <v>62559.51</v>
       </c>
       <c r="K47" t="n">
-        <v>61904.1</v>
+        <v>63807.18</v>
       </c>
       <c r="L47" t="n">
-        <v>63634.42</v>
+        <v>65054.85</v>
       </c>
       <c r="M47" t="n">
-        <v>66819.94</v>
+        <v>67406.24000000001</v>
       </c>
       <c r="N47" t="n">
-        <v>70005.45</v>
+        <v>69757.62</v>
       </c>
       <c r="O47" t="n">
-        <v>70280.56</v>
+        <v>69901.58</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4479,11 +4479,13 @@
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4502,75 +4504,75 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>65905.10000000001</v>
+        <v>68882.06</v>
       </c>
       <c r="C48" t="n">
-        <v>69608.24000000001</v>
+        <v>69225.57000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>65848.58</v>
+        <v>65133.98</v>
       </c>
       <c r="E48" t="n">
-        <v>68713.8</v>
+        <v>66016.36</v>
       </c>
       <c r="F48" t="n">
-        <v>3107.09</v>
+        <v>-2697.44</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0474</v>
+        <v>-0.0393</v>
       </c>
       <c r="H48" t="n">
-        <v>3759.66</v>
+        <v>4091.59</v>
       </c>
       <c r="I48" t="n">
-        <v>59104.41</v>
+        <v>62088.91</v>
       </c>
       <c r="J48" t="n">
-        <v>62559.51</v>
+        <v>65446.83</v>
       </c>
       <c r="K48" t="n">
-        <v>63807.18</v>
+        <v>66833.96000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>65054.85</v>
+        <v>68221.10000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>67406.24000000001</v>
+        <v>70593.63</v>
       </c>
       <c r="N48" t="n">
-        <v>69757.62</v>
+        <v>72966.14999999999</v>
       </c>
       <c r="O48" t="n">
-        <v>69901.58</v>
+        <v>73367.91</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
+      <c r="Q48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
@@ -4579,76 +4581,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>68882.06</v>
+        <v>65978.95</v>
       </c>
       <c r="C49" t="n">
-        <v>69225.57000000001</v>
+        <v>66954.69</v>
       </c>
       <c r="D49" t="n">
-        <v>65133.98</v>
+        <v>64609.47</v>
       </c>
       <c r="E49" t="n">
-        <v>66016.36</v>
+        <v>66405.56</v>
       </c>
       <c r="F49" t="n">
-        <v>-2697.44</v>
+        <v>389.2</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0393</v>
+        <v>0.0059</v>
       </c>
       <c r="H49" t="n">
-        <v>4091.59</v>
+        <v>2345.22</v>
       </c>
       <c r="I49" t="n">
-        <v>62088.91</v>
+        <v>61042.39</v>
       </c>
       <c r="J49" t="n">
-        <v>65446.83</v>
+        <v>61343.06</v>
       </c>
       <c r="K49" t="n">
-        <v>66833.96000000001</v>
+        <v>63970.56</v>
       </c>
       <c r="L49" t="n">
-        <v>68221.10000000001</v>
+        <v>66598.07000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>70593.63</v>
+        <v>68062.14999999999</v>
       </c>
       <c r="N49" t="n">
-        <v>72966.14999999999</v>
+        <v>69526.24000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>73367.91</v>
+        <v>73317.16</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4665,68 +4659,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>65978.95</v>
+        <v>65668.50999999999</v>
       </c>
       <c r="C50" t="n">
-        <v>66954.69</v>
+        <v>66525.7</v>
       </c>
       <c r="D50" t="n">
-        <v>64609.47</v>
+        <v>63772.8</v>
       </c>
       <c r="E50" t="n">
-        <v>66405.56</v>
+        <v>65020.94</v>
       </c>
       <c r="F50" t="n">
-        <v>389.2</v>
+        <v>-1384.62</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0209</v>
       </c>
       <c r="H50" t="n">
-        <v>2345.22</v>
+        <v>2752.9</v>
       </c>
       <c r="I50" t="n">
-        <v>61042.39</v>
+        <v>62264.25</v>
       </c>
       <c r="J50" t="n">
-        <v>61343.06</v>
+        <v>64372.09</v>
       </c>
       <c r="K50" t="n">
-        <v>63970.56</v>
+        <v>65232.95</v>
       </c>
       <c r="L50" t="n">
-        <v>66598.07000000001</v>
+        <v>66093.82000000001</v>
       </c>
       <c r="M50" t="n">
-        <v>68062.14999999999</v>
+        <v>67578.17</v>
       </c>
       <c r="N50" t="n">
-        <v>69526.24000000001</v>
+        <v>69062.52</v>
       </c>
       <c r="O50" t="n">
-        <v>73317.16</v>
+        <v>69299.91</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4743,67 +4745,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>65668.50999999999</v>
+        <v>65600.42</v>
       </c>
       <c r="C51" t="n">
-        <v>66525.7</v>
+        <v>66791.84</v>
       </c>
       <c r="D51" t="n">
-        <v>63772.8</v>
+        <v>63208.63</v>
       </c>
       <c r="E51" t="n">
-        <v>65020.94</v>
+        <v>64011.34</v>
       </c>
       <c r="F51" t="n">
-        <v>-1384.62</v>
+        <v>-1009.6</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0209</v>
+        <v>-0.0155</v>
       </c>
       <c r="H51" t="n">
-        <v>2752.9</v>
+        <v>3583.21</v>
       </c>
       <c r="I51" t="n">
-        <v>62264.25</v>
+        <v>61019.9</v>
       </c>
       <c r="J51" t="n">
-        <v>64372.09</v>
+        <v>62203.88</v>
       </c>
       <c r="K51" t="n">
-        <v>65232.95</v>
+        <v>63644.49</v>
       </c>
       <c r="L51" t="n">
-        <v>66093.82000000001</v>
+        <v>65085.1</v>
       </c>
       <c r="M51" t="n">
-        <v>67578.17</v>
+        <v>66397.39</v>
       </c>
       <c r="N51" t="n">
-        <v>69062.52</v>
+        <v>67709.69</v>
       </c>
       <c r="O51" t="n">
-        <v>69299.91</v>
+        <v>69278.61</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q51" s="6" t="n">
+        <v/>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
@@ -4815,8 +4811,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4829,55 +4827,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>65600.42</v>
+        <v>63659.53</v>
       </c>
       <c r="C52" t="n">
-        <v>66791.84</v>
+        <v>65436.57</v>
       </c>
       <c r="D52" t="n">
-        <v>63208.63</v>
+        <v>62726.18</v>
       </c>
       <c r="E52" t="n">
-        <v>64011.34</v>
+        <v>65018.95</v>
       </c>
       <c r="F52" t="n">
-        <v>-1009.6</v>
+        <v>1007.61</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0157</v>
       </c>
       <c r="H52" t="n">
-        <v>3583.21</v>
+        <v>2710.39</v>
       </c>
       <c r="I52" t="n">
-        <v>61019.9</v>
+        <v>59625.41</v>
       </c>
       <c r="J52" t="n">
-        <v>62203.88</v>
+        <v>59933.68</v>
       </c>
       <c r="K52" t="n">
-        <v>63644.49</v>
+        <v>62219.73</v>
       </c>
       <c r="L52" t="n">
-        <v>65085.1</v>
+        <v>64505.79</v>
       </c>
       <c r="M52" t="n">
-        <v>66397.39</v>
+        <v>65802.95</v>
       </c>
       <c r="N52" t="n">
-        <v>67709.69</v>
+        <v>67100.11</v>
       </c>
       <c r="O52" t="n">
-        <v>69278.61</v>
+        <v>70375.06</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4885,20 +4887,16 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4920,50 +4918,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>63659.53</v>
+        <v>65476.44</v>
       </c>
       <c r="C53" t="n">
-        <v>65436.57</v>
+        <v>66410.27</v>
       </c>
       <c r="D53" t="n">
-        <v>62726.18</v>
+        <v>65407.37</v>
       </c>
       <c r="E53" t="n">
-        <v>65018.95</v>
+        <v>66364.2</v>
       </c>
       <c r="F53" t="n">
-        <v>1007.61</v>
+        <v>1345.25</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0157</v>
+        <v>0.0207</v>
       </c>
       <c r="H53" t="n">
-        <v>2710.39</v>
+        <v>1002.9</v>
       </c>
       <c r="I53" t="n">
-        <v>59625.41</v>
+        <v>60015.79</v>
       </c>
       <c r="J53" t="n">
-        <v>59933.68</v>
+        <v>62777.35</v>
       </c>
       <c r="K53" t="n">
-        <v>62219.73</v>
+        <v>63663.75</v>
       </c>
       <c r="L53" t="n">
-        <v>64505.79</v>
+        <v>64550.16</v>
       </c>
       <c r="M53" t="n">
-        <v>65802.95</v>
+        <v>66374.14</v>
       </c>
       <c r="N53" t="n">
-        <v>67100.11</v>
+        <v>68198.13</v>
       </c>
       <c r="O53" t="n">
-        <v>70375.06</v>
+        <v>68146.96000000001</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4976,11 +4974,13 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4995,66 +4995,70 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>65476.44</v>
+        <v>66505.94</v>
       </c>
       <c r="C54" t="n">
-        <v>66410.27</v>
+        <v>68995.3</v>
       </c>
       <c r="D54" t="n">
-        <v>65407.37</v>
+        <v>64699.49</v>
       </c>
       <c r="E54" t="n">
-        <v>66364.2</v>
+        <v>68309.46000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>1345.25</v>
+        <v>1945.26</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0207</v>
+        <v>0.0293</v>
       </c>
       <c r="H54" t="n">
-        <v>1002.9</v>
+        <v>4295.81</v>
       </c>
       <c r="I54" t="n">
-        <v>60015.79</v>
+        <v>64404.47</v>
       </c>
       <c r="J54" t="n">
-        <v>62777.35</v>
+        <v>65588.99000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>63663.75</v>
+        <v>65862.75</v>
       </c>
       <c r="L54" t="n">
-        <v>64550.16</v>
+        <v>66136.50999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>66374.14</v>
+        <v>66865.64999999999</v>
       </c>
       <c r="N54" t="n">
-        <v>68198.13</v>
+        <v>67594.8</v>
       </c>
       <c r="O54" t="n">
-        <v>68146.96000000001</v>
+        <v>67413.17999999999</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
@@ -5063,86 +5067,86 @@
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W54" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W54" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>66505.94</v>
+        <v>69113.74000000001</v>
       </c>
       <c r="C55" t="n">
-        <v>68995.3</v>
+        <v>70798.62</v>
       </c>
       <c r="D55" t="n">
-        <v>64699.49</v>
+        <v>68150.02</v>
       </c>
       <c r="E55" t="n">
-        <v>68309.46000000001</v>
+        <v>69030.92</v>
       </c>
       <c r="F55" t="n">
-        <v>1945.26</v>
+        <v>721.46</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0293</v>
+        <v>0.0106</v>
       </c>
       <c r="H55" t="n">
-        <v>4295.81</v>
+        <v>2648.59</v>
       </c>
       <c r="I55" t="n">
-        <v>64404.47</v>
+        <v>60403.68</v>
       </c>
       <c r="J55" t="n">
-        <v>65588.99000000001</v>
+        <v>64744.69</v>
       </c>
       <c r="K55" t="n">
-        <v>65862.75</v>
+        <v>66161.56</v>
       </c>
       <c r="L55" t="n">
-        <v>66136.50999999999</v>
+        <v>67578.42999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>66865.64999999999</v>
+        <v>70457.37</v>
       </c>
       <c r="N55" t="n">
-        <v>67594.8</v>
+        <v>73336.3</v>
       </c>
       <c r="O55" t="n">
-        <v>67413.17999999999</v>
+        <v>73291.11</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
@@ -5151,106 +5155,102 @@
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
       </c>
       <c r="W55" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>69113.74000000001</v>
+        <v>68564.85000000001</v>
       </c>
       <c r="C56" t="n">
-        <v>70798.62</v>
+        <v>68710.99000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>68150.02</v>
+        <v>64092.74</v>
       </c>
       <c r="E56" t="n">
-        <v>69030.92</v>
+        <v>65324.29</v>
       </c>
       <c r="F56" t="n">
-        <v>721.46</v>
+        <v>-3706.63</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0106</v>
+        <v>-0.0537</v>
       </c>
       <c r="H56" t="n">
-        <v>2648.59</v>
+        <v>4618.25</v>
       </c>
       <c r="I56" t="n">
-        <v>60403.68</v>
+        <v>65501.43</v>
       </c>
       <c r="J56" t="n">
-        <v>64744.69</v>
+        <v>66160.63</v>
       </c>
       <c r="K56" t="n">
-        <v>66161.56</v>
+        <v>67706.62</v>
       </c>
       <c r="L56" t="n">
-        <v>67578.42999999999</v>
+        <v>69252.62</v>
       </c>
       <c r="M56" t="n">
-        <v>70457.37</v>
+        <v>70355.22</v>
       </c>
       <c r="N56" t="n">
-        <v>73336.3</v>
+        <v>71457.82000000001</v>
       </c>
       <c r="O56" t="n">
-        <v>73291.11</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
+        <v>73447.21000000001</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W56" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X56" t="inlineStr"/>
@@ -5258,66 +5258,62 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>68564.85000000001</v>
+        <v>64819.56</v>
       </c>
       <c r="C57" t="n">
-        <v>68710.99000000001</v>
+        <v>65404.63</v>
       </c>
       <c r="D57" t="n">
-        <v>64092.74</v>
+        <v>61462.61</v>
       </c>
       <c r="E57" t="n">
-        <v>65324.29</v>
+        <v>62693.16</v>
       </c>
       <c r="F57" t="n">
-        <v>-3706.63</v>
+        <v>-2631.13</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0537</v>
+        <v>-0.0403</v>
       </c>
       <c r="H57" t="n">
-        <v>4618.25</v>
+        <v>3942.02</v>
       </c>
       <c r="I57" t="n">
-        <v>65501.43</v>
+        <v>59474.48</v>
       </c>
       <c r="J57" t="n">
-        <v>66160.63</v>
+        <v>60167.25</v>
       </c>
       <c r="K57" t="n">
-        <v>67706.62</v>
+        <v>63015.16</v>
       </c>
       <c r="L57" t="n">
-        <v>69252.62</v>
+        <v>65863.08</v>
       </c>
       <c r="M57" t="n">
-        <v>70355.22</v>
+        <v>67633.42</v>
       </c>
       <c r="N57" t="n">
-        <v>71457.82000000001</v>
+        <v>69403.75</v>
       </c>
       <c r="O57" t="n">
-        <v>73447.21000000001</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
+        <v>73329.25</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5338,84 +5334,6 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>64819.56</v>
-      </c>
-      <c r="C58" t="n">
-        <v>65404.63</v>
-      </c>
-      <c r="D58" t="n">
-        <v>63807.15</v>
-      </c>
-      <c r="E58" t="n">
-        <v>64621.24</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-703.05</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0108</v>
-      </c>
-      <c r="H58" t="n">
-        <v>1597.48</v>
-      </c>
-      <c r="I58" t="n">
-        <v>59474.48</v>
-      </c>
-      <c r="J58" t="n">
-        <v>60167.25</v>
-      </c>
-      <c r="K58" t="n">
-        <v>63015.16</v>
-      </c>
-      <c r="L58" t="n">
-        <v>65863.08</v>
-      </c>
-      <c r="M58" t="n">
-        <v>67633.42</v>
-      </c>
-      <c r="N58" t="n">
-        <v>69403.75</v>
-      </c>
-      <c r="O58" t="n">
-        <v>73329.25</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5335,6 +5338,90 @@
       </c>
       <c r="X57" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>62449.96</v>
+      </c>
+      <c r="C58" t="n">
+        <v>62902.95</v>
+      </c>
+      <c r="D58" t="n">
+        <v>62094.34</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>808.61</v>
+      </c>
+      <c r="I58" t="n">
+        <v>57520.59</v>
+      </c>
+      <c r="J58" t="n">
+        <v>58380.91</v>
+      </c>
+      <c r="K58" t="n">
+        <v>60722.15</v>
+      </c>
+      <c r="L58" t="n">
+        <v>63063.39</v>
+      </c>
+      <c r="M58" t="n">
+        <v>64664.17</v>
+      </c>
+      <c r="N58" t="n">
+        <v>66264.95</v>
+      </c>
+      <c r="O58" t="n">
+        <v>69346.64999999999</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,25 +659,25 @@
         <v>1421.01</v>
       </c>
       <c r="I2" t="n">
-        <v>44562.85</v>
+        <v>44586.25</v>
       </c>
       <c r="J2" t="n">
-        <v>44646.95</v>
+        <v>44655.72</v>
       </c>
       <c r="K2" t="n">
-        <v>45039.53</v>
+        <v>45045.38</v>
       </c>
       <c r="L2" t="n">
-        <v>45432.11</v>
+        <v>45435.03</v>
       </c>
       <c r="M2" t="n">
-        <v>45670.45</v>
+        <v>45664.6</v>
       </c>
       <c r="N2" t="n">
-        <v>45908.79</v>
+        <v>45894.17</v>
       </c>
       <c r="O2" t="n">
-        <v>46455.61</v>
+        <v>46443.91</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -5354,13 +5351,13 @@
         <v>62094.34</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>62189.65</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>-503.51</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>-0.008</v>
       </c>
       <c r="H58" t="n">
         <v>808.61</v>
@@ -5386,10 +5383,8 @@
       <c r="O58" t="n">
         <v>69346.64999999999</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5397,9 +5392,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -5345,22 +5345,22 @@
         <v>62449.96</v>
       </c>
       <c r="C58" t="n">
-        <v>62902.95</v>
+        <v>63684.69</v>
       </c>
       <c r="D58" t="n">
         <v>62094.34</v>
       </c>
       <c r="E58" t="n">
-        <v>62189.65</v>
+        <v>63268.37</v>
       </c>
       <c r="F58" t="n">
-        <v>-503.51</v>
+        <v>575.21</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.008</v>
+        <v>0.0092</v>
       </c>
       <c r="H58" t="n">
-        <v>808.61</v>
+        <v>1590.35</v>
       </c>
       <c r="I58" t="n">
         <v>57520.59</v>
@@ -5392,9 +5392,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>1421.01</v>
       </c>
       <c r="I2" t="n">
-        <v>44586.25</v>
+        <v>44885.29</v>
       </c>
       <c r="J2" t="n">
-        <v>44655.72</v>
+        <v>44767.86</v>
       </c>
       <c r="K2" t="n">
-        <v>45045.38</v>
+        <v>45120.14</v>
       </c>
       <c r="L2" t="n">
-        <v>45435.03</v>
+        <v>45472.41</v>
       </c>
       <c r="M2" t="n">
-        <v>45664.6</v>
+        <v>45589.84</v>
       </c>
       <c r="N2" t="n">
-        <v>45894.17</v>
+        <v>45707.27</v>
       </c>
       <c r="O2" t="n">
-        <v>46443.91</v>
+        <v>46294.39</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -701,11 +701,13 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -5345,22 +5347,22 @@
         <v>62449.96</v>
       </c>
       <c r="C58" t="n">
-        <v>63684.69</v>
+        <v>64308.71</v>
       </c>
       <c r="D58" t="n">
         <v>62094.34</v>
       </c>
       <c r="E58" t="n">
-        <v>63268.37</v>
+        <v>63954.19</v>
       </c>
       <c r="F58" t="n">
-        <v>575.21</v>
+        <v>1261.03</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0092</v>
+        <v>0.0201</v>
       </c>
       <c r="H58" t="n">
-        <v>1590.35</v>
+        <v>2214.37</v>
       </c>
       <c r="I58" t="n">
         <v>57520.59</v>
@@ -5394,11 +5396,13 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>1421.01</v>
       </c>
       <c r="I2" t="n">
-        <v>44885.29</v>
+        <v>44943.21</v>
       </c>
       <c r="J2" t="n">
-        <v>44767.86</v>
+        <v>44840.26</v>
       </c>
       <c r="K2" t="n">
-        <v>45120.14</v>
+        <v>45149.1</v>
       </c>
       <c r="L2" t="n">
-        <v>45472.41</v>
+        <v>45457.93</v>
       </c>
       <c r="M2" t="n">
-        <v>45589.84</v>
+        <v>45560.88</v>
       </c>
       <c r="N2" t="n">
-        <v>45707.27</v>
+        <v>45663.82</v>
       </c>
       <c r="O2" t="n">
-        <v>46294.39</v>
+        <v>46178.55</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -5347,22 +5347,22 @@
         <v>62449.96</v>
       </c>
       <c r="C58" t="n">
-        <v>64308.71</v>
+        <v>64831.29</v>
       </c>
       <c r="D58" t="n">
         <v>62094.34</v>
       </c>
       <c r="E58" t="n">
-        <v>63954.19</v>
+        <v>64659.47</v>
       </c>
       <c r="F58" t="n">
-        <v>1261.03</v>
+        <v>1966.31</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0201</v>
+        <v>0.0314</v>
       </c>
       <c r="H58" t="n">
-        <v>2214.37</v>
+        <v>2736.95</v>
       </c>
       <c r="I58" t="n">
         <v>57520.59</v>

--- a/three_gate/analysis/N225_weekly.xlsx
+++ b/three_gate/analysis/N225_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,65 +634,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45113.29</v>
+        <v>46636.07</v>
       </c>
       <c r="C2" t="n">
-        <v>45778.66</v>
+        <v>48597.08</v>
       </c>
       <c r="D2" t="n">
-        <v>44357.65</v>
+        <v>46592.99</v>
       </c>
       <c r="E2" t="n">
-        <v>45769.5</v>
+        <v>48088.8</v>
       </c>
       <c r="F2" t="n">
-        <v>414.51</v>
+        <v>2319.3</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0507</v>
       </c>
       <c r="H2" t="n">
-        <v>1421.01</v>
+        <v>2004.09</v>
       </c>
       <c r="I2" t="n">
-        <v>44943.21</v>
+        <v>42936.64</v>
       </c>
       <c r="J2" t="n">
-        <v>44840.26</v>
+        <v>44699.16</v>
       </c>
       <c r="K2" t="n">
-        <v>45149.1</v>
+        <v>45058.99</v>
       </c>
       <c r="L2" t="n">
-        <v>45457.93</v>
+        <v>45418.83</v>
       </c>
       <c r="M2" t="n">
-        <v>45560.88</v>
+        <v>46480.01</v>
       </c>
       <c r="N2" t="n">
-        <v>45663.82</v>
+        <v>47541.18</v>
       </c>
       <c r="O2" t="n">
-        <v>46178.55</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>47199.67</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -709,67 +703,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46636.07</v>
+        <v>47446.73</v>
       </c>
       <c r="C3" t="n">
-        <v>48597.08</v>
+        <v>48317.34</v>
       </c>
       <c r="D3" t="n">
-        <v>46592.99</v>
+        <v>46544.05</v>
       </c>
       <c r="E3" t="n">
-        <v>48088.8</v>
+        <v>47582.15</v>
       </c>
       <c r="F3" t="n">
-        <v>2319.3</v>
+        <v>-506.65</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0507</v>
+        <v>-0.0105</v>
       </c>
       <c r="H3" t="n">
-        <v>2004.09</v>
+        <v>1773.29</v>
       </c>
       <c r="I3" t="n">
-        <v>42936.64</v>
+        <v>44588.9</v>
       </c>
       <c r="J3" t="n">
-        <v>44699.16</v>
+        <v>46331.59</v>
       </c>
       <c r="K3" t="n">
-        <v>45058.99</v>
+        <v>47086.76</v>
       </c>
       <c r="L3" t="n">
-        <v>45418.83</v>
+        <v>47841.92</v>
       </c>
       <c r="M3" t="n">
-        <v>46480.01</v>
+        <v>49090.85</v>
       </c>
       <c r="N3" t="n">
-        <v>47541.18</v>
+        <v>50339.77</v>
       </c>
       <c r="O3" t="n">
-        <v>47199.67</v>
+        <v>50601.17</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -777,83 +769,83 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47446.73</v>
+        <v>48332.71</v>
       </c>
       <c r="C4" t="n">
-        <v>48317.34</v>
+        <v>49945.95</v>
       </c>
       <c r="D4" t="n">
-        <v>46544.05</v>
+        <v>48254.83</v>
       </c>
       <c r="E4" t="n">
-        <v>47582.15</v>
+        <v>49299.65</v>
       </c>
       <c r="F4" t="n">
-        <v>-506.65</v>
+        <v>1717.5</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0105</v>
+        <v>0.0361</v>
       </c>
       <c r="H4" t="n">
-        <v>1773.29</v>
+        <v>1691.12</v>
       </c>
       <c r="I4" t="n">
-        <v>44588.9</v>
+        <v>44770.76</v>
       </c>
       <c r="J4" t="n">
-        <v>46331.59</v>
+        <v>45884.59</v>
       </c>
       <c r="K4" t="n">
-        <v>47086.76</v>
+        <v>46695.5</v>
       </c>
       <c r="L4" t="n">
-        <v>47841.92</v>
+        <v>47506.42</v>
       </c>
       <c r="M4" t="n">
-        <v>49090.85</v>
+        <v>48468.79</v>
       </c>
       <c r="N4" t="n">
-        <v>50339.77</v>
+        <v>49431.16</v>
       </c>
       <c r="O4" t="n">
-        <v>50601.17</v>
+        <v>50090.63</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -861,21 +853,23 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -885,59 +879,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48332.71</v>
+        <v>49905.8</v>
       </c>
       <c r="C5" t="n">
-        <v>49945.95</v>
+        <v>52411.34</v>
       </c>
       <c r="D5" t="n">
-        <v>48254.83</v>
+        <v>49838.98</v>
       </c>
       <c r="E5" t="n">
-        <v>49299.65</v>
+        <v>52411.34</v>
       </c>
       <c r="F5" t="n">
-        <v>1717.5</v>
+        <v>3111.69</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0361</v>
+        <v>0.0631</v>
       </c>
       <c r="H5" t="n">
-        <v>1691.12</v>
+        <v>2572.36</v>
       </c>
       <c r="I5" t="n">
-        <v>44770.76</v>
+        <v>46563.71</v>
       </c>
       <c r="J5" t="n">
-        <v>45884.59</v>
+        <v>47708.16</v>
       </c>
       <c r="K5" t="n">
-        <v>46695.5</v>
+        <v>48454.09</v>
       </c>
       <c r="L5" t="n">
-        <v>47506.42</v>
+        <v>49200.02</v>
       </c>
       <c r="M5" t="n">
-        <v>48468.79</v>
+        <v>50145.21</v>
       </c>
       <c r="N5" t="n">
-        <v>49431.16</v>
+        <v>51090.4</v>
       </c>
       <c r="O5" t="n">
-        <v>50090.63</v>
+        <v>51637.07</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -960,11 +950,13 @@
       </c>
       <c r="U5" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
@@ -976,151 +968,149 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49905.8</v>
+        <v>52294.31</v>
       </c>
       <c r="C6" t="n">
-        <v>52411.34</v>
+        <v>52636.87</v>
       </c>
       <c r="D6" t="n">
-        <v>49838.98</v>
+        <v>49073.58</v>
       </c>
       <c r="E6" t="n">
-        <v>52411.34</v>
+        <v>50276.37</v>
       </c>
       <c r="F6" t="n">
-        <v>3111.69</v>
+        <v>-2134.97</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0631</v>
+        <v>-0.0407</v>
       </c>
       <c r="H6" t="n">
-        <v>2572.36</v>
+        <v>3563.29</v>
       </c>
       <c r="I6" t="n">
-        <v>46563.71</v>
+        <v>47266.62</v>
       </c>
       <c r="J6" t="n">
-        <v>47708.16</v>
+        <v>50482.07</v>
       </c>
       <c r="K6" t="n">
-        <v>48454.09</v>
+        <v>51125.16</v>
       </c>
       <c r="L6" t="n">
-        <v>49200.02</v>
+        <v>51768.25</v>
       </c>
       <c r="M6" t="n">
-        <v>50145.21</v>
+        <v>53697.52</v>
       </c>
       <c r="N6" t="n">
-        <v>51090.4</v>
+        <v>55626.79</v>
       </c>
       <c r="O6" t="n">
-        <v>51637.07</v>
+        <v>54983.7</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
+      <c r="Q6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W6" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>52294.31</v>
+        <v>50645.27</v>
       </c>
       <c r="C7" t="n">
-        <v>52636.87</v>
+        <v>51513.16</v>
       </c>
       <c r="D7" t="n">
-        <v>49073.58</v>
+        <v>50246.6</v>
       </c>
       <c r="E7" t="n">
-        <v>50276.37</v>
+        <v>50376.53</v>
       </c>
       <c r="F7" t="n">
-        <v>-2134.97</v>
+        <v>100.16</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0407</v>
+        <v>0.002</v>
       </c>
       <c r="H7" t="n">
-        <v>3563.29</v>
+        <v>1266.56</v>
       </c>
       <c r="I7" t="n">
-        <v>47266.62</v>
+        <v>45510.29</v>
       </c>
       <c r="J7" t="n">
-        <v>50482.07</v>
+        <v>46423.65</v>
       </c>
       <c r="K7" t="n">
-        <v>51125.16</v>
+        <v>48494.72</v>
       </c>
       <c r="L7" t="n">
-        <v>51768.25</v>
+        <v>50565.8</v>
       </c>
       <c r="M7" t="n">
-        <v>53697.52</v>
+        <v>52058.02</v>
       </c>
       <c r="N7" t="n">
-        <v>55626.79</v>
+        <v>53550.24</v>
       </c>
       <c r="O7" t="n">
-        <v>54983.7</v>
+        <v>56200.16</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1139,70 +1129,76 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50645.27</v>
+        <v>50282.39</v>
       </c>
       <c r="C8" t="n">
-        <v>51513.16</v>
+        <v>50574.82</v>
       </c>
       <c r="D8" t="n">
-        <v>50246.6</v>
+        <v>48235.3</v>
       </c>
       <c r="E8" t="n">
-        <v>50376.53</v>
+        <v>48625.88</v>
       </c>
       <c r="F8" t="n">
-        <v>100.16</v>
+        <v>-1750.65</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0348</v>
       </c>
       <c r="H8" t="n">
-        <v>1266.56</v>
+        <v>2339.52</v>
       </c>
       <c r="I8" t="n">
-        <v>45510.29</v>
+        <v>48980.04</v>
       </c>
       <c r="J8" t="n">
-        <v>46423.65</v>
+        <v>48858.3</v>
       </c>
       <c r="K8" t="n">
-        <v>48494.72</v>
+        <v>49743.25</v>
       </c>
       <c r="L8" t="n">
-        <v>50565.8</v>
+        <v>50628.21</v>
       </c>
       <c r="M8" t="n">
-        <v>52058.02</v>
+        <v>51009.81</v>
       </c>
       <c r="N8" t="n">
-        <v>53550.24</v>
+        <v>51391.42</v>
       </c>
       <c r="O8" t="n">
-        <v>56200.16</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+        <v>52779.72</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1219,86 +1215,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50282.39</v>
+        <v>49113.82</v>
       </c>
       <c r="C9" t="n">
-        <v>50574.82</v>
+        <v>50322.14</v>
       </c>
       <c r="D9" t="n">
-        <v>48235.3</v>
+        <v>48511.95</v>
       </c>
       <c r="E9" t="n">
-        <v>48625.88</v>
+        <v>50253.91</v>
       </c>
       <c r="F9" t="n">
-        <v>-1750.65</v>
+        <v>1628.03</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0348</v>
+        <v>0.0335</v>
       </c>
       <c r="H9" t="n">
-        <v>2339.52</v>
+        <v>1810.19</v>
       </c>
       <c r="I9" t="n">
-        <v>48980.04</v>
+        <v>45895.78</v>
       </c>
       <c r="J9" t="n">
-        <v>48858.3</v>
+        <v>45896.77</v>
       </c>
       <c r="K9" t="n">
-        <v>49743.25</v>
+        <v>47456.12</v>
       </c>
       <c r="L9" t="n">
-        <v>50628.21</v>
+        <v>49015.47</v>
       </c>
       <c r="M9" t="n">
-        <v>51009.81</v>
+        <v>49795.64</v>
       </c>
       <c r="N9" t="n">
-        <v>51391.42</v>
+        <v>50575.81</v>
       </c>
       <c r="O9" t="n">
-        <v>52779.72</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
+        <v>52914.34</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
@@ -1307,55 +1297,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49113.82</v>
+        <v>50318.59</v>
       </c>
       <c r="C10" t="n">
-        <v>50322.14</v>
+        <v>51028.42</v>
       </c>
       <c r="D10" t="n">
-        <v>48511.95</v>
+        <v>49215.96</v>
       </c>
       <c r="E10" t="n">
-        <v>50253.91</v>
+        <v>50491.87</v>
       </c>
       <c r="F10" t="n">
-        <v>1628.03</v>
+        <v>237.96</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0335</v>
+        <v>0.0047</v>
       </c>
       <c r="H10" t="n">
-        <v>1810.19</v>
+        <v>1812.46</v>
       </c>
       <c r="I10" t="n">
-        <v>45895.78</v>
+        <v>46701.76</v>
       </c>
       <c r="J10" t="n">
-        <v>45896.77</v>
+        <v>48862.15</v>
       </c>
       <c r="K10" t="n">
-        <v>47456.12</v>
+        <v>49348.81</v>
       </c>
       <c r="L10" t="n">
-        <v>49015.47</v>
+        <v>49835.48</v>
       </c>
       <c r="M10" t="n">
-        <v>49795.64</v>
+        <v>51159.01</v>
       </c>
       <c r="N10" t="n">
-        <v>50575.81</v>
+        <v>52482.53</v>
       </c>
       <c r="O10" t="n">
-        <v>52914.34</v>
+        <v>52132.33</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1363,23 +1357,21 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1391,57 +1383,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50318.59</v>
+        <v>50643.09</v>
       </c>
       <c r="C11" t="n">
-        <v>51028.42</v>
+        <v>51127.69</v>
       </c>
       <c r="D11" t="n">
-        <v>49215.96</v>
+        <v>49926.27</v>
       </c>
       <c r="E11" t="n">
-        <v>50491.87</v>
+        <v>50836.55</v>
       </c>
       <c r="F11" t="n">
-        <v>237.96</v>
+        <v>344.68</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0047</v>
+        <v>0.0068</v>
       </c>
       <c r="H11" t="n">
-        <v>1812.46</v>
+        <v>1201.42</v>
       </c>
       <c r="I11" t="n">
-        <v>46701.76</v>
+        <v>47403.5</v>
       </c>
       <c r="J11" t="n">
-        <v>48862.15</v>
+        <v>48864.25</v>
       </c>
       <c r="K11" t="n">
-        <v>49348.81</v>
+        <v>49585.64</v>
       </c>
       <c r="L11" t="n">
-        <v>49835.48</v>
+        <v>50307.03</v>
       </c>
       <c r="M11" t="n">
-        <v>51159.01</v>
+        <v>51398.1</v>
       </c>
       <c r="N11" t="n">
-        <v>52482.53</v>
+        <v>52489.17</v>
       </c>
       <c r="O11" t="n">
-        <v>52132.33</v>
+        <v>52840.88</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1449,10 +1441,8 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R11" s="6" t="n">
+        <v/>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
@@ -1482,63 +1472,69 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50643.09</v>
+        <v>50352.09</v>
       </c>
       <c r="C12" t="n">
-        <v>51127.69</v>
+        <v>50432.1</v>
       </c>
       <c r="D12" t="n">
-        <v>49926.27</v>
+        <v>48643.78</v>
       </c>
       <c r="E12" t="n">
-        <v>50836.55</v>
+        <v>49507.21</v>
       </c>
       <c r="F12" t="n">
-        <v>344.68</v>
+        <v>-1329.34</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0261</v>
       </c>
       <c r="H12" t="n">
-        <v>1201.42</v>
+        <v>1788.32</v>
       </c>
       <c r="I12" t="n">
-        <v>47403.5</v>
+        <v>48724.85</v>
       </c>
       <c r="J12" t="n">
-        <v>48864.25</v>
+        <v>49789.91</v>
       </c>
       <c r="K12" t="n">
-        <v>49585.64</v>
+        <v>50235.84</v>
       </c>
       <c r="L12" t="n">
-        <v>50307.03</v>
+        <v>50681.77</v>
       </c>
       <c r="M12" t="n">
-        <v>51398.1</v>
+        <v>51437.26</v>
       </c>
       <c r="N12" t="n">
-        <v>52489.17</v>
+        <v>52192.76</v>
       </c>
       <c r="O12" t="n">
-        <v>52840.88</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>52329.11</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1555,83 +1551,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>50352.09</v>
+        <v>50084.55</v>
       </c>
       <c r="C13" t="n">
-        <v>50432.1</v>
+        <v>50941.89</v>
       </c>
       <c r="D13" t="n">
-        <v>48643.78</v>
+        <v>49982.2</v>
       </c>
       <c r="E13" t="n">
-        <v>49507.21</v>
+        <v>50750.39</v>
       </c>
       <c r="F13" t="n">
-        <v>-1329.34</v>
+        <v>1243.18</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0261</v>
+        <v>0.0251</v>
       </c>
       <c r="H13" t="n">
-        <v>1788.32</v>
+        <v>959.6900000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>48724.85</v>
+        <v>46855.46</v>
       </c>
       <c r="J13" t="n">
-        <v>49789.91</v>
+        <v>47703.53</v>
       </c>
       <c r="K13" t="n">
-        <v>50235.84</v>
+        <v>48613.05</v>
       </c>
       <c r="L13" t="n">
-        <v>50681.77</v>
+        <v>49522.58</v>
       </c>
       <c r="M13" t="n">
-        <v>51437.26</v>
+        <v>50401.37</v>
       </c>
       <c r="N13" t="n">
-        <v>52192.76</v>
+        <v>51280.17</v>
       </c>
       <c r="O13" t="n">
-        <v>52329.11</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
+        <v>52220.42</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1643,55 +1631,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>50084.55</v>
+        <v>50691.22</v>
       </c>
       <c r="C14" t="n">
-        <v>50941.89</v>
+        <v>50707.23</v>
       </c>
       <c r="D14" t="n">
-        <v>49982.2</v>
+        <v>50198.97</v>
       </c>
       <c r="E14" t="n">
-        <v>50750.39</v>
+        <v>50339.48</v>
       </c>
       <c r="F14" t="n">
-        <v>1243.18</v>
+        <v>-410.91</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0251</v>
+        <v>-0.0081</v>
       </c>
       <c r="H14" t="n">
-        <v>959.6900000000001</v>
+        <v>508.26</v>
       </c>
       <c r="I14" t="n">
-        <v>46855.46</v>
+        <v>49022.51</v>
       </c>
       <c r="J14" t="n">
-        <v>47703.53</v>
+        <v>49934.87</v>
       </c>
       <c r="K14" t="n">
-        <v>48613.05</v>
+        <v>50270.54</v>
       </c>
       <c r="L14" t="n">
-        <v>49522.58</v>
+        <v>50606.22</v>
       </c>
       <c r="M14" t="n">
-        <v>50401.37</v>
+        <v>51230.24</v>
       </c>
       <c r="N14" t="n">
-        <v>51280.17</v>
+        <v>51854.25</v>
       </c>
       <c r="O14" t="n">
-        <v>52220.42</v>
+        <v>51901.58</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1699,19 +1691,19 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
@@ -1725,57 +1717,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>50691.22</v>
+        <v>51010.28</v>
       </c>
       <c r="C15" t="n">
-        <v>50707.23</v>
+        <v>52523.77</v>
       </c>
       <c r="D15" t="n">
-        <v>50198.97</v>
+        <v>50995.67</v>
       </c>
       <c r="E15" t="n">
-        <v>50339.48</v>
+        <v>51939.89</v>
       </c>
       <c r="F15" t="n">
-        <v>-410.91</v>
+        <v>1600.41</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0081</v>
+        <v>0.0318</v>
       </c>
       <c r="H15" t="n">
-        <v>508.26</v>
+        <v>1528.1</v>
       </c>
       <c r="I15" t="n">
-        <v>49022.51</v>
+        <v>49690.71</v>
       </c>
       <c r="J15" t="n">
-        <v>49934.87</v>
+        <v>49774.41</v>
       </c>
       <c r="K15" t="n">
-        <v>50270.54</v>
+        <v>50085.35</v>
       </c>
       <c r="L15" t="n">
-        <v>50606.22</v>
+        <v>50396.29</v>
       </c>
       <c r="M15" t="n">
-        <v>51230.24</v>
+        <v>50593.61</v>
       </c>
       <c r="N15" t="n">
-        <v>51854.25</v>
+        <v>50790.93</v>
       </c>
       <c r="O15" t="n">
-        <v>51901.58</v>
+        <v>51215.49</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1783,83 +1775,83 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W15" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W15" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>51010.28</v>
+        <v>52808.29</v>
       </c>
       <c r="C16" t="n">
-        <v>52523.77</v>
+        <v>54487.32</v>
       </c>
       <c r="D16" t="n">
-        <v>50995.67</v>
+        <v>52741.64</v>
       </c>
       <c r="E16" t="n">
-        <v>51939.89</v>
+        <v>53936.17</v>
       </c>
       <c r="F16" t="n">
-        <v>1600.41</v>
+        <v>1996.28</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0318</v>
+        <v>0.0384</v>
       </c>
       <c r="H16" t="n">
-        <v>1528.1</v>
+        <v>1745.68</v>
       </c>
       <c r="I16" t="n">
-        <v>49690.71</v>
+        <v>49467.57</v>
       </c>
       <c r="J16" t="n">
-        <v>49774.41</v>
+        <v>50501.88</v>
       </c>
       <c r="K16" t="n">
-        <v>50085.35</v>
+        <v>51175.84</v>
       </c>
       <c r="L16" t="n">
-        <v>50396.29</v>
+        <v>51849.81</v>
       </c>
       <c r="M16" t="n">
-        <v>50593.61</v>
+        <v>52703.94</v>
       </c>
       <c r="N16" t="n">
-        <v>50790.93</v>
+        <v>53558.07</v>
       </c>
       <c r="O16" t="n">
-        <v>51215.49</v>
+        <v>54051.87</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1900,151 +1892,151 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52808.29</v>
+        <v>53390.05</v>
       </c>
       <c r="C17" t="n">
-        <v>54487.32</v>
+        <v>54050.84</v>
       </c>
       <c r="D17" t="n">
-        <v>52741.64</v>
+        <v>52194.81</v>
       </c>
       <c r="E17" t="n">
-        <v>53936.17</v>
+        <v>53846.87</v>
       </c>
       <c r="F17" t="n">
-        <v>1996.28</v>
+        <v>-89.3</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0384</v>
+        <v>-0.0017</v>
       </c>
       <c r="H17" t="n">
-        <v>1745.68</v>
+        <v>1856.03</v>
       </c>
       <c r="I17" t="n">
-        <v>49467.57</v>
+        <v>50995.96</v>
       </c>
       <c r="J17" t="n">
-        <v>50501.88</v>
+        <v>52351.34</v>
       </c>
       <c r="K17" t="n">
-        <v>51175.84</v>
+        <v>53063.33</v>
       </c>
       <c r="L17" t="n">
-        <v>51849.81</v>
+        <v>53775.33</v>
       </c>
       <c r="M17" t="n">
-        <v>52703.94</v>
+        <v>54809.01</v>
       </c>
       <c r="N17" t="n">
-        <v>53558.07</v>
+        <v>55842.7</v>
       </c>
       <c r="O17" t="n">
-        <v>54051.87</v>
+        <v>56233</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53390.05</v>
+        <v>53023.28</v>
       </c>
       <c r="C18" t="n">
-        <v>54050.84</v>
+        <v>53742.69</v>
       </c>
       <c r="D18" t="n">
-        <v>52194.81</v>
+        <v>52637.66</v>
       </c>
       <c r="E18" t="n">
-        <v>53846.87</v>
+        <v>53322.85</v>
       </c>
       <c r="F18" t="n">
-        <v>-89.3</v>
+        <v>-524.02</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0097</v>
       </c>
       <c r="H18" t="n">
-        <v>1856.03</v>
+        <v>1105.03</v>
       </c>
       <c r="I18" t="n">
-        <v>50995.96</v>
+        <v>50338.78</v>
       </c>
       <c r="J18" t="n">
-        <v>52351.34</v>
+        <v>52352.86</v>
       </c>
       <c r="K18" t="n">
-        <v>53063.33</v>
+        <v>52918.86</v>
       </c>
       <c r="L18" t="n">
-        <v>53775.33</v>
+        <v>53484.85</v>
       </c>
       <c r="M18" t="n">
-        <v>54809.01</v>
+        <v>54774.89</v>
       </c>
       <c r="N18" t="n">
-        <v>55842.7</v>
+        <v>56064.93</v>
       </c>
       <c r="O18" t="n">
-        <v>56233</v>
+        <v>55906.87</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q18" s="6" t="n">
+        <v/>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2063,57 +2055,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>53023.28</v>
+        <v>53575.37</v>
       </c>
       <c r="C19" t="n">
-        <v>53742.69</v>
+        <v>54782.83</v>
       </c>
       <c r="D19" t="n">
-        <v>52637.66</v>
+        <v>52655.18</v>
       </c>
       <c r="E19" t="n">
-        <v>53322.85</v>
+        <v>54253.68</v>
       </c>
       <c r="F19" t="n">
-        <v>-524.02</v>
+        <v>930.83</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0175</v>
       </c>
       <c r="H19" t="n">
-        <v>1105.03</v>
+        <v>2127.65</v>
       </c>
       <c r="I19" t="n">
-        <v>50338.78</v>
+        <v>51532.63</v>
       </c>
       <c r="J19" t="n">
-        <v>52352.86</v>
+        <v>52284.16</v>
       </c>
       <c r="K19" t="n">
-        <v>52918.86</v>
+        <v>52770.34</v>
       </c>
       <c r="L19" t="n">
-        <v>53484.85</v>
+        <v>53256.51</v>
       </c>
       <c r="M19" t="n">
-        <v>54774.89</v>
+        <v>53875.37</v>
       </c>
       <c r="N19" t="n">
-        <v>56064.93</v>
+        <v>54494.22</v>
       </c>
       <c r="O19" t="n">
-        <v>55906.87</v>
+        <v>54847.72</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2126,16 +2118,20 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2145,59 +2141,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>53575.37</v>
+        <v>55130.63</v>
       </c>
       <c r="C20" t="n">
-        <v>54782.83</v>
+        <v>58015.08</v>
       </c>
       <c r="D20" t="n">
-        <v>52655.18</v>
+        <v>55018.57</v>
       </c>
       <c r="E20" t="n">
-        <v>54253.68</v>
+        <v>56941.97</v>
       </c>
       <c r="F20" t="n">
-        <v>930.83</v>
+        <v>2688.29</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0496</v>
       </c>
       <c r="H20" t="n">
-        <v>2127.65</v>
+        <v>2996.51</v>
       </c>
       <c r="I20" t="n">
-        <v>51532.63</v>
+        <v>50527.53</v>
       </c>
       <c r="J20" t="n">
-        <v>52284.16</v>
+        <v>52393.37</v>
       </c>
       <c r="K20" t="n">
-        <v>52770.34</v>
+        <v>53189.86</v>
       </c>
       <c r="L20" t="n">
-        <v>53256.51</v>
+        <v>53986.34</v>
       </c>
       <c r="M20" t="n">
-        <v>53875.37</v>
+        <v>55317.5</v>
       </c>
       <c r="N20" t="n">
-        <v>54494.22</v>
+        <v>56648.67</v>
       </c>
       <c r="O20" t="n">
-        <v>54847.72</v>
+        <v>56910.48</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2205,10 +2197,8 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R20" s="6" t="n">
+        <v/>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
@@ -2222,11 +2212,13 @@
       </c>
       <c r="U20" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
@@ -2238,50 +2230,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>55130.63</v>
+        <v>57212.97</v>
       </c>
       <c r="C21" t="n">
-        <v>58015.08</v>
+        <v>57709.82</v>
       </c>
       <c r="D21" t="n">
-        <v>55018.57</v>
+        <v>56135.12</v>
       </c>
       <c r="E21" t="n">
-        <v>56941.97</v>
+        <v>56825.7</v>
       </c>
       <c r="F21" t="n">
-        <v>2688.29</v>
+        <v>-116.27</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0496</v>
+        <v>-0.002</v>
       </c>
       <c r="H21" t="n">
-        <v>2996.51</v>
+        <v>1574.7</v>
       </c>
       <c r="I21" t="n">
-        <v>50527.53</v>
+        <v>52022.06</v>
       </c>
       <c r="J21" t="n">
-        <v>52393.37</v>
+        <v>54158.03</v>
       </c>
       <c r="K21" t="n">
-        <v>53189.86</v>
+        <v>55443.71</v>
       </c>
       <c r="L21" t="n">
-        <v>53986.34</v>
+        <v>56729.4</v>
       </c>
       <c r="M21" t="n">
-        <v>55317.5</v>
+        <v>58440.22</v>
       </c>
       <c r="N21" t="n">
-        <v>56648.67</v>
+        <v>60151.05</v>
       </c>
       <c r="O21" t="n">
-        <v>56910.48</v>
+        <v>61011.59</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2294,78 +2286,76 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>57212.97</v>
+        <v>56764.14</v>
       </c>
       <c r="C22" t="n">
-        <v>57709.82</v>
+        <v>59332.43</v>
       </c>
       <c r="D22" t="n">
-        <v>56135.12</v>
+        <v>56732.93</v>
       </c>
       <c r="E22" t="n">
-        <v>56825.7</v>
+        <v>58850.27</v>
       </c>
       <c r="F22" t="n">
-        <v>-116.27</v>
+        <v>2024.57</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0356</v>
       </c>
       <c r="H22" t="n">
-        <v>1574.7</v>
+        <v>2599.5</v>
       </c>
       <c r="I22" t="n">
-        <v>52022.06</v>
+        <v>54560.42</v>
       </c>
       <c r="J22" t="n">
-        <v>54158.03</v>
+        <v>55202.61</v>
       </c>
       <c r="K22" t="n">
-        <v>55443.71</v>
+        <v>56038.35</v>
       </c>
       <c r="L22" t="n">
-        <v>56729.4</v>
+        <v>56874.08</v>
       </c>
       <c r="M22" t="n">
-        <v>58440.22</v>
+        <v>57613.05</v>
       </c>
       <c r="N22" t="n">
-        <v>60151.05</v>
+        <v>58352.01</v>
       </c>
       <c r="O22" t="n">
-        <v>61011.59</v>
+        <v>59284.52</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2378,109 +2368,111 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>56764.14</v>
+        <v>57976.2</v>
       </c>
       <c r="C23" t="n">
-        <v>59332.43</v>
+        <v>58365.21</v>
       </c>
       <c r="D23" t="n">
-        <v>56732.93</v>
+        <v>53618.2</v>
       </c>
       <c r="E23" t="n">
-        <v>58850.27</v>
+        <v>55620.84</v>
       </c>
       <c r="F23" t="n">
-        <v>2024.57</v>
+        <v>-3229.43</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0356</v>
+        <v>-0.0549</v>
       </c>
       <c r="H23" t="n">
-        <v>2599.5</v>
+        <v>4747.01</v>
       </c>
       <c r="I23" t="n">
-        <v>54560.42</v>
+        <v>54133.43</v>
       </c>
       <c r="J23" t="n">
-        <v>55202.61</v>
+        <v>56659.56</v>
       </c>
       <c r="K23" t="n">
-        <v>56038.35</v>
+        <v>57550.52</v>
       </c>
       <c r="L23" t="n">
-        <v>56874.08</v>
+        <v>58441.47</v>
       </c>
       <c r="M23" t="n">
-        <v>57613.05</v>
+        <v>60150.02</v>
       </c>
       <c r="N23" t="n">
-        <v>58352.01</v>
+        <v>61858.56</v>
       </c>
       <c r="O23" t="n">
-        <v>59284.52</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
+        <v>61931.93</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W23" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W23" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
@@ -2488,64 +2480,60 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>57976.2</v>
+        <v>54608.63</v>
       </c>
       <c r="C24" t="n">
-        <v>58365.21</v>
+        <v>55745.38</v>
       </c>
       <c r="D24" t="n">
-        <v>53618.2</v>
+        <v>51407.66</v>
       </c>
       <c r="E24" t="n">
-        <v>55620.84</v>
+        <v>53819.61</v>
       </c>
       <c r="F24" t="n">
-        <v>-3229.43</v>
+        <v>-1801.23</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0549</v>
+        <v>-0.0324</v>
       </c>
       <c r="H24" t="n">
-        <v>4747.01</v>
+        <v>4337.72</v>
       </c>
       <c r="I24" t="n">
-        <v>54133.43</v>
+        <v>48871.19</v>
       </c>
       <c r="J24" t="n">
-        <v>56659.56</v>
+        <v>50688.4</v>
       </c>
       <c r="K24" t="n">
-        <v>57550.52</v>
+        <v>53247.33</v>
       </c>
       <c r="L24" t="n">
-        <v>58441.47</v>
+        <v>55806.27</v>
       </c>
       <c r="M24" t="n">
-        <v>60150.02</v>
+        <v>57994.35</v>
       </c>
       <c r="N24" t="n">
-        <v>61858.56</v>
+        <v>60182.42</v>
       </c>
       <c r="O24" t="n">
-        <v>61931.93</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q24" s="6" t="inlineStr">
+        <v>63112.22</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S24" s="10" t="inlineStr">
@@ -2572,50 +2560,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>54608.63</v>
+        <v>53627.86</v>
       </c>
       <c r="C25" t="n">
-        <v>55745.38</v>
+        <v>55239.4</v>
       </c>
       <c r="D25" t="n">
-        <v>51407.66</v>
+        <v>53113.95</v>
       </c>
       <c r="E25" t="n">
-        <v>53819.61</v>
+        <v>53372.53</v>
       </c>
       <c r="F25" t="n">
-        <v>-1801.23</v>
+        <v>-447.08</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0324</v>
+        <v>-0.0083</v>
       </c>
       <c r="H25" t="n">
-        <v>4337.72</v>
+        <v>2125.45</v>
       </c>
       <c r="I25" t="n">
-        <v>48871.19</v>
+        <v>47069.94</v>
       </c>
       <c r="J25" t="n">
-        <v>50688.4</v>
+        <v>49603.44</v>
       </c>
       <c r="K25" t="n">
-        <v>53247.33</v>
+        <v>51650.75</v>
       </c>
       <c r="L25" t="n">
-        <v>55806.27</v>
+        <v>53698.06</v>
       </c>
       <c r="M25" t="n">
-        <v>57994.35</v>
+        <v>55988.47</v>
       </c>
       <c r="N25" t="n">
-        <v>60182.42</v>
+        <v>58278.87</v>
       </c>
       <c r="O25" t="n">
-        <v>63112.22</v>
+        <v>60083.1</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2623,14 +2611,12 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2647,64 +2633,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>53627.86</v>
+        <v>52468.72</v>
       </c>
       <c r="C26" t="n">
-        <v>55239.4</v>
+        <v>54175.8</v>
       </c>
       <c r="D26" t="n">
-        <v>53113.95</v>
+        <v>50688.76</v>
       </c>
       <c r="E26" t="n">
-        <v>53372.53</v>
+        <v>53373.07</v>
       </c>
       <c r="F26" t="n">
-        <v>-447.08</v>
+        <v>0.54</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0083</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2125.45</v>
+        <v>3487.04</v>
       </c>
       <c r="I26" t="n">
-        <v>47069.94</v>
+        <v>50988.5</v>
       </c>
       <c r="J26" t="n">
-        <v>49603.44</v>
+        <v>50845.01</v>
       </c>
       <c r="K26" t="n">
-        <v>51650.75</v>
+        <v>52309.81</v>
       </c>
       <c r="L26" t="n">
-        <v>53698.06</v>
+        <v>53774.6</v>
       </c>
       <c r="M26" t="n">
-        <v>55988.47</v>
+        <v>54435.26</v>
       </c>
       <c r="N26" t="n">
-        <v>58278.87</v>
+        <v>55095.91</v>
       </c>
       <c r="O26" t="n">
-        <v>60083.1</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+        <v>57364.85</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
@@ -2734,69 +2730,65 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>52468.72</v>
+        <v>52054.68</v>
       </c>
       <c r="C27" t="n">
-        <v>54175.8</v>
+        <v>54258.48</v>
       </c>
       <c r="D27" t="n">
-        <v>50688.76</v>
+        <v>50558.91</v>
       </c>
       <c r="E27" t="n">
-        <v>53373.07</v>
+        <v>53123.49</v>
       </c>
       <c r="F27" t="n">
-        <v>0.54</v>
+        <v>-249.58</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0</v>
+        <v>-0.0047</v>
       </c>
       <c r="H27" t="n">
-        <v>3487.04</v>
+        <v>3699.57</v>
       </c>
       <c r="I27" t="n">
-        <v>50988.5</v>
+        <v>47201.72</v>
       </c>
       <c r="J27" t="n">
-        <v>50845.01</v>
+        <v>50356.43</v>
       </c>
       <c r="K27" t="n">
-        <v>52309.81</v>
+        <v>51629.55</v>
       </c>
       <c r="L27" t="n">
-        <v>53774.6</v>
+        <v>52902.68</v>
       </c>
       <c r="M27" t="n">
-        <v>54435.26</v>
+        <v>55116.59</v>
       </c>
       <c r="N27" t="n">
-        <v>55095.91</v>
+        <v>57330.5</v>
       </c>
       <c r="O27" t="n">
-        <v>57364.85</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>57662.84</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2822,50 +2814,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>52054.68</v>
+        <v>53205.93</v>
       </c>
       <c r="C28" t="n">
-        <v>54258.48</v>
+        <v>57012.77</v>
       </c>
       <c r="D28" t="n">
-        <v>50558.91</v>
+        <v>53156.94</v>
       </c>
       <c r="E28" t="n">
-        <v>53123.49</v>
+        <v>56924.11</v>
       </c>
       <c r="F28" t="n">
-        <v>-249.58</v>
+        <v>3800.62</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0047</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>3699.57</v>
+        <v>3855.83</v>
       </c>
       <c r="I28" t="n">
-        <v>47201.72</v>
+        <v>46859.34</v>
       </c>
       <c r="J28" t="n">
-        <v>50356.43</v>
+        <v>49781.31</v>
       </c>
       <c r="K28" t="n">
-        <v>51629.55</v>
+        <v>51273.7</v>
       </c>
       <c r="L28" t="n">
-        <v>52902.68</v>
+        <v>52766.09</v>
       </c>
       <c r="M28" t="n">
-        <v>55116.59</v>
+        <v>54973.27</v>
       </c>
       <c r="N28" t="n">
-        <v>57330.5</v>
+        <v>57180.46</v>
       </c>
       <c r="O28" t="n">
-        <v>57662.84</v>
+        <v>57958.05</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2873,21 +2865,23 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R28" s="6" t="n">
+        <v/>
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2899,57 +2893,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>53205.93</v>
+        <v>56421.46</v>
       </c>
       <c r="C29" t="n">
-        <v>57012.77</v>
+        <v>59688.1</v>
       </c>
       <c r="D29" t="n">
-        <v>53156.94</v>
+        <v>56232.78</v>
       </c>
       <c r="E29" t="n">
-        <v>56924.11</v>
+        <v>58475.9</v>
       </c>
       <c r="F29" t="n">
-        <v>3800.62</v>
+        <v>1551.79</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0273</v>
       </c>
       <c r="H29" t="n">
-        <v>3855.83</v>
+        <v>3455.32</v>
       </c>
       <c r="I29" t="n">
-        <v>46859.34</v>
+        <v>49301.11</v>
       </c>
       <c r="J29" t="n">
-        <v>49781.31</v>
+        <v>53987.91</v>
       </c>
       <c r="K29" t="n">
-        <v>51273.7</v>
+        <v>54996.2</v>
       </c>
       <c r="L29" t="n">
-        <v>52766.09</v>
+        <v>56004.48</v>
       </c>
       <c r="M29" t="n">
-        <v>54973.27</v>
+        <v>58852.02</v>
       </c>
       <c r="N29" t="n">
-        <v>57180.46</v>
+        <v>61699.56</v>
       </c>
       <c r="O29" t="n">
-        <v>57958.05</v>
+        <v>60868.6</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2967,13 +2961,11 @@
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2992,50 +2984,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>56421.46</v>
+        <v>58821.16</v>
       </c>
       <c r="C30" t="n">
-        <v>59688.1</v>
+        <v>60013.98</v>
       </c>
       <c r="D30" t="n">
-        <v>56232.78</v>
+        <v>58621.48</v>
       </c>
       <c r="E30" t="n">
-        <v>58475.9</v>
+        <v>59716.18</v>
       </c>
       <c r="F30" t="n">
-        <v>1551.79</v>
+        <v>1240.28</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0273</v>
+        <v>0.0212</v>
       </c>
       <c r="H30" t="n">
-        <v>3455.32</v>
+        <v>1392.5</v>
       </c>
       <c r="I30" t="n">
-        <v>49301.11</v>
+        <v>52777.46</v>
       </c>
       <c r="J30" t="n">
-        <v>53987.91</v>
+        <v>55278.31</v>
       </c>
       <c r="K30" t="n">
-        <v>54996.2</v>
+        <v>56748.24</v>
       </c>
       <c r="L30" t="n">
-        <v>56004.48</v>
+        <v>58218.17</v>
       </c>
       <c r="M30" t="n">
-        <v>58852.02</v>
+        <v>60203.56</v>
       </c>
       <c r="N30" t="n">
-        <v>61699.56</v>
+        <v>62188.95</v>
       </c>
       <c r="O30" t="n">
-        <v>60868.6</v>
+        <v>63143.42</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3076,50 +3068,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>58821.16</v>
+        <v>59880.71</v>
       </c>
       <c r="C31" t="n">
-        <v>60013.98</v>
+        <v>60903.95</v>
       </c>
       <c r="D31" t="n">
-        <v>58621.48</v>
+        <v>58928.2</v>
       </c>
       <c r="E31" t="n">
-        <v>59716.18</v>
+        <v>59513.12</v>
       </c>
       <c r="F31" t="n">
-        <v>1240.28</v>
+        <v>-203.06</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0034</v>
       </c>
       <c r="H31" t="n">
-        <v>1392.5</v>
+        <v>1975.75</v>
       </c>
       <c r="I31" t="n">
-        <v>52777.46</v>
+        <v>57228.98</v>
       </c>
       <c r="J31" t="n">
-        <v>55278.31</v>
+        <v>58522.9</v>
       </c>
       <c r="K31" t="n">
-        <v>56748.24</v>
+        <v>59019.93</v>
       </c>
       <c r="L31" t="n">
-        <v>58218.17</v>
+        <v>59516.96</v>
       </c>
       <c r="M31" t="n">
-        <v>60203.56</v>
+        <v>60412.43</v>
       </c>
       <c r="N31" t="n">
-        <v>62188.95</v>
+        <v>61307.9</v>
       </c>
       <c r="O31" t="n">
-        <v>63143.42</v>
+        <v>61406.48</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3127,17 +3119,19 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U31" s="8" t="n">
@@ -3153,57 +3147,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>59880.71</v>
+        <v>60241.31</v>
       </c>
       <c r="C32" t="n">
-        <v>60903.95</v>
+        <v>63091.14</v>
       </c>
       <c r="D32" t="n">
-        <v>58928.2</v>
+        <v>60213.02</v>
       </c>
       <c r="E32" t="n">
-        <v>59513.12</v>
+        <v>62713.65</v>
       </c>
       <c r="F32" t="n">
-        <v>-203.06</v>
+        <v>3200.53</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0538</v>
       </c>
       <c r="H32" t="n">
-        <v>1975.75</v>
+        <v>2878.12</v>
       </c>
       <c r="I32" t="n">
-        <v>57228.98</v>
+        <v>56952.45</v>
       </c>
       <c r="J32" t="n">
-        <v>58522.9</v>
+        <v>57335.89</v>
       </c>
       <c r="K32" t="n">
-        <v>59019.93</v>
+        <v>58525.25</v>
       </c>
       <c r="L32" t="n">
-        <v>59516.96</v>
+        <v>59714.6</v>
       </c>
       <c r="M32" t="n">
-        <v>60412.43</v>
+        <v>60501</v>
       </c>
       <c r="N32" t="n">
-        <v>61307.9</v>
+        <v>61287.39</v>
       </c>
       <c r="O32" t="n">
-        <v>61406.48</v>
+        <v>62879.7</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3211,14 +3205,12 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
@@ -3226,70 +3218,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W32" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W32" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>60241.31</v>
+        <v>63203.44</v>
       </c>
       <c r="C33" t="n">
-        <v>63091.14</v>
+        <v>63799.32</v>
       </c>
       <c r="D33" t="n">
-        <v>60213.02</v>
+        <v>60937.3</v>
       </c>
       <c r="E33" t="n">
-        <v>62713.65</v>
+        <v>61409.29</v>
       </c>
       <c r="F33" t="n">
-        <v>3200.53</v>
+        <v>-1304.36</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0538</v>
+        <v>-0.0208</v>
       </c>
       <c r="H33" t="n">
-        <v>2878.12</v>
+        <v>2862.02</v>
       </c>
       <c r="I33" t="n">
-        <v>56952.45</v>
+        <v>57334.9</v>
       </c>
       <c r="J33" t="n">
-        <v>57335.89</v>
+        <v>60366.31</v>
       </c>
       <c r="K33" t="n">
-        <v>58525.25</v>
+        <v>61274.59</v>
       </c>
       <c r="L33" t="n">
-        <v>59714.6</v>
+        <v>62182.86</v>
       </c>
       <c r="M33" t="n">
-        <v>60501</v>
+        <v>64152.71</v>
       </c>
       <c r="N33" t="n">
-        <v>61287.39</v>
+        <v>66122.55</v>
       </c>
       <c r="O33" t="n">
-        <v>62879.7</v>
+        <v>65969.25999999999</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3297,83 +3289,83 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
+      <c r="R33" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
+      </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>63203.44</v>
+        <v>61299.87</v>
       </c>
       <c r="C34" t="n">
-        <v>63799.32</v>
+        <v>63432.41</v>
       </c>
       <c r="D34" t="n">
-        <v>60937.3</v>
+        <v>59292.25</v>
       </c>
       <c r="E34" t="n">
-        <v>61409.29</v>
+        <v>63339.07</v>
       </c>
       <c r="F34" t="n">
-        <v>-1304.36</v>
+        <v>1929.78</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0314</v>
       </c>
       <c r="H34" t="n">
-        <v>2862.02</v>
+        <v>4140.16</v>
       </c>
       <c r="I34" t="n">
-        <v>57334.9</v>
+        <v>58075.28</v>
       </c>
       <c r="J34" t="n">
-        <v>60366.31</v>
+        <v>58067.76</v>
       </c>
       <c r="K34" t="n">
-        <v>61274.59</v>
+        <v>59978.28</v>
       </c>
       <c r="L34" t="n">
-        <v>62182.86</v>
+        <v>61888.8</v>
       </c>
       <c r="M34" t="n">
-        <v>64152.71</v>
+        <v>62840.3</v>
       </c>
       <c r="N34" t="n">
-        <v>66122.55</v>
+        <v>63791.8</v>
       </c>
       <c r="O34" t="n">
-        <v>65969.25999999999</v>
+        <v>66661.34</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3383,20 +3375,24 @@
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
@@ -3407,57 +3403,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>61299.87</v>
+        <v>63658.95</v>
       </c>
       <c r="C35" t="n">
-        <v>63432.41</v>
+        <v>66505.02</v>
       </c>
       <c r="D35" t="n">
-        <v>59292.25</v>
+        <v>63562.51</v>
       </c>
       <c r="E35" t="n">
-        <v>63339.07</v>
+        <v>66329.5</v>
       </c>
       <c r="F35" t="n">
-        <v>1929.78</v>
+        <v>2990.43</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0314</v>
+        <v>0.0472</v>
       </c>
       <c r="H35" t="n">
-        <v>4140.16</v>
+        <v>2942.51</v>
       </c>
       <c r="I35" t="n">
-        <v>58075.28</v>
+        <v>55152.09</v>
       </c>
       <c r="J35" t="n">
-        <v>58067.76</v>
+        <v>60187.28</v>
       </c>
       <c r="K35" t="n">
-        <v>59978.28</v>
+        <v>61268.99</v>
       </c>
       <c r="L35" t="n">
-        <v>61888.8</v>
+        <v>62350.7</v>
       </c>
       <c r="M35" t="n">
-        <v>62840.3</v>
+        <v>65409.15</v>
       </c>
       <c r="N35" t="n">
-        <v>63791.8</v>
+        <v>68467.60000000001</v>
       </c>
       <c r="O35" t="n">
-        <v>66661.34</v>
+        <v>67572.57000000001</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3465,10 +3461,8 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R35" s="6" t="n">
+        <v/>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
@@ -3477,14 +3471,12 @@
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
@@ -3493,59 +3485,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>63658.95</v>
+        <v>66363.42999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>66505.02</v>
+        <v>68786.49000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>63562.51</v>
+        <v>65551.13</v>
       </c>
       <c r="E36" t="n">
-        <v>66329.5</v>
+        <v>66588.12</v>
       </c>
       <c r="F36" t="n">
-        <v>2990.43</v>
+        <v>258.62</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0472</v>
+        <v>0.0039</v>
       </c>
       <c r="H36" t="n">
-        <v>2942.51</v>
+        <v>3235.36</v>
       </c>
       <c r="I36" t="n">
-        <v>55152.09</v>
+        <v>60620</v>
       </c>
       <c r="J36" t="n">
-        <v>60187.28</v>
+        <v>64034.85</v>
       </c>
       <c r="K36" t="n">
-        <v>61268.99</v>
+        <v>64858.24</v>
       </c>
       <c r="L36" t="n">
-        <v>62350.7</v>
+        <v>65681.63</v>
       </c>
       <c r="M36" t="n">
-        <v>65409.15</v>
+        <v>67800.75999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>68467.60000000001</v>
+        <v>69919.88</v>
       </c>
       <c r="O36" t="n">
-        <v>67572.57000000001</v>
+        <v>69447.53999999999</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3558,12 +3546,12 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U36" s="8" t="n">
@@ -3582,69 +3570,71 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>66363.42999999999</v>
+        <v>65947.56</v>
       </c>
       <c r="C37" t="n">
-        <v>68786.49000000001</v>
+        <v>67065.94</v>
       </c>
       <c r="D37" t="n">
-        <v>65551.13</v>
+        <v>62335.75</v>
       </c>
       <c r="E37" t="n">
-        <v>66588.12</v>
+        <v>66020.03999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>258.62</v>
+        <v>-568.08</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0039</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>3235.36</v>
+        <v>4730.19</v>
       </c>
       <c r="I37" t="n">
-        <v>60620</v>
+        <v>62315.77</v>
       </c>
       <c r="J37" t="n">
-        <v>64034.85</v>
+        <v>63062.41</v>
       </c>
       <c r="K37" t="n">
-        <v>64858.24</v>
+        <v>64970.44</v>
       </c>
       <c r="L37" t="n">
-        <v>65681.63</v>
+        <v>66878.46000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>67800.75999999999</v>
+        <v>68205.8</v>
       </c>
       <c r="N37" t="n">
-        <v>69919.88</v>
+        <v>69533.13</v>
       </c>
       <c r="O37" t="n">
-        <v>69447.53999999999</v>
+        <v>72021.85000000001</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3657,141 +3647,143 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>65947.56</v>
+        <v>66783.22</v>
       </c>
       <c r="C38" t="n">
-        <v>67065.94</v>
+        <v>71952.99000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>62335.75</v>
+        <v>66783.22</v>
       </c>
       <c r="E38" t="n">
-        <v>66020.03999999999</v>
+        <v>71250.06</v>
       </c>
       <c r="F38" t="n">
-        <v>-568.08</v>
+        <v>5230.02</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>4730.19</v>
+        <v>5169.77</v>
       </c>
       <c r="I38" t="n">
-        <v>62315.77</v>
+        <v>57605.56</v>
       </c>
       <c r="J38" t="n">
-        <v>63062.41</v>
+        <v>61949.45</v>
       </c>
       <c r="K38" t="n">
-        <v>64970.44</v>
+        <v>63654.95</v>
       </c>
       <c r="L38" t="n">
-        <v>66878.46000000001</v>
+        <v>65360.44</v>
       </c>
       <c r="M38" t="n">
-        <v>68205.8</v>
+        <v>68385.13</v>
       </c>
       <c r="N38" t="n">
-        <v>69533.13</v>
+        <v>71409.82000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>72021.85000000001</v>
+        <v>71796.12</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v/>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>66783.22</v>
+        <v>71067.14999999999</v>
       </c>
       <c r="C39" t="n">
-        <v>71952.99000000001</v>
+        <v>72831.73</v>
       </c>
       <c r="D39" t="n">
-        <v>66783.22</v>
+        <v>68461.10000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>71250.06</v>
+        <v>69360.88</v>
       </c>
       <c r="F39" t="n">
-        <v>5230.02</v>
+        <v>-1889.18</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.07920000000000001</v>
+        <v>-0.0265</v>
       </c>
       <c r="H39" t="n">
-        <v>5169.77</v>
+        <v>4370.62</v>
       </c>
       <c r="I39" t="n">
-        <v>57605.56</v>
+        <v>61613.45</v>
       </c>
       <c r="J39" t="n">
-        <v>61949.45</v>
+        <v>67021.27</v>
       </c>
       <c r="K39" t="n">
-        <v>63654.95</v>
+        <v>68665.17999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>65360.44</v>
+        <v>70309.08</v>
       </c>
       <c r="M39" t="n">
-        <v>68385.13</v>
+        <v>73834.95</v>
       </c>
       <c r="N39" t="n">
-        <v>71409.82000000001</v>
+        <v>77360.81</v>
       </c>
       <c r="O39" t="n">
-        <v>71796.12</v>
+        <v>77122.77</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3799,83 +3791,83 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>71067.14999999999</v>
+        <v>69609.88</v>
       </c>
       <c r="C40" t="n">
-        <v>72831.73</v>
+        <v>71962.34</v>
       </c>
       <c r="D40" t="n">
-        <v>68461.10000000001</v>
+        <v>67609.49000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>69360.88</v>
+        <v>69744.07000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>-1889.18</v>
+        <v>383.19</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0265</v>
+        <v>0.0055</v>
       </c>
       <c r="H40" t="n">
-        <v>4370.62</v>
+        <v>4352.85</v>
       </c>
       <c r="I40" t="n">
-        <v>61613.45</v>
+        <v>64090.48</v>
       </c>
       <c r="J40" t="n">
-        <v>67021.27</v>
+        <v>64347.49</v>
       </c>
       <c r="K40" t="n">
-        <v>68665.17999999999</v>
+        <v>67175.57000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>70309.08</v>
+        <v>70003.64999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>73834.95</v>
+        <v>71546.2</v>
       </c>
       <c r="N40" t="n">
-        <v>77360.81</v>
+        <v>73088.74000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>77122.77</v>
+        <v>77202.35000000001</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3883,18 +3875,18 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3909,57 +3901,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>69609.88</v>
+        <v>69973.34</v>
       </c>
       <c r="C41" t="n">
-        <v>71962.34</v>
+        <v>70384.59</v>
       </c>
       <c r="D41" t="n">
-        <v>67609.49000000001</v>
+        <v>66819.05</v>
       </c>
       <c r="E41" t="n">
-        <v>69744.07000000001</v>
+        <v>68557.73</v>
       </c>
       <c r="F41" t="n">
-        <v>383.19</v>
+        <v>-1186.34</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0055</v>
+        <v>-0.017</v>
       </c>
       <c r="H41" t="n">
-        <v>4352.85</v>
+        <v>3565.55</v>
       </c>
       <c r="I41" t="n">
-        <v>64090.48</v>
+        <v>63256.64</v>
       </c>
       <c r="J41" t="n">
-        <v>64347.49</v>
+        <v>65370.29</v>
       </c>
       <c r="K41" t="n">
-        <v>67175.57000000001</v>
+        <v>67567.64</v>
       </c>
       <c r="L41" t="n">
-        <v>70003.64999999999</v>
+        <v>69764.99000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>71546.2</v>
+        <v>71920.5</v>
       </c>
       <c r="N41" t="n">
-        <v>73088.74000000001</v>
+        <v>74076</v>
       </c>
       <c r="O41" t="n">
-        <v>77202.35000000001</v>
+        <v>76315.2</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3967,18 +3959,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3993,67 +3985,71 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>69973.34</v>
+        <v>68410.63</v>
       </c>
       <c r="C42" t="n">
-        <v>70384.59</v>
+        <v>69078.21000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>66819.05</v>
+        <v>62704.6</v>
       </c>
       <c r="E42" t="n">
-        <v>68557.73</v>
+        <v>64141.12</v>
       </c>
       <c r="F42" t="n">
-        <v>-1186.34</v>
+        <v>-4416.61</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0644</v>
       </c>
       <c r="H42" t="n">
-        <v>3565.55</v>
+        <v>6373.61</v>
       </c>
       <c r="I42" t="n">
-        <v>63256.64</v>
+        <v>63253.5</v>
       </c>
       <c r="J42" t="n">
-        <v>65370.29</v>
+        <v>64970.13</v>
       </c>
       <c r="K42" t="n">
-        <v>67567.64</v>
+        <v>66774.95</v>
       </c>
       <c r="L42" t="n">
-        <v>69764.99000000001</v>
+        <v>68579.77</v>
       </c>
       <c r="M42" t="n">
-        <v>71920.5</v>
+        <v>70340.5</v>
       </c>
       <c r="N42" t="n">
-        <v>74076</v>
+        <v>72101.23</v>
       </c>
       <c r="O42" t="n">
-        <v>76315.2</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
+        <v>73950.14</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
@@ -4070,87 +4066,79 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W42" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>68410.63</v>
+        <v>64544.05</v>
       </c>
       <c r="C43" t="n">
-        <v>69078.21000000001</v>
+        <v>67592.2</v>
       </c>
       <c r="D43" t="n">
-        <v>62704.6</v>
+        <v>64201.03</v>
       </c>
       <c r="E43" t="n">
-        <v>64141.12</v>
+        <v>64611.15</v>
       </c>
       <c r="F43" t="n">
-        <v>-4416.61</v>
+        <v>470.03</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0644</v>
+        <v>0.0073</v>
       </c>
       <c r="H43" t="n">
-        <v>6373.61</v>
+        <v>3391.17</v>
       </c>
       <c r="I43" t="n">
-        <v>63253.5</v>
+        <v>56330.99</v>
       </c>
       <c r="J43" t="n">
-        <v>64970.13</v>
+        <v>56892.37</v>
       </c>
       <c r="K43" t="n">
-        <v>66774.95</v>
+        <v>60954.32</v>
       </c>
       <c r="L43" t="n">
-        <v>68579.77</v>
+        <v>65016.26</v>
       </c>
       <c r="M43" t="n">
-        <v>70340.5</v>
+        <v>67327.92999999999</v>
       </c>
       <c r="N43" t="n">
-        <v>72101.23</v>
+        <v>69639.59</v>
       </c>
       <c r="O43" t="n">
-        <v>73950.14</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>75451.82000000001</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4163,74 +4151,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>64544.05</v>
+        <v>65164.98</v>
       </c>
       <c r="C44" t="n">
-        <v>67592.2</v>
+        <v>65364.73</v>
       </c>
       <c r="D44" t="n">
-        <v>64201.03</v>
+        <v>60448.9</v>
       </c>
       <c r="E44" t="n">
-        <v>64611.15</v>
+        <v>64362.02</v>
       </c>
       <c r="F44" t="n">
-        <v>470.03</v>
+        <v>-249.13</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0073</v>
+        <v>-0.0039</v>
       </c>
       <c r="H44" t="n">
-        <v>3391.17</v>
+        <v>4915.83</v>
       </c>
       <c r="I44" t="n">
-        <v>56330.99</v>
+        <v>60809.86</v>
       </c>
       <c r="J44" t="n">
-        <v>56892.37</v>
+        <v>60577.24</v>
       </c>
       <c r="K44" t="n">
-        <v>60954.32</v>
+        <v>62915.56</v>
       </c>
       <c r="L44" t="n">
-        <v>65016.26</v>
+        <v>65253.88</v>
       </c>
       <c r="M44" t="n">
-        <v>67327.92999999999</v>
+        <v>66306.73</v>
       </c>
       <c r="N44" t="n">
-        <v>69639.59</v>
+        <v>67359.59</v>
       </c>
       <c r="O44" t="n">
-        <v>75451.82000000001</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+        <v>70983.38</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4243,82 +4239,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>65164.98</v>
+        <v>63834.95</v>
       </c>
       <c r="C45" t="n">
-        <v>65364.73</v>
+        <v>66302.52</v>
       </c>
       <c r="D45" t="n">
-        <v>60448.9</v>
+        <v>62703.47</v>
       </c>
       <c r="E45" t="n">
-        <v>64362.02</v>
+        <v>65606.71000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>-249.13</v>
+        <v>1244.69</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0193</v>
       </c>
       <c r="H45" t="n">
-        <v>4915.83</v>
+        <v>3599.05</v>
       </c>
       <c r="I45" t="n">
-        <v>60809.86</v>
+        <v>55533.07</v>
       </c>
       <c r="J45" t="n">
-        <v>60577.24</v>
+        <v>60173.79</v>
       </c>
       <c r="K45" t="n">
-        <v>62915.56</v>
+        <v>61904.1</v>
       </c>
       <c r="L45" t="n">
-        <v>65253.88</v>
+        <v>63634.42</v>
       </c>
       <c r="M45" t="n">
-        <v>66306.73</v>
+        <v>66819.94</v>
       </c>
       <c r="N45" t="n">
-        <v>67359.59</v>
+        <v>70005.45</v>
       </c>
       <c r="O45" t="n">
-        <v>70983.38</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+        <v>70280.56</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4331,55 +4319,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>63834.95</v>
+        <v>65905.10000000001</v>
       </c>
       <c r="C46" t="n">
-        <v>66302.52</v>
+        <v>69608.24000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>62703.47</v>
+        <v>65848.58</v>
       </c>
       <c r="E46" t="n">
-        <v>65606.71000000001</v>
+        <v>68713.8</v>
       </c>
       <c r="F46" t="n">
-        <v>1244.69</v>
+        <v>3107.09</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0193</v>
+        <v>0.0474</v>
       </c>
       <c r="H46" t="n">
-        <v>3599.05</v>
+        <v>3759.66</v>
       </c>
       <c r="I46" t="n">
-        <v>55533.07</v>
+        <v>59104.41</v>
       </c>
       <c r="J46" t="n">
-        <v>60173.79</v>
+        <v>62559.51</v>
       </c>
       <c r="K46" t="n">
-        <v>61904.1</v>
+        <v>63807.18</v>
       </c>
       <c r="L46" t="n">
-        <v>63634.42</v>
+        <v>65054.85</v>
       </c>
       <c r="M46" t="n">
-        <v>66819.94</v>
+        <v>67406.24000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>70005.45</v>
+        <v>69757.62</v>
       </c>
       <c r="O46" t="n">
-        <v>70280.56</v>
+        <v>69901.58</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4397,11 +4389,13 @@
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4420,75 +4414,75 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>65905.10000000001</v>
+        <v>68882.06</v>
       </c>
       <c r="C47" t="n">
-        <v>69608.24000000001</v>
+        <v>69225.57000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>65848.58</v>
+        <v>65133.98</v>
       </c>
       <c r="E47" t="n">
-        <v>68713.8</v>
+        <v>66016.36</v>
       </c>
       <c r="F47" t="n">
-        <v>3107.09</v>
+        <v>-2697.44</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0474</v>
+        <v>-0.0393</v>
       </c>
       <c r="H47" t="n">
-        <v>3759.66</v>
+        <v>4091.59</v>
       </c>
       <c r="I47" t="n">
-        <v>59104.41</v>
+        <v>62088.91</v>
       </c>
       <c r="J47" t="n">
-        <v>62559.51</v>
+        <v>65446.83</v>
       </c>
       <c r="K47" t="n">
-        <v>63807.18</v>
+        <v>66833.96000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>65054.85</v>
+        <v>68221.10000000001</v>
       </c>
       <c r="M47" t="n">
-        <v>67406.24000000001</v>
+        <v>70593.63</v>
       </c>
       <c r="N47" t="n">
-        <v>69757.62</v>
+        <v>72966.14999999999</v>
       </c>
       <c r="O47" t="n">
-        <v>69901.58</v>
+        <v>73367.91</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
+      <c r="Q47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
@@ -4497,76 +4491,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>68882.06</v>
+        <v>65978.95</v>
       </c>
       <c r="C48" t="n">
-        <v>69225.57000000001</v>
+        <v>66954.69</v>
       </c>
       <c r="D48" t="n">
-        <v>65133.98</v>
+        <v>64609.47</v>
       </c>
       <c r="E48" t="n">
-        <v>66016.36</v>
+        <v>66405.56</v>
       </c>
       <c r="F48" t="n">
-        <v>-2697.44</v>
+        <v>389.2</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0393</v>
+        <v>0.0059</v>
       </c>
       <c r="H48" t="n">
-        <v>4091.59</v>
+        <v>2345.22</v>
       </c>
       <c r="I48" t="n">
-        <v>62088.91</v>
+        <v>61042.39</v>
       </c>
       <c r="J48" t="n">
-        <v>65446.83</v>
+        <v>61343.06</v>
       </c>
       <c r="K48" t="n">
-        <v>66833.96000000001</v>
+        <v>63970.56</v>
       </c>
       <c r="L48" t="n">
-        <v>68221.10000000001</v>
+        <v>66598.07000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>70593.63</v>
+        <v>68062.14999999999</v>
       </c>
       <c r="N48" t="n">
-        <v>72966.14999999999</v>
+        <v>69526.24000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>73367.91</v>
+        <v>73317.16</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4583,68 +4569,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>65978.95</v>
+        <v>65668.50999999999</v>
       </c>
       <c r="C49" t="n">
-        <v>66954.69</v>
+        <v>66525.7</v>
       </c>
       <c r="D49" t="n">
-        <v>64609.47</v>
+        <v>63772.8</v>
       </c>
       <c r="E49" t="n">
-        <v>66405.56</v>
+        <v>65020.94</v>
       </c>
       <c r="F49" t="n">
-        <v>389.2</v>
+        <v>-1384.62</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0209</v>
       </c>
       <c r="H49" t="n">
-        <v>2345.22</v>
+        <v>2752.9</v>
       </c>
       <c r="I49" t="n">
-        <v>61042.39</v>
+        <v>62264.25</v>
       </c>
       <c r="J49" t="n">
-        <v>61343.06</v>
+        <v>64372.09</v>
       </c>
       <c r="K49" t="n">
-        <v>63970.56</v>
+        <v>65232.95</v>
       </c>
       <c r="L49" t="n">
-        <v>66598.07000000001</v>
+        <v>66093.82000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>68062.14999999999</v>
+        <v>67578.17</v>
       </c>
       <c r="N49" t="n">
-        <v>69526.24000000001</v>
+        <v>69062.52</v>
       </c>
       <c r="O49" t="n">
-        <v>73317.16</v>
+        <v>69299.91</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4661,67 +4655,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>65668.50999999999</v>
+        <v>65600.42</v>
       </c>
       <c r="C50" t="n">
-        <v>66525.7</v>
+        <v>66791.84</v>
       </c>
       <c r="D50" t="n">
-        <v>63772.8</v>
+        <v>63208.63</v>
       </c>
       <c r="E50" t="n">
-        <v>65020.94</v>
+        <v>64011.34</v>
       </c>
       <c r="F50" t="n">
-        <v>-1384.62</v>
+        <v>-1009.6</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0209</v>
+        <v>-0.0155</v>
       </c>
       <c r="H50" t="n">
-        <v>2752.9</v>
+        <v>3583.21</v>
       </c>
       <c r="I50" t="n">
-        <v>62264.25</v>
+        <v>61019.9</v>
       </c>
       <c r="J50" t="n">
-        <v>64372.09</v>
+        <v>62203.88</v>
       </c>
       <c r="K50" t="n">
-        <v>65232.95</v>
+        <v>63644.49</v>
       </c>
       <c r="L50" t="n">
-        <v>66093.82000000001</v>
+        <v>65085.1</v>
       </c>
       <c r="M50" t="n">
-        <v>67578.17</v>
+        <v>66397.39</v>
       </c>
       <c r="N50" t="n">
-        <v>69062.52</v>
+        <v>67709.69</v>
       </c>
       <c r="O50" t="n">
-        <v>69299.91</v>
+        <v>69278.61</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q50" s="6" t="n">
+        <v/>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
@@ -4733,8 +4721,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4747,55 +4737,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>65600.42</v>
+        <v>63659.53</v>
       </c>
       <c r="C51" t="n">
-        <v>66791.84</v>
+        <v>65436.57</v>
       </c>
       <c r="D51" t="n">
-        <v>63208.63</v>
+        <v>62726.18</v>
       </c>
       <c r="E51" t="n">
-        <v>64011.34</v>
+        <v>65018.95</v>
       </c>
       <c r="F51" t="n">
-        <v>-1009.6</v>
+        <v>1007.61</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0157</v>
       </c>
       <c r="H51" t="n">
-        <v>3583.21</v>
+        <v>2710.39</v>
       </c>
       <c r="I51" t="n">
-        <v>61019.9</v>
+        <v>59625.41</v>
       </c>
       <c r="J51" t="n">
-        <v>62203.88</v>
+        <v>59933.68</v>
       </c>
       <c r="K51" t="n">
-        <v>63644.49</v>
+        <v>62219.73</v>
       </c>
       <c r="L51" t="n">
-        <v>65085.1</v>
+        <v>64505.79</v>
       </c>
       <c r="M51" t="n">
-        <v>66397.39</v>
+        <v>65802.95</v>
       </c>
       <c r="N51" t="n">
-        <v>67709.69</v>
+        <v>67100.11</v>
       </c>
       <c r="O51" t="n">
-        <v>69278.61</v>
+        <v>70375.06</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4803,20 +4797,16 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4838,50 +4828,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>63659.53</v>
+        <v>65476.44</v>
       </c>
       <c r="C52" t="n">
-        <v>65436.57</v>
+        <v>66410.27</v>
       </c>
       <c r="D52" t="n">
-        <v>62726.18</v>
+        <v>65407.37</v>
       </c>
       <c r="E52" t="n">
-        <v>65018.95</v>
+        <v>66364.2</v>
       </c>
       <c r="F52" t="n">
-        <v>1007.61</v>
+        <v>1345.25</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0157</v>
+        <v>0.0207</v>
       </c>
       <c r="H52" t="n">
-        <v>2710.39</v>
+        <v>1002.9</v>
       </c>
       <c r="I52" t="n">
-        <v>59625.41</v>
+        <v>60015.79</v>
       </c>
       <c r="J52" t="n">
-        <v>59933.68</v>
+        <v>62777.35</v>
       </c>
       <c r="K52" t="n">
-        <v>62219.73</v>
+        <v>63663.75</v>
       </c>
       <c r="L52" t="n">
-        <v>64505.79</v>
+        <v>64550.16</v>
       </c>
       <c r="M52" t="n">
-        <v>65802.95</v>
+        <v>66374.14</v>
       </c>
       <c r="N52" t="n">
-        <v>67100.11</v>
+        <v>68198.13</v>
       </c>
       <c r="O52" t="n">
-        <v>70375.06</v>
+        <v>68146.96000000001</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4894,11 +4884,13 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4913,66 +4905,70 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>65476.44</v>
+        <v>66505.94</v>
       </c>
       <c r="C53" t="n">
-        <v>66410.27</v>
+        <v>68995.3</v>
       </c>
       <c r="D53" t="n">
-        <v>65407.37</v>
+        <v>64699.49</v>
       </c>
       <c r="E53" t="n">
-        <v>66364.2</v>
+        <v>68309.46000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>1345.25</v>
+        <v>1945.26</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0207</v>
+        <v>0.0293</v>
       </c>
       <c r="H53" t="n">
-        <v>1002.9</v>
+        <v>4295.81</v>
       </c>
       <c r="I53" t="n">
-        <v>60015.79</v>
+        <v>64404.47</v>
       </c>
       <c r="J53" t="n">
-        <v>62777.35</v>
+        <v>65588.99000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>63663.75</v>
+        <v>65862.75</v>
       </c>
       <c r="L53" t="n">
-        <v>64550.16</v>
+        <v>66136.50999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>66374.14</v>
+        <v>66865.64999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>68198.13</v>
+        <v>67594.8</v>
       </c>
       <c r="O53" t="n">
-        <v>68146.96000000001</v>
+        <v>67413.17999999999</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
@@ -4981,86 +4977,86 @@
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W53" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W53" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>66505.94</v>
+        <v>69113.74000000001</v>
       </c>
       <c r="C54" t="n">
-        <v>68995.3</v>
+        <v>70798.62</v>
       </c>
       <c r="D54" t="n">
-        <v>64699.49</v>
+        <v>68150.02</v>
       </c>
       <c r="E54" t="n">
-        <v>68309.46000000001</v>
+        <v>69030.92</v>
       </c>
       <c r="F54" t="n">
-        <v>1945.26</v>
+        <v>721.46</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0293</v>
+        <v>0.0106</v>
       </c>
       <c r="H54" t="n">
-        <v>4295.81</v>
+        <v>2648.59</v>
       </c>
       <c r="I54" t="n">
-        <v>64404.47</v>
+        <v>60403.68</v>
       </c>
       <c r="J54" t="n">
-        <v>65588.99000000001</v>
+        <v>64744.69</v>
       </c>
       <c r="K54" t="n">
-        <v>65862.75</v>
+        <v>66161.56</v>
       </c>
       <c r="L54" t="n">
-        <v>66136.50999999999</v>
+        <v>67578.42999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>66865.64999999999</v>
+        <v>70457.37</v>
       </c>
       <c r="N54" t="n">
-        <v>67594.8</v>
+        <v>73336.3</v>
       </c>
       <c r="O54" t="n">
-        <v>67413.17999999999</v>
+        <v>73291.11</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
@@ -5069,106 +5065,102 @@
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
       </c>
       <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>69113.74000000001</v>
+        <v>68564.85000000001</v>
       </c>
       <c r="C55" t="n">
-        <v>70798.62</v>
+        <v>68710.99000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>68150.02</v>
+        <v>64092.74</v>
       </c>
       <c r="E55" t="n">
-        <v>69030.92</v>
+        <v>65324.29</v>
       </c>
       <c r="F55" t="n">
-        <v>721.46</v>
+        <v>-3706.63</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0106</v>
+        <v>-0.0537</v>
       </c>
       <c r="H55" t="n">
-        <v>2648.59</v>
+        <v>4618.25</v>
       </c>
       <c r="I55" t="n">
-        <v>60403.68</v>
+        <v>65501.43</v>
       </c>
       <c r="J55" t="n">
-        <v>64744.69</v>
+        <v>66160.63</v>
       </c>
       <c r="K55" t="n">
-        <v>66161.56</v>
+        <v>67706.62</v>
       </c>
       <c r="L55" t="n">
-        <v>67578.42999999999</v>
+        <v>69252.62</v>
       </c>
       <c r="M55" t="n">
-        <v>70457.37</v>
+        <v>70355.22</v>
       </c>
       <c r="N55" t="n">
-        <v>73336.3</v>
+        <v>71457.82000000001</v>
       </c>
       <c r="O55" t="n">
-        <v>73291.11</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
+        <v>73447.21000000001</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
       <c r="U55" s="8" t="n">
         <v/>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W55" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X55" t="inlineStr"/>
@@ -5176,64 +5168,60 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>68564.85000000001</v>
+        <v>64819.56</v>
       </c>
       <c r="C56" t="n">
-        <v>68710.99000000001</v>
+        <v>65404.63</v>
       </c>
       <c r="D56" t="n">
-        <v>64092.74</v>
+        <v>61462.61</v>
       </c>
       <c r="E56" t="n">
-        <v>65324.29</v>
+        <v>62693.16</v>
       </c>
       <c r="F56" t="n">
-        <v>-3706.63</v>
+        <v>-2631.13</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0537</v>
+        <v>-0.0403</v>
       </c>
       <c r="H56" t="n">
-        <v>4618.25</v>
+        <v>3942.02</v>
       </c>
       <c r="I56" t="n">
-        <v>65501.43</v>
+        <v>59474.48</v>
       </c>
       <c r="J56" t="n">
-        <v>66160.63</v>
+        <v>60167.25</v>
       </c>
       <c r="K56" t="n">
-        <v>67706.62</v>
+        <v>63015.16</v>
       </c>
       <c r="L56" t="n">
-        <v>69252.62</v>
+        <v>65863.08</v>
       </c>
       <c r="M56" t="n">
-        <v>70355.22</v>
+        <v>67633.42</v>
       </c>
       <c r="N56" t="n">
-        <v>71457.82000000001</v>
+        <v>69403.75</v>
       </c>
       <c r="O56" t="n">
-        <v>73447.21000000001</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
+        <v>73329.25</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
@@ -5260,50 +5248,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>64819.56</v>
+        <v>62449.96</v>
       </c>
       <c r="C57" t="n">
-        <v>65404.63</v>
+        <v>64831.29</v>
       </c>
       <c r="D57" t="n">
-        <v>61462.61</v>
+        <v>62094.34</v>
       </c>
       <c r="E57" t="n">
-        <v>62693.16</v>
+        <v>63290.11</v>
       </c>
       <c r="F57" t="n">
-        <v>-2631.13</v>
+        <v>596.95</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0403</v>
+        <v>0.0095</v>
       </c>
       <c r="H57" t="n">
-        <v>3942.02</v>
+        <v>2736.95</v>
       </c>
       <c r="I57" t="n">
-        <v>59474.48</v>
+        <v>57520.59</v>
       </c>
       <c r="J57" t="n">
-        <v>60167.25</v>
+        <v>58380.91</v>
       </c>
       <c r="K57" t="n">
-        <v>63015.16</v>
+        <v>60722.15</v>
       </c>
       <c r="L57" t="n">
-        <v>65863.08</v>
+        <v>63063.39</v>
       </c>
       <c r="M57" t="n">
-        <v>67633.42</v>
+        <v>64664.17</v>
       </c>
       <c r="N57" t="n">
-        <v>69403.75</v>
+        <v>66264.95</v>
       </c>
       <c r="O57" t="n">
-        <v>73329.25</v>
+        <v>69346.64999999999</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5311,18 +5299,18 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5335,87 +5323,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>62449.96</v>
-      </c>
-      <c r="C58" t="n">
-        <v>64831.29</v>
-      </c>
-      <c r="D58" t="n">
-        <v>62094.34</v>
-      </c>
-      <c r="E58" t="n">
-        <v>64659.47</v>
-      </c>
-      <c r="F58" t="n">
-        <v>1966.31</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0314</v>
-      </c>
-      <c r="H58" t="n">
-        <v>2736.95</v>
-      </c>
-      <c r="I58" t="n">
-        <v>57520.59</v>
-      </c>
-      <c r="J58" t="n">
-        <v>58380.91</v>
-      </c>
-      <c r="K58" t="n">
-        <v>60722.15</v>
-      </c>
-      <c r="L58" t="n">
-        <v>63063.39</v>
-      </c>
-      <c r="M58" t="n">
-        <v>64664.17</v>
-      </c>
-      <c r="N58" t="n">
-        <v>66264.95</v>
-      </c>
-      <c r="O58" t="n">
-        <v>69346.64999999999</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>中警訊</t>
         </is>
